--- a/ig/main/CodeSystem-terminologie-nabm.xlsx
+++ b/ig/main/CodeSystem-terminologie-nabm.xlsx
@@ -31,7 +31,7 @@
     <t>Identifier</t>
   </si>
   <si>
-    <t>https://smt.esante.gouv.fr/#terminologie-nabm</t>
+    <t>OID:1.2.250.1.215.300.2</t>
   </si>
   <si>
     <t>Version</t>

--- a/ig/main/CodeSystem-terminologie-nabm.xlsx
+++ b/ig/main/CodeSystem-terminologie-nabm.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="115" uniqueCount="91">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="111" uniqueCount="87">
   <si>
     <t>Property</t>
   </si>
@@ -73,19 +73,7 @@
     <t>Publisher</t>
   </si>
   <si>
-    <t>ANS</t>
-  </si>
-  <si>
-    <t>Contact</t>
-  </si>
-  <si>
-    <t>ANS (https://esante.gouv.fr)</t>
-  </si>
-  <si>
-    <t>Jurisdiction</t>
-  </si>
-  <si>
-    <t>France</t>
+    <t>Agence du numérique en santé</t>
   </si>
   <si>
     <t>Description</t>
@@ -420,7 +408,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B23"/>
+  <dimension ref="A1:B21"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="15.703125" customWidth="true"/>
@@ -511,88 +499,72 @@
       <c r="A11" t="s" s="2">
         <v>20</v>
       </c>
-      <c r="B11" t="s" s="2">
-        <v>21</v>
-      </c>
+      <c r="B11" s="2"/>
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="B12" t="s" s="2">
-        <v>23</v>
-      </c>
+        <v>21</v>
+      </c>
+      <c r="B12" s="2"/>
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B13" s="2"/>
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B14" s="2"/>
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>26</v>
-      </c>
-      <c r="B15" s="2"/>
+        <v>24</v>
+      </c>
+      <c r="B15" t="s" s="2">
+        <v>25</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B16" s="2"/>
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>28</v>
-      </c>
-      <c r="B17" t="s" s="2">
-        <v>29</v>
-      </c>
+        <v>27</v>
+      </c>
+      <c r="B17" s="2"/>
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="B18" s="2"/>
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>31</v>
-      </c>
-      <c r="B19" s="2"/>
+        <v>29</v>
+      </c>
+      <c r="B19" t="s" s="2">
+        <v>30</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B20" s="2"/>
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
+        <v>32</v>
+      </c>
+      <c r="B21" t="s" s="2">
         <v>33</v>
-      </c>
-      <c r="B21" t="s" s="2">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="B22" s="2"/>
-    </row>
-    <row r="23">
-      <c r="A23" t="s" s="2">
-        <v>36</v>
-      </c>
-      <c r="B23" t="s" s="2">
-        <v>37</v>
       </c>
     </row>
   </sheetData>
@@ -607,250 +579,250 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="1">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="B1" t="s" s="1">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="C1" t="s" s="1">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="D1" t="s" s="1">
-        <v>40</v>
+        <v>36</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="B2" t="s" s="2">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" t="s" s="2">
-        <v>43</v>
+        <v>39</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="C3" s="2"/>
       <c r="D3" t="s" s="2">
-        <v>43</v>
+        <v>39</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="C4" t="s" s="2">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="D4" t="s" s="2">
-        <v>43</v>
+        <v>39</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="C5" s="2"/>
       <c r="D5" t="s" s="2">
-        <v>51</v>
+        <v>47</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="C6" s="2"/>
       <c r="D6" t="s" s="2">
-        <v>51</v>
+        <v>47</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="C7" s="2"/>
       <c r="D7" t="s" s="2">
-        <v>51</v>
+        <v>47</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="C8" s="2"/>
       <c r="D8" t="s" s="2">
-        <v>51</v>
+        <v>47</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="C9" s="2"/>
       <c r="D9" t="s" s="2">
-        <v>60</v>
+        <v>56</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="C10" s="2"/>
       <c r="D10" t="s" s="2">
-        <v>43</v>
+        <v>39</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" t="s" s="2">
-        <v>51</v>
+        <v>47</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" t="s" s="2">
-        <v>51</v>
+        <v>47</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
-        <v>51</v>
+        <v>47</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
-        <v>71</v>
+        <v>67</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
-        <v>60</v>
+        <v>56</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
-        <v>60</v>
+        <v>56</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="C17" t="s" s="2">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="D17" t="s" s="2">
-        <v>60</v>
+        <v>56</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="C18" t="s" s="2">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="D18" t="s" s="2">
-        <v>60</v>
+        <v>56</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="B19" s="2"/>
       <c r="C19" t="s" s="2">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="D19" t="s" s="2">
-        <v>51</v>
+        <v>47</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="B20" s="2"/>
       <c r="C20" t="s" s="2">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="D20" t="s" s="2">
-        <v>51</v>
+        <v>47</v>
       </c>
     </row>
   </sheetData>
@@ -865,13 +837,13 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="1">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="B1" t="s" s="1">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="C1" t="s" s="1">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="D1" t="s" s="1">
         <v>1</v>
@@ -879,38 +851,38 @@
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" t="s" s="2">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="D2" t="s" s="2">
-        <v>88</v>
+        <v>84</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="B3" s="2"/>
       <c r="C3" t="s" s="2">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="D3" t="s" s="2">
-        <v>88</v>
+        <v>84</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="B4" s="2"/>
       <c r="C4" t="s" s="2">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="D4" t="s" s="2">
-        <v>90</v>
+        <v>86</v>
       </c>
     </row>
   </sheetData>

--- a/ig/main/CodeSystem-terminologie-nabm.xlsx
+++ b/ig/main/CodeSystem-terminologie-nabm.xlsx
@@ -31,13 +31,13 @@
     <t>Identifier</t>
   </si>
   <si>
-    <t>OID:1.2.250.1.215.300.2</t>
+    <t>https://smt.esante.gouv.fr/#terminologie-nabm</t>
   </si>
   <si>
     <t>Version</t>
   </si>
   <si>
-    <t>V93</t>
+    <t>V94</t>
   </si>
   <si>
     <t>Name</t>
@@ -67,7 +67,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-11T00:00:00+00:00</t>
+    <t>2025-01-10T00:00:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/CodeSystem-terminologie-nabm.xlsx
+++ b/ig/main/CodeSystem-terminologie-nabm.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="111" uniqueCount="87">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="113" uniqueCount="88">
   <si>
     <t>Property</t>
   </si>
@@ -31,13 +31,16 @@
     <t>Identifier</t>
   </si>
   <si>
-    <t>https://smt.esante.gouv.fr/#terminologie-nabm</t>
+    <t>OID:1.2.250.1.215.300.2 (use: usual, )</t>
+  </si>
+  <si>
+    <t>https://smt.esante.gouv.fr/#terminologie-nabm (use: secondary, )</t>
   </si>
   <si>
     <t>Version</t>
   </si>
   <si>
-    <t>V94</t>
+    <t>V96</t>
   </si>
   <si>
     <t>Name</t>
@@ -408,7 +411,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B21"/>
+  <dimension ref="A1:B22"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="15.703125" customWidth="true"/>
@@ -441,65 +444,67 @@
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
+        <v>4</v>
+      </c>
+      <c r="B4" t="s" s="2">
         <v>6</v>
-      </c>
-      <c r="B4" t="s" s="2">
-        <v>7</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
+        <v>7</v>
+      </c>
+      <c r="B5" t="s" s="2">
         <v>8</v>
-      </c>
-      <c r="B5" t="s" s="2">
-        <v>9</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
+        <v>9</v>
+      </c>
+      <c r="B6" t="s" s="2">
         <v>10</v>
-      </c>
-      <c r="B6" t="s" s="2">
-        <v>11</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
+        <v>11</v>
+      </c>
+      <c r="B7" t="s" s="2">
         <v>12</v>
-      </c>
-      <c r="B7" t="s" s="2">
-        <v>13</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="B8" t="s" s="2">
         <v>14</v>
-      </c>
-      <c r="B8" t="s" s="2">
-        <v>15</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="B9" t="s" s="2">
         <v>16</v>
-      </c>
-      <c r="B9" t="s" s="2">
-        <v>17</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
+        <v>17</v>
+      </c>
+      <c r="B10" t="s" s="2">
         <v>18</v>
-      </c>
-      <c r="B10" t="s" s="2">
-        <v>19</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="B11" t="s" s="2">
         <v>20</v>
       </c>
-      <c r="B11" s="2"/>
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
@@ -523,15 +528,15 @@
       <c r="A15" t="s" s="2">
         <v>24</v>
       </c>
-      <c r="B15" t="s" s="2">
-        <v>25</v>
-      </c>
+      <c r="B15" s="2"/>
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
+        <v>25</v>
+      </c>
+      <c r="B16" t="s" s="2">
         <v>26</v>
       </c>
-      <c r="B16" s="2"/>
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
@@ -549,22 +554,28 @@
       <c r="A19" t="s" s="2">
         <v>29</v>
       </c>
-      <c r="B19" t="s" s="2">
-        <v>30</v>
-      </c>
+      <c r="B19" s="2"/>
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
+        <v>30</v>
+      </c>
+      <c r="B20" t="s" s="2">
         <v>31</v>
       </c>
-      <c r="B20" s="2"/>
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
         <v>32</v>
       </c>
-      <c r="B21" t="s" s="2">
+      <c r="B21" s="2"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="s" s="2">
         <v>33</v>
+      </c>
+      <c r="B22" t="s" s="2">
+        <v>34</v>
       </c>
     </row>
   </sheetData>
@@ -579,250 +590,250 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="1">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B1" t="s" s="1">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C1" t="s" s="1">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D1" t="s" s="1">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B2" t="s" s="2">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" t="s" s="2">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C3" s="2"/>
       <c r="D3" t="s" s="2">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C4" t="s" s="2">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D4" t="s" s="2">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C5" s="2"/>
       <c r="D5" t="s" s="2">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C6" s="2"/>
       <c r="D6" t="s" s="2">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C7" s="2"/>
       <c r="D7" t="s" s="2">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C8" s="2"/>
       <c r="D8" t="s" s="2">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="C9" s="2"/>
       <c r="D9" t="s" s="2">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C10" s="2"/>
       <c r="D10" t="s" s="2">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" t="s" s="2">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" t="s" s="2">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C17" t="s" s="2">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="D17" t="s" s="2">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C18" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="D18" t="s" s="2">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="B19" s="2"/>
       <c r="C19" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D19" t="s" s="2">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="B20" s="2"/>
       <c r="C20" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D20" t="s" s="2">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
   </sheetData>
@@ -837,13 +848,13 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="1">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B1" t="s" s="1">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C1" t="s" s="1">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="D1" t="s" s="1">
         <v>1</v>
@@ -851,38 +862,38 @@
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="D2" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B3" s="2"/>
       <c r="C3" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="D3" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="B4" s="2"/>
       <c r="C4" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="D4" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
   </sheetData>

--- a/ig/main/CodeSystem-terminologie-nabm.xlsx
+++ b/ig/main/CodeSystem-terminologie-nabm.xlsx
@@ -41,7 +41,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>V96</t>
+    <t>V97</t>
   </si>
   <si>
     <t>Name</t>
@@ -71,7 +71,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-10T00:00:00+00:00</t>
+    <t>2025-06-02T00:00:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -314,7 +314,7 @@
     <t>2004</t>
   </si>
   <si>
-    <t>UR.PROTEINURIE: DOSAGE</t>
+    <t>PROTEINES TOTALES (PROTEINURIE):</t>
   </si>
   <si>
     <t>4207</t>
@@ -356,7 +356,7 @@
     <t>1133</t>
   </si>
   <si>
-    <t>UR.:ALBUMINURIE:DOSAGE</t>
+    <t>ALBUMINE (ALBUMINURIE):</t>
   </si>
   <si>
     <t>1024</t>
@@ -650,10 +650,16 @@
     <t>HISTOPLASMOSE : SD DE DEPISTAGE</t>
   </si>
   <si>
+    <t>9011</t>
+  </si>
+  <si>
+    <t>FORFAIT DE PRISE EN CHARGE PRE-ANALYTIQUE DU PATIENT EN CAS DE DEPISTAGE COVID</t>
+  </si>
+  <si>
     <t>0592</t>
   </si>
   <si>
-    <t>SANG : CREATININE</t>
+    <t>CREATININE (CREATININEMIE):</t>
   </si>
   <si>
     <t>0350</t>
@@ -2697,7 +2703,7 @@
     <t>4086</t>
   </si>
   <si>
-    <t>DPN:SECONDE DETERMINATION PRENAT. DU GENOTYPE RHD F TAL A PARTIR DU SANG MATERN</t>
+    <t>DPN:SECONDE DETERMINATION PRENAT.DU GENOTYPE RHD F TAL A PARTIR DU SANG MATERN</t>
   </si>
   <si>
     <t>0016</t>
@@ -3106,7 +3112,7 @@
     <t>4721</t>
   </si>
   <si>
-    <t>RECHERCHE D'IGG ET D'IGM OU D'IG TOTAUX TESTS SERO. PAR IMMUNOCHROMATOGRAPHIE</t>
+    <t>RECHERCHE D'IGG ET D'IGM OU D'IG TOTAUX PAR IMMUNOCHROMATOGRAPHIE (SARS-COV-2)</t>
   </si>
   <si>
     <t>0214</t>
@@ -4835,7 +4841,7 @@
     <t>0627</t>
   </si>
   <si>
-    <t>UR. : CREATININE (CREATININURIE)</t>
+    <t>CREATININE (CREATININURIE)</t>
   </si>
   <si>
     <t>5214</t>
@@ -5666,12 +5672,6 @@
     <t>UR. : ACETONE  (ACETONURIE)</t>
   </si>
   <si>
-    <t>4274</t>
-  </si>
-  <si>
-    <t>DETECTION DE L'ANTIGENE DU VIRUS SARS-COV-2</t>
-  </si>
-  <si>
     <t>0668</t>
   </si>
   <si>
@@ -5825,7 +5825,7 @@
     <t>5272</t>
   </si>
   <si>
-    <t>DETECTION DES GENOMES DU VIRUS DE LA GRIPPE A ET B, ET DU SARS-COV-2 PAR RT-PCR</t>
+    <t>DETECTION DU GENOME DES VIRUS INFLUENZA A ET B DE LA GRIPPE</t>
   </si>
   <si>
     <t>1662</t>
@@ -10651,21 +10651,21 @@
       <c r="C286" t="s" s="2">
         <v>664</v>
       </c>
-      <c r="D286" t="s" s="2">
-        <v>665</v>
-      </c>
+      <c r="D286" s="2"/>
     </row>
     <row r="287">
       <c r="A287" t="s" s="2">
         <v>95</v>
       </c>
       <c r="B287" t="s" s="2">
+        <v>665</v>
+      </c>
+      <c r="C287" t="s" s="2">
         <v>666</v>
       </c>
-      <c r="C287" t="s" s="2">
+      <c r="D287" t="s" s="2">
         <v>667</v>
       </c>
-      <c r="D287" s="2"/>
     </row>
     <row r="288">
       <c r="A288" t="s" s="2">
@@ -10845,21 +10845,21 @@
       <c r="C302" t="s" s="2">
         <v>697</v>
       </c>
-      <c r="D302" t="s" s="2">
-        <v>698</v>
-      </c>
+      <c r="D302" s="2"/>
     </row>
     <row r="303">
       <c r="A303" t="s" s="2">
         <v>95</v>
       </c>
       <c r="B303" t="s" s="2">
+        <v>698</v>
+      </c>
+      <c r="C303" t="s" s="2">
         <v>699</v>
       </c>
-      <c r="C303" t="s" s="2">
+      <c r="D303" t="s" s="2">
         <v>700</v>
       </c>
-      <c r="D303" s="2"/>
     </row>
     <row r="304">
       <c r="A304" t="s" s="2">
@@ -11015,21 +11015,21 @@
       <c r="C316" t="s" s="2">
         <v>726</v>
       </c>
-      <c r="D316" t="s" s="2">
-        <v>727</v>
-      </c>
+      <c r="D316" s="2"/>
     </row>
     <row r="317">
       <c r="A317" t="s" s="2">
         <v>95</v>
       </c>
       <c r="B317" t="s" s="2">
+        <v>727</v>
+      </c>
+      <c r="C317" t="s" s="2">
         <v>728</v>
       </c>
-      <c r="C317" t="s" s="2">
+      <c r="D317" t="s" s="2">
         <v>729</v>
       </c>
-      <c r="D317" s="2"/>
     </row>
     <row r="318">
       <c r="A318" t="s" s="2">
@@ -11137,21 +11137,21 @@
       <c r="C326" t="s" s="2">
         <v>747</v>
       </c>
-      <c r="D326" t="s" s="2">
-        <v>748</v>
-      </c>
+      <c r="D326" s="2"/>
     </row>
     <row r="327">
       <c r="A327" t="s" s="2">
         <v>95</v>
       </c>
       <c r="B327" t="s" s="2">
+        <v>748</v>
+      </c>
+      <c r="C327" t="s" s="2">
         <v>749</v>
       </c>
-      <c r="C327" t="s" s="2">
+      <c r="D327" t="s" s="2">
         <v>750</v>
       </c>
-      <c r="D327" s="2"/>
     </row>
     <row r="328">
       <c r="A328" t="s" s="2">
@@ -11259,21 +11259,21 @@
       <c r="C336" t="s" s="2">
         <v>768</v>
       </c>
-      <c r="D336" t="s" s="2">
-        <v>769</v>
-      </c>
+      <c r="D336" s="2"/>
     </row>
     <row r="337">
       <c r="A337" t="s" s="2">
         <v>95</v>
       </c>
       <c r="B337" t="s" s="2">
+        <v>769</v>
+      </c>
+      <c r="C337" t="s" s="2">
         <v>770</v>
       </c>
-      <c r="C337" t="s" s="2">
+      <c r="D337" t="s" s="2">
         <v>771</v>
       </c>
-      <c r="D337" s="2"/>
     </row>
     <row r="338">
       <c r="A338" t="s" s="2">
@@ -11513,21 +11513,21 @@
       <c r="C357" t="s" s="2">
         <v>811</v>
       </c>
-      <c r="D357" t="s" s="2">
-        <v>812</v>
-      </c>
+      <c r="D357" s="2"/>
     </row>
     <row r="358">
       <c r="A358" t="s" s="2">
         <v>95</v>
       </c>
       <c r="B358" t="s" s="2">
+        <v>812</v>
+      </c>
+      <c r="C358" t="s" s="2">
         <v>813</v>
       </c>
-      <c r="C358" t="s" s="2">
+      <c r="D358" t="s" s="2">
         <v>814</v>
       </c>
-      <c r="D358" s="2"/>
     </row>
     <row r="359">
       <c r="A359" t="s" s="2">
@@ -11755,21 +11755,21 @@
       <c r="C377" t="s" s="2">
         <v>852</v>
       </c>
-      <c r="D377" t="s" s="2">
-        <v>853</v>
-      </c>
+      <c r="D377" s="2"/>
     </row>
     <row r="378">
       <c r="A378" t="s" s="2">
         <v>95</v>
       </c>
       <c r="B378" t="s" s="2">
+        <v>853</v>
+      </c>
+      <c r="C378" t="s" s="2">
         <v>854</v>
       </c>
-      <c r="C378" t="s" s="2">
+      <c r="D378" t="s" s="2">
         <v>855</v>
       </c>
-      <c r="D378" s="2"/>
     </row>
     <row r="379">
       <c r="A379" t="s" s="2">
@@ -12580,10 +12580,10 @@
         <v>95</v>
       </c>
       <c r="B446" t="s" s="2">
-        <v>10</v>
+        <v>990</v>
       </c>
       <c r="C446" t="s" s="2">
-        <v>10</v>
+        <v>991</v>
       </c>
       <c r="D446" s="2"/>
     </row>
@@ -12592,10 +12592,10 @@
         <v>95</v>
       </c>
       <c r="B447" t="s" s="2">
-        <v>990</v>
+        <v>10</v>
       </c>
       <c r="C447" t="s" s="2">
-        <v>991</v>
+        <v>10</v>
       </c>
       <c r="D447" s="2"/>
     </row>

--- a/ig/main/CodeSystem-terminologie-nabm.xlsx
+++ b/ig/main/CodeSystem-terminologie-nabm.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3259" uniqueCount="2187">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3280" uniqueCount="2200">
   <si>
     <t>Property</t>
   </si>
@@ -41,7 +41,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>V97</t>
+    <t>V98</t>
   </si>
   <si>
     <t>Name</t>
@@ -71,7 +71,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-06-02T00:00:00+00:00</t>
+    <t>2025-06-20T00:00:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -131,7 +131,7 @@
     <t>Count</t>
   </si>
   <si>
-    <t>1043</t>
+    <t>1050</t>
   </si>
   <si>
     <t>Code</t>
@@ -356,7 +356,7 @@
     <t>1133</t>
   </si>
   <si>
-    <t>ALBUMINE (ALBUMINURIE):</t>
+    <t>ALBUMINE (ALBUMINURIE)</t>
   </si>
   <si>
     <t>1024</t>
@@ -1154,6 +1154,12 @@
     <t>UR. : PORPHYRINES : RECH.</t>
   </si>
   <si>
+    <t>5313</t>
+  </si>
+  <si>
+    <t>C. TRACHOMATIS ET/OU N. GONORRHOEAE: 3 SITES (IST SANS ORDO)</t>
+  </si>
+  <si>
     <t>4006</t>
   </si>
   <si>
@@ -1208,6 +1214,12 @@
     <t>LCR : DYSGLOBULINORACHIE : ELECTROPHORESE ET TYPAGE</t>
   </si>
   <si>
+    <t>5312</t>
+  </si>
+  <si>
+    <t>C. TRACHOMATIS ET/OU N. GONORRHOEAE: - 2 SITES (IST SANS ORDO)</t>
+  </si>
+  <si>
     <t>0638</t>
   </si>
   <si>
@@ -1692,6 +1704,12 @@
   </si>
   <si>
     <t>EX MICROBIO SECRETIONS, ULCERATIONS, EXSUDATS (ANO) GENITAUX FEMME (PV)</t>
+  </si>
+  <si>
+    <t>5311</t>
+  </si>
+  <si>
+    <t>C. TRACHOMATIS ET/OU N. GONORRHOEAE: - 1 SITE (IST SANS ORD)</t>
   </si>
   <si>
     <t>5226</t>
@@ -4058,6 +4076,12 @@
     <t>TEST DE RESISTANCE GENOTYPIQUE AUX ANTIRETROVIRAUX</t>
   </si>
   <si>
+    <t>5501</t>
+  </si>
+  <si>
+    <t>HEPATITE B (VHB): DEPISTAGE ET/OU DIAGNOSTIC IGM ANTI HBC (IST SANS ORDO)</t>
+  </si>
+  <si>
     <t>1498</t>
   </si>
   <si>
@@ -4130,6 +4154,12 @@
     <t>RESISTANCES AUX MACROLIDES CHEZ M.GENITALIUM</t>
   </si>
   <si>
+    <t>5500</t>
+  </si>
+  <si>
+    <t>HEPATITE B (VHB): DEPISTAGE ET/OU DIAGNOSTIC (IST SANS ORDO)</t>
+  </si>
+  <si>
     <t>0806</t>
   </si>
   <si>
@@ -4412,9 +4442,6 @@
     <t>UR. : UROBILINE : RECH.</t>
   </si>
   <si>
-    <t>1050</t>
-  </si>
-  <si>
     <t>MESURE DE L'ACTIVITE D'ADAMTS 13</t>
   </si>
   <si>
@@ -4439,7 +4466,7 @@
     <t>5303</t>
   </si>
   <si>
-    <t>C. TRACHOMATIS ET/OU N. GONORRHOEAE: AMPLIFCATION GENIQUE -  3 SITES</t>
+    <t>C. TRACHOMATIS ET/OU N. GONORRHOEAE: AMPLIFCATION GENIQUE - 3 SITES</t>
   </si>
   <si>
     <t>1627</t>
@@ -4523,7 +4550,7 @@
     <t>5302</t>
   </si>
   <si>
-    <t>C. TRACHOMATIS ET/OU N. GONORRHOEAE: AMPLIFCATION GENIQUE -  2 SITES</t>
+    <t>C. TRACHOMATIS ET/OU N. GONORRHOEAE: AMPLIFCATION GENIQUE - 2 SITES</t>
   </si>
   <si>
     <t>2012</t>
@@ -6038,6 +6065,12 @@
     <t>TULAREMIE : SD</t>
   </si>
   <si>
+    <t>1357</t>
+  </si>
+  <si>
+    <t>SYPHILIS: SD TEST NON TREPONEMIQUE(TNT) TITRAGE (VDRL, RPR,  ) (IST SANS ORDO)</t>
+  </si>
+  <si>
     <t>07-02</t>
   </si>
   <si>
@@ -6144,6 +6177,12 @@
   </si>
   <si>
     <t>MYCOPLASMOSES RESPIRATOIRES : SD : IGM</t>
+  </si>
+  <si>
+    <t>1356</t>
+  </si>
+  <si>
+    <t>SYPHILIS:SD DE DEPISTAGE_ TEST TREPONEMIQUE (TT)(IST SANS ORDO</t>
   </si>
   <si>
     <t>1465</t>
@@ -7216,7 +7255,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:D1044"/>
+  <dimension ref="A1:D1051"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -10663,19 +10702,17 @@
       <c r="C287" t="s" s="2">
         <v>666</v>
       </c>
-      <c r="D287" t="s" s="2">
-        <v>667</v>
-      </c>
+      <c r="D287" s="2"/>
     </row>
     <row r="288">
       <c r="A288" t="s" s="2">
         <v>95</v>
       </c>
       <c r="B288" t="s" s="2">
+        <v>667</v>
+      </c>
+      <c r="C288" t="s" s="2">
         <v>668</v>
-      </c>
-      <c r="C288" t="s" s="2">
-        <v>669</v>
       </c>
       <c r="D288" s="2"/>
     </row>
@@ -10684,10 +10721,10 @@
         <v>95</v>
       </c>
       <c r="B289" t="s" s="2">
+        <v>669</v>
+      </c>
+      <c r="C289" t="s" s="2">
         <v>670</v>
-      </c>
-      <c r="C289" t="s" s="2">
-        <v>671</v>
       </c>
       <c r="D289" s="2"/>
     </row>
@@ -10696,12 +10733,14 @@
         <v>95</v>
       </c>
       <c r="B290" t="s" s="2">
+        <v>671</v>
+      </c>
+      <c r="C290" t="s" s="2">
         <v>672</v>
       </c>
-      <c r="C290" t="s" s="2">
+      <c r="D290" t="s" s="2">
         <v>673</v>
       </c>
-      <c r="D290" s="2"/>
     </row>
     <row r="291">
       <c r="A291" t="s" s="2">
@@ -10857,19 +10896,17 @@
       <c r="C303" t="s" s="2">
         <v>699</v>
       </c>
-      <c r="D303" t="s" s="2">
-        <v>700</v>
-      </c>
+      <c r="D303" s="2"/>
     </row>
     <row r="304">
       <c r="A304" t="s" s="2">
         <v>95</v>
       </c>
       <c r="B304" t="s" s="2">
+        <v>700</v>
+      </c>
+      <c r="C304" t="s" s="2">
         <v>701</v>
-      </c>
-      <c r="C304" t="s" s="2">
-        <v>702</v>
       </c>
       <c r="D304" s="2"/>
     </row>
@@ -10878,10 +10915,10 @@
         <v>95</v>
       </c>
       <c r="B305" t="s" s="2">
+        <v>702</v>
+      </c>
+      <c r="C305" t="s" s="2">
         <v>703</v>
-      </c>
-      <c r="C305" t="s" s="2">
-        <v>704</v>
       </c>
       <c r="D305" s="2"/>
     </row>
@@ -10890,12 +10927,14 @@
         <v>95</v>
       </c>
       <c r="B306" t="s" s="2">
+        <v>704</v>
+      </c>
+      <c r="C306" t="s" s="2">
         <v>705</v>
       </c>
-      <c r="C306" t="s" s="2">
+      <c r="D306" t="s" s="2">
         <v>706</v>
       </c>
-      <c r="D306" s="2"/>
     </row>
     <row r="307">
       <c r="A307" t="s" s="2">
@@ -11027,19 +11066,17 @@
       <c r="C317" t="s" s="2">
         <v>728</v>
       </c>
-      <c r="D317" t="s" s="2">
-        <v>729</v>
-      </c>
+      <c r="D317" s="2"/>
     </row>
     <row r="318">
       <c r="A318" t="s" s="2">
         <v>95</v>
       </c>
       <c r="B318" t="s" s="2">
+        <v>729</v>
+      </c>
+      <c r="C318" t="s" s="2">
         <v>730</v>
-      </c>
-      <c r="C318" t="s" s="2">
-        <v>731</v>
       </c>
       <c r="D318" s="2"/>
     </row>
@@ -11048,10 +11085,10 @@
         <v>95</v>
       </c>
       <c r="B319" t="s" s="2">
+        <v>731</v>
+      </c>
+      <c r="C319" t="s" s="2">
         <v>732</v>
-      </c>
-      <c r="C319" t="s" s="2">
-        <v>733</v>
       </c>
       <c r="D319" s="2"/>
     </row>
@@ -11060,12 +11097,14 @@
         <v>95</v>
       </c>
       <c r="B320" t="s" s="2">
+        <v>733</v>
+      </c>
+      <c r="C320" t="s" s="2">
         <v>734</v>
       </c>
-      <c r="C320" t="s" s="2">
+      <c r="D320" t="s" s="2">
         <v>735</v>
       </c>
-      <c r="D320" s="2"/>
     </row>
     <row r="321">
       <c r="A321" t="s" s="2">
@@ -11149,19 +11188,17 @@
       <c r="C327" t="s" s="2">
         <v>749</v>
       </c>
-      <c r="D327" t="s" s="2">
-        <v>750</v>
-      </c>
+      <c r="D327" s="2"/>
     </row>
     <row r="328">
       <c r="A328" t="s" s="2">
         <v>95</v>
       </c>
       <c r="B328" t="s" s="2">
+        <v>750</v>
+      </c>
+      <c r="C328" t="s" s="2">
         <v>751</v>
-      </c>
-      <c r="C328" t="s" s="2">
-        <v>752</v>
       </c>
       <c r="D328" s="2"/>
     </row>
@@ -11170,10 +11207,10 @@
         <v>95</v>
       </c>
       <c r="B329" t="s" s="2">
+        <v>752</v>
+      </c>
+      <c r="C329" t="s" s="2">
         <v>753</v>
-      </c>
-      <c r="C329" t="s" s="2">
-        <v>754</v>
       </c>
       <c r="D329" s="2"/>
     </row>
@@ -11182,12 +11219,14 @@
         <v>95</v>
       </c>
       <c r="B330" t="s" s="2">
+        <v>754</v>
+      </c>
+      <c r="C330" t="s" s="2">
         <v>755</v>
       </c>
-      <c r="C330" t="s" s="2">
+      <c r="D330" t="s" s="2">
         <v>756</v>
       </c>
-      <c r="D330" s="2"/>
     </row>
     <row r="331">
       <c r="A331" t="s" s="2">
@@ -11271,19 +11310,17 @@
       <c r="C337" t="s" s="2">
         <v>770</v>
       </c>
-      <c r="D337" t="s" s="2">
-        <v>771</v>
-      </c>
+      <c r="D337" s="2"/>
     </row>
     <row r="338">
       <c r="A338" t="s" s="2">
         <v>95</v>
       </c>
       <c r="B338" t="s" s="2">
+        <v>771</v>
+      </c>
+      <c r="C338" t="s" s="2">
         <v>772</v>
-      </c>
-      <c r="C338" t="s" s="2">
-        <v>773</v>
       </c>
       <c r="D338" s="2"/>
     </row>
@@ -11292,10 +11329,10 @@
         <v>95</v>
       </c>
       <c r="B339" t="s" s="2">
+        <v>773</v>
+      </c>
+      <c r="C339" t="s" s="2">
         <v>774</v>
-      </c>
-      <c r="C339" t="s" s="2">
-        <v>775</v>
       </c>
       <c r="D339" s="2"/>
     </row>
@@ -11304,12 +11341,14 @@
         <v>95</v>
       </c>
       <c r="B340" t="s" s="2">
+        <v>775</v>
+      </c>
+      <c r="C340" t="s" s="2">
         <v>776</v>
       </c>
-      <c r="C340" t="s" s="2">
+      <c r="D340" t="s" s="2">
         <v>777</v>
       </c>
-      <c r="D340" s="2"/>
     </row>
     <row r="341">
       <c r="A341" t="s" s="2">
@@ -11525,19 +11564,17 @@
       <c r="C358" t="s" s="2">
         <v>813</v>
       </c>
-      <c r="D358" t="s" s="2">
-        <v>814</v>
-      </c>
+      <c r="D358" s="2"/>
     </row>
     <row r="359">
       <c r="A359" t="s" s="2">
         <v>95</v>
       </c>
       <c r="B359" t="s" s="2">
+        <v>814</v>
+      </c>
+      <c r="C359" t="s" s="2">
         <v>815</v>
-      </c>
-      <c r="C359" t="s" s="2">
-        <v>816</v>
       </c>
       <c r="D359" s="2"/>
     </row>
@@ -11546,10 +11583,10 @@
         <v>95</v>
       </c>
       <c r="B360" t="s" s="2">
+        <v>816</v>
+      </c>
+      <c r="C360" t="s" s="2">
         <v>817</v>
-      </c>
-      <c r="C360" t="s" s="2">
-        <v>818</v>
       </c>
       <c r="D360" s="2"/>
     </row>
@@ -11558,12 +11595,14 @@
         <v>95</v>
       </c>
       <c r="B361" t="s" s="2">
+        <v>818</v>
+      </c>
+      <c r="C361" t="s" s="2">
         <v>819</v>
       </c>
-      <c r="C361" t="s" s="2">
+      <c r="D361" t="s" s="2">
         <v>820</v>
       </c>
-      <c r="D361" s="2"/>
     </row>
     <row r="362">
       <c r="A362" t="s" s="2">
@@ -11767,19 +11806,17 @@
       <c r="C378" t="s" s="2">
         <v>854</v>
       </c>
-      <c r="D378" t="s" s="2">
-        <v>855</v>
-      </c>
+      <c r="D378" s="2"/>
     </row>
     <row r="379">
       <c r="A379" t="s" s="2">
         <v>95</v>
       </c>
       <c r="B379" t="s" s="2">
+        <v>855</v>
+      </c>
+      <c r="C379" t="s" s="2">
         <v>856</v>
-      </c>
-      <c r="C379" t="s" s="2">
-        <v>857</v>
       </c>
       <c r="D379" s="2"/>
     </row>
@@ -11788,10 +11825,10 @@
         <v>95</v>
       </c>
       <c r="B380" t="s" s="2">
+        <v>857</v>
+      </c>
+      <c r="C380" t="s" s="2">
         <v>858</v>
-      </c>
-      <c r="C380" t="s" s="2">
-        <v>859</v>
       </c>
       <c r="D380" s="2"/>
     </row>
@@ -11800,12 +11837,14 @@
         <v>95</v>
       </c>
       <c r="B381" t="s" s="2">
+        <v>859</v>
+      </c>
+      <c r="C381" t="s" s="2">
         <v>860</v>
       </c>
-      <c r="C381" t="s" s="2">
+      <c r="D381" t="s" s="2">
         <v>861</v>
       </c>
-      <c r="D381" s="2"/>
     </row>
     <row r="382">
       <c r="A382" t="s" s="2">
@@ -12592,10 +12631,10 @@
         <v>95</v>
       </c>
       <c r="B447" t="s" s="2">
-        <v>10</v>
+        <v>992</v>
       </c>
       <c r="C447" t="s" s="2">
-        <v>10</v>
+        <v>993</v>
       </c>
       <c r="D447" s="2"/>
     </row>
@@ -12604,10 +12643,10 @@
         <v>95</v>
       </c>
       <c r="B448" t="s" s="2">
-        <v>992</v>
+        <v>994</v>
       </c>
       <c r="C448" t="s" s="2">
-        <v>993</v>
+        <v>995</v>
       </c>
       <c r="D448" s="2"/>
     </row>
@@ -12616,10 +12655,10 @@
         <v>95</v>
       </c>
       <c r="B449" t="s" s="2">
-        <v>994</v>
+        <v>996</v>
       </c>
       <c r="C449" t="s" s="2">
-        <v>995</v>
+        <v>997</v>
       </c>
       <c r="D449" s="2"/>
     </row>
@@ -12628,10 +12667,10 @@
         <v>95</v>
       </c>
       <c r="B450" t="s" s="2">
-        <v>996</v>
+        <v>10</v>
       </c>
       <c r="C450" t="s" s="2">
-        <v>997</v>
+        <v>10</v>
       </c>
       <c r="D450" s="2"/>
     </row>
@@ -15496,10 +15535,10 @@
         <v>95</v>
       </c>
       <c r="B689" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="C689" t="s" s="2">
         <v>1474</v>
-      </c>
-      <c r="C689" t="s" s="2">
-        <v>1475</v>
       </c>
       <c r="D689" s="2"/>
     </row>
@@ -15508,10 +15547,10 @@
         <v>95</v>
       </c>
       <c r="B690" t="s" s="2">
+        <v>1475</v>
+      </c>
+      <c r="C690" t="s" s="2">
         <v>1476</v>
-      </c>
-      <c r="C690" t="s" s="2">
-        <v>1477</v>
       </c>
       <c r="D690" s="2"/>
     </row>
@@ -15520,10 +15559,10 @@
         <v>95</v>
       </c>
       <c r="B691" t="s" s="2">
+        <v>1477</v>
+      </c>
+      <c r="C691" t="s" s="2">
         <v>1478</v>
-      </c>
-      <c r="C691" t="s" s="2">
-        <v>1479</v>
       </c>
       <c r="D691" s="2"/>
     </row>
@@ -15532,10 +15571,10 @@
         <v>95</v>
       </c>
       <c r="B692" t="s" s="2">
+        <v>1479</v>
+      </c>
+      <c r="C692" t="s" s="2">
         <v>1480</v>
-      </c>
-      <c r="C692" t="s" s="2">
-        <v>1481</v>
       </c>
       <c r="D692" s="2"/>
     </row>
@@ -15544,10 +15583,10 @@
         <v>95</v>
       </c>
       <c r="B693" t="s" s="2">
+        <v>1481</v>
+      </c>
+      <c r="C693" t="s" s="2">
         <v>1482</v>
-      </c>
-      <c r="C693" t="s" s="2">
-        <v>1483</v>
       </c>
       <c r="D693" s="2"/>
     </row>
@@ -15556,10 +15595,10 @@
         <v>95</v>
       </c>
       <c r="B694" t="s" s="2">
+        <v>1483</v>
+      </c>
+      <c r="C694" t="s" s="2">
         <v>1484</v>
-      </c>
-      <c r="C694" t="s" s="2">
-        <v>1485</v>
       </c>
       <c r="D694" s="2"/>
     </row>
@@ -15568,10 +15607,10 @@
         <v>95</v>
       </c>
       <c r="B695" t="s" s="2">
+        <v>1485</v>
+      </c>
+      <c r="C695" t="s" s="2">
         <v>1486</v>
-      </c>
-      <c r="C695" t="s" s="2">
-        <v>1487</v>
       </c>
       <c r="D695" s="2"/>
     </row>
@@ -15580,10 +15619,10 @@
         <v>95</v>
       </c>
       <c r="B696" t="s" s="2">
+        <v>1487</v>
+      </c>
+      <c r="C696" t="s" s="2">
         <v>1488</v>
-      </c>
-      <c r="C696" t="s" s="2">
-        <v>1489</v>
       </c>
       <c r="D696" s="2"/>
     </row>
@@ -15592,10 +15631,10 @@
         <v>95</v>
       </c>
       <c r="B697" t="s" s="2">
+        <v>1489</v>
+      </c>
+      <c r="C697" t="s" s="2">
         <v>1490</v>
-      </c>
-      <c r="C697" t="s" s="2">
-        <v>1491</v>
       </c>
       <c r="D697" s="2"/>
     </row>
@@ -15604,10 +15643,10 @@
         <v>95</v>
       </c>
       <c r="B698" t="s" s="2">
+        <v>1491</v>
+      </c>
+      <c r="C698" t="s" s="2">
         <v>1492</v>
-      </c>
-      <c r="C698" t="s" s="2">
-        <v>1493</v>
       </c>
       <c r="D698" s="2"/>
     </row>
@@ -15616,10 +15655,10 @@
         <v>95</v>
       </c>
       <c r="B699" t="s" s="2">
+        <v>1493</v>
+      </c>
+      <c r="C699" t="s" s="2">
         <v>1494</v>
-      </c>
-      <c r="C699" t="s" s="2">
-        <v>1495</v>
       </c>
       <c r="D699" s="2"/>
     </row>
@@ -15628,10 +15667,10 @@
         <v>95</v>
       </c>
       <c r="B700" t="s" s="2">
+        <v>1495</v>
+      </c>
+      <c r="C700" t="s" s="2">
         <v>1496</v>
-      </c>
-      <c r="C700" t="s" s="2">
-        <v>1497</v>
       </c>
       <c r="D700" s="2"/>
     </row>
@@ -15640,10 +15679,10 @@
         <v>95</v>
       </c>
       <c r="B701" t="s" s="2">
+        <v>1497</v>
+      </c>
+      <c r="C701" t="s" s="2">
         <v>1498</v>
-      </c>
-      <c r="C701" t="s" s="2">
-        <v>1499</v>
       </c>
       <c r="D701" s="2"/>
     </row>
@@ -15652,10 +15691,10 @@
         <v>95</v>
       </c>
       <c r="B702" t="s" s="2">
+        <v>1499</v>
+      </c>
+      <c r="C702" t="s" s="2">
         <v>1500</v>
-      </c>
-      <c r="C702" t="s" s="2">
-        <v>1501</v>
       </c>
       <c r="D702" s="2"/>
     </row>
@@ -15664,10 +15703,10 @@
         <v>95</v>
       </c>
       <c r="B703" t="s" s="2">
+        <v>1501</v>
+      </c>
+      <c r="C703" t="s" s="2">
         <v>1502</v>
-      </c>
-      <c r="C703" t="s" s="2">
-        <v>1503</v>
       </c>
       <c r="D703" s="2"/>
     </row>
@@ -15676,10 +15715,10 @@
         <v>95</v>
       </c>
       <c r="B704" t="s" s="2">
+        <v>1503</v>
+      </c>
+      <c r="C704" t="s" s="2">
         <v>1504</v>
-      </c>
-      <c r="C704" t="s" s="2">
-        <v>1505</v>
       </c>
       <c r="D704" s="2"/>
     </row>
@@ -15688,10 +15727,10 @@
         <v>95</v>
       </c>
       <c r="B705" t="s" s="2">
+        <v>1505</v>
+      </c>
+      <c r="C705" t="s" s="2">
         <v>1506</v>
-      </c>
-      <c r="C705" t="s" s="2">
-        <v>1507</v>
       </c>
       <c r="D705" s="2"/>
     </row>
@@ -15700,10 +15739,10 @@
         <v>95</v>
       </c>
       <c r="B706" t="s" s="2">
+        <v>1507</v>
+      </c>
+      <c r="C706" t="s" s="2">
         <v>1508</v>
-      </c>
-      <c r="C706" t="s" s="2">
-        <v>1509</v>
       </c>
       <c r="D706" s="2"/>
     </row>
@@ -15712,10 +15751,10 @@
         <v>95</v>
       </c>
       <c r="B707" t="s" s="2">
+        <v>1509</v>
+      </c>
+      <c r="C707" t="s" s="2">
         <v>1510</v>
-      </c>
-      <c r="C707" t="s" s="2">
-        <v>1511</v>
       </c>
       <c r="D707" s="2"/>
     </row>
@@ -15724,10 +15763,10 @@
         <v>95</v>
       </c>
       <c r="B708" t="s" s="2">
+        <v>1511</v>
+      </c>
+      <c r="C708" t="s" s="2">
         <v>1512</v>
-      </c>
-      <c r="C708" t="s" s="2">
-        <v>1513</v>
       </c>
       <c r="D708" s="2"/>
     </row>
@@ -15736,10 +15775,10 @@
         <v>95</v>
       </c>
       <c r="B709" t="s" s="2">
+        <v>1513</v>
+      </c>
+      <c r="C709" t="s" s="2">
         <v>1514</v>
-      </c>
-      <c r="C709" t="s" s="2">
-        <v>1515</v>
       </c>
       <c r="D709" s="2"/>
     </row>
@@ -15748,10 +15787,10 @@
         <v>95</v>
       </c>
       <c r="B710" t="s" s="2">
+        <v>1515</v>
+      </c>
+      <c r="C710" t="s" s="2">
         <v>1516</v>
-      </c>
-      <c r="C710" t="s" s="2">
-        <v>1517</v>
       </c>
       <c r="D710" s="2"/>
     </row>
@@ -15760,10 +15799,10 @@
         <v>95</v>
       </c>
       <c r="B711" t="s" s="2">
+        <v>1517</v>
+      </c>
+      <c r="C711" t="s" s="2">
         <v>1518</v>
-      </c>
-      <c r="C711" t="s" s="2">
-        <v>1519</v>
       </c>
       <c r="D711" s="2"/>
     </row>
@@ -15772,10 +15811,10 @@
         <v>95</v>
       </c>
       <c r="B712" t="s" s="2">
+        <v>1519</v>
+      </c>
+      <c r="C712" t="s" s="2">
         <v>1520</v>
-      </c>
-      <c r="C712" t="s" s="2">
-        <v>1521</v>
       </c>
       <c r="D712" s="2"/>
     </row>
@@ -15784,10 +15823,10 @@
         <v>95</v>
       </c>
       <c r="B713" t="s" s="2">
+        <v>1521</v>
+      </c>
+      <c r="C713" t="s" s="2">
         <v>1522</v>
-      </c>
-      <c r="C713" t="s" s="2">
-        <v>1523</v>
       </c>
       <c r="D713" s="2"/>
     </row>
@@ -15796,10 +15835,10 @@
         <v>95</v>
       </c>
       <c r="B714" t="s" s="2">
+        <v>1523</v>
+      </c>
+      <c r="C714" t="s" s="2">
         <v>1524</v>
-      </c>
-      <c r="C714" t="s" s="2">
-        <v>1525</v>
       </c>
       <c r="D714" s="2"/>
     </row>
@@ -15808,10 +15847,10 @@
         <v>95</v>
       </c>
       <c r="B715" t="s" s="2">
+        <v>1525</v>
+      </c>
+      <c r="C715" t="s" s="2">
         <v>1526</v>
-      </c>
-      <c r="C715" t="s" s="2">
-        <v>1527</v>
       </c>
       <c r="D715" s="2"/>
     </row>
@@ -15820,10 +15859,10 @@
         <v>95</v>
       </c>
       <c r="B716" t="s" s="2">
+        <v>1527</v>
+      </c>
+      <c r="C716" t="s" s="2">
         <v>1528</v>
-      </c>
-      <c r="C716" t="s" s="2">
-        <v>1529</v>
       </c>
       <c r="D716" s="2"/>
     </row>
@@ -15832,10 +15871,10 @@
         <v>95</v>
       </c>
       <c r="B717" t="s" s="2">
+        <v>1529</v>
+      </c>
+      <c r="C717" t="s" s="2">
         <v>1530</v>
-      </c>
-      <c r="C717" t="s" s="2">
-        <v>1531</v>
       </c>
       <c r="D717" s="2"/>
     </row>
@@ -15844,10 +15883,10 @@
         <v>95</v>
       </c>
       <c r="B718" t="s" s="2">
+        <v>1531</v>
+      </c>
+      <c r="C718" t="s" s="2">
         <v>1532</v>
-      </c>
-      <c r="C718" t="s" s="2">
-        <v>1533</v>
       </c>
       <c r="D718" s="2"/>
     </row>
@@ -15856,10 +15895,10 @@
         <v>95</v>
       </c>
       <c r="B719" t="s" s="2">
+        <v>1533</v>
+      </c>
+      <c r="C719" t="s" s="2">
         <v>1534</v>
-      </c>
-      <c r="C719" t="s" s="2">
-        <v>1535</v>
       </c>
       <c r="D719" s="2"/>
     </row>
@@ -15868,10 +15907,10 @@
         <v>95</v>
       </c>
       <c r="B720" t="s" s="2">
+        <v>1535</v>
+      </c>
+      <c r="C720" t="s" s="2">
         <v>1536</v>
-      </c>
-      <c r="C720" t="s" s="2">
-        <v>1537</v>
       </c>
       <c r="D720" s="2"/>
     </row>
@@ -15880,10 +15919,10 @@
         <v>95</v>
       </c>
       <c r="B721" t="s" s="2">
+        <v>1537</v>
+      </c>
+      <c r="C721" t="s" s="2">
         <v>1538</v>
-      </c>
-      <c r="C721" t="s" s="2">
-        <v>1539</v>
       </c>
       <c r="D721" s="2"/>
     </row>
@@ -15892,10 +15931,10 @@
         <v>95</v>
       </c>
       <c r="B722" t="s" s="2">
+        <v>1539</v>
+      </c>
+      <c r="C722" t="s" s="2">
         <v>1540</v>
-      </c>
-      <c r="C722" t="s" s="2">
-        <v>1541</v>
       </c>
       <c r="D722" s="2"/>
     </row>
@@ -15904,10 +15943,10 @@
         <v>95</v>
       </c>
       <c r="B723" t="s" s="2">
+        <v>1541</v>
+      </c>
+      <c r="C723" t="s" s="2">
         <v>1542</v>
-      </c>
-      <c r="C723" t="s" s="2">
-        <v>1543</v>
       </c>
       <c r="D723" s="2"/>
     </row>
@@ -15916,10 +15955,10 @@
         <v>95</v>
       </c>
       <c r="B724" t="s" s="2">
+        <v>1543</v>
+      </c>
+      <c r="C724" t="s" s="2">
         <v>1544</v>
-      </c>
-      <c r="C724" t="s" s="2">
-        <v>1545</v>
       </c>
       <c r="D724" s="2"/>
     </row>
@@ -15928,10 +15967,10 @@
         <v>95</v>
       </c>
       <c r="B725" t="s" s="2">
+        <v>1545</v>
+      </c>
+      <c r="C725" t="s" s="2">
         <v>1546</v>
-      </c>
-      <c r="C725" t="s" s="2">
-        <v>1547</v>
       </c>
       <c r="D725" s="2"/>
     </row>
@@ -15940,10 +15979,10 @@
         <v>95</v>
       </c>
       <c r="B726" t="s" s="2">
+        <v>1547</v>
+      </c>
+      <c r="C726" t="s" s="2">
         <v>1548</v>
-      </c>
-      <c r="C726" t="s" s="2">
-        <v>1549</v>
       </c>
       <c r="D726" s="2"/>
     </row>
@@ -15952,10 +15991,10 @@
         <v>95</v>
       </c>
       <c r="B727" t="s" s="2">
+        <v>1549</v>
+      </c>
+      <c r="C727" t="s" s="2">
         <v>1550</v>
-      </c>
-      <c r="C727" t="s" s="2">
-        <v>1551</v>
       </c>
       <c r="D727" s="2"/>
     </row>
@@ -15964,10 +16003,10 @@
         <v>95</v>
       </c>
       <c r="B728" t="s" s="2">
+        <v>1551</v>
+      </c>
+      <c r="C728" t="s" s="2">
         <v>1552</v>
-      </c>
-      <c r="C728" t="s" s="2">
-        <v>1553</v>
       </c>
       <c r="D728" s="2"/>
     </row>
@@ -15976,10 +16015,10 @@
         <v>95</v>
       </c>
       <c r="B729" t="s" s="2">
+        <v>1553</v>
+      </c>
+      <c r="C729" t="s" s="2">
         <v>1554</v>
-      </c>
-      <c r="C729" t="s" s="2">
-        <v>1555</v>
       </c>
       <c r="D729" s="2"/>
     </row>
@@ -15988,10 +16027,10 @@
         <v>95</v>
       </c>
       <c r="B730" t="s" s="2">
+        <v>1555</v>
+      </c>
+      <c r="C730" t="s" s="2">
         <v>1556</v>
-      </c>
-      <c r="C730" t="s" s="2">
-        <v>1557</v>
       </c>
       <c r="D730" s="2"/>
     </row>
@@ -16000,10 +16039,10 @@
         <v>95</v>
       </c>
       <c r="B731" t="s" s="2">
+        <v>1557</v>
+      </c>
+      <c r="C731" t="s" s="2">
         <v>1558</v>
-      </c>
-      <c r="C731" t="s" s="2">
-        <v>1559</v>
       </c>
       <c r="D731" s="2"/>
     </row>
@@ -16012,10 +16051,10 @@
         <v>95</v>
       </c>
       <c r="B732" t="s" s="2">
+        <v>1559</v>
+      </c>
+      <c r="C732" t="s" s="2">
         <v>1560</v>
-      </c>
-      <c r="C732" t="s" s="2">
-        <v>1561</v>
       </c>
       <c r="D732" s="2"/>
     </row>
@@ -16024,10 +16063,10 @@
         <v>95</v>
       </c>
       <c r="B733" t="s" s="2">
+        <v>1561</v>
+      </c>
+      <c r="C733" t="s" s="2">
         <v>1562</v>
-      </c>
-      <c r="C733" t="s" s="2">
-        <v>1563</v>
       </c>
       <c r="D733" s="2"/>
     </row>
@@ -16036,10 +16075,10 @@
         <v>95</v>
       </c>
       <c r="B734" t="s" s="2">
+        <v>1563</v>
+      </c>
+      <c r="C734" t="s" s="2">
         <v>1564</v>
-      </c>
-      <c r="C734" t="s" s="2">
-        <v>1565</v>
       </c>
       <c r="D734" s="2"/>
     </row>
@@ -16048,10 +16087,10 @@
         <v>95</v>
       </c>
       <c r="B735" t="s" s="2">
+        <v>1565</v>
+      </c>
+      <c r="C735" t="s" s="2">
         <v>1566</v>
-      </c>
-      <c r="C735" t="s" s="2">
-        <v>1567</v>
       </c>
       <c r="D735" s="2"/>
     </row>
@@ -16060,10 +16099,10 @@
         <v>95</v>
       </c>
       <c r="B736" t="s" s="2">
+        <v>1567</v>
+      </c>
+      <c r="C736" t="s" s="2">
         <v>1568</v>
-      </c>
-      <c r="C736" t="s" s="2">
-        <v>1569</v>
       </c>
       <c r="D736" s="2"/>
     </row>
@@ -16072,10 +16111,10 @@
         <v>95</v>
       </c>
       <c r="B737" t="s" s="2">
+        <v>1569</v>
+      </c>
+      <c r="C737" t="s" s="2">
         <v>1570</v>
-      </c>
-      <c r="C737" t="s" s="2">
-        <v>1571</v>
       </c>
       <c r="D737" s="2"/>
     </row>
@@ -16084,10 +16123,10 @@
         <v>95</v>
       </c>
       <c r="B738" t="s" s="2">
+        <v>1571</v>
+      </c>
+      <c r="C738" t="s" s="2">
         <v>1572</v>
-      </c>
-      <c r="C738" t="s" s="2">
-        <v>1573</v>
       </c>
       <c r="D738" s="2"/>
     </row>
@@ -16096,10 +16135,10 @@
         <v>95</v>
       </c>
       <c r="B739" t="s" s="2">
+        <v>1573</v>
+      </c>
+      <c r="C739" t="s" s="2">
         <v>1574</v>
-      </c>
-      <c r="C739" t="s" s="2">
-        <v>1575</v>
       </c>
       <c r="D739" s="2"/>
     </row>
@@ -16108,10 +16147,10 @@
         <v>95</v>
       </c>
       <c r="B740" t="s" s="2">
+        <v>1575</v>
+      </c>
+      <c r="C740" t="s" s="2">
         <v>1576</v>
-      </c>
-      <c r="C740" t="s" s="2">
-        <v>1577</v>
       </c>
       <c r="D740" s="2"/>
     </row>
@@ -16120,10 +16159,10 @@
         <v>95</v>
       </c>
       <c r="B741" t="s" s="2">
+        <v>1577</v>
+      </c>
+      <c r="C741" t="s" s="2">
         <v>1578</v>
-      </c>
-      <c r="C741" t="s" s="2">
-        <v>1579</v>
       </c>
       <c r="D741" s="2"/>
     </row>
@@ -16132,10 +16171,10 @@
         <v>95</v>
       </c>
       <c r="B742" t="s" s="2">
+        <v>1579</v>
+      </c>
+      <c r="C742" t="s" s="2">
         <v>1580</v>
-      </c>
-      <c r="C742" t="s" s="2">
-        <v>1581</v>
       </c>
       <c r="D742" s="2"/>
     </row>
@@ -16144,10 +16183,10 @@
         <v>95</v>
       </c>
       <c r="B743" t="s" s="2">
+        <v>1581</v>
+      </c>
+      <c r="C743" t="s" s="2">
         <v>1582</v>
-      </c>
-      <c r="C743" t="s" s="2">
-        <v>1583</v>
       </c>
       <c r="D743" s="2"/>
     </row>
@@ -16156,10 +16195,10 @@
         <v>95</v>
       </c>
       <c r="B744" t="s" s="2">
+        <v>1583</v>
+      </c>
+      <c r="C744" t="s" s="2">
         <v>1584</v>
-      </c>
-      <c r="C744" t="s" s="2">
-        <v>1585</v>
       </c>
       <c r="D744" s="2"/>
     </row>
@@ -16168,10 +16207,10 @@
         <v>95</v>
       </c>
       <c r="B745" t="s" s="2">
+        <v>1585</v>
+      </c>
+      <c r="C745" t="s" s="2">
         <v>1586</v>
-      </c>
-      <c r="C745" t="s" s="2">
-        <v>1587</v>
       </c>
       <c r="D745" s="2"/>
     </row>
@@ -16180,10 +16219,10 @@
         <v>95</v>
       </c>
       <c r="B746" t="s" s="2">
+        <v>1587</v>
+      </c>
+      <c r="C746" t="s" s="2">
         <v>1588</v>
-      </c>
-      <c r="C746" t="s" s="2">
-        <v>1589</v>
       </c>
       <c r="D746" s="2"/>
     </row>
@@ -16192,10 +16231,10 @@
         <v>95</v>
       </c>
       <c r="B747" t="s" s="2">
+        <v>1589</v>
+      </c>
+      <c r="C747" t="s" s="2">
         <v>1590</v>
-      </c>
-      <c r="C747" t="s" s="2">
-        <v>1591</v>
       </c>
       <c r="D747" s="2"/>
     </row>
@@ -16204,10 +16243,10 @@
         <v>95</v>
       </c>
       <c r="B748" t="s" s="2">
+        <v>1591</v>
+      </c>
+      <c r="C748" t="s" s="2">
         <v>1592</v>
-      </c>
-      <c r="C748" t="s" s="2">
-        <v>1593</v>
       </c>
       <c r="D748" s="2"/>
     </row>
@@ -16216,10 +16255,10 @@
         <v>95</v>
       </c>
       <c r="B749" t="s" s="2">
+        <v>1593</v>
+      </c>
+      <c r="C749" t="s" s="2">
         <v>1594</v>
-      </c>
-      <c r="C749" t="s" s="2">
-        <v>1595</v>
       </c>
       <c r="D749" s="2"/>
     </row>
@@ -16228,10 +16267,10 @@
         <v>95</v>
       </c>
       <c r="B750" t="s" s="2">
+        <v>1595</v>
+      </c>
+      <c r="C750" t="s" s="2">
         <v>1596</v>
-      </c>
-      <c r="C750" t="s" s="2">
-        <v>1597</v>
       </c>
       <c r="D750" s="2"/>
     </row>
@@ -16240,10 +16279,10 @@
         <v>95</v>
       </c>
       <c r="B751" t="s" s="2">
+        <v>1597</v>
+      </c>
+      <c r="C751" t="s" s="2">
         <v>1598</v>
-      </c>
-      <c r="C751" t="s" s="2">
-        <v>1599</v>
       </c>
       <c r="D751" s="2"/>
     </row>
@@ -16252,10 +16291,10 @@
         <v>95</v>
       </c>
       <c r="B752" t="s" s="2">
+        <v>1599</v>
+      </c>
+      <c r="C752" t="s" s="2">
         <v>1600</v>
-      </c>
-      <c r="C752" t="s" s="2">
-        <v>1601</v>
       </c>
       <c r="D752" s="2"/>
     </row>
@@ -16264,10 +16303,10 @@
         <v>95</v>
       </c>
       <c r="B753" t="s" s="2">
+        <v>1601</v>
+      </c>
+      <c r="C753" t="s" s="2">
         <v>1602</v>
-      </c>
-      <c r="C753" t="s" s="2">
-        <v>1603</v>
       </c>
       <c r="D753" s="2"/>
     </row>
@@ -16276,10 +16315,10 @@
         <v>95</v>
       </c>
       <c r="B754" t="s" s="2">
+        <v>1603</v>
+      </c>
+      <c r="C754" t="s" s="2">
         <v>1604</v>
-      </c>
-      <c r="C754" t="s" s="2">
-        <v>1605</v>
       </c>
       <c r="D754" s="2"/>
     </row>
@@ -16288,10 +16327,10 @@
         <v>95</v>
       </c>
       <c r="B755" t="s" s="2">
+        <v>1605</v>
+      </c>
+      <c r="C755" t="s" s="2">
         <v>1606</v>
-      </c>
-      <c r="C755" t="s" s="2">
-        <v>1607</v>
       </c>
       <c r="D755" s="2"/>
     </row>
@@ -16300,10 +16339,10 @@
         <v>95</v>
       </c>
       <c r="B756" t="s" s="2">
+        <v>1607</v>
+      </c>
+      <c r="C756" t="s" s="2">
         <v>1608</v>
-      </c>
-      <c r="C756" t="s" s="2">
-        <v>1609</v>
       </c>
       <c r="D756" s="2"/>
     </row>
@@ -16312,10 +16351,10 @@
         <v>95</v>
       </c>
       <c r="B757" t="s" s="2">
+        <v>1609</v>
+      </c>
+      <c r="C757" t="s" s="2">
         <v>1610</v>
-      </c>
-      <c r="C757" t="s" s="2">
-        <v>1611</v>
       </c>
       <c r="D757" s="2"/>
     </row>
@@ -16324,10 +16363,10 @@
         <v>95</v>
       </c>
       <c r="B758" t="s" s="2">
+        <v>1611</v>
+      </c>
+      <c r="C758" t="s" s="2">
         <v>1612</v>
-      </c>
-      <c r="C758" t="s" s="2">
-        <v>1613</v>
       </c>
       <c r="D758" s="2"/>
     </row>
@@ -16336,10 +16375,10 @@
         <v>95</v>
       </c>
       <c r="B759" t="s" s="2">
+        <v>1613</v>
+      </c>
+      <c r="C759" t="s" s="2">
         <v>1614</v>
-      </c>
-      <c r="C759" t="s" s="2">
-        <v>1615</v>
       </c>
       <c r="D759" s="2"/>
     </row>
@@ -16348,10 +16387,10 @@
         <v>95</v>
       </c>
       <c r="B760" t="s" s="2">
+        <v>1615</v>
+      </c>
+      <c r="C760" t="s" s="2">
         <v>1616</v>
-      </c>
-      <c r="C760" t="s" s="2">
-        <v>1617</v>
       </c>
       <c r="D760" s="2"/>
     </row>
@@ -16360,10 +16399,10 @@
         <v>95</v>
       </c>
       <c r="B761" t="s" s="2">
+        <v>1617</v>
+      </c>
+      <c r="C761" t="s" s="2">
         <v>1618</v>
-      </c>
-      <c r="C761" t="s" s="2">
-        <v>1619</v>
       </c>
       <c r="D761" s="2"/>
     </row>
@@ -16372,10 +16411,10 @@
         <v>95</v>
       </c>
       <c r="B762" t="s" s="2">
+        <v>1619</v>
+      </c>
+      <c r="C762" t="s" s="2">
         <v>1620</v>
-      </c>
-      <c r="C762" t="s" s="2">
-        <v>1621</v>
       </c>
       <c r="D762" s="2"/>
     </row>
@@ -16384,10 +16423,10 @@
         <v>95</v>
       </c>
       <c r="B763" t="s" s="2">
+        <v>1621</v>
+      </c>
+      <c r="C763" t="s" s="2">
         <v>1622</v>
-      </c>
-      <c r="C763" t="s" s="2">
-        <v>1623</v>
       </c>
       <c r="D763" s="2"/>
     </row>
@@ -16396,10 +16435,10 @@
         <v>95</v>
       </c>
       <c r="B764" t="s" s="2">
+        <v>1623</v>
+      </c>
+      <c r="C764" t="s" s="2">
         <v>1624</v>
-      </c>
-      <c r="C764" t="s" s="2">
-        <v>1625</v>
       </c>
       <c r="D764" s="2"/>
     </row>
@@ -16408,10 +16447,10 @@
         <v>95</v>
       </c>
       <c r="B765" t="s" s="2">
+        <v>1625</v>
+      </c>
+      <c r="C765" t="s" s="2">
         <v>1626</v>
-      </c>
-      <c r="C765" t="s" s="2">
-        <v>1627</v>
       </c>
       <c r="D765" s="2"/>
     </row>
@@ -16420,10 +16459,10 @@
         <v>95</v>
       </c>
       <c r="B766" t="s" s="2">
+        <v>1627</v>
+      </c>
+      <c r="C766" t="s" s="2">
         <v>1628</v>
-      </c>
-      <c r="C766" t="s" s="2">
-        <v>1629</v>
       </c>
       <c r="D766" s="2"/>
     </row>
@@ -16432,10 +16471,10 @@
         <v>95</v>
       </c>
       <c r="B767" t="s" s="2">
+        <v>1629</v>
+      </c>
+      <c r="C767" t="s" s="2">
         <v>1630</v>
-      </c>
-      <c r="C767" t="s" s="2">
-        <v>1631</v>
       </c>
       <c r="D767" s="2"/>
     </row>
@@ -16444,10 +16483,10 @@
         <v>95</v>
       </c>
       <c r="B768" t="s" s="2">
+        <v>1631</v>
+      </c>
+      <c r="C768" t="s" s="2">
         <v>1632</v>
-      </c>
-      <c r="C768" t="s" s="2">
-        <v>1633</v>
       </c>
       <c r="D768" s="2"/>
     </row>
@@ -16456,10 +16495,10 @@
         <v>95</v>
       </c>
       <c r="B769" t="s" s="2">
+        <v>1633</v>
+      </c>
+      <c r="C769" t="s" s="2">
         <v>1634</v>
-      </c>
-      <c r="C769" t="s" s="2">
-        <v>1635</v>
       </c>
       <c r="D769" s="2"/>
     </row>
@@ -16468,10 +16507,10 @@
         <v>95</v>
       </c>
       <c r="B770" t="s" s="2">
+        <v>1635</v>
+      </c>
+      <c r="C770" t="s" s="2">
         <v>1636</v>
-      </c>
-      <c r="C770" t="s" s="2">
-        <v>1637</v>
       </c>
       <c r="D770" s="2"/>
     </row>
@@ -16480,10 +16519,10 @@
         <v>95</v>
       </c>
       <c r="B771" t="s" s="2">
+        <v>1637</v>
+      </c>
+      <c r="C771" t="s" s="2">
         <v>1638</v>
-      </c>
-      <c r="C771" t="s" s="2">
-        <v>1639</v>
       </c>
       <c r="D771" s="2"/>
     </row>
@@ -16492,10 +16531,10 @@
         <v>95</v>
       </c>
       <c r="B772" t="s" s="2">
+        <v>1639</v>
+      </c>
+      <c r="C772" t="s" s="2">
         <v>1640</v>
-      </c>
-      <c r="C772" t="s" s="2">
-        <v>1641</v>
       </c>
       <c r="D772" s="2"/>
     </row>
@@ -16504,10 +16543,10 @@
         <v>95</v>
       </c>
       <c r="B773" t="s" s="2">
+        <v>1641</v>
+      </c>
+      <c r="C773" t="s" s="2">
         <v>1642</v>
-      </c>
-      <c r="C773" t="s" s="2">
-        <v>1643</v>
       </c>
       <c r="D773" s="2"/>
     </row>
@@ -16516,10 +16555,10 @@
         <v>95</v>
       </c>
       <c r="B774" t="s" s="2">
+        <v>1643</v>
+      </c>
+      <c r="C774" t="s" s="2">
         <v>1644</v>
-      </c>
-      <c r="C774" t="s" s="2">
-        <v>1645</v>
       </c>
       <c r="D774" s="2"/>
     </row>
@@ -16528,10 +16567,10 @@
         <v>95</v>
       </c>
       <c r="B775" t="s" s="2">
+        <v>1645</v>
+      </c>
+      <c r="C775" t="s" s="2">
         <v>1646</v>
-      </c>
-      <c r="C775" t="s" s="2">
-        <v>1647</v>
       </c>
       <c r="D775" s="2"/>
     </row>
@@ -16540,10 +16579,10 @@
         <v>95</v>
       </c>
       <c r="B776" t="s" s="2">
+        <v>1647</v>
+      </c>
+      <c r="C776" t="s" s="2">
         <v>1648</v>
-      </c>
-      <c r="C776" t="s" s="2">
-        <v>1649</v>
       </c>
       <c r="D776" s="2"/>
     </row>
@@ -16552,10 +16591,10 @@
         <v>95</v>
       </c>
       <c r="B777" t="s" s="2">
+        <v>1649</v>
+      </c>
+      <c r="C777" t="s" s="2">
         <v>1650</v>
-      </c>
-      <c r="C777" t="s" s="2">
-        <v>1651</v>
       </c>
       <c r="D777" s="2"/>
     </row>
@@ -16564,10 +16603,10 @@
         <v>95</v>
       </c>
       <c r="B778" t="s" s="2">
+        <v>1651</v>
+      </c>
+      <c r="C778" t="s" s="2">
         <v>1652</v>
-      </c>
-      <c r="C778" t="s" s="2">
-        <v>1653</v>
       </c>
       <c r="D778" s="2"/>
     </row>
@@ -16576,10 +16615,10 @@
         <v>95</v>
       </c>
       <c r="B779" t="s" s="2">
+        <v>1653</v>
+      </c>
+      <c r="C779" t="s" s="2">
         <v>1654</v>
-      </c>
-      <c r="C779" t="s" s="2">
-        <v>1655</v>
       </c>
       <c r="D779" s="2"/>
     </row>
@@ -16588,10 +16627,10 @@
         <v>95</v>
       </c>
       <c r="B780" t="s" s="2">
+        <v>1655</v>
+      </c>
+      <c r="C780" t="s" s="2">
         <v>1656</v>
-      </c>
-      <c r="C780" t="s" s="2">
-        <v>1657</v>
       </c>
       <c r="D780" s="2"/>
     </row>
@@ -16600,10 +16639,10 @@
         <v>95</v>
       </c>
       <c r="B781" t="s" s="2">
+        <v>1657</v>
+      </c>
+      <c r="C781" t="s" s="2">
         <v>1658</v>
-      </c>
-      <c r="C781" t="s" s="2">
-        <v>1659</v>
       </c>
       <c r="D781" s="2"/>
     </row>
@@ -16612,10 +16651,10 @@
         <v>95</v>
       </c>
       <c r="B782" t="s" s="2">
+        <v>1659</v>
+      </c>
+      <c r="C782" t="s" s="2">
         <v>1660</v>
-      </c>
-      <c r="C782" t="s" s="2">
-        <v>1661</v>
       </c>
       <c r="D782" s="2"/>
     </row>
@@ -16624,10 +16663,10 @@
         <v>95</v>
       </c>
       <c r="B783" t="s" s="2">
+        <v>1661</v>
+      </c>
+      <c r="C783" t="s" s="2">
         <v>1662</v>
-      </c>
-      <c r="C783" t="s" s="2">
-        <v>1663</v>
       </c>
       <c r="D783" s="2"/>
     </row>
@@ -16636,10 +16675,10 @@
         <v>95</v>
       </c>
       <c r="B784" t="s" s="2">
+        <v>1663</v>
+      </c>
+      <c r="C784" t="s" s="2">
         <v>1664</v>
-      </c>
-      <c r="C784" t="s" s="2">
-        <v>1665</v>
       </c>
       <c r="D784" s="2"/>
     </row>
@@ -16648,10 +16687,10 @@
         <v>95</v>
       </c>
       <c r="B785" t="s" s="2">
+        <v>1665</v>
+      </c>
+      <c r="C785" t="s" s="2">
         <v>1666</v>
-      </c>
-      <c r="C785" t="s" s="2">
-        <v>1667</v>
       </c>
       <c r="D785" s="2"/>
     </row>
@@ -16660,10 +16699,10 @@
         <v>95</v>
       </c>
       <c r="B786" t="s" s="2">
+        <v>1667</v>
+      </c>
+      <c r="C786" t="s" s="2">
         <v>1668</v>
-      </c>
-      <c r="C786" t="s" s="2">
-        <v>1669</v>
       </c>
       <c r="D786" s="2"/>
     </row>
@@ -16672,10 +16711,10 @@
         <v>95</v>
       </c>
       <c r="B787" t="s" s="2">
+        <v>1669</v>
+      </c>
+      <c r="C787" t="s" s="2">
         <v>1670</v>
-      </c>
-      <c r="C787" t="s" s="2">
-        <v>1671</v>
       </c>
       <c r="D787" s="2"/>
     </row>
@@ -16684,10 +16723,10 @@
         <v>95</v>
       </c>
       <c r="B788" t="s" s="2">
+        <v>1671</v>
+      </c>
+      <c r="C788" t="s" s="2">
         <v>1672</v>
-      </c>
-      <c r="C788" t="s" s="2">
-        <v>1673</v>
       </c>
       <c r="D788" s="2"/>
     </row>
@@ -16696,10 +16735,10 @@
         <v>95</v>
       </c>
       <c r="B789" t="s" s="2">
+        <v>1673</v>
+      </c>
+      <c r="C789" t="s" s="2">
         <v>1674</v>
-      </c>
-      <c r="C789" t="s" s="2">
-        <v>1675</v>
       </c>
       <c r="D789" s="2"/>
     </row>
@@ -16708,10 +16747,10 @@
         <v>95</v>
       </c>
       <c r="B790" t="s" s="2">
+        <v>1675</v>
+      </c>
+      <c r="C790" t="s" s="2">
         <v>1676</v>
-      </c>
-      <c r="C790" t="s" s="2">
-        <v>1677</v>
       </c>
       <c r="D790" s="2"/>
     </row>
@@ -16720,10 +16759,10 @@
         <v>95</v>
       </c>
       <c r="B791" t="s" s="2">
+        <v>1677</v>
+      </c>
+      <c r="C791" t="s" s="2">
         <v>1678</v>
-      </c>
-      <c r="C791" t="s" s="2">
-        <v>1679</v>
       </c>
       <c r="D791" s="2"/>
     </row>
@@ -16732,10 +16771,10 @@
         <v>95</v>
       </c>
       <c r="B792" t="s" s="2">
+        <v>1679</v>
+      </c>
+      <c r="C792" t="s" s="2">
         <v>1680</v>
-      </c>
-      <c r="C792" t="s" s="2">
-        <v>1681</v>
       </c>
       <c r="D792" s="2"/>
     </row>
@@ -16744,10 +16783,10 @@
         <v>95</v>
       </c>
       <c r="B793" t="s" s="2">
+        <v>1681</v>
+      </c>
+      <c r="C793" t="s" s="2">
         <v>1682</v>
-      </c>
-      <c r="C793" t="s" s="2">
-        <v>1683</v>
       </c>
       <c r="D793" s="2"/>
     </row>
@@ -16756,10 +16795,10 @@
         <v>95</v>
       </c>
       <c r="B794" t="s" s="2">
+        <v>1683</v>
+      </c>
+      <c r="C794" t="s" s="2">
         <v>1684</v>
-      </c>
-      <c r="C794" t="s" s="2">
-        <v>1685</v>
       </c>
       <c r="D794" s="2"/>
     </row>
@@ -16768,10 +16807,10 @@
         <v>95</v>
       </c>
       <c r="B795" t="s" s="2">
+        <v>1685</v>
+      </c>
+      <c r="C795" t="s" s="2">
         <v>1686</v>
-      </c>
-      <c r="C795" t="s" s="2">
-        <v>1687</v>
       </c>
       <c r="D795" s="2"/>
     </row>
@@ -16780,10 +16819,10 @@
         <v>95</v>
       </c>
       <c r="B796" t="s" s="2">
+        <v>1687</v>
+      </c>
+      <c r="C796" t="s" s="2">
         <v>1688</v>
-      </c>
-      <c r="C796" t="s" s="2">
-        <v>1689</v>
       </c>
       <c r="D796" s="2"/>
     </row>
@@ -16792,10 +16831,10 @@
         <v>95</v>
       </c>
       <c r="B797" t="s" s="2">
+        <v>1689</v>
+      </c>
+      <c r="C797" t="s" s="2">
         <v>1690</v>
-      </c>
-      <c r="C797" t="s" s="2">
-        <v>1691</v>
       </c>
       <c r="D797" s="2"/>
     </row>
@@ -16804,10 +16843,10 @@
         <v>95</v>
       </c>
       <c r="B798" t="s" s="2">
+        <v>1691</v>
+      </c>
+      <c r="C798" t="s" s="2">
         <v>1692</v>
-      </c>
-      <c r="C798" t="s" s="2">
-        <v>1693</v>
       </c>
       <c r="D798" s="2"/>
     </row>
@@ -16816,10 +16855,10 @@
         <v>95</v>
       </c>
       <c r="B799" t="s" s="2">
+        <v>1693</v>
+      </c>
+      <c r="C799" t="s" s="2">
         <v>1694</v>
-      </c>
-      <c r="C799" t="s" s="2">
-        <v>1695</v>
       </c>
       <c r="D799" s="2"/>
     </row>
@@ -16828,10 +16867,10 @@
         <v>95</v>
       </c>
       <c r="B800" t="s" s="2">
+        <v>1695</v>
+      </c>
+      <c r="C800" t="s" s="2">
         <v>1696</v>
-      </c>
-      <c r="C800" t="s" s="2">
-        <v>1697</v>
       </c>
       <c r="D800" s="2"/>
     </row>
@@ -16840,10 +16879,10 @@
         <v>95</v>
       </c>
       <c r="B801" t="s" s="2">
+        <v>1697</v>
+      </c>
+      <c r="C801" t="s" s="2">
         <v>1698</v>
-      </c>
-      <c r="C801" t="s" s="2">
-        <v>1699</v>
       </c>
       <c r="D801" s="2"/>
     </row>
@@ -16852,10 +16891,10 @@
         <v>95</v>
       </c>
       <c r="B802" t="s" s="2">
+        <v>1699</v>
+      </c>
+      <c r="C802" t="s" s="2">
         <v>1700</v>
-      </c>
-      <c r="C802" t="s" s="2">
-        <v>1701</v>
       </c>
       <c r="D802" s="2"/>
     </row>
@@ -16864,10 +16903,10 @@
         <v>95</v>
       </c>
       <c r="B803" t="s" s="2">
+        <v>1701</v>
+      </c>
+      <c r="C803" t="s" s="2">
         <v>1702</v>
-      </c>
-      <c r="C803" t="s" s="2">
-        <v>1703</v>
       </c>
       <c r="D803" s="2"/>
     </row>
@@ -16876,10 +16915,10 @@
         <v>95</v>
       </c>
       <c r="B804" t="s" s="2">
+        <v>1703</v>
+      </c>
+      <c r="C804" t="s" s="2">
         <v>1704</v>
-      </c>
-      <c r="C804" t="s" s="2">
-        <v>1705</v>
       </c>
       <c r="D804" s="2"/>
     </row>
@@ -16888,10 +16927,10 @@
         <v>95</v>
       </c>
       <c r="B805" t="s" s="2">
+        <v>1705</v>
+      </c>
+      <c r="C805" t="s" s="2">
         <v>1706</v>
-      </c>
-      <c r="C805" t="s" s="2">
-        <v>1707</v>
       </c>
       <c r="D805" s="2"/>
     </row>
@@ -16900,10 +16939,10 @@
         <v>95</v>
       </c>
       <c r="B806" t="s" s="2">
+        <v>1707</v>
+      </c>
+      <c r="C806" t="s" s="2">
         <v>1708</v>
-      </c>
-      <c r="C806" t="s" s="2">
-        <v>1709</v>
       </c>
       <c r="D806" s="2"/>
     </row>
@@ -16912,10 +16951,10 @@
         <v>95</v>
       </c>
       <c r="B807" t="s" s="2">
+        <v>1709</v>
+      </c>
+      <c r="C807" t="s" s="2">
         <v>1710</v>
-      </c>
-      <c r="C807" t="s" s="2">
-        <v>1711</v>
       </c>
       <c r="D807" s="2"/>
     </row>
@@ -16924,10 +16963,10 @@
         <v>95</v>
       </c>
       <c r="B808" t="s" s="2">
+        <v>1711</v>
+      </c>
+      <c r="C808" t="s" s="2">
         <v>1712</v>
-      </c>
-      <c r="C808" t="s" s="2">
-        <v>1713</v>
       </c>
       <c r="D808" s="2"/>
     </row>
@@ -16936,10 +16975,10 @@
         <v>95</v>
       </c>
       <c r="B809" t="s" s="2">
+        <v>1713</v>
+      </c>
+      <c r="C809" t="s" s="2">
         <v>1714</v>
-      </c>
-      <c r="C809" t="s" s="2">
-        <v>1715</v>
       </c>
       <c r="D809" s="2"/>
     </row>
@@ -16948,10 +16987,10 @@
         <v>95</v>
       </c>
       <c r="B810" t="s" s="2">
+        <v>1715</v>
+      </c>
+      <c r="C810" t="s" s="2">
         <v>1716</v>
-      </c>
-      <c r="C810" t="s" s="2">
-        <v>1717</v>
       </c>
       <c r="D810" s="2"/>
     </row>
@@ -16960,10 +16999,10 @@
         <v>95</v>
       </c>
       <c r="B811" t="s" s="2">
+        <v>1717</v>
+      </c>
+      <c r="C811" t="s" s="2">
         <v>1718</v>
-      </c>
-      <c r="C811" t="s" s="2">
-        <v>1719</v>
       </c>
       <c r="D811" s="2"/>
     </row>
@@ -16972,10 +17011,10 @@
         <v>95</v>
       </c>
       <c r="B812" t="s" s="2">
+        <v>1719</v>
+      </c>
+      <c r="C812" t="s" s="2">
         <v>1720</v>
-      </c>
-      <c r="C812" t="s" s="2">
-        <v>1721</v>
       </c>
       <c r="D812" s="2"/>
     </row>
@@ -16984,10 +17023,10 @@
         <v>95</v>
       </c>
       <c r="B813" t="s" s="2">
+        <v>1721</v>
+      </c>
+      <c r="C813" t="s" s="2">
         <v>1722</v>
-      </c>
-      <c r="C813" t="s" s="2">
-        <v>1723</v>
       </c>
       <c r="D813" s="2"/>
     </row>
@@ -16996,10 +17035,10 @@
         <v>95</v>
       </c>
       <c r="B814" t="s" s="2">
+        <v>1723</v>
+      </c>
+      <c r="C814" t="s" s="2">
         <v>1724</v>
-      </c>
-      <c r="C814" t="s" s="2">
-        <v>1725</v>
       </c>
       <c r="D814" s="2"/>
     </row>
@@ -17008,10 +17047,10 @@
         <v>95</v>
       </c>
       <c r="B815" t="s" s="2">
+        <v>1725</v>
+      </c>
+      <c r="C815" t="s" s="2">
         <v>1726</v>
-      </c>
-      <c r="C815" t="s" s="2">
-        <v>1727</v>
       </c>
       <c r="D815" s="2"/>
     </row>
@@ -17020,10 +17059,10 @@
         <v>95</v>
       </c>
       <c r="B816" t="s" s="2">
+        <v>1727</v>
+      </c>
+      <c r="C816" t="s" s="2">
         <v>1728</v>
-      </c>
-      <c r="C816" t="s" s="2">
-        <v>1729</v>
       </c>
       <c r="D816" s="2"/>
     </row>
@@ -17032,10 +17071,10 @@
         <v>95</v>
       </c>
       <c r="B817" t="s" s="2">
+        <v>1729</v>
+      </c>
+      <c r="C817" t="s" s="2">
         <v>1730</v>
-      </c>
-      <c r="C817" t="s" s="2">
-        <v>1731</v>
       </c>
       <c r="D817" s="2"/>
     </row>
@@ -17044,10 +17083,10 @@
         <v>95</v>
       </c>
       <c r="B818" t="s" s="2">
+        <v>1731</v>
+      </c>
+      <c r="C818" t="s" s="2">
         <v>1732</v>
-      </c>
-      <c r="C818" t="s" s="2">
-        <v>1733</v>
       </c>
       <c r="D818" s="2"/>
     </row>
@@ -17056,10 +17095,10 @@
         <v>95</v>
       </c>
       <c r="B819" t="s" s="2">
+        <v>1733</v>
+      </c>
+      <c r="C819" t="s" s="2">
         <v>1734</v>
-      </c>
-      <c r="C819" t="s" s="2">
-        <v>1735</v>
       </c>
       <c r="D819" s="2"/>
     </row>
@@ -17068,10 +17107,10 @@
         <v>95</v>
       </c>
       <c r="B820" t="s" s="2">
+        <v>1735</v>
+      </c>
+      <c r="C820" t="s" s="2">
         <v>1736</v>
-      </c>
-      <c r="C820" t="s" s="2">
-        <v>1737</v>
       </c>
       <c r="D820" s="2"/>
     </row>
@@ -17080,10 +17119,10 @@
         <v>95</v>
       </c>
       <c r="B821" t="s" s="2">
+        <v>1737</v>
+      </c>
+      <c r="C821" t="s" s="2">
         <v>1738</v>
-      </c>
-      <c r="C821" t="s" s="2">
-        <v>1739</v>
       </c>
       <c r="D821" s="2"/>
     </row>
@@ -17092,10 +17131,10 @@
         <v>95</v>
       </c>
       <c r="B822" t="s" s="2">
+        <v>1739</v>
+      </c>
+      <c r="C822" t="s" s="2">
         <v>1740</v>
-      </c>
-      <c r="C822" t="s" s="2">
-        <v>1741</v>
       </c>
       <c r="D822" s="2"/>
     </row>
@@ -17104,10 +17143,10 @@
         <v>95</v>
       </c>
       <c r="B823" t="s" s="2">
+        <v>1741</v>
+      </c>
+      <c r="C823" t="s" s="2">
         <v>1742</v>
-      </c>
-      <c r="C823" t="s" s="2">
-        <v>1743</v>
       </c>
       <c r="D823" s="2"/>
     </row>
@@ -17116,10 +17155,10 @@
         <v>95</v>
       </c>
       <c r="B824" t="s" s="2">
+        <v>1743</v>
+      </c>
+      <c r="C824" t="s" s="2">
         <v>1744</v>
-      </c>
-      <c r="C824" t="s" s="2">
-        <v>1745</v>
       </c>
       <c r="D824" s="2"/>
     </row>
@@ -17128,10 +17167,10 @@
         <v>95</v>
       </c>
       <c r="B825" t="s" s="2">
+        <v>1745</v>
+      </c>
+      <c r="C825" t="s" s="2">
         <v>1746</v>
-      </c>
-      <c r="C825" t="s" s="2">
-        <v>1747</v>
       </c>
       <c r="D825" s="2"/>
     </row>
@@ -17140,10 +17179,10 @@
         <v>95</v>
       </c>
       <c r="B826" t="s" s="2">
+        <v>1747</v>
+      </c>
+      <c r="C826" t="s" s="2">
         <v>1748</v>
-      </c>
-      <c r="C826" t="s" s="2">
-        <v>1749</v>
       </c>
       <c r="D826" s="2"/>
     </row>
@@ -17152,10 +17191,10 @@
         <v>95</v>
       </c>
       <c r="B827" t="s" s="2">
+        <v>1749</v>
+      </c>
+      <c r="C827" t="s" s="2">
         <v>1750</v>
-      </c>
-      <c r="C827" t="s" s="2">
-        <v>1751</v>
       </c>
       <c r="D827" s="2"/>
     </row>
@@ -17164,10 +17203,10 @@
         <v>95</v>
       </c>
       <c r="B828" t="s" s="2">
+        <v>1751</v>
+      </c>
+      <c r="C828" t="s" s="2">
         <v>1752</v>
-      </c>
-      <c r="C828" t="s" s="2">
-        <v>1753</v>
       </c>
       <c r="D828" s="2"/>
     </row>
@@ -17176,10 +17215,10 @@
         <v>95</v>
       </c>
       <c r="B829" t="s" s="2">
+        <v>1753</v>
+      </c>
+      <c r="C829" t="s" s="2">
         <v>1754</v>
-      </c>
-      <c r="C829" t="s" s="2">
-        <v>1755</v>
       </c>
       <c r="D829" s="2"/>
     </row>
@@ -17188,10 +17227,10 @@
         <v>95</v>
       </c>
       <c r="B830" t="s" s="2">
+        <v>1755</v>
+      </c>
+      <c r="C830" t="s" s="2">
         <v>1756</v>
-      </c>
-      <c r="C830" t="s" s="2">
-        <v>1757</v>
       </c>
       <c r="D830" s="2"/>
     </row>
@@ -17200,10 +17239,10 @@
         <v>95</v>
       </c>
       <c r="B831" t="s" s="2">
+        <v>1757</v>
+      </c>
+      <c r="C831" t="s" s="2">
         <v>1758</v>
-      </c>
-      <c r="C831" t="s" s="2">
-        <v>1759</v>
       </c>
       <c r="D831" s="2"/>
     </row>
@@ -17212,10 +17251,10 @@
         <v>95</v>
       </c>
       <c r="B832" t="s" s="2">
+        <v>1759</v>
+      </c>
+      <c r="C832" t="s" s="2">
         <v>1760</v>
-      </c>
-      <c r="C832" t="s" s="2">
-        <v>1761</v>
       </c>
       <c r="D832" s="2"/>
     </row>
@@ -17224,10 +17263,10 @@
         <v>95</v>
       </c>
       <c r="B833" t="s" s="2">
+        <v>1761</v>
+      </c>
+      <c r="C833" t="s" s="2">
         <v>1762</v>
-      </c>
-      <c r="C833" t="s" s="2">
-        <v>1763</v>
       </c>
       <c r="D833" s="2"/>
     </row>
@@ -17236,10 +17275,10 @@
         <v>95</v>
       </c>
       <c r="B834" t="s" s="2">
+        <v>1763</v>
+      </c>
+      <c r="C834" t="s" s="2">
         <v>1764</v>
-      </c>
-      <c r="C834" t="s" s="2">
-        <v>1765</v>
       </c>
       <c r="D834" s="2"/>
     </row>
@@ -17248,10 +17287,10 @@
         <v>95</v>
       </c>
       <c r="B835" t="s" s="2">
+        <v>1765</v>
+      </c>
+      <c r="C835" t="s" s="2">
         <v>1766</v>
-      </c>
-      <c r="C835" t="s" s="2">
-        <v>1767</v>
       </c>
       <c r="D835" s="2"/>
     </row>
@@ -17260,10 +17299,10 @@
         <v>95</v>
       </c>
       <c r="B836" t="s" s="2">
+        <v>1767</v>
+      </c>
+      <c r="C836" t="s" s="2">
         <v>1768</v>
-      </c>
-      <c r="C836" t="s" s="2">
-        <v>1769</v>
       </c>
       <c r="D836" s="2"/>
     </row>
@@ -17272,10 +17311,10 @@
         <v>95</v>
       </c>
       <c r="B837" t="s" s="2">
+        <v>1769</v>
+      </c>
+      <c r="C837" t="s" s="2">
         <v>1770</v>
-      </c>
-      <c r="C837" t="s" s="2">
-        <v>1771</v>
       </c>
       <c r="D837" s="2"/>
     </row>
@@ -17284,10 +17323,10 @@
         <v>95</v>
       </c>
       <c r="B838" t="s" s="2">
+        <v>1771</v>
+      </c>
+      <c r="C838" t="s" s="2">
         <v>1772</v>
-      </c>
-      <c r="C838" t="s" s="2">
-        <v>1773</v>
       </c>
       <c r="D838" s="2"/>
     </row>
@@ -17296,10 +17335,10 @@
         <v>95</v>
       </c>
       <c r="B839" t="s" s="2">
+        <v>1773</v>
+      </c>
+      <c r="C839" t="s" s="2">
         <v>1774</v>
-      </c>
-      <c r="C839" t="s" s="2">
-        <v>1775</v>
       </c>
       <c r="D839" s="2"/>
     </row>
@@ -17308,10 +17347,10 @@
         <v>95</v>
       </c>
       <c r="B840" t="s" s="2">
+        <v>1775</v>
+      </c>
+      <c r="C840" t="s" s="2">
         <v>1776</v>
-      </c>
-      <c r="C840" t="s" s="2">
-        <v>1777</v>
       </c>
       <c r="D840" s="2"/>
     </row>
@@ -17320,10 +17359,10 @@
         <v>95</v>
       </c>
       <c r="B841" t="s" s="2">
+        <v>1777</v>
+      </c>
+      <c r="C841" t="s" s="2">
         <v>1778</v>
-      </c>
-      <c r="C841" t="s" s="2">
-        <v>1779</v>
       </c>
       <c r="D841" s="2"/>
     </row>
@@ -17332,10 +17371,10 @@
         <v>95</v>
       </c>
       <c r="B842" t="s" s="2">
+        <v>1779</v>
+      </c>
+      <c r="C842" t="s" s="2">
         <v>1780</v>
-      </c>
-      <c r="C842" t="s" s="2">
-        <v>1781</v>
       </c>
       <c r="D842" s="2"/>
     </row>
@@ -17344,10 +17383,10 @@
         <v>95</v>
       </c>
       <c r="B843" t="s" s="2">
+        <v>1781</v>
+      </c>
+      <c r="C843" t="s" s="2">
         <v>1782</v>
-      </c>
-      <c r="C843" t="s" s="2">
-        <v>1783</v>
       </c>
       <c r="D843" s="2"/>
     </row>
@@ -17356,10 +17395,10 @@
         <v>95</v>
       </c>
       <c r="B844" t="s" s="2">
+        <v>1783</v>
+      </c>
+      <c r="C844" t="s" s="2">
         <v>1784</v>
-      </c>
-      <c r="C844" t="s" s="2">
-        <v>1785</v>
       </c>
       <c r="D844" s="2"/>
     </row>
@@ -17368,10 +17407,10 @@
         <v>95</v>
       </c>
       <c r="B845" t="s" s="2">
+        <v>1785</v>
+      </c>
+      <c r="C845" t="s" s="2">
         <v>1786</v>
-      </c>
-      <c r="C845" t="s" s="2">
-        <v>1787</v>
       </c>
       <c r="D845" s="2"/>
     </row>
@@ -17380,10 +17419,10 @@
         <v>95</v>
       </c>
       <c r="B846" t="s" s="2">
+        <v>1787</v>
+      </c>
+      <c r="C846" t="s" s="2">
         <v>1788</v>
-      </c>
-      <c r="C846" t="s" s="2">
-        <v>1789</v>
       </c>
       <c r="D846" s="2"/>
     </row>
@@ -17392,10 +17431,10 @@
         <v>95</v>
       </c>
       <c r="B847" t="s" s="2">
+        <v>1789</v>
+      </c>
+      <c r="C847" t="s" s="2">
         <v>1790</v>
-      </c>
-      <c r="C847" t="s" s="2">
-        <v>1791</v>
       </c>
       <c r="D847" s="2"/>
     </row>
@@ -17404,10 +17443,10 @@
         <v>95</v>
       </c>
       <c r="B848" t="s" s="2">
+        <v>1791</v>
+      </c>
+      <c r="C848" t="s" s="2">
         <v>1792</v>
-      </c>
-      <c r="C848" t="s" s="2">
-        <v>1793</v>
       </c>
       <c r="D848" s="2"/>
     </row>
@@ -17416,10 +17455,10 @@
         <v>95</v>
       </c>
       <c r="B849" t="s" s="2">
+        <v>1793</v>
+      </c>
+      <c r="C849" t="s" s="2">
         <v>1794</v>
-      </c>
-      <c r="C849" t="s" s="2">
-        <v>1795</v>
       </c>
       <c r="D849" s="2"/>
     </row>
@@ -17428,10 +17467,10 @@
         <v>95</v>
       </c>
       <c r="B850" t="s" s="2">
+        <v>1795</v>
+      </c>
+      <c r="C850" t="s" s="2">
         <v>1796</v>
-      </c>
-      <c r="C850" t="s" s="2">
-        <v>1797</v>
       </c>
       <c r="D850" s="2"/>
     </row>
@@ -17440,10 +17479,10 @@
         <v>95</v>
       </c>
       <c r="B851" t="s" s="2">
+        <v>1797</v>
+      </c>
+      <c r="C851" t="s" s="2">
         <v>1798</v>
-      </c>
-      <c r="C851" t="s" s="2">
-        <v>1799</v>
       </c>
       <c r="D851" s="2"/>
     </row>
@@ -17452,10 +17491,10 @@
         <v>95</v>
       </c>
       <c r="B852" t="s" s="2">
+        <v>1799</v>
+      </c>
+      <c r="C852" t="s" s="2">
         <v>1800</v>
-      </c>
-      <c r="C852" t="s" s="2">
-        <v>1801</v>
       </c>
       <c r="D852" s="2"/>
     </row>
@@ -17464,10 +17503,10 @@
         <v>95</v>
       </c>
       <c r="B853" t="s" s="2">
+        <v>1801</v>
+      </c>
+      <c r="C853" t="s" s="2">
         <v>1802</v>
-      </c>
-      <c r="C853" t="s" s="2">
-        <v>1803</v>
       </c>
       <c r="D853" s="2"/>
     </row>
@@ -17476,10 +17515,10 @@
         <v>95</v>
       </c>
       <c r="B854" t="s" s="2">
+        <v>1803</v>
+      </c>
+      <c r="C854" t="s" s="2">
         <v>1804</v>
-      </c>
-      <c r="C854" t="s" s="2">
-        <v>1805</v>
       </c>
       <c r="D854" s="2"/>
     </row>
@@ -17488,10 +17527,10 @@
         <v>95</v>
       </c>
       <c r="B855" t="s" s="2">
+        <v>1805</v>
+      </c>
+      <c r="C855" t="s" s="2">
         <v>1806</v>
-      </c>
-      <c r="C855" t="s" s="2">
-        <v>1807</v>
       </c>
       <c r="D855" s="2"/>
     </row>
@@ -17500,10 +17539,10 @@
         <v>95</v>
       </c>
       <c r="B856" t="s" s="2">
+        <v>1807</v>
+      </c>
+      <c r="C856" t="s" s="2">
         <v>1808</v>
-      </c>
-      <c r="C856" t="s" s="2">
-        <v>1809</v>
       </c>
       <c r="D856" s="2"/>
     </row>
@@ -17512,10 +17551,10 @@
         <v>95</v>
       </c>
       <c r="B857" t="s" s="2">
+        <v>1809</v>
+      </c>
+      <c r="C857" t="s" s="2">
         <v>1810</v>
-      </c>
-      <c r="C857" t="s" s="2">
-        <v>1811</v>
       </c>
       <c r="D857" s="2"/>
     </row>
@@ -17524,10 +17563,10 @@
         <v>95</v>
       </c>
       <c r="B858" t="s" s="2">
+        <v>1811</v>
+      </c>
+      <c r="C858" t="s" s="2">
         <v>1812</v>
-      </c>
-      <c r="C858" t="s" s="2">
-        <v>1813</v>
       </c>
       <c r="D858" s="2"/>
     </row>
@@ -17536,10 +17575,10 @@
         <v>95</v>
       </c>
       <c r="B859" t="s" s="2">
+        <v>1813</v>
+      </c>
+      <c r="C859" t="s" s="2">
         <v>1814</v>
-      </c>
-      <c r="C859" t="s" s="2">
-        <v>1815</v>
       </c>
       <c r="D859" s="2"/>
     </row>
@@ -17548,10 +17587,10 @@
         <v>95</v>
       </c>
       <c r="B860" t="s" s="2">
+        <v>1815</v>
+      </c>
+      <c r="C860" t="s" s="2">
         <v>1816</v>
-      </c>
-      <c r="C860" t="s" s="2">
-        <v>1817</v>
       </c>
       <c r="D860" s="2"/>
     </row>
@@ -17560,10 +17599,10 @@
         <v>95</v>
       </c>
       <c r="B861" t="s" s="2">
+        <v>1817</v>
+      </c>
+      <c r="C861" t="s" s="2">
         <v>1818</v>
-      </c>
-      <c r="C861" t="s" s="2">
-        <v>1819</v>
       </c>
       <c r="D861" s="2"/>
     </row>
@@ -17572,10 +17611,10 @@
         <v>95</v>
       </c>
       <c r="B862" t="s" s="2">
+        <v>1819</v>
+      </c>
+      <c r="C862" t="s" s="2">
         <v>1820</v>
-      </c>
-      <c r="C862" t="s" s="2">
-        <v>1821</v>
       </c>
       <c r="D862" s="2"/>
     </row>
@@ -17584,10 +17623,10 @@
         <v>95</v>
       </c>
       <c r="B863" t="s" s="2">
+        <v>1821</v>
+      </c>
+      <c r="C863" t="s" s="2">
         <v>1822</v>
-      </c>
-      <c r="C863" t="s" s="2">
-        <v>1823</v>
       </c>
       <c r="D863" s="2"/>
     </row>
@@ -17596,10 +17635,10 @@
         <v>95</v>
       </c>
       <c r="B864" t="s" s="2">
+        <v>1823</v>
+      </c>
+      <c r="C864" t="s" s="2">
         <v>1824</v>
-      </c>
-      <c r="C864" t="s" s="2">
-        <v>1825</v>
       </c>
       <c r="D864" s="2"/>
     </row>
@@ -17608,10 +17647,10 @@
         <v>95</v>
       </c>
       <c r="B865" t="s" s="2">
+        <v>1825</v>
+      </c>
+      <c r="C865" t="s" s="2">
         <v>1826</v>
-      </c>
-      <c r="C865" t="s" s="2">
-        <v>1827</v>
       </c>
       <c r="D865" s="2"/>
     </row>
@@ -17620,10 +17659,10 @@
         <v>95</v>
       </c>
       <c r="B866" t="s" s="2">
+        <v>1827</v>
+      </c>
+      <c r="C866" t="s" s="2">
         <v>1828</v>
-      </c>
-      <c r="C866" t="s" s="2">
-        <v>1829</v>
       </c>
       <c r="D866" s="2"/>
     </row>
@@ -17632,10 +17671,10 @@
         <v>95</v>
       </c>
       <c r="B867" t="s" s="2">
+        <v>1829</v>
+      </c>
+      <c r="C867" t="s" s="2">
         <v>1830</v>
-      </c>
-      <c r="C867" t="s" s="2">
-        <v>1831</v>
       </c>
       <c r="D867" s="2"/>
     </row>
@@ -17644,10 +17683,10 @@
         <v>95</v>
       </c>
       <c r="B868" t="s" s="2">
+        <v>1831</v>
+      </c>
+      <c r="C868" t="s" s="2">
         <v>1832</v>
-      </c>
-      <c r="C868" t="s" s="2">
-        <v>1833</v>
       </c>
       <c r="D868" s="2"/>
     </row>
@@ -17656,10 +17695,10 @@
         <v>95</v>
       </c>
       <c r="B869" t="s" s="2">
+        <v>1833</v>
+      </c>
+      <c r="C869" t="s" s="2">
         <v>1834</v>
-      </c>
-      <c r="C869" t="s" s="2">
-        <v>1835</v>
       </c>
       <c r="D869" s="2"/>
     </row>
@@ -17668,10 +17707,10 @@
         <v>95</v>
       </c>
       <c r="B870" t="s" s="2">
+        <v>1835</v>
+      </c>
+      <c r="C870" t="s" s="2">
         <v>1836</v>
-      </c>
-      <c r="C870" t="s" s="2">
-        <v>1837</v>
       </c>
       <c r="D870" s="2"/>
     </row>
@@ -17680,10 +17719,10 @@
         <v>95</v>
       </c>
       <c r="B871" t="s" s="2">
+        <v>1837</v>
+      </c>
+      <c r="C871" t="s" s="2">
         <v>1838</v>
-      </c>
-      <c r="C871" t="s" s="2">
-        <v>1839</v>
       </c>
       <c r="D871" s="2"/>
     </row>
@@ -17692,10 +17731,10 @@
         <v>95</v>
       </c>
       <c r="B872" t="s" s="2">
+        <v>1839</v>
+      </c>
+      <c r="C872" t="s" s="2">
         <v>1840</v>
-      </c>
-      <c r="C872" t="s" s="2">
-        <v>1841</v>
       </c>
       <c r="D872" s="2"/>
     </row>
@@ -17704,10 +17743,10 @@
         <v>95</v>
       </c>
       <c r="B873" t="s" s="2">
+        <v>1841</v>
+      </c>
+      <c r="C873" t="s" s="2">
         <v>1842</v>
-      </c>
-      <c r="C873" t="s" s="2">
-        <v>1843</v>
       </c>
       <c r="D873" s="2"/>
     </row>
@@ -17716,10 +17755,10 @@
         <v>95</v>
       </c>
       <c r="B874" t="s" s="2">
+        <v>1843</v>
+      </c>
+      <c r="C874" t="s" s="2">
         <v>1844</v>
-      </c>
-      <c r="C874" t="s" s="2">
-        <v>1845</v>
       </c>
       <c r="D874" s="2"/>
     </row>
@@ -17728,10 +17767,10 @@
         <v>95</v>
       </c>
       <c r="B875" t="s" s="2">
+        <v>1845</v>
+      </c>
+      <c r="C875" t="s" s="2">
         <v>1846</v>
-      </c>
-      <c r="C875" t="s" s="2">
-        <v>1847</v>
       </c>
       <c r="D875" s="2"/>
     </row>
@@ -17740,10 +17779,10 @@
         <v>95</v>
       </c>
       <c r="B876" t="s" s="2">
+        <v>1847</v>
+      </c>
+      <c r="C876" t="s" s="2">
         <v>1848</v>
-      </c>
-      <c r="C876" t="s" s="2">
-        <v>1849</v>
       </c>
       <c r="D876" s="2"/>
     </row>
@@ -17752,10 +17791,10 @@
         <v>95</v>
       </c>
       <c r="B877" t="s" s="2">
+        <v>1849</v>
+      </c>
+      <c r="C877" t="s" s="2">
         <v>1850</v>
-      </c>
-      <c r="C877" t="s" s="2">
-        <v>1851</v>
       </c>
       <c r="D877" s="2"/>
     </row>
@@ -17764,10 +17803,10 @@
         <v>95</v>
       </c>
       <c r="B878" t="s" s="2">
+        <v>1851</v>
+      </c>
+      <c r="C878" t="s" s="2">
         <v>1852</v>
-      </c>
-      <c r="C878" t="s" s="2">
-        <v>1853</v>
       </c>
       <c r="D878" s="2"/>
     </row>
@@ -17776,10 +17815,10 @@
         <v>95</v>
       </c>
       <c r="B879" t="s" s="2">
+        <v>1853</v>
+      </c>
+      <c r="C879" t="s" s="2">
         <v>1854</v>
-      </c>
-      <c r="C879" t="s" s="2">
-        <v>1855</v>
       </c>
       <c r="D879" s="2"/>
     </row>
@@ -17788,10 +17827,10 @@
         <v>95</v>
       </c>
       <c r="B880" t="s" s="2">
+        <v>1855</v>
+      </c>
+      <c r="C880" t="s" s="2">
         <v>1856</v>
-      </c>
-      <c r="C880" t="s" s="2">
-        <v>1857</v>
       </c>
       <c r="D880" s="2"/>
     </row>
@@ -17800,10 +17839,10 @@
         <v>95</v>
       </c>
       <c r="B881" t="s" s="2">
+        <v>1857</v>
+      </c>
+      <c r="C881" t="s" s="2">
         <v>1858</v>
-      </c>
-      <c r="C881" t="s" s="2">
-        <v>1859</v>
       </c>
       <c r="D881" s="2"/>
     </row>
@@ -17812,10 +17851,10 @@
         <v>95</v>
       </c>
       <c r="B882" t="s" s="2">
+        <v>1859</v>
+      </c>
+      <c r="C882" t="s" s="2">
         <v>1860</v>
-      </c>
-      <c r="C882" t="s" s="2">
-        <v>1861</v>
       </c>
       <c r="D882" s="2"/>
     </row>
@@ -17824,10 +17863,10 @@
         <v>95</v>
       </c>
       <c r="B883" t="s" s="2">
+        <v>1861</v>
+      </c>
+      <c r="C883" t="s" s="2">
         <v>1862</v>
-      </c>
-      <c r="C883" t="s" s="2">
-        <v>1863</v>
       </c>
       <c r="D883" s="2"/>
     </row>
@@ -17836,10 +17875,10 @@
         <v>95</v>
       </c>
       <c r="B884" t="s" s="2">
+        <v>1863</v>
+      </c>
+      <c r="C884" t="s" s="2">
         <v>1864</v>
-      </c>
-      <c r="C884" t="s" s="2">
-        <v>1865</v>
       </c>
       <c r="D884" s="2"/>
     </row>
@@ -17848,10 +17887,10 @@
         <v>95</v>
       </c>
       <c r="B885" t="s" s="2">
+        <v>1865</v>
+      </c>
+      <c r="C885" t="s" s="2">
         <v>1866</v>
-      </c>
-      <c r="C885" t="s" s="2">
-        <v>1867</v>
       </c>
       <c r="D885" s="2"/>
     </row>
@@ -17860,10 +17899,10 @@
         <v>95</v>
       </c>
       <c r="B886" t="s" s="2">
+        <v>1867</v>
+      </c>
+      <c r="C886" t="s" s="2">
         <v>1868</v>
-      </c>
-      <c r="C886" t="s" s="2">
-        <v>1869</v>
       </c>
       <c r="D886" s="2"/>
     </row>
@@ -17872,10 +17911,10 @@
         <v>95</v>
       </c>
       <c r="B887" t="s" s="2">
+        <v>1869</v>
+      </c>
+      <c r="C887" t="s" s="2">
         <v>1870</v>
-      </c>
-      <c r="C887" t="s" s="2">
-        <v>1871</v>
       </c>
       <c r="D887" s="2"/>
     </row>
@@ -17884,10 +17923,10 @@
         <v>95</v>
       </c>
       <c r="B888" t="s" s="2">
+        <v>1871</v>
+      </c>
+      <c r="C888" t="s" s="2">
         <v>1872</v>
-      </c>
-      <c r="C888" t="s" s="2">
-        <v>1873</v>
       </c>
       <c r="D888" s="2"/>
     </row>
@@ -17896,10 +17935,10 @@
         <v>95</v>
       </c>
       <c r="B889" t="s" s="2">
+        <v>1873</v>
+      </c>
+      <c r="C889" t="s" s="2">
         <v>1874</v>
-      </c>
-      <c r="C889" t="s" s="2">
-        <v>1875</v>
       </c>
       <c r="D889" s="2"/>
     </row>
@@ -17908,10 +17947,10 @@
         <v>95</v>
       </c>
       <c r="B890" t="s" s="2">
+        <v>1875</v>
+      </c>
+      <c r="C890" t="s" s="2">
         <v>1876</v>
-      </c>
-      <c r="C890" t="s" s="2">
-        <v>1877</v>
       </c>
       <c r="D890" s="2"/>
     </row>
@@ -17920,10 +17959,10 @@
         <v>95</v>
       </c>
       <c r="B891" t="s" s="2">
+        <v>1877</v>
+      </c>
+      <c r="C891" t="s" s="2">
         <v>1878</v>
-      </c>
-      <c r="C891" t="s" s="2">
-        <v>1879</v>
       </c>
       <c r="D891" s="2"/>
     </row>
@@ -17932,10 +17971,10 @@
         <v>95</v>
       </c>
       <c r="B892" t="s" s="2">
+        <v>1879</v>
+      </c>
+      <c r="C892" t="s" s="2">
         <v>1880</v>
-      </c>
-      <c r="C892" t="s" s="2">
-        <v>1881</v>
       </c>
       <c r="D892" s="2"/>
     </row>
@@ -17944,10 +17983,10 @@
         <v>95</v>
       </c>
       <c r="B893" t="s" s="2">
+        <v>1881</v>
+      </c>
+      <c r="C893" t="s" s="2">
         <v>1882</v>
-      </c>
-      <c r="C893" t="s" s="2">
-        <v>1883</v>
       </c>
       <c r="D893" s="2"/>
     </row>
@@ -17956,10 +17995,10 @@
         <v>95</v>
       </c>
       <c r="B894" t="s" s="2">
+        <v>1883</v>
+      </c>
+      <c r="C894" t="s" s="2">
         <v>1884</v>
-      </c>
-      <c r="C894" t="s" s="2">
-        <v>1885</v>
       </c>
       <c r="D894" s="2"/>
     </row>
@@ -17968,10 +18007,10 @@
         <v>95</v>
       </c>
       <c r="B895" t="s" s="2">
+        <v>1885</v>
+      </c>
+      <c r="C895" t="s" s="2">
         <v>1886</v>
-      </c>
-      <c r="C895" t="s" s="2">
-        <v>1887</v>
       </c>
       <c r="D895" s="2"/>
     </row>
@@ -17980,10 +18019,10 @@
         <v>95</v>
       </c>
       <c r="B896" t="s" s="2">
+        <v>1887</v>
+      </c>
+      <c r="C896" t="s" s="2">
         <v>1888</v>
-      </c>
-      <c r="C896" t="s" s="2">
-        <v>1889</v>
       </c>
       <c r="D896" s="2"/>
     </row>
@@ -17992,10 +18031,10 @@
         <v>95</v>
       </c>
       <c r="B897" t="s" s="2">
+        <v>1889</v>
+      </c>
+      <c r="C897" t="s" s="2">
         <v>1890</v>
-      </c>
-      <c r="C897" t="s" s="2">
-        <v>1891</v>
       </c>
       <c r="D897" s="2"/>
     </row>
@@ -18004,10 +18043,10 @@
         <v>95</v>
       </c>
       <c r="B898" t="s" s="2">
+        <v>1891</v>
+      </c>
+      <c r="C898" t="s" s="2">
         <v>1892</v>
-      </c>
-      <c r="C898" t="s" s="2">
-        <v>1893</v>
       </c>
       <c r="D898" s="2"/>
     </row>
@@ -18016,10 +18055,10 @@
         <v>95</v>
       </c>
       <c r="B899" t="s" s="2">
+        <v>1893</v>
+      </c>
+      <c r="C899" t="s" s="2">
         <v>1894</v>
-      </c>
-      <c r="C899" t="s" s="2">
-        <v>1895</v>
       </c>
       <c r="D899" s="2"/>
     </row>
@@ -18028,10 +18067,10 @@
         <v>95</v>
       </c>
       <c r="B900" t="s" s="2">
+        <v>1895</v>
+      </c>
+      <c r="C900" t="s" s="2">
         <v>1896</v>
-      </c>
-      <c r="C900" t="s" s="2">
-        <v>1897</v>
       </c>
       <c r="D900" s="2"/>
     </row>
@@ -18040,10 +18079,10 @@
         <v>95</v>
       </c>
       <c r="B901" t="s" s="2">
+        <v>1897</v>
+      </c>
+      <c r="C901" t="s" s="2">
         <v>1898</v>
-      </c>
-      <c r="C901" t="s" s="2">
-        <v>1899</v>
       </c>
       <c r="D901" s="2"/>
     </row>
@@ -18052,10 +18091,10 @@
         <v>95</v>
       </c>
       <c r="B902" t="s" s="2">
+        <v>1899</v>
+      </c>
+      <c r="C902" t="s" s="2">
         <v>1900</v>
-      </c>
-      <c r="C902" t="s" s="2">
-        <v>1901</v>
       </c>
       <c r="D902" s="2"/>
     </row>
@@ -18064,10 +18103,10 @@
         <v>95</v>
       </c>
       <c r="B903" t="s" s="2">
+        <v>1901</v>
+      </c>
+      <c r="C903" t="s" s="2">
         <v>1902</v>
-      </c>
-      <c r="C903" t="s" s="2">
-        <v>1903</v>
       </c>
       <c r="D903" s="2"/>
     </row>
@@ -18076,10 +18115,10 @@
         <v>95</v>
       </c>
       <c r="B904" t="s" s="2">
+        <v>1903</v>
+      </c>
+      <c r="C904" t="s" s="2">
         <v>1904</v>
-      </c>
-      <c r="C904" t="s" s="2">
-        <v>1905</v>
       </c>
       <c r="D904" s="2"/>
     </row>
@@ -18088,10 +18127,10 @@
         <v>95</v>
       </c>
       <c r="B905" t="s" s="2">
+        <v>1905</v>
+      </c>
+      <c r="C905" t="s" s="2">
         <v>1906</v>
-      </c>
-      <c r="C905" t="s" s="2">
-        <v>1907</v>
       </c>
       <c r="D905" s="2"/>
     </row>
@@ -18100,10 +18139,10 @@
         <v>95</v>
       </c>
       <c r="B906" t="s" s="2">
+        <v>1907</v>
+      </c>
+      <c r="C906" t="s" s="2">
         <v>1908</v>
-      </c>
-      <c r="C906" t="s" s="2">
-        <v>1909</v>
       </c>
       <c r="D906" s="2"/>
     </row>
@@ -18112,10 +18151,10 @@
         <v>95</v>
       </c>
       <c r="B907" t="s" s="2">
+        <v>1909</v>
+      </c>
+      <c r="C907" t="s" s="2">
         <v>1910</v>
-      </c>
-      <c r="C907" t="s" s="2">
-        <v>1911</v>
       </c>
       <c r="D907" s="2"/>
     </row>
@@ -18124,10 +18163,10 @@
         <v>95</v>
       </c>
       <c r="B908" t="s" s="2">
+        <v>1911</v>
+      </c>
+      <c r="C908" t="s" s="2">
         <v>1912</v>
-      </c>
-      <c r="C908" t="s" s="2">
-        <v>1913</v>
       </c>
       <c r="D908" s="2"/>
     </row>
@@ -18136,10 +18175,10 @@
         <v>95</v>
       </c>
       <c r="B909" t="s" s="2">
+        <v>1913</v>
+      </c>
+      <c r="C909" t="s" s="2">
         <v>1914</v>
-      </c>
-      <c r="C909" t="s" s="2">
-        <v>1915</v>
       </c>
       <c r="D909" s="2"/>
     </row>
@@ -18148,10 +18187,10 @@
         <v>95</v>
       </c>
       <c r="B910" t="s" s="2">
+        <v>1915</v>
+      </c>
+      <c r="C910" t="s" s="2">
         <v>1916</v>
-      </c>
-      <c r="C910" t="s" s="2">
-        <v>1917</v>
       </c>
       <c r="D910" s="2"/>
     </row>
@@ -18160,10 +18199,10 @@
         <v>95</v>
       </c>
       <c r="B911" t="s" s="2">
+        <v>1917</v>
+      </c>
+      <c r="C911" t="s" s="2">
         <v>1918</v>
-      </c>
-      <c r="C911" t="s" s="2">
-        <v>1919</v>
       </c>
       <c r="D911" s="2"/>
     </row>
@@ -18172,10 +18211,10 @@
         <v>95</v>
       </c>
       <c r="B912" t="s" s="2">
+        <v>1919</v>
+      </c>
+      <c r="C912" t="s" s="2">
         <v>1920</v>
-      </c>
-      <c r="C912" t="s" s="2">
-        <v>1921</v>
       </c>
       <c r="D912" s="2"/>
     </row>
@@ -18184,10 +18223,10 @@
         <v>95</v>
       </c>
       <c r="B913" t="s" s="2">
+        <v>1921</v>
+      </c>
+      <c r="C913" t="s" s="2">
         <v>1922</v>
-      </c>
-      <c r="C913" t="s" s="2">
-        <v>1923</v>
       </c>
       <c r="D913" s="2"/>
     </row>
@@ -18196,10 +18235,10 @@
         <v>95</v>
       </c>
       <c r="B914" t="s" s="2">
+        <v>1923</v>
+      </c>
+      <c r="C914" t="s" s="2">
         <v>1924</v>
-      </c>
-      <c r="C914" t="s" s="2">
-        <v>1925</v>
       </c>
       <c r="D914" s="2"/>
     </row>
@@ -18208,10 +18247,10 @@
         <v>95</v>
       </c>
       <c r="B915" t="s" s="2">
+        <v>1925</v>
+      </c>
+      <c r="C915" t="s" s="2">
         <v>1926</v>
-      </c>
-      <c r="C915" t="s" s="2">
-        <v>1927</v>
       </c>
       <c r="D915" s="2"/>
     </row>
@@ -18220,10 +18259,10 @@
         <v>95</v>
       </c>
       <c r="B916" t="s" s="2">
+        <v>1927</v>
+      </c>
+      <c r="C916" t="s" s="2">
         <v>1928</v>
-      </c>
-      <c r="C916" t="s" s="2">
-        <v>1929</v>
       </c>
       <c r="D916" s="2"/>
     </row>
@@ -18232,10 +18271,10 @@
         <v>95</v>
       </c>
       <c r="B917" t="s" s="2">
+        <v>1929</v>
+      </c>
+      <c r="C917" t="s" s="2">
         <v>1930</v>
-      </c>
-      <c r="C917" t="s" s="2">
-        <v>1931</v>
       </c>
       <c r="D917" s="2"/>
     </row>
@@ -18244,10 +18283,10 @@
         <v>95</v>
       </c>
       <c r="B918" t="s" s="2">
+        <v>1931</v>
+      </c>
+      <c r="C918" t="s" s="2">
         <v>1932</v>
-      </c>
-      <c r="C918" t="s" s="2">
-        <v>1933</v>
       </c>
       <c r="D918" s="2"/>
     </row>
@@ -18256,10 +18295,10 @@
         <v>95</v>
       </c>
       <c r="B919" t="s" s="2">
+        <v>1933</v>
+      </c>
+      <c r="C919" t="s" s="2">
         <v>1934</v>
-      </c>
-      <c r="C919" t="s" s="2">
-        <v>1935</v>
       </c>
       <c r="D919" s="2"/>
     </row>
@@ -18268,10 +18307,10 @@
         <v>95</v>
       </c>
       <c r="B920" t="s" s="2">
+        <v>1935</v>
+      </c>
+      <c r="C920" t="s" s="2">
         <v>1936</v>
-      </c>
-      <c r="C920" t="s" s="2">
-        <v>1937</v>
       </c>
       <c r="D920" s="2"/>
     </row>
@@ -18280,10 +18319,10 @@
         <v>95</v>
       </c>
       <c r="B921" t="s" s="2">
+        <v>1937</v>
+      </c>
+      <c r="C921" t="s" s="2">
         <v>1938</v>
-      </c>
-      <c r="C921" t="s" s="2">
-        <v>1939</v>
       </c>
       <c r="D921" s="2"/>
     </row>
@@ -18292,10 +18331,10 @@
         <v>95</v>
       </c>
       <c r="B922" t="s" s="2">
+        <v>1939</v>
+      </c>
+      <c r="C922" t="s" s="2">
         <v>1940</v>
-      </c>
-      <c r="C922" t="s" s="2">
-        <v>1941</v>
       </c>
       <c r="D922" s="2"/>
     </row>
@@ -18304,10 +18343,10 @@
         <v>95</v>
       </c>
       <c r="B923" t="s" s="2">
+        <v>1941</v>
+      </c>
+      <c r="C923" t="s" s="2">
         <v>1942</v>
-      </c>
-      <c r="C923" t="s" s="2">
-        <v>1943</v>
       </c>
       <c r="D923" s="2"/>
     </row>
@@ -18316,10 +18355,10 @@
         <v>95</v>
       </c>
       <c r="B924" t="s" s="2">
+        <v>1943</v>
+      </c>
+      <c r="C924" t="s" s="2">
         <v>1944</v>
-      </c>
-      <c r="C924" t="s" s="2">
-        <v>1945</v>
       </c>
       <c r="D924" s="2"/>
     </row>
@@ -18328,10 +18367,10 @@
         <v>95</v>
       </c>
       <c r="B925" t="s" s="2">
+        <v>1945</v>
+      </c>
+      <c r="C925" t="s" s="2">
         <v>1946</v>
-      </c>
-      <c r="C925" t="s" s="2">
-        <v>1947</v>
       </c>
       <c r="D925" s="2"/>
     </row>
@@ -18340,10 +18379,10 @@
         <v>95</v>
       </c>
       <c r="B926" t="s" s="2">
+        <v>1947</v>
+      </c>
+      <c r="C926" t="s" s="2">
         <v>1948</v>
-      </c>
-      <c r="C926" t="s" s="2">
-        <v>1949</v>
       </c>
       <c r="D926" s="2"/>
     </row>
@@ -18352,10 +18391,10 @@
         <v>95</v>
       </c>
       <c r="B927" t="s" s="2">
+        <v>1949</v>
+      </c>
+      <c r="C927" t="s" s="2">
         <v>1950</v>
-      </c>
-      <c r="C927" t="s" s="2">
-        <v>1951</v>
       </c>
       <c r="D927" s="2"/>
     </row>
@@ -18364,10 +18403,10 @@
         <v>95</v>
       </c>
       <c r="B928" t="s" s="2">
+        <v>1951</v>
+      </c>
+      <c r="C928" t="s" s="2">
         <v>1952</v>
-      </c>
-      <c r="C928" t="s" s="2">
-        <v>1953</v>
       </c>
       <c r="D928" s="2"/>
     </row>
@@ -18376,10 +18415,10 @@
         <v>95</v>
       </c>
       <c r="B929" t="s" s="2">
+        <v>1953</v>
+      </c>
+      <c r="C929" t="s" s="2">
         <v>1954</v>
-      </c>
-      <c r="C929" t="s" s="2">
-        <v>1955</v>
       </c>
       <c r="D929" s="2"/>
     </row>
@@ -18388,10 +18427,10 @@
         <v>95</v>
       </c>
       <c r="B930" t="s" s="2">
+        <v>1955</v>
+      </c>
+      <c r="C930" t="s" s="2">
         <v>1956</v>
-      </c>
-      <c r="C930" t="s" s="2">
-        <v>1957</v>
       </c>
       <c r="D930" s="2"/>
     </row>
@@ -18400,10 +18439,10 @@
         <v>95</v>
       </c>
       <c r="B931" t="s" s="2">
+        <v>1957</v>
+      </c>
+      <c r="C931" t="s" s="2">
         <v>1958</v>
-      </c>
-      <c r="C931" t="s" s="2">
-        <v>1959</v>
       </c>
       <c r="D931" s="2"/>
     </row>
@@ -18412,10 +18451,10 @@
         <v>95</v>
       </c>
       <c r="B932" t="s" s="2">
+        <v>1959</v>
+      </c>
+      <c r="C932" t="s" s="2">
         <v>1960</v>
-      </c>
-      <c r="C932" t="s" s="2">
-        <v>1961</v>
       </c>
       <c r="D932" s="2"/>
     </row>
@@ -18424,10 +18463,10 @@
         <v>95</v>
       </c>
       <c r="B933" t="s" s="2">
+        <v>1961</v>
+      </c>
+      <c r="C933" t="s" s="2">
         <v>1962</v>
-      </c>
-      <c r="C933" t="s" s="2">
-        <v>1963</v>
       </c>
       <c r="D933" s="2"/>
     </row>
@@ -18436,10 +18475,10 @@
         <v>95</v>
       </c>
       <c r="B934" t="s" s="2">
+        <v>1963</v>
+      </c>
+      <c r="C934" t="s" s="2">
         <v>1964</v>
-      </c>
-      <c r="C934" t="s" s="2">
-        <v>1965</v>
       </c>
       <c r="D934" s="2"/>
     </row>
@@ -18448,10 +18487,10 @@
         <v>95</v>
       </c>
       <c r="B935" t="s" s="2">
+        <v>1965</v>
+      </c>
+      <c r="C935" t="s" s="2">
         <v>1966</v>
-      </c>
-      <c r="C935" t="s" s="2">
-        <v>1967</v>
       </c>
       <c r="D935" s="2"/>
     </row>
@@ -18460,10 +18499,10 @@
         <v>95</v>
       </c>
       <c r="B936" t="s" s="2">
+        <v>1967</v>
+      </c>
+      <c r="C936" t="s" s="2">
         <v>1968</v>
-      </c>
-      <c r="C936" t="s" s="2">
-        <v>1969</v>
       </c>
       <c r="D936" s="2"/>
     </row>
@@ -18472,10 +18511,10 @@
         <v>95</v>
       </c>
       <c r="B937" t="s" s="2">
+        <v>1969</v>
+      </c>
+      <c r="C937" t="s" s="2">
         <v>1970</v>
-      </c>
-      <c r="C937" t="s" s="2">
-        <v>1971</v>
       </c>
       <c r="D937" s="2"/>
     </row>
@@ -18484,10 +18523,10 @@
         <v>95</v>
       </c>
       <c r="B938" t="s" s="2">
+        <v>1971</v>
+      </c>
+      <c r="C938" t="s" s="2">
         <v>1972</v>
-      </c>
-      <c r="C938" t="s" s="2">
-        <v>1973</v>
       </c>
       <c r="D938" s="2"/>
     </row>
@@ -18496,10 +18535,10 @@
         <v>95</v>
       </c>
       <c r="B939" t="s" s="2">
+        <v>1973</v>
+      </c>
+      <c r="C939" t="s" s="2">
         <v>1974</v>
-      </c>
-      <c r="C939" t="s" s="2">
-        <v>1975</v>
       </c>
       <c r="D939" s="2"/>
     </row>
@@ -18508,10 +18547,10 @@
         <v>95</v>
       </c>
       <c r="B940" t="s" s="2">
+        <v>1975</v>
+      </c>
+      <c r="C940" t="s" s="2">
         <v>1976</v>
-      </c>
-      <c r="C940" t="s" s="2">
-        <v>1977</v>
       </c>
       <c r="D940" s="2"/>
     </row>
@@ -18520,10 +18559,10 @@
         <v>95</v>
       </c>
       <c r="B941" t="s" s="2">
+        <v>1977</v>
+      </c>
+      <c r="C941" t="s" s="2">
         <v>1978</v>
-      </c>
-      <c r="C941" t="s" s="2">
-        <v>1979</v>
       </c>
       <c r="D941" s="2"/>
     </row>
@@ -18532,10 +18571,10 @@
         <v>95</v>
       </c>
       <c r="B942" t="s" s="2">
+        <v>1979</v>
+      </c>
+      <c r="C942" t="s" s="2">
         <v>1980</v>
-      </c>
-      <c r="C942" t="s" s="2">
-        <v>1981</v>
       </c>
       <c r="D942" s="2"/>
     </row>
@@ -18544,10 +18583,10 @@
         <v>95</v>
       </c>
       <c r="B943" t="s" s="2">
+        <v>1981</v>
+      </c>
+      <c r="C943" t="s" s="2">
         <v>1982</v>
-      </c>
-      <c r="C943" t="s" s="2">
-        <v>1983</v>
       </c>
       <c r="D943" s="2"/>
     </row>
@@ -18556,10 +18595,10 @@
         <v>95</v>
       </c>
       <c r="B944" t="s" s="2">
+        <v>1983</v>
+      </c>
+      <c r="C944" t="s" s="2">
         <v>1984</v>
-      </c>
-      <c r="C944" t="s" s="2">
-        <v>1985</v>
       </c>
       <c r="D944" s="2"/>
     </row>
@@ -18568,10 +18607,10 @@
         <v>95</v>
       </c>
       <c r="B945" t="s" s="2">
+        <v>1985</v>
+      </c>
+      <c r="C945" t="s" s="2">
         <v>1986</v>
-      </c>
-      <c r="C945" t="s" s="2">
-        <v>1987</v>
       </c>
       <c r="D945" s="2"/>
     </row>
@@ -18580,10 +18619,10 @@
         <v>95</v>
       </c>
       <c r="B946" t="s" s="2">
+        <v>1987</v>
+      </c>
+      <c r="C946" t="s" s="2">
         <v>1988</v>
-      </c>
-      <c r="C946" t="s" s="2">
-        <v>1989</v>
       </c>
       <c r="D946" s="2"/>
     </row>
@@ -18592,10 +18631,10 @@
         <v>95</v>
       </c>
       <c r="B947" t="s" s="2">
+        <v>1989</v>
+      </c>
+      <c r="C947" t="s" s="2">
         <v>1990</v>
-      </c>
-      <c r="C947" t="s" s="2">
-        <v>1991</v>
       </c>
       <c r="D947" s="2"/>
     </row>
@@ -18604,10 +18643,10 @@
         <v>95</v>
       </c>
       <c r="B948" t="s" s="2">
+        <v>1991</v>
+      </c>
+      <c r="C948" t="s" s="2">
         <v>1992</v>
-      </c>
-      <c r="C948" t="s" s="2">
-        <v>1993</v>
       </c>
       <c r="D948" s="2"/>
     </row>
@@ -18616,10 +18655,10 @@
         <v>95</v>
       </c>
       <c r="B949" t="s" s="2">
+        <v>1993</v>
+      </c>
+      <c r="C949" t="s" s="2">
         <v>1994</v>
-      </c>
-      <c r="C949" t="s" s="2">
-        <v>1995</v>
       </c>
       <c r="D949" s="2"/>
     </row>
@@ -18628,10 +18667,10 @@
         <v>95</v>
       </c>
       <c r="B950" t="s" s="2">
+        <v>1995</v>
+      </c>
+      <c r="C950" t="s" s="2">
         <v>1996</v>
-      </c>
-      <c r="C950" t="s" s="2">
-        <v>1997</v>
       </c>
       <c r="D950" s="2"/>
     </row>
@@ -18640,10 +18679,10 @@
         <v>95</v>
       </c>
       <c r="B951" t="s" s="2">
+        <v>1997</v>
+      </c>
+      <c r="C951" t="s" s="2">
         <v>1998</v>
-      </c>
-      <c r="C951" t="s" s="2">
-        <v>1999</v>
       </c>
       <c r="D951" s="2"/>
     </row>
@@ -18652,10 +18691,10 @@
         <v>95</v>
       </c>
       <c r="B952" t="s" s="2">
+        <v>1999</v>
+      </c>
+      <c r="C952" t="s" s="2">
         <v>2000</v>
-      </c>
-      <c r="C952" t="s" s="2">
-        <v>2001</v>
       </c>
       <c r="D952" s="2"/>
     </row>
@@ -18664,10 +18703,10 @@
         <v>95</v>
       </c>
       <c r="B953" t="s" s="2">
+        <v>2001</v>
+      </c>
+      <c r="C953" t="s" s="2">
         <v>2002</v>
-      </c>
-      <c r="C953" t="s" s="2">
-        <v>2003</v>
       </c>
       <c r="D953" s="2"/>
     </row>
@@ -18676,10 +18715,10 @@
         <v>95</v>
       </c>
       <c r="B954" t="s" s="2">
+        <v>2003</v>
+      </c>
+      <c r="C954" t="s" s="2">
         <v>2004</v>
-      </c>
-      <c r="C954" t="s" s="2">
-        <v>2005</v>
       </c>
       <c r="D954" s="2"/>
     </row>
@@ -18688,10 +18727,10 @@
         <v>95</v>
       </c>
       <c r="B955" t="s" s="2">
+        <v>2005</v>
+      </c>
+      <c r="C955" t="s" s="2">
         <v>2006</v>
-      </c>
-      <c r="C955" t="s" s="2">
-        <v>2007</v>
       </c>
       <c r="D955" s="2"/>
     </row>
@@ -18700,10 +18739,10 @@
         <v>95</v>
       </c>
       <c r="B956" t="s" s="2">
+        <v>2007</v>
+      </c>
+      <c r="C956" t="s" s="2">
         <v>2008</v>
-      </c>
-      <c r="C956" t="s" s="2">
-        <v>2009</v>
       </c>
       <c r="D956" s="2"/>
     </row>
@@ -18712,10 +18751,10 @@
         <v>95</v>
       </c>
       <c r="B957" t="s" s="2">
+        <v>2009</v>
+      </c>
+      <c r="C957" t="s" s="2">
         <v>2010</v>
-      </c>
-      <c r="C957" t="s" s="2">
-        <v>2011</v>
       </c>
       <c r="D957" s="2"/>
     </row>
@@ -18724,10 +18763,10 @@
         <v>95</v>
       </c>
       <c r="B958" t="s" s="2">
+        <v>2011</v>
+      </c>
+      <c r="C958" t="s" s="2">
         <v>2012</v>
-      </c>
-      <c r="C958" t="s" s="2">
-        <v>2013</v>
       </c>
       <c r="D958" s="2"/>
     </row>
@@ -18736,10 +18775,10 @@
         <v>95</v>
       </c>
       <c r="B959" t="s" s="2">
+        <v>2013</v>
+      </c>
+      <c r="C959" t="s" s="2">
         <v>2014</v>
-      </c>
-      <c r="C959" t="s" s="2">
-        <v>2015</v>
       </c>
       <c r="D959" s="2"/>
     </row>
@@ -18748,10 +18787,10 @@
         <v>95</v>
       </c>
       <c r="B960" t="s" s="2">
+        <v>2015</v>
+      </c>
+      <c r="C960" t="s" s="2">
         <v>2016</v>
-      </c>
-      <c r="C960" t="s" s="2">
-        <v>2017</v>
       </c>
       <c r="D960" s="2"/>
     </row>
@@ -18760,10 +18799,10 @@
         <v>95</v>
       </c>
       <c r="B961" t="s" s="2">
+        <v>2017</v>
+      </c>
+      <c r="C961" t="s" s="2">
         <v>2018</v>
-      </c>
-      <c r="C961" t="s" s="2">
-        <v>2019</v>
       </c>
       <c r="D961" s="2"/>
     </row>
@@ -18772,10 +18811,10 @@
         <v>95</v>
       </c>
       <c r="B962" t="s" s="2">
+        <v>2019</v>
+      </c>
+      <c r="C962" t="s" s="2">
         <v>2020</v>
-      </c>
-      <c r="C962" t="s" s="2">
-        <v>2021</v>
       </c>
       <c r="D962" s="2"/>
     </row>
@@ -18784,10 +18823,10 @@
         <v>95</v>
       </c>
       <c r="B963" t="s" s="2">
+        <v>2021</v>
+      </c>
+      <c r="C963" t="s" s="2">
         <v>2022</v>
-      </c>
-      <c r="C963" t="s" s="2">
-        <v>2023</v>
       </c>
       <c r="D963" s="2"/>
     </row>
@@ -18796,10 +18835,10 @@
         <v>95</v>
       </c>
       <c r="B964" t="s" s="2">
+        <v>2023</v>
+      </c>
+      <c r="C964" t="s" s="2">
         <v>2024</v>
-      </c>
-      <c r="C964" t="s" s="2">
-        <v>2025</v>
       </c>
       <c r="D964" s="2"/>
     </row>
@@ -18808,10 +18847,10 @@
         <v>95</v>
       </c>
       <c r="B965" t="s" s="2">
+        <v>2025</v>
+      </c>
+      <c r="C965" t="s" s="2">
         <v>2026</v>
-      </c>
-      <c r="C965" t="s" s="2">
-        <v>2027</v>
       </c>
       <c r="D965" s="2"/>
     </row>
@@ -18820,10 +18859,10 @@
         <v>95</v>
       </c>
       <c r="B966" t="s" s="2">
+        <v>2027</v>
+      </c>
+      <c r="C966" t="s" s="2">
         <v>2028</v>
-      </c>
-      <c r="C966" t="s" s="2">
-        <v>2029</v>
       </c>
       <c r="D966" s="2"/>
     </row>
@@ -18832,10 +18871,10 @@
         <v>95</v>
       </c>
       <c r="B967" t="s" s="2">
+        <v>2029</v>
+      </c>
+      <c r="C967" t="s" s="2">
         <v>2030</v>
-      </c>
-      <c r="C967" t="s" s="2">
-        <v>2031</v>
       </c>
       <c r="D967" s="2"/>
     </row>
@@ -18844,10 +18883,10 @@
         <v>95</v>
       </c>
       <c r="B968" t="s" s="2">
+        <v>2031</v>
+      </c>
+      <c r="C968" t="s" s="2">
         <v>2032</v>
-      </c>
-      <c r="C968" t="s" s="2">
-        <v>2033</v>
       </c>
       <c r="D968" s="2"/>
     </row>
@@ -18856,10 +18895,10 @@
         <v>95</v>
       </c>
       <c r="B969" t="s" s="2">
+        <v>2033</v>
+      </c>
+      <c r="C969" t="s" s="2">
         <v>2034</v>
-      </c>
-      <c r="C969" t="s" s="2">
-        <v>2035</v>
       </c>
       <c r="D969" s="2"/>
     </row>
@@ -18868,10 +18907,10 @@
         <v>95</v>
       </c>
       <c r="B970" t="s" s="2">
+        <v>2035</v>
+      </c>
+      <c r="C970" t="s" s="2">
         <v>2036</v>
-      </c>
-      <c r="C970" t="s" s="2">
-        <v>2037</v>
       </c>
       <c r="D970" s="2"/>
     </row>
@@ -18880,10 +18919,10 @@
         <v>95</v>
       </c>
       <c r="B971" t="s" s="2">
+        <v>2037</v>
+      </c>
+      <c r="C971" t="s" s="2">
         <v>2038</v>
-      </c>
-      <c r="C971" t="s" s="2">
-        <v>2039</v>
       </c>
       <c r="D971" s="2"/>
     </row>
@@ -18892,10 +18931,10 @@
         <v>95</v>
       </c>
       <c r="B972" t="s" s="2">
+        <v>2039</v>
+      </c>
+      <c r="C972" t="s" s="2">
         <v>2040</v>
-      </c>
-      <c r="C972" t="s" s="2">
-        <v>2041</v>
       </c>
       <c r="D972" s="2"/>
     </row>
@@ -18904,10 +18943,10 @@
         <v>95</v>
       </c>
       <c r="B973" t="s" s="2">
+        <v>2041</v>
+      </c>
+      <c r="C973" t="s" s="2">
         <v>2042</v>
-      </c>
-      <c r="C973" t="s" s="2">
-        <v>2043</v>
       </c>
       <c r="D973" s="2"/>
     </row>
@@ -18916,10 +18955,10 @@
         <v>95</v>
       </c>
       <c r="B974" t="s" s="2">
+        <v>2043</v>
+      </c>
+      <c r="C974" t="s" s="2">
         <v>2044</v>
-      </c>
-      <c r="C974" t="s" s="2">
-        <v>2045</v>
       </c>
       <c r="D974" s="2"/>
     </row>
@@ -18928,10 +18967,10 @@
         <v>95</v>
       </c>
       <c r="B975" t="s" s="2">
+        <v>2045</v>
+      </c>
+      <c r="C975" t="s" s="2">
         <v>2046</v>
-      </c>
-      <c r="C975" t="s" s="2">
-        <v>2047</v>
       </c>
       <c r="D975" s="2"/>
     </row>
@@ -18940,10 +18979,10 @@
         <v>95</v>
       </c>
       <c r="B976" t="s" s="2">
+        <v>2047</v>
+      </c>
+      <c r="C976" t="s" s="2">
         <v>2048</v>
-      </c>
-      <c r="C976" t="s" s="2">
-        <v>2049</v>
       </c>
       <c r="D976" s="2"/>
     </row>
@@ -18952,10 +18991,10 @@
         <v>95</v>
       </c>
       <c r="B977" t="s" s="2">
+        <v>2049</v>
+      </c>
+      <c r="C977" t="s" s="2">
         <v>2050</v>
-      </c>
-      <c r="C977" t="s" s="2">
-        <v>2051</v>
       </c>
       <c r="D977" s="2"/>
     </row>
@@ -18964,10 +19003,10 @@
         <v>95</v>
       </c>
       <c r="B978" t="s" s="2">
+        <v>2051</v>
+      </c>
+      <c r="C978" t="s" s="2">
         <v>2052</v>
-      </c>
-      <c r="C978" t="s" s="2">
-        <v>2053</v>
       </c>
       <c r="D978" s="2"/>
     </row>
@@ -18976,10 +19015,10 @@
         <v>95</v>
       </c>
       <c r="B979" t="s" s="2">
+        <v>2053</v>
+      </c>
+      <c r="C979" t="s" s="2">
         <v>2054</v>
-      </c>
-      <c r="C979" t="s" s="2">
-        <v>2055</v>
       </c>
       <c r="D979" s="2"/>
     </row>
@@ -18988,10 +19027,10 @@
         <v>95</v>
       </c>
       <c r="B980" t="s" s="2">
+        <v>2055</v>
+      </c>
+      <c r="C980" t="s" s="2">
         <v>2056</v>
-      </c>
-      <c r="C980" t="s" s="2">
-        <v>2057</v>
       </c>
       <c r="D980" s="2"/>
     </row>
@@ -19000,10 +19039,10 @@
         <v>95</v>
       </c>
       <c r="B981" t="s" s="2">
+        <v>2057</v>
+      </c>
+      <c r="C981" t="s" s="2">
         <v>2058</v>
-      </c>
-      <c r="C981" t="s" s="2">
-        <v>2059</v>
       </c>
       <c r="D981" s="2"/>
     </row>
@@ -19012,10 +19051,10 @@
         <v>95</v>
       </c>
       <c r="B982" t="s" s="2">
+        <v>2059</v>
+      </c>
+      <c r="C982" t="s" s="2">
         <v>2060</v>
-      </c>
-      <c r="C982" t="s" s="2">
-        <v>2061</v>
       </c>
       <c r="D982" s="2"/>
     </row>
@@ -19024,10 +19063,10 @@
         <v>95</v>
       </c>
       <c r="B983" t="s" s="2">
+        <v>2061</v>
+      </c>
+      <c r="C983" t="s" s="2">
         <v>2062</v>
-      </c>
-      <c r="C983" t="s" s="2">
-        <v>2063</v>
       </c>
       <c r="D983" s="2"/>
     </row>
@@ -19036,10 +19075,10 @@
         <v>95</v>
       </c>
       <c r="B984" t="s" s="2">
+        <v>2063</v>
+      </c>
+      <c r="C984" t="s" s="2">
         <v>2064</v>
-      </c>
-      <c r="C984" t="s" s="2">
-        <v>2065</v>
       </c>
       <c r="D984" s="2"/>
     </row>
@@ -19048,10 +19087,10 @@
         <v>95</v>
       </c>
       <c r="B985" t="s" s="2">
+        <v>2065</v>
+      </c>
+      <c r="C985" t="s" s="2">
         <v>2066</v>
-      </c>
-      <c r="C985" t="s" s="2">
-        <v>2067</v>
       </c>
       <c r="D985" s="2"/>
     </row>
@@ -19060,10 +19099,10 @@
         <v>95</v>
       </c>
       <c r="B986" t="s" s="2">
+        <v>2067</v>
+      </c>
+      <c r="C986" t="s" s="2">
         <v>2068</v>
-      </c>
-      <c r="C986" t="s" s="2">
-        <v>2069</v>
       </c>
       <c r="D986" s="2"/>
     </row>
@@ -19072,10 +19111,10 @@
         <v>95</v>
       </c>
       <c r="B987" t="s" s="2">
+        <v>2069</v>
+      </c>
+      <c r="C987" t="s" s="2">
         <v>2070</v>
-      </c>
-      <c r="C987" t="s" s="2">
-        <v>2071</v>
       </c>
       <c r="D987" s="2"/>
     </row>
@@ -19084,10 +19123,10 @@
         <v>95</v>
       </c>
       <c r="B988" t="s" s="2">
+        <v>2071</v>
+      </c>
+      <c r="C988" t="s" s="2">
         <v>2072</v>
-      </c>
-      <c r="C988" t="s" s="2">
-        <v>2073</v>
       </c>
       <c r="D988" s="2"/>
     </row>
@@ -19096,24 +19135,22 @@
         <v>95</v>
       </c>
       <c r="B989" t="s" s="2">
+        <v>2073</v>
+      </c>
+      <c r="C989" t="s" s="2">
         <v>2074</v>
       </c>
-      <c r="C989" t="s" s="2">
-        <v>2075</v>
-      </c>
-      <c r="D989" t="s" s="2">
-        <v>2076</v>
-      </c>
+      <c r="D989" s="2"/>
     </row>
     <row r="990">
       <c r="A990" t="s" s="2">
         <v>95</v>
       </c>
       <c r="B990" t="s" s="2">
-        <v>2077</v>
+        <v>2075</v>
       </c>
       <c r="C990" t="s" s="2">
-        <v>2078</v>
+        <v>2076</v>
       </c>
       <c r="D990" s="2"/>
     </row>
@@ -19122,10 +19159,10 @@
         <v>95</v>
       </c>
       <c r="B991" t="s" s="2">
-        <v>2079</v>
+        <v>2077</v>
       </c>
       <c r="C991" t="s" s="2">
-        <v>2080</v>
+        <v>2078</v>
       </c>
       <c r="D991" s="2"/>
     </row>
@@ -19134,10 +19171,10 @@
         <v>95</v>
       </c>
       <c r="B992" t="s" s="2">
-        <v>2081</v>
+        <v>2079</v>
       </c>
       <c r="C992" t="s" s="2">
-        <v>2082</v>
+        <v>2080</v>
       </c>
       <c r="D992" s="2"/>
     </row>
@@ -19146,10 +19183,10 @@
         <v>95</v>
       </c>
       <c r="B993" t="s" s="2">
-        <v>2083</v>
+        <v>2081</v>
       </c>
       <c r="C993" t="s" s="2">
-        <v>2084</v>
+        <v>2082</v>
       </c>
       <c r="D993" s="2"/>
     </row>
@@ -19158,10 +19195,10 @@
         <v>95</v>
       </c>
       <c r="B994" t="s" s="2">
-        <v>2085</v>
+        <v>2083</v>
       </c>
       <c r="C994" t="s" s="2">
-        <v>2086</v>
+        <v>2084</v>
       </c>
       <c r="D994" s="2"/>
     </row>
@@ -19170,10 +19207,10 @@
         <v>95</v>
       </c>
       <c r="B995" t="s" s="2">
-        <v>2087</v>
+        <v>2085</v>
       </c>
       <c r="C995" t="s" s="2">
-        <v>2088</v>
+        <v>2086</v>
       </c>
       <c r="D995" s="2"/>
     </row>
@@ -19182,22 +19219,24 @@
         <v>95</v>
       </c>
       <c r="B996" t="s" s="2">
+        <v>2087</v>
+      </c>
+      <c r="C996" t="s" s="2">
+        <v>2088</v>
+      </c>
+      <c r="D996" t="s" s="2">
         <v>2089</v>
       </c>
-      <c r="C996" t="s" s="2">
-        <v>2090</v>
-      </c>
-      <c r="D996" s="2"/>
     </row>
     <row r="997">
       <c r="A997" t="s" s="2">
         <v>95</v>
       </c>
       <c r="B997" t="s" s="2">
+        <v>2090</v>
+      </c>
+      <c r="C997" t="s" s="2">
         <v>2091</v>
-      </c>
-      <c r="C997" t="s" s="2">
-        <v>2092</v>
       </c>
       <c r="D997" s="2"/>
     </row>
@@ -19206,7 +19245,7 @@
         <v>95</v>
       </c>
       <c r="B998" t="s" s="2">
-        <v>2093</v>
+        <v>2092</v>
       </c>
       <c r="C998" t="s" s="2">
         <v>2093</v>
@@ -19259,19 +19298,17 @@
       <c r="C1002" t="s" s="2">
         <v>2101</v>
       </c>
-      <c r="D1002" t="s" s="2">
-        <v>2102</v>
-      </c>
+      <c r="D1002" s="2"/>
     </row>
     <row r="1003">
       <c r="A1003" t="s" s="2">
         <v>95</v>
       </c>
       <c r="B1003" t="s" s="2">
+        <v>2102</v>
+      </c>
+      <c r="C1003" t="s" s="2">
         <v>2103</v>
-      </c>
-      <c r="C1003" t="s" s="2">
-        <v>2104</v>
       </c>
       <c r="D1003" s="2"/>
     </row>
@@ -19280,10 +19317,10 @@
         <v>95</v>
       </c>
       <c r="B1004" t="s" s="2">
+        <v>2104</v>
+      </c>
+      <c r="C1004" t="s" s="2">
         <v>2105</v>
-      </c>
-      <c r="C1004" t="s" s="2">
-        <v>2106</v>
       </c>
       <c r="D1004" s="2"/>
     </row>
@@ -19292,10 +19329,10 @@
         <v>95</v>
       </c>
       <c r="B1005" t="s" s="2">
-        <v>2107</v>
+        <v>2106</v>
       </c>
       <c r="C1005" t="s" s="2">
-        <v>2108</v>
+        <v>2106</v>
       </c>
       <c r="D1005" s="2"/>
     </row>
@@ -19304,10 +19341,10 @@
         <v>95</v>
       </c>
       <c r="B1006" t="s" s="2">
-        <v>2109</v>
+        <v>2107</v>
       </c>
       <c r="C1006" t="s" s="2">
-        <v>2110</v>
+        <v>2108</v>
       </c>
       <c r="D1006" s="2"/>
     </row>
@@ -19316,10 +19353,10 @@
         <v>95</v>
       </c>
       <c r="B1007" t="s" s="2">
-        <v>2111</v>
+        <v>2109</v>
       </c>
       <c r="C1007" t="s" s="2">
-        <v>2112</v>
+        <v>2110</v>
       </c>
       <c r="D1007" s="2"/>
     </row>
@@ -19328,10 +19365,10 @@
         <v>95</v>
       </c>
       <c r="B1008" t="s" s="2">
-        <v>2113</v>
+        <v>2111</v>
       </c>
       <c r="C1008" t="s" s="2">
-        <v>2114</v>
+        <v>2112</v>
       </c>
       <c r="D1008" s="2"/>
     </row>
@@ -19340,22 +19377,24 @@
         <v>95</v>
       </c>
       <c r="B1009" t="s" s="2">
+        <v>2113</v>
+      </c>
+      <c r="C1009" t="s" s="2">
+        <v>2114</v>
+      </c>
+      <c r="D1009" t="s" s="2">
         <v>2115</v>
       </c>
-      <c r="C1009" t="s" s="2">
-        <v>2116</v>
-      </c>
-      <c r="D1009" s="2"/>
     </row>
     <row r="1010">
       <c r="A1010" t="s" s="2">
         <v>95</v>
       </c>
       <c r="B1010" t="s" s="2">
+        <v>2116</v>
+      </c>
+      <c r="C1010" t="s" s="2">
         <v>2117</v>
-      </c>
-      <c r="C1010" t="s" s="2">
-        <v>2118</v>
       </c>
       <c r="D1010" s="2"/>
     </row>
@@ -19364,10 +19403,10 @@
         <v>95</v>
       </c>
       <c r="B1011" t="s" s="2">
+        <v>2118</v>
+      </c>
+      <c r="C1011" t="s" s="2">
         <v>2119</v>
-      </c>
-      <c r="C1011" t="s" s="2">
-        <v>2120</v>
       </c>
       <c r="D1011" s="2"/>
     </row>
@@ -19376,10 +19415,10 @@
         <v>95</v>
       </c>
       <c r="B1012" t="s" s="2">
+        <v>2120</v>
+      </c>
+      <c r="C1012" t="s" s="2">
         <v>2121</v>
-      </c>
-      <c r="C1012" t="s" s="2">
-        <v>2122</v>
       </c>
       <c r="D1012" s="2"/>
     </row>
@@ -19388,10 +19427,10 @@
         <v>95</v>
       </c>
       <c r="B1013" t="s" s="2">
+        <v>2122</v>
+      </c>
+      <c r="C1013" t="s" s="2">
         <v>2123</v>
-      </c>
-      <c r="C1013" t="s" s="2">
-        <v>2124</v>
       </c>
       <c r="D1013" s="2"/>
     </row>
@@ -19400,10 +19439,10 @@
         <v>95</v>
       </c>
       <c r="B1014" t="s" s="2">
+        <v>2124</v>
+      </c>
+      <c r="C1014" t="s" s="2">
         <v>2125</v>
-      </c>
-      <c r="C1014" t="s" s="2">
-        <v>2126</v>
       </c>
       <c r="D1014" s="2"/>
     </row>
@@ -19412,10 +19451,10 @@
         <v>95</v>
       </c>
       <c r="B1015" t="s" s="2">
+        <v>2126</v>
+      </c>
+      <c r="C1015" t="s" s="2">
         <v>2127</v>
-      </c>
-      <c r="C1015" t="s" s="2">
-        <v>2128</v>
       </c>
       <c r="D1015" s="2"/>
     </row>
@@ -19424,10 +19463,10 @@
         <v>95</v>
       </c>
       <c r="B1016" t="s" s="2">
+        <v>2128</v>
+      </c>
+      <c r="C1016" t="s" s="2">
         <v>2129</v>
-      </c>
-      <c r="C1016" t="s" s="2">
-        <v>2130</v>
       </c>
       <c r="D1016" s="2"/>
     </row>
@@ -19436,10 +19475,10 @@
         <v>95</v>
       </c>
       <c r="B1017" t="s" s="2">
+        <v>2130</v>
+      </c>
+      <c r="C1017" t="s" s="2">
         <v>2131</v>
-      </c>
-      <c r="C1017" t="s" s="2">
-        <v>2132</v>
       </c>
       <c r="D1017" s="2"/>
     </row>
@@ -19448,10 +19487,10 @@
         <v>95</v>
       </c>
       <c r="B1018" t="s" s="2">
+        <v>2132</v>
+      </c>
+      <c r="C1018" t="s" s="2">
         <v>2133</v>
-      </c>
-      <c r="C1018" t="s" s="2">
-        <v>2134</v>
       </c>
       <c r="D1018" s="2"/>
     </row>
@@ -19460,10 +19499,10 @@
         <v>95</v>
       </c>
       <c r="B1019" t="s" s="2">
+        <v>2134</v>
+      </c>
+      <c r="C1019" t="s" s="2">
         <v>2135</v>
-      </c>
-      <c r="C1019" t="s" s="2">
-        <v>2136</v>
       </c>
       <c r="D1019" s="2"/>
     </row>
@@ -19472,10 +19511,10 @@
         <v>95</v>
       </c>
       <c r="B1020" t="s" s="2">
+        <v>2136</v>
+      </c>
+      <c r="C1020" t="s" s="2">
         <v>2137</v>
-      </c>
-      <c r="C1020" t="s" s="2">
-        <v>2138</v>
       </c>
       <c r="D1020" s="2"/>
     </row>
@@ -19484,10 +19523,10 @@
         <v>95</v>
       </c>
       <c r="B1021" t="s" s="2">
+        <v>2138</v>
+      </c>
+      <c r="C1021" t="s" s="2">
         <v>2139</v>
-      </c>
-      <c r="C1021" t="s" s="2">
-        <v>2140</v>
       </c>
       <c r="D1021" s="2"/>
     </row>
@@ -19496,10 +19535,10 @@
         <v>95</v>
       </c>
       <c r="B1022" t="s" s="2">
+        <v>2140</v>
+      </c>
+      <c r="C1022" t="s" s="2">
         <v>2141</v>
-      </c>
-      <c r="C1022" t="s" s="2">
-        <v>2142</v>
       </c>
       <c r="D1022" s="2"/>
     </row>
@@ -19508,10 +19547,10 @@
         <v>95</v>
       </c>
       <c r="B1023" t="s" s="2">
+        <v>2142</v>
+      </c>
+      <c r="C1023" t="s" s="2">
         <v>2143</v>
-      </c>
-      <c r="C1023" t="s" s="2">
-        <v>2144</v>
       </c>
       <c r="D1023" s="2"/>
     </row>
@@ -19520,10 +19559,10 @@
         <v>95</v>
       </c>
       <c r="B1024" t="s" s="2">
+        <v>2144</v>
+      </c>
+      <c r="C1024" t="s" s="2">
         <v>2145</v>
-      </c>
-      <c r="C1024" t="s" s="2">
-        <v>2146</v>
       </c>
       <c r="D1024" s="2"/>
     </row>
@@ -19532,10 +19571,10 @@
         <v>95</v>
       </c>
       <c r="B1025" t="s" s="2">
+        <v>2146</v>
+      </c>
+      <c r="C1025" t="s" s="2">
         <v>2147</v>
-      </c>
-      <c r="C1025" t="s" s="2">
-        <v>2148</v>
       </c>
       <c r="D1025" s="2"/>
     </row>
@@ -19544,10 +19583,10 @@
         <v>95</v>
       </c>
       <c r="B1026" t="s" s="2">
+        <v>2148</v>
+      </c>
+      <c r="C1026" t="s" s="2">
         <v>2149</v>
-      </c>
-      <c r="C1026" t="s" s="2">
-        <v>2150</v>
       </c>
       <c r="D1026" s="2"/>
     </row>
@@ -19556,10 +19595,10 @@
         <v>95</v>
       </c>
       <c r="B1027" t="s" s="2">
+        <v>2150</v>
+      </c>
+      <c r="C1027" t="s" s="2">
         <v>2151</v>
-      </c>
-      <c r="C1027" t="s" s="2">
-        <v>2152</v>
       </c>
       <c r="D1027" s="2"/>
     </row>
@@ -19568,10 +19607,10 @@
         <v>95</v>
       </c>
       <c r="B1028" t="s" s="2">
+        <v>2152</v>
+      </c>
+      <c r="C1028" t="s" s="2">
         <v>2153</v>
-      </c>
-      <c r="C1028" t="s" s="2">
-        <v>2154</v>
       </c>
       <c r="D1028" s="2"/>
     </row>
@@ -19580,10 +19619,10 @@
         <v>95</v>
       </c>
       <c r="B1029" t="s" s="2">
+        <v>2154</v>
+      </c>
+      <c r="C1029" t="s" s="2">
         <v>2155</v>
-      </c>
-      <c r="C1029" t="s" s="2">
-        <v>2156</v>
       </c>
       <c r="D1029" s="2"/>
     </row>
@@ -19592,10 +19631,10 @@
         <v>95</v>
       </c>
       <c r="B1030" t="s" s="2">
+        <v>2156</v>
+      </c>
+      <c r="C1030" t="s" s="2">
         <v>2157</v>
-      </c>
-      <c r="C1030" t="s" s="2">
-        <v>2158</v>
       </c>
       <c r="D1030" s="2"/>
     </row>
@@ -19604,10 +19643,10 @@
         <v>95</v>
       </c>
       <c r="B1031" t="s" s="2">
+        <v>2158</v>
+      </c>
+      <c r="C1031" t="s" s="2">
         <v>2159</v>
-      </c>
-      <c r="C1031" t="s" s="2">
-        <v>2160</v>
       </c>
       <c r="D1031" s="2"/>
     </row>
@@ -19616,10 +19655,10 @@
         <v>95</v>
       </c>
       <c r="B1032" t="s" s="2">
+        <v>2160</v>
+      </c>
+      <c r="C1032" t="s" s="2">
         <v>2161</v>
-      </c>
-      <c r="C1032" t="s" s="2">
-        <v>2162</v>
       </c>
       <c r="D1032" s="2"/>
     </row>
@@ -19628,10 +19667,10 @@
         <v>95</v>
       </c>
       <c r="B1033" t="s" s="2">
+        <v>2162</v>
+      </c>
+      <c r="C1033" t="s" s="2">
         <v>2163</v>
-      </c>
-      <c r="C1033" t="s" s="2">
-        <v>2164</v>
       </c>
       <c r="D1033" s="2"/>
     </row>
@@ -19640,10 +19679,10 @@
         <v>95</v>
       </c>
       <c r="B1034" t="s" s="2">
+        <v>2164</v>
+      </c>
+      <c r="C1034" t="s" s="2">
         <v>2165</v>
-      </c>
-      <c r="C1034" t="s" s="2">
-        <v>2166</v>
       </c>
       <c r="D1034" s="2"/>
     </row>
@@ -19652,10 +19691,10 @@
         <v>95</v>
       </c>
       <c r="B1035" t="s" s="2">
+        <v>2166</v>
+      </c>
+      <c r="C1035" t="s" s="2">
         <v>2167</v>
-      </c>
-      <c r="C1035" t="s" s="2">
-        <v>2168</v>
       </c>
       <c r="D1035" s="2"/>
     </row>
@@ -19664,10 +19703,10 @@
         <v>95</v>
       </c>
       <c r="B1036" t="s" s="2">
+        <v>2168</v>
+      </c>
+      <c r="C1036" t="s" s="2">
         <v>2169</v>
-      </c>
-      <c r="C1036" t="s" s="2">
-        <v>2170</v>
       </c>
       <c r="D1036" s="2"/>
     </row>
@@ -19676,10 +19715,10 @@
         <v>95</v>
       </c>
       <c r="B1037" t="s" s="2">
+        <v>2170</v>
+      </c>
+      <c r="C1037" t="s" s="2">
         <v>2171</v>
-      </c>
-      <c r="C1037" t="s" s="2">
-        <v>2172</v>
       </c>
       <c r="D1037" s="2"/>
     </row>
@@ -19688,10 +19727,10 @@
         <v>95</v>
       </c>
       <c r="B1038" t="s" s="2">
+        <v>2172</v>
+      </c>
+      <c r="C1038" t="s" s="2">
         <v>2173</v>
-      </c>
-      <c r="C1038" t="s" s="2">
-        <v>2174</v>
       </c>
       <c r="D1038" s="2"/>
     </row>
@@ -19700,10 +19739,10 @@
         <v>95</v>
       </c>
       <c r="B1039" t="s" s="2">
+        <v>2174</v>
+      </c>
+      <c r="C1039" t="s" s="2">
         <v>2175</v>
-      </c>
-      <c r="C1039" t="s" s="2">
-        <v>2176</v>
       </c>
       <c r="D1039" s="2"/>
     </row>
@@ -19712,10 +19751,10 @@
         <v>95</v>
       </c>
       <c r="B1040" t="s" s="2">
+        <v>2176</v>
+      </c>
+      <c r="C1040" t="s" s="2">
         <v>2177</v>
-      </c>
-      <c r="C1040" t="s" s="2">
-        <v>2178</v>
       </c>
       <c r="D1040" s="2"/>
     </row>
@@ -19724,10 +19763,10 @@
         <v>95</v>
       </c>
       <c r="B1041" t="s" s="2">
+        <v>2178</v>
+      </c>
+      <c r="C1041" t="s" s="2">
         <v>2179</v>
-      </c>
-      <c r="C1041" t="s" s="2">
-        <v>2180</v>
       </c>
       <c r="D1041" s="2"/>
     </row>
@@ -19736,10 +19775,10 @@
         <v>95</v>
       </c>
       <c r="B1042" t="s" s="2">
+        <v>2180</v>
+      </c>
+      <c r="C1042" t="s" s="2">
         <v>2181</v>
-      </c>
-      <c r="C1042" t="s" s="2">
-        <v>2182</v>
       </c>
       <c r="D1042" s="2"/>
     </row>
@@ -19748,10 +19787,10 @@
         <v>95</v>
       </c>
       <c r="B1043" t="s" s="2">
+        <v>2182</v>
+      </c>
+      <c r="C1043" t="s" s="2">
         <v>2183</v>
-      </c>
-      <c r="C1043" t="s" s="2">
-        <v>2184</v>
       </c>
       <c r="D1043" s="2"/>
     </row>
@@ -19760,12 +19799,96 @@
         <v>95</v>
       </c>
       <c r="B1044" t="s" s="2">
+        <v>2184</v>
+      </c>
+      <c r="C1044" t="s" s="2">
         <v>2185</v>
       </c>
-      <c r="C1044" t="s" s="2">
+      <c r="D1044" s="2"/>
+    </row>
+    <row r="1045">
+      <c r="A1045" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="B1045" t="s" s="2">
         <v>2186</v>
       </c>
-      <c r="D1044" s="2"/>
+      <c r="C1045" t="s" s="2">
+        <v>2187</v>
+      </c>
+      <c r="D1045" s="2"/>
+    </row>
+    <row r="1046">
+      <c r="A1046" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="B1046" t="s" s="2">
+        <v>2188</v>
+      </c>
+      <c r="C1046" t="s" s="2">
+        <v>2189</v>
+      </c>
+      <c r="D1046" s="2"/>
+    </row>
+    <row r="1047">
+      <c r="A1047" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="B1047" t="s" s="2">
+        <v>2190</v>
+      </c>
+      <c r="C1047" t="s" s="2">
+        <v>2191</v>
+      </c>
+      <c r="D1047" s="2"/>
+    </row>
+    <row r="1048">
+      <c r="A1048" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="B1048" t="s" s="2">
+        <v>2192</v>
+      </c>
+      <c r="C1048" t="s" s="2">
+        <v>2193</v>
+      </c>
+      <c r="D1048" s="2"/>
+    </row>
+    <row r="1049">
+      <c r="A1049" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="B1049" t="s" s="2">
+        <v>2194</v>
+      </c>
+      <c r="C1049" t="s" s="2">
+        <v>2195</v>
+      </c>
+      <c r="D1049" s="2"/>
+    </row>
+    <row r="1050">
+      <c r="A1050" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="B1050" t="s" s="2">
+        <v>2196</v>
+      </c>
+      <c r="C1050" t="s" s="2">
+        <v>2197</v>
+      </c>
+      <c r="D1050" s="2"/>
+    </row>
+    <row r="1051">
+      <c r="A1051" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="B1051" t="s" s="2">
+        <v>2198</v>
+      </c>
+      <c r="C1051" t="s" s="2">
+        <v>2199</v>
+      </c>
+      <c r="D1051" s="2"/>
     </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>

--- a/ig/main/CodeSystem-terminologie-nabm.xlsx
+++ b/ig/main/CodeSystem-terminologie-nabm.xlsx
@@ -41,7 +41,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>V98</t>
+    <t>V99</t>
   </si>
   <si>
     <t>Name</t>
@@ -71,7 +71,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-06-20T00:00:00+00:00</t>
+    <t>2025-09-08T00:00:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -4343,7 +4343,7 @@
     <t>4103</t>
   </si>
   <si>
-    <t>TEST DE DETECTION DE LA PRODUCTION D'INTERFERON GAMMA (IGRA)</t>
+    <t>IGRA:TEST DE DETECTION DE LA PRODUCTION D'INTERFERON GAMMA</t>
   </si>
   <si>
     <t>0290</t>

--- a/ig/main/CodeSystem-terminologie-nabm.xlsx
+++ b/ig/main/CodeSystem-terminologie-nabm.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3280" uniqueCount="2200">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3271" uniqueCount="2193">
   <si>
     <t>Property</t>
   </si>
@@ -41,7 +41,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>V99</t>
+    <t>V100</t>
   </si>
   <si>
     <t>Name</t>
@@ -71,7 +71,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-09-08T00:00:00+00:00</t>
+    <t>2025-12-18T00:00:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -131,7 +131,7 @@
     <t>Count</t>
   </si>
   <si>
-    <t>1050</t>
+    <t>1047</t>
   </si>
   <si>
     <t>Code</t>
@@ -791,7 +791,7 @@
     <t>0024</t>
   </si>
   <si>
-    <t>HPV:DETECTION DU GENOME DES PAPILLOMAVIRUS ONCOGENES-DEPISTAGE INDIVIDUEL</t>
+    <t>DETECTION DES ACIDES NUCLEIQUES DES HPV ONCOGENES DI</t>
   </si>
   <si>
     <t>0242</t>
@@ -3009,7 +3009,7 @@
     <t>4509</t>
   </si>
   <si>
-    <t>PAPILLOMAVIRUS HUMAINS A HAUTS RISQUES (HPV) GENOME VIRAL - DEPISTAGE ORGANISE</t>
+    <t>DETECTION DES ACIDES NUCLEIQUES DES HPV ONCOGENES DO</t>
   </si>
   <si>
     <t>5261</t>
@@ -3021,7 +3021,7 @@
     <t>4720</t>
   </si>
   <si>
-    <t>RECHERCHE D'IGG PAR TESTS AUTOMATISABLES DE TYPE ELISA</t>
+    <t>RECHERCHE D'IGG PAR TESTS AUTOMATISABLES DE TYPE ELISA (SARS-COV2)</t>
   </si>
   <si>
     <t>1678</t>
@@ -3058,12 +3058,6 @@
   </si>
   <si>
     <t>BARBITURIQUES (SAUF PHENOBARBITAL) : DOSAGE DANS UN AUTRE LIQ BIOL QUE LE SANG</t>
-  </si>
-  <si>
-    <t>9007</t>
-  </si>
-  <si>
-    <t>FORFAIT SEQUENCAGE</t>
   </si>
   <si>
     <t>4080</t>
@@ -3163,12 +3157,6 @@
     <t>BARTURIQUES : RECHERCHE ET DOSAGE DANS UN AUTRE LIQUIDE BIOLOGIQUE QUE LE SANG</t>
   </si>
   <si>
-    <t>9008</t>
-  </si>
-  <si>
-    <t>FORFAIT ENVOI D'ECHANTILLONS</t>
-  </si>
-  <si>
     <t>4081</t>
   </si>
   <si>
@@ -3232,7 +3220,7 @@
     <t>4722</t>
   </si>
   <si>
-    <t>RECHERCHE D'IGG PAR TESTS SEROLOGIQUES PAR IMMUNOCHROMATOGRAPHIE</t>
+    <t>RECHERCHE D'IGG PAR TESTS SEROLOGIQUES PAR IMMUNOCHROMATOGRAPHIE (SARS-COV2)</t>
   </si>
   <si>
     <t>1458</t>
@@ -3331,12 +3319,6 @@
     <t>INFECTION A CMV : RECHERCHE DES IGG:</t>
   </si>
   <si>
-    <t>9006</t>
-  </si>
-  <si>
-    <t>FORFAIT DU TRAITEMENT DES DONNEES ADMINISTRATIVES DU COVID-19</t>
-  </si>
-  <si>
     <t>5280</t>
   </si>
   <si>
@@ -3482,9 +3464,6 @@
   </si>
   <si>
     <t>0031</t>
-  </si>
-  <si>
-    <t>HPV:DETECTION DU GENOME DES PAPILLOMAVIRUS HUMAINS ONCOGENES DEPISTAGE ORGANISE</t>
   </si>
   <si>
     <t>0164</t>
@@ -4295,9 +4274,6 @@
     <t>4127</t>
   </si>
   <si>
-    <t>PAPILLOMAVIRUS HUMAINS A HAUTS RISQUES (HPV) GENOME VIRAL - DEPISTAGE INDIVIDUEL</t>
-  </si>
-  <si>
     <t>0072</t>
   </si>
   <si>
@@ -4442,6 +4418,9 @@
     <t>UR. : UROBILINE : RECH.</t>
   </si>
   <si>
+    <t>1050</t>
+  </si>
+  <si>
     <t>MESURE DE L'ACTIVITE D'ADAMTS 13</t>
   </si>
   <si>
@@ -5948,7 +5927,7 @@
     <t>5271</t>
   </si>
   <si>
-    <t>SARS-COV-2 : DETECTION GENOME PAR LES TECHNIQUES D'AMPLIFICATION GENIQUE</t>
+    <t>SARS-COV-2:DETECTION GENOME PAR LES TECHNIQUES D'AMPLIFICATION GENIQUE</t>
   </si>
   <si>
     <t>1661</t>
@@ -7255,7 +7234,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:D1051"/>
+  <dimension ref="A1:D1048"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -13582,7 +13561,7 @@
         <v>1148</v>
       </c>
       <c r="C526" t="s" s="2">
-        <v>1149</v>
+        <v>997</v>
       </c>
       <c r="D526" s="2"/>
     </row>
@@ -13591,10 +13570,10 @@
         <v>95</v>
       </c>
       <c r="B527" t="s" s="2">
+        <v>1149</v>
+      </c>
+      <c r="C527" t="s" s="2">
         <v>1150</v>
-      </c>
-      <c r="C527" t="s" s="2">
-        <v>1151</v>
       </c>
       <c r="D527" s="2"/>
     </row>
@@ -13603,10 +13582,10 @@
         <v>95</v>
       </c>
       <c r="B528" t="s" s="2">
+        <v>1151</v>
+      </c>
+      <c r="C528" t="s" s="2">
         <v>1152</v>
-      </c>
-      <c r="C528" t="s" s="2">
-        <v>1153</v>
       </c>
       <c r="D528" s="2"/>
     </row>
@@ -13615,10 +13594,10 @@
         <v>95</v>
       </c>
       <c r="B529" t="s" s="2">
+        <v>1153</v>
+      </c>
+      <c r="C529" t="s" s="2">
         <v>1154</v>
-      </c>
-      <c r="C529" t="s" s="2">
-        <v>1155</v>
       </c>
       <c r="D529" s="2"/>
     </row>
@@ -13627,10 +13606,10 @@
         <v>95</v>
       </c>
       <c r="B530" t="s" s="2">
+        <v>1155</v>
+      </c>
+      <c r="C530" t="s" s="2">
         <v>1156</v>
-      </c>
-      <c r="C530" t="s" s="2">
-        <v>1157</v>
       </c>
       <c r="D530" s="2"/>
     </row>
@@ -13639,10 +13618,10 @@
         <v>95</v>
       </c>
       <c r="B531" t="s" s="2">
+        <v>1157</v>
+      </c>
+      <c r="C531" t="s" s="2">
         <v>1158</v>
-      </c>
-      <c r="C531" t="s" s="2">
-        <v>1159</v>
       </c>
       <c r="D531" s="2"/>
     </row>
@@ -13651,10 +13630,10 @@
         <v>95</v>
       </c>
       <c r="B532" t="s" s="2">
+        <v>1159</v>
+      </c>
+      <c r="C532" t="s" s="2">
         <v>1160</v>
-      </c>
-      <c r="C532" t="s" s="2">
-        <v>1161</v>
       </c>
       <c r="D532" s="2"/>
     </row>
@@ -13663,10 +13642,10 @@
         <v>95</v>
       </c>
       <c r="B533" t="s" s="2">
+        <v>1161</v>
+      </c>
+      <c r="C533" t="s" s="2">
         <v>1162</v>
-      </c>
-      <c r="C533" t="s" s="2">
-        <v>1163</v>
       </c>
       <c r="D533" s="2"/>
     </row>
@@ -13675,10 +13654,10 @@
         <v>95</v>
       </c>
       <c r="B534" t="s" s="2">
+        <v>1163</v>
+      </c>
+      <c r="C534" t="s" s="2">
         <v>1164</v>
-      </c>
-      <c r="C534" t="s" s="2">
-        <v>1165</v>
       </c>
       <c r="D534" s="2"/>
     </row>
@@ -13687,10 +13666,10 @@
         <v>95</v>
       </c>
       <c r="B535" t="s" s="2">
+        <v>1165</v>
+      </c>
+      <c r="C535" t="s" s="2">
         <v>1166</v>
-      </c>
-      <c r="C535" t="s" s="2">
-        <v>1167</v>
       </c>
       <c r="D535" s="2"/>
     </row>
@@ -13699,10 +13678,10 @@
         <v>95</v>
       </c>
       <c r="B536" t="s" s="2">
+        <v>1167</v>
+      </c>
+      <c r="C536" t="s" s="2">
         <v>1168</v>
-      </c>
-      <c r="C536" t="s" s="2">
-        <v>1169</v>
       </c>
       <c r="D536" s="2"/>
     </row>
@@ -13711,10 +13690,10 @@
         <v>95</v>
       </c>
       <c r="B537" t="s" s="2">
+        <v>1169</v>
+      </c>
+      <c r="C537" t="s" s="2">
         <v>1170</v>
-      </c>
-      <c r="C537" t="s" s="2">
-        <v>1171</v>
       </c>
       <c r="D537" s="2"/>
     </row>
@@ -13723,10 +13702,10 @@
         <v>95</v>
       </c>
       <c r="B538" t="s" s="2">
+        <v>1171</v>
+      </c>
+      <c r="C538" t="s" s="2">
         <v>1172</v>
-      </c>
-      <c r="C538" t="s" s="2">
-        <v>1173</v>
       </c>
       <c r="D538" s="2"/>
     </row>
@@ -13735,10 +13714,10 @@
         <v>95</v>
       </c>
       <c r="B539" t="s" s="2">
+        <v>1173</v>
+      </c>
+      <c r="C539" t="s" s="2">
         <v>1174</v>
-      </c>
-      <c r="C539" t="s" s="2">
-        <v>1175</v>
       </c>
       <c r="D539" s="2"/>
     </row>
@@ -13747,10 +13726,10 @@
         <v>95</v>
       </c>
       <c r="B540" t="s" s="2">
+        <v>1175</v>
+      </c>
+      <c r="C540" t="s" s="2">
         <v>1176</v>
-      </c>
-      <c r="C540" t="s" s="2">
-        <v>1177</v>
       </c>
       <c r="D540" s="2"/>
     </row>
@@ -13759,10 +13738,10 @@
         <v>95</v>
       </c>
       <c r="B541" t="s" s="2">
+        <v>1177</v>
+      </c>
+      <c r="C541" t="s" s="2">
         <v>1178</v>
-      </c>
-      <c r="C541" t="s" s="2">
-        <v>1179</v>
       </c>
       <c r="D541" s="2"/>
     </row>
@@ -13771,10 +13750,10 @@
         <v>95</v>
       </c>
       <c r="B542" t="s" s="2">
+        <v>1179</v>
+      </c>
+      <c r="C542" t="s" s="2">
         <v>1180</v>
-      </c>
-      <c r="C542" t="s" s="2">
-        <v>1181</v>
       </c>
       <c r="D542" s="2"/>
     </row>
@@ -13783,10 +13762,10 @@
         <v>95</v>
       </c>
       <c r="B543" t="s" s="2">
+        <v>1181</v>
+      </c>
+      <c r="C543" t="s" s="2">
         <v>1182</v>
-      </c>
-      <c r="C543" t="s" s="2">
-        <v>1183</v>
       </c>
       <c r="D543" s="2"/>
     </row>
@@ -13795,10 +13774,10 @@
         <v>95</v>
       </c>
       <c r="B544" t="s" s="2">
+        <v>1183</v>
+      </c>
+      <c r="C544" t="s" s="2">
         <v>1184</v>
-      </c>
-      <c r="C544" t="s" s="2">
-        <v>1185</v>
       </c>
       <c r="D544" s="2"/>
     </row>
@@ -13807,10 +13786,10 @@
         <v>95</v>
       </c>
       <c r="B545" t="s" s="2">
+        <v>1185</v>
+      </c>
+      <c r="C545" t="s" s="2">
         <v>1186</v>
-      </c>
-      <c r="C545" t="s" s="2">
-        <v>1187</v>
       </c>
       <c r="D545" s="2"/>
     </row>
@@ -13819,10 +13798,10 @@
         <v>95</v>
       </c>
       <c r="B546" t="s" s="2">
+        <v>1187</v>
+      </c>
+      <c r="C546" t="s" s="2">
         <v>1188</v>
-      </c>
-      <c r="C546" t="s" s="2">
-        <v>1189</v>
       </c>
       <c r="D546" s="2"/>
     </row>
@@ -13831,10 +13810,10 @@
         <v>95</v>
       </c>
       <c r="B547" t="s" s="2">
+        <v>1189</v>
+      </c>
+      <c r="C547" t="s" s="2">
         <v>1190</v>
-      </c>
-      <c r="C547" t="s" s="2">
-        <v>1191</v>
       </c>
       <c r="D547" s="2"/>
     </row>
@@ -13843,10 +13822,10 @@
         <v>95</v>
       </c>
       <c r="B548" t="s" s="2">
+        <v>1191</v>
+      </c>
+      <c r="C548" t="s" s="2">
         <v>1192</v>
-      </c>
-      <c r="C548" t="s" s="2">
-        <v>1193</v>
       </c>
       <c r="D548" s="2"/>
     </row>
@@ -13855,10 +13834,10 @@
         <v>95</v>
       </c>
       <c r="B549" t="s" s="2">
+        <v>1193</v>
+      </c>
+      <c r="C549" t="s" s="2">
         <v>1194</v>
-      </c>
-      <c r="C549" t="s" s="2">
-        <v>1195</v>
       </c>
       <c r="D549" s="2"/>
     </row>
@@ -13867,10 +13846,10 @@
         <v>95</v>
       </c>
       <c r="B550" t="s" s="2">
+        <v>1195</v>
+      </c>
+      <c r="C550" t="s" s="2">
         <v>1196</v>
-      </c>
-      <c r="C550" t="s" s="2">
-        <v>1197</v>
       </c>
       <c r="D550" s="2"/>
     </row>
@@ -13879,10 +13858,10 @@
         <v>95</v>
       </c>
       <c r="B551" t="s" s="2">
+        <v>1197</v>
+      </c>
+      <c r="C551" t="s" s="2">
         <v>1198</v>
-      </c>
-      <c r="C551" t="s" s="2">
-        <v>1199</v>
       </c>
       <c r="D551" s="2"/>
     </row>
@@ -13891,10 +13870,10 @@
         <v>95</v>
       </c>
       <c r="B552" t="s" s="2">
+        <v>1199</v>
+      </c>
+      <c r="C552" t="s" s="2">
         <v>1200</v>
-      </c>
-      <c r="C552" t="s" s="2">
-        <v>1201</v>
       </c>
       <c r="D552" s="2"/>
     </row>
@@ -13903,10 +13882,10 @@
         <v>95</v>
       </c>
       <c r="B553" t="s" s="2">
+        <v>1201</v>
+      </c>
+      <c r="C553" t="s" s="2">
         <v>1202</v>
-      </c>
-      <c r="C553" t="s" s="2">
-        <v>1203</v>
       </c>
       <c r="D553" s="2"/>
     </row>
@@ -13915,10 +13894,10 @@
         <v>95</v>
       </c>
       <c r="B554" t="s" s="2">
+        <v>1203</v>
+      </c>
+      <c r="C554" t="s" s="2">
         <v>1204</v>
-      </c>
-      <c r="C554" t="s" s="2">
-        <v>1205</v>
       </c>
       <c r="D554" s="2"/>
     </row>
@@ -13927,10 +13906,10 @@
         <v>95</v>
       </c>
       <c r="B555" t="s" s="2">
+        <v>1205</v>
+      </c>
+      <c r="C555" t="s" s="2">
         <v>1206</v>
-      </c>
-      <c r="C555" t="s" s="2">
-        <v>1207</v>
       </c>
       <c r="D555" s="2"/>
     </row>
@@ -13939,10 +13918,10 @@
         <v>95</v>
       </c>
       <c r="B556" t="s" s="2">
+        <v>1207</v>
+      </c>
+      <c r="C556" t="s" s="2">
         <v>1208</v>
-      </c>
-      <c r="C556" t="s" s="2">
-        <v>1209</v>
       </c>
       <c r="D556" s="2"/>
     </row>
@@ -13951,10 +13930,10 @@
         <v>95</v>
       </c>
       <c r="B557" t="s" s="2">
+        <v>1209</v>
+      </c>
+      <c r="C557" t="s" s="2">
         <v>1210</v>
-      </c>
-      <c r="C557" t="s" s="2">
-        <v>1211</v>
       </c>
       <c r="D557" s="2"/>
     </row>
@@ -13963,10 +13942,10 @@
         <v>95</v>
       </c>
       <c r="B558" t="s" s="2">
+        <v>1211</v>
+      </c>
+      <c r="C558" t="s" s="2">
         <v>1212</v>
-      </c>
-      <c r="C558" t="s" s="2">
-        <v>1213</v>
       </c>
       <c r="D558" s="2"/>
     </row>
@@ -13975,10 +13954,10 @@
         <v>95</v>
       </c>
       <c r="B559" t="s" s="2">
+        <v>1213</v>
+      </c>
+      <c r="C559" t="s" s="2">
         <v>1214</v>
-      </c>
-      <c r="C559" t="s" s="2">
-        <v>1215</v>
       </c>
       <c r="D559" s="2"/>
     </row>
@@ -13987,10 +13966,10 @@
         <v>95</v>
       </c>
       <c r="B560" t="s" s="2">
+        <v>1215</v>
+      </c>
+      <c r="C560" t="s" s="2">
         <v>1216</v>
-      </c>
-      <c r="C560" t="s" s="2">
-        <v>1217</v>
       </c>
       <c r="D560" s="2"/>
     </row>
@@ -13999,10 +13978,10 @@
         <v>95</v>
       </c>
       <c r="B561" t="s" s="2">
+        <v>1217</v>
+      </c>
+      <c r="C561" t="s" s="2">
         <v>1218</v>
-      </c>
-      <c r="C561" t="s" s="2">
-        <v>1219</v>
       </c>
       <c r="D561" s="2"/>
     </row>
@@ -14011,10 +13990,10 @@
         <v>95</v>
       </c>
       <c r="B562" t="s" s="2">
+        <v>1219</v>
+      </c>
+      <c r="C562" t="s" s="2">
         <v>1220</v>
-      </c>
-      <c r="C562" t="s" s="2">
-        <v>1221</v>
       </c>
       <c r="D562" s="2"/>
     </row>
@@ -14023,10 +14002,10 @@
         <v>95</v>
       </c>
       <c r="B563" t="s" s="2">
+        <v>1221</v>
+      </c>
+      <c r="C563" t="s" s="2">
         <v>1222</v>
-      </c>
-      <c r="C563" t="s" s="2">
-        <v>1223</v>
       </c>
       <c r="D563" s="2"/>
     </row>
@@ -14035,10 +14014,10 @@
         <v>95</v>
       </c>
       <c r="B564" t="s" s="2">
+        <v>1223</v>
+      </c>
+      <c r="C564" t="s" s="2">
         <v>1224</v>
-      </c>
-      <c r="C564" t="s" s="2">
-        <v>1225</v>
       </c>
       <c r="D564" s="2"/>
     </row>
@@ -14047,10 +14026,10 @@
         <v>95</v>
       </c>
       <c r="B565" t="s" s="2">
+        <v>1225</v>
+      </c>
+      <c r="C565" t="s" s="2">
         <v>1226</v>
-      </c>
-      <c r="C565" t="s" s="2">
-        <v>1227</v>
       </c>
       <c r="D565" s="2"/>
     </row>
@@ -14059,10 +14038,10 @@
         <v>95</v>
       </c>
       <c r="B566" t="s" s="2">
+        <v>1227</v>
+      </c>
+      <c r="C566" t="s" s="2">
         <v>1228</v>
-      </c>
-      <c r="C566" t="s" s="2">
-        <v>1229</v>
       </c>
       <c r="D566" s="2"/>
     </row>
@@ -14071,10 +14050,10 @@
         <v>95</v>
       </c>
       <c r="B567" t="s" s="2">
+        <v>1229</v>
+      </c>
+      <c r="C567" t="s" s="2">
         <v>1230</v>
-      </c>
-      <c r="C567" t="s" s="2">
-        <v>1231</v>
       </c>
       <c r="D567" s="2"/>
     </row>
@@ -14083,10 +14062,10 @@
         <v>95</v>
       </c>
       <c r="B568" t="s" s="2">
+        <v>1231</v>
+      </c>
+      <c r="C568" t="s" s="2">
         <v>1232</v>
-      </c>
-      <c r="C568" t="s" s="2">
-        <v>1233</v>
       </c>
       <c r="D568" s="2"/>
     </row>
@@ -14095,10 +14074,10 @@
         <v>95</v>
       </c>
       <c r="B569" t="s" s="2">
+        <v>1233</v>
+      </c>
+      <c r="C569" t="s" s="2">
         <v>1234</v>
-      </c>
-      <c r="C569" t="s" s="2">
-        <v>1235</v>
       </c>
       <c r="D569" s="2"/>
     </row>
@@ -14107,10 +14086,10 @@
         <v>95</v>
       </c>
       <c r="B570" t="s" s="2">
+        <v>1235</v>
+      </c>
+      <c r="C570" t="s" s="2">
         <v>1236</v>
-      </c>
-      <c r="C570" t="s" s="2">
-        <v>1237</v>
       </c>
       <c r="D570" s="2"/>
     </row>
@@ -14119,10 +14098,10 @@
         <v>95</v>
       </c>
       <c r="B571" t="s" s="2">
+        <v>1237</v>
+      </c>
+      <c r="C571" t="s" s="2">
         <v>1238</v>
-      </c>
-      <c r="C571" t="s" s="2">
-        <v>1239</v>
       </c>
       <c r="D571" s="2"/>
     </row>
@@ -14131,10 +14110,10 @@
         <v>95</v>
       </c>
       <c r="B572" t="s" s="2">
+        <v>1239</v>
+      </c>
+      <c r="C572" t="s" s="2">
         <v>1240</v>
-      </c>
-      <c r="C572" t="s" s="2">
-        <v>1241</v>
       </c>
       <c r="D572" s="2"/>
     </row>
@@ -14143,10 +14122,10 @@
         <v>95</v>
       </c>
       <c r="B573" t="s" s="2">
+        <v>1241</v>
+      </c>
+      <c r="C573" t="s" s="2">
         <v>1242</v>
-      </c>
-      <c r="C573" t="s" s="2">
-        <v>1243</v>
       </c>
       <c r="D573" s="2"/>
     </row>
@@ -14155,10 +14134,10 @@
         <v>95</v>
       </c>
       <c r="B574" t="s" s="2">
+        <v>1243</v>
+      </c>
+      <c r="C574" t="s" s="2">
         <v>1244</v>
-      </c>
-      <c r="C574" t="s" s="2">
-        <v>1245</v>
       </c>
       <c r="D574" s="2"/>
     </row>
@@ -14167,10 +14146,10 @@
         <v>95</v>
       </c>
       <c r="B575" t="s" s="2">
+        <v>1245</v>
+      </c>
+      <c r="C575" t="s" s="2">
         <v>1246</v>
-      </c>
-      <c r="C575" t="s" s="2">
-        <v>1247</v>
       </c>
       <c r="D575" s="2"/>
     </row>
@@ -14179,10 +14158,10 @@
         <v>95</v>
       </c>
       <c r="B576" t="s" s="2">
+        <v>1247</v>
+      </c>
+      <c r="C576" t="s" s="2">
         <v>1248</v>
-      </c>
-      <c r="C576" t="s" s="2">
-        <v>1249</v>
       </c>
       <c r="D576" s="2"/>
     </row>
@@ -14191,10 +14170,10 @@
         <v>95</v>
       </c>
       <c r="B577" t="s" s="2">
+        <v>1249</v>
+      </c>
+      <c r="C577" t="s" s="2">
         <v>1250</v>
-      </c>
-      <c r="C577" t="s" s="2">
-        <v>1251</v>
       </c>
       <c r="D577" s="2"/>
     </row>
@@ -14203,10 +14182,10 @@
         <v>95</v>
       </c>
       <c r="B578" t="s" s="2">
+        <v>1251</v>
+      </c>
+      <c r="C578" t="s" s="2">
         <v>1252</v>
-      </c>
-      <c r="C578" t="s" s="2">
-        <v>1253</v>
       </c>
       <c r="D578" s="2"/>
     </row>
@@ -14215,10 +14194,10 @@
         <v>95</v>
       </c>
       <c r="B579" t="s" s="2">
+        <v>1253</v>
+      </c>
+      <c r="C579" t="s" s="2">
         <v>1254</v>
-      </c>
-      <c r="C579" t="s" s="2">
-        <v>1255</v>
       </c>
       <c r="D579" s="2"/>
     </row>
@@ -14227,10 +14206,10 @@
         <v>95</v>
       </c>
       <c r="B580" t="s" s="2">
+        <v>1255</v>
+      </c>
+      <c r="C580" t="s" s="2">
         <v>1256</v>
-      </c>
-      <c r="C580" t="s" s="2">
-        <v>1257</v>
       </c>
       <c r="D580" s="2"/>
     </row>
@@ -14239,10 +14218,10 @@
         <v>95</v>
       </c>
       <c r="B581" t="s" s="2">
+        <v>1257</v>
+      </c>
+      <c r="C581" t="s" s="2">
         <v>1258</v>
-      </c>
-      <c r="C581" t="s" s="2">
-        <v>1259</v>
       </c>
       <c r="D581" s="2"/>
     </row>
@@ -14251,10 +14230,10 @@
         <v>95</v>
       </c>
       <c r="B582" t="s" s="2">
+        <v>1259</v>
+      </c>
+      <c r="C582" t="s" s="2">
         <v>1260</v>
-      </c>
-      <c r="C582" t="s" s="2">
-        <v>1261</v>
       </c>
       <c r="D582" s="2"/>
     </row>
@@ -14263,10 +14242,10 @@
         <v>95</v>
       </c>
       <c r="B583" t="s" s="2">
+        <v>1261</v>
+      </c>
+      <c r="C583" t="s" s="2">
         <v>1262</v>
-      </c>
-      <c r="C583" t="s" s="2">
-        <v>1263</v>
       </c>
       <c r="D583" s="2"/>
     </row>
@@ -14275,10 +14254,10 @@
         <v>95</v>
       </c>
       <c r="B584" t="s" s="2">
+        <v>1263</v>
+      </c>
+      <c r="C584" t="s" s="2">
         <v>1264</v>
-      </c>
-      <c r="C584" t="s" s="2">
-        <v>1265</v>
       </c>
       <c r="D584" s="2"/>
     </row>
@@ -14287,10 +14266,10 @@
         <v>95</v>
       </c>
       <c r="B585" t="s" s="2">
+        <v>1265</v>
+      </c>
+      <c r="C585" t="s" s="2">
         <v>1266</v>
-      </c>
-      <c r="C585" t="s" s="2">
-        <v>1267</v>
       </c>
       <c r="D585" s="2"/>
     </row>
@@ -14299,10 +14278,10 @@
         <v>95</v>
       </c>
       <c r="B586" t="s" s="2">
+        <v>1267</v>
+      </c>
+      <c r="C586" t="s" s="2">
         <v>1268</v>
-      </c>
-      <c r="C586" t="s" s="2">
-        <v>1269</v>
       </c>
       <c r="D586" s="2"/>
     </row>
@@ -14311,10 +14290,10 @@
         <v>95</v>
       </c>
       <c r="B587" t="s" s="2">
+        <v>1269</v>
+      </c>
+      <c r="C587" t="s" s="2">
         <v>1270</v>
-      </c>
-      <c r="C587" t="s" s="2">
-        <v>1271</v>
       </c>
       <c r="D587" s="2"/>
     </row>
@@ -14323,10 +14302,10 @@
         <v>95</v>
       </c>
       <c r="B588" t="s" s="2">
+        <v>1271</v>
+      </c>
+      <c r="C588" t="s" s="2">
         <v>1272</v>
-      </c>
-      <c r="C588" t="s" s="2">
-        <v>1273</v>
       </c>
       <c r="D588" s="2"/>
     </row>
@@ -14335,10 +14314,10 @@
         <v>95</v>
       </c>
       <c r="B589" t="s" s="2">
+        <v>1273</v>
+      </c>
+      <c r="C589" t="s" s="2">
         <v>1274</v>
-      </c>
-      <c r="C589" t="s" s="2">
-        <v>1275</v>
       </c>
       <c r="D589" s="2"/>
     </row>
@@ -14347,10 +14326,10 @@
         <v>95</v>
       </c>
       <c r="B590" t="s" s="2">
+        <v>1275</v>
+      </c>
+      <c r="C590" t="s" s="2">
         <v>1276</v>
-      </c>
-      <c r="C590" t="s" s="2">
-        <v>1277</v>
       </c>
       <c r="D590" s="2"/>
     </row>
@@ -14359,10 +14338,10 @@
         <v>95</v>
       </c>
       <c r="B591" t="s" s="2">
+        <v>1277</v>
+      </c>
+      <c r="C591" t="s" s="2">
         <v>1278</v>
-      </c>
-      <c r="C591" t="s" s="2">
-        <v>1279</v>
       </c>
       <c r="D591" s="2"/>
     </row>
@@ -14371,10 +14350,10 @@
         <v>95</v>
       </c>
       <c r="B592" t="s" s="2">
+        <v>1279</v>
+      </c>
+      <c r="C592" t="s" s="2">
         <v>1280</v>
-      </c>
-      <c r="C592" t="s" s="2">
-        <v>1281</v>
       </c>
       <c r="D592" s="2"/>
     </row>
@@ -14383,10 +14362,10 @@
         <v>95</v>
       </c>
       <c r="B593" t="s" s="2">
+        <v>1281</v>
+      </c>
+      <c r="C593" t="s" s="2">
         <v>1282</v>
-      </c>
-      <c r="C593" t="s" s="2">
-        <v>1283</v>
       </c>
       <c r="D593" s="2"/>
     </row>
@@ -14395,10 +14374,10 @@
         <v>95</v>
       </c>
       <c r="B594" t="s" s="2">
+        <v>1283</v>
+      </c>
+      <c r="C594" t="s" s="2">
         <v>1284</v>
-      </c>
-      <c r="C594" t="s" s="2">
-        <v>1285</v>
       </c>
       <c r="D594" s="2"/>
     </row>
@@ -14407,10 +14386,10 @@
         <v>95</v>
       </c>
       <c r="B595" t="s" s="2">
+        <v>1285</v>
+      </c>
+      <c r="C595" t="s" s="2">
         <v>1286</v>
-      </c>
-      <c r="C595" t="s" s="2">
-        <v>1287</v>
       </c>
       <c r="D595" s="2"/>
     </row>
@@ -14419,10 +14398,10 @@
         <v>95</v>
       </c>
       <c r="B596" t="s" s="2">
+        <v>1287</v>
+      </c>
+      <c r="C596" t="s" s="2">
         <v>1288</v>
-      </c>
-      <c r="C596" t="s" s="2">
-        <v>1289</v>
       </c>
       <c r="D596" s="2"/>
     </row>
@@ -14431,10 +14410,10 @@
         <v>95</v>
       </c>
       <c r="B597" t="s" s="2">
+        <v>1289</v>
+      </c>
+      <c r="C597" t="s" s="2">
         <v>1290</v>
-      </c>
-      <c r="C597" t="s" s="2">
-        <v>1291</v>
       </c>
       <c r="D597" s="2"/>
     </row>
@@ -14443,10 +14422,10 @@
         <v>95</v>
       </c>
       <c r="B598" t="s" s="2">
+        <v>1291</v>
+      </c>
+      <c r="C598" t="s" s="2">
         <v>1292</v>
-      </c>
-      <c r="C598" t="s" s="2">
-        <v>1293</v>
       </c>
       <c r="D598" s="2"/>
     </row>
@@ -14455,10 +14434,10 @@
         <v>95</v>
       </c>
       <c r="B599" t="s" s="2">
+        <v>1293</v>
+      </c>
+      <c r="C599" t="s" s="2">
         <v>1294</v>
-      </c>
-      <c r="C599" t="s" s="2">
-        <v>1295</v>
       </c>
       <c r="D599" s="2"/>
     </row>
@@ -14467,10 +14446,10 @@
         <v>95</v>
       </c>
       <c r="B600" t="s" s="2">
+        <v>1295</v>
+      </c>
+      <c r="C600" t="s" s="2">
         <v>1296</v>
-      </c>
-      <c r="C600" t="s" s="2">
-        <v>1297</v>
       </c>
       <c r="D600" s="2"/>
     </row>
@@ -14479,10 +14458,10 @@
         <v>95</v>
       </c>
       <c r="B601" t="s" s="2">
+        <v>1297</v>
+      </c>
+      <c r="C601" t="s" s="2">
         <v>1298</v>
-      </c>
-      <c r="C601" t="s" s="2">
-        <v>1299</v>
       </c>
       <c r="D601" s="2"/>
     </row>
@@ -14491,10 +14470,10 @@
         <v>95</v>
       </c>
       <c r="B602" t="s" s="2">
+        <v>1299</v>
+      </c>
+      <c r="C602" t="s" s="2">
         <v>1300</v>
-      </c>
-      <c r="C602" t="s" s="2">
-        <v>1301</v>
       </c>
       <c r="D602" s="2"/>
     </row>
@@ -14503,10 +14482,10 @@
         <v>95</v>
       </c>
       <c r="B603" t="s" s="2">
+        <v>1301</v>
+      </c>
+      <c r="C603" t="s" s="2">
         <v>1302</v>
-      </c>
-      <c r="C603" t="s" s="2">
-        <v>1303</v>
       </c>
       <c r="D603" s="2"/>
     </row>
@@ -14515,10 +14494,10 @@
         <v>95</v>
       </c>
       <c r="B604" t="s" s="2">
+        <v>1303</v>
+      </c>
+      <c r="C604" t="s" s="2">
         <v>1304</v>
-      </c>
-      <c r="C604" t="s" s="2">
-        <v>1305</v>
       </c>
       <c r="D604" s="2"/>
     </row>
@@ -14527,10 +14506,10 @@
         <v>95</v>
       </c>
       <c r="B605" t="s" s="2">
+        <v>1305</v>
+      </c>
+      <c r="C605" t="s" s="2">
         <v>1306</v>
-      </c>
-      <c r="C605" t="s" s="2">
-        <v>1307</v>
       </c>
       <c r="D605" s="2"/>
     </row>
@@ -14539,10 +14518,10 @@
         <v>95</v>
       </c>
       <c r="B606" t="s" s="2">
+        <v>1307</v>
+      </c>
+      <c r="C606" t="s" s="2">
         <v>1308</v>
-      </c>
-      <c r="C606" t="s" s="2">
-        <v>1309</v>
       </c>
       <c r="D606" s="2"/>
     </row>
@@ -14551,10 +14530,10 @@
         <v>95</v>
       </c>
       <c r="B607" t="s" s="2">
+        <v>1309</v>
+      </c>
+      <c r="C607" t="s" s="2">
         <v>1310</v>
-      </c>
-      <c r="C607" t="s" s="2">
-        <v>1311</v>
       </c>
       <c r="D607" s="2"/>
     </row>
@@ -14563,10 +14542,10 @@
         <v>95</v>
       </c>
       <c r="B608" t="s" s="2">
+        <v>1311</v>
+      </c>
+      <c r="C608" t="s" s="2">
         <v>1312</v>
-      </c>
-      <c r="C608" t="s" s="2">
-        <v>1313</v>
       </c>
       <c r="D608" s="2"/>
     </row>
@@ -14575,10 +14554,10 @@
         <v>95</v>
       </c>
       <c r="B609" t="s" s="2">
+        <v>1313</v>
+      </c>
+      <c r="C609" t="s" s="2">
         <v>1314</v>
-      </c>
-      <c r="C609" t="s" s="2">
-        <v>1315</v>
       </c>
       <c r="D609" s="2"/>
     </row>
@@ -14587,10 +14566,10 @@
         <v>95</v>
       </c>
       <c r="B610" t="s" s="2">
+        <v>1315</v>
+      </c>
+      <c r="C610" t="s" s="2">
         <v>1316</v>
-      </c>
-      <c r="C610" t="s" s="2">
-        <v>1317</v>
       </c>
       <c r="D610" s="2"/>
     </row>
@@ -14599,10 +14578,10 @@
         <v>95</v>
       </c>
       <c r="B611" t="s" s="2">
+        <v>1317</v>
+      </c>
+      <c r="C611" t="s" s="2">
         <v>1318</v>
-      </c>
-      <c r="C611" t="s" s="2">
-        <v>1319</v>
       </c>
       <c r="D611" s="2"/>
     </row>
@@ -14611,10 +14590,10 @@
         <v>95</v>
       </c>
       <c r="B612" t="s" s="2">
+        <v>1319</v>
+      </c>
+      <c r="C612" t="s" s="2">
         <v>1320</v>
-      </c>
-      <c r="C612" t="s" s="2">
-        <v>1321</v>
       </c>
       <c r="D612" s="2"/>
     </row>
@@ -14623,10 +14602,10 @@
         <v>95</v>
       </c>
       <c r="B613" t="s" s="2">
+        <v>1321</v>
+      </c>
+      <c r="C613" t="s" s="2">
         <v>1322</v>
-      </c>
-      <c r="C613" t="s" s="2">
-        <v>1323</v>
       </c>
       <c r="D613" s="2"/>
     </row>
@@ -14635,10 +14614,10 @@
         <v>95</v>
       </c>
       <c r="B614" t="s" s="2">
+        <v>1323</v>
+      </c>
+      <c r="C614" t="s" s="2">
         <v>1324</v>
-      </c>
-      <c r="C614" t="s" s="2">
-        <v>1325</v>
       </c>
       <c r="D614" s="2"/>
     </row>
@@ -14647,10 +14626,10 @@
         <v>95</v>
       </c>
       <c r="B615" t="s" s="2">
+        <v>1325</v>
+      </c>
+      <c r="C615" t="s" s="2">
         <v>1326</v>
-      </c>
-      <c r="C615" t="s" s="2">
-        <v>1327</v>
       </c>
       <c r="D615" s="2"/>
     </row>
@@ -14659,10 +14638,10 @@
         <v>95</v>
       </c>
       <c r="B616" t="s" s="2">
+        <v>1327</v>
+      </c>
+      <c r="C616" t="s" s="2">
         <v>1328</v>
-      </c>
-      <c r="C616" t="s" s="2">
-        <v>1329</v>
       </c>
       <c r="D616" s="2"/>
     </row>
@@ -14671,10 +14650,10 @@
         <v>95</v>
       </c>
       <c r="B617" t="s" s="2">
+        <v>1329</v>
+      </c>
+      <c r="C617" t="s" s="2">
         <v>1330</v>
-      </c>
-      <c r="C617" t="s" s="2">
-        <v>1331</v>
       </c>
       <c r="D617" s="2"/>
     </row>
@@ -14683,10 +14662,10 @@
         <v>95</v>
       </c>
       <c r="B618" t="s" s="2">
+        <v>1331</v>
+      </c>
+      <c r="C618" t="s" s="2">
         <v>1332</v>
-      </c>
-      <c r="C618" t="s" s="2">
-        <v>1333</v>
       </c>
       <c r="D618" s="2"/>
     </row>
@@ -14695,10 +14674,10 @@
         <v>95</v>
       </c>
       <c r="B619" t="s" s="2">
+        <v>1333</v>
+      </c>
+      <c r="C619" t="s" s="2">
         <v>1334</v>
-      </c>
-      <c r="C619" t="s" s="2">
-        <v>1335</v>
       </c>
       <c r="D619" s="2"/>
     </row>
@@ -14707,10 +14686,10 @@
         <v>95</v>
       </c>
       <c r="B620" t="s" s="2">
+        <v>1335</v>
+      </c>
+      <c r="C620" t="s" s="2">
         <v>1336</v>
-      </c>
-      <c r="C620" t="s" s="2">
-        <v>1337</v>
       </c>
       <c r="D620" s="2"/>
     </row>
@@ -14719,10 +14698,10 @@
         <v>95</v>
       </c>
       <c r="B621" t="s" s="2">
+        <v>1337</v>
+      </c>
+      <c r="C621" t="s" s="2">
         <v>1338</v>
-      </c>
-      <c r="C621" t="s" s="2">
-        <v>1339</v>
       </c>
       <c r="D621" s="2"/>
     </row>
@@ -14731,10 +14710,10 @@
         <v>95</v>
       </c>
       <c r="B622" t="s" s="2">
+        <v>1339</v>
+      </c>
+      <c r="C622" t="s" s="2">
         <v>1340</v>
-      </c>
-      <c r="C622" t="s" s="2">
-        <v>1341</v>
       </c>
       <c r="D622" s="2"/>
     </row>
@@ -14743,10 +14722,10 @@
         <v>95</v>
       </c>
       <c r="B623" t="s" s="2">
+        <v>1341</v>
+      </c>
+      <c r="C623" t="s" s="2">
         <v>1342</v>
-      </c>
-      <c r="C623" t="s" s="2">
-        <v>1343</v>
       </c>
       <c r="D623" s="2"/>
     </row>
@@ -14755,10 +14734,10 @@
         <v>95</v>
       </c>
       <c r="B624" t="s" s="2">
+        <v>1343</v>
+      </c>
+      <c r="C624" t="s" s="2">
         <v>1344</v>
-      </c>
-      <c r="C624" t="s" s="2">
-        <v>1345</v>
       </c>
       <c r="D624" s="2"/>
     </row>
@@ -14767,10 +14746,10 @@
         <v>95</v>
       </c>
       <c r="B625" t="s" s="2">
+        <v>1345</v>
+      </c>
+      <c r="C625" t="s" s="2">
         <v>1346</v>
-      </c>
-      <c r="C625" t="s" s="2">
-        <v>1347</v>
       </c>
       <c r="D625" s="2"/>
     </row>
@@ -14779,10 +14758,10 @@
         <v>95</v>
       </c>
       <c r="B626" t="s" s="2">
+        <v>1347</v>
+      </c>
+      <c r="C626" t="s" s="2">
         <v>1348</v>
-      </c>
-      <c r="C626" t="s" s="2">
-        <v>1349</v>
       </c>
       <c r="D626" s="2"/>
     </row>
@@ -14791,10 +14770,10 @@
         <v>95</v>
       </c>
       <c r="B627" t="s" s="2">
+        <v>1349</v>
+      </c>
+      <c r="C627" t="s" s="2">
         <v>1350</v>
-      </c>
-      <c r="C627" t="s" s="2">
-        <v>1351</v>
       </c>
       <c r="D627" s="2"/>
     </row>
@@ -14803,10 +14782,10 @@
         <v>95</v>
       </c>
       <c r="B628" t="s" s="2">
+        <v>1351</v>
+      </c>
+      <c r="C628" t="s" s="2">
         <v>1352</v>
-      </c>
-      <c r="C628" t="s" s="2">
-        <v>1353</v>
       </c>
       <c r="D628" s="2"/>
     </row>
@@ -14815,10 +14794,10 @@
         <v>95</v>
       </c>
       <c r="B629" t="s" s="2">
+        <v>1353</v>
+      </c>
+      <c r="C629" t="s" s="2">
         <v>1354</v>
-      </c>
-      <c r="C629" t="s" s="2">
-        <v>1355</v>
       </c>
       <c r="D629" s="2"/>
     </row>
@@ -14827,10 +14806,10 @@
         <v>95</v>
       </c>
       <c r="B630" t="s" s="2">
+        <v>1355</v>
+      </c>
+      <c r="C630" t="s" s="2">
         <v>1356</v>
-      </c>
-      <c r="C630" t="s" s="2">
-        <v>1357</v>
       </c>
       <c r="D630" s="2"/>
     </row>
@@ -14839,10 +14818,10 @@
         <v>95</v>
       </c>
       <c r="B631" t="s" s="2">
+        <v>1357</v>
+      </c>
+      <c r="C631" t="s" s="2">
         <v>1358</v>
-      </c>
-      <c r="C631" t="s" s="2">
-        <v>1359</v>
       </c>
       <c r="D631" s="2"/>
     </row>
@@ -14851,10 +14830,10 @@
         <v>95</v>
       </c>
       <c r="B632" t="s" s="2">
+        <v>1359</v>
+      </c>
+      <c r="C632" t="s" s="2">
         <v>1360</v>
-      </c>
-      <c r="C632" t="s" s="2">
-        <v>1361</v>
       </c>
       <c r="D632" s="2"/>
     </row>
@@ -14863,10 +14842,10 @@
         <v>95</v>
       </c>
       <c r="B633" t="s" s="2">
+        <v>1361</v>
+      </c>
+      <c r="C633" t="s" s="2">
         <v>1362</v>
-      </c>
-      <c r="C633" t="s" s="2">
-        <v>1363</v>
       </c>
       <c r="D633" s="2"/>
     </row>
@@ -14875,10 +14854,10 @@
         <v>95</v>
       </c>
       <c r="B634" t="s" s="2">
+        <v>1363</v>
+      </c>
+      <c r="C634" t="s" s="2">
         <v>1364</v>
-      </c>
-      <c r="C634" t="s" s="2">
-        <v>1365</v>
       </c>
       <c r="D634" s="2"/>
     </row>
@@ -14887,10 +14866,10 @@
         <v>95</v>
       </c>
       <c r="B635" t="s" s="2">
+        <v>1365</v>
+      </c>
+      <c r="C635" t="s" s="2">
         <v>1366</v>
-      </c>
-      <c r="C635" t="s" s="2">
-        <v>1367</v>
       </c>
       <c r="D635" s="2"/>
     </row>
@@ -14899,10 +14878,10 @@
         <v>95</v>
       </c>
       <c r="B636" t="s" s="2">
+        <v>1367</v>
+      </c>
+      <c r="C636" t="s" s="2">
         <v>1368</v>
-      </c>
-      <c r="C636" t="s" s="2">
-        <v>1369</v>
       </c>
       <c r="D636" s="2"/>
     </row>
@@ -14911,10 +14890,10 @@
         <v>95</v>
       </c>
       <c r="B637" t="s" s="2">
+        <v>1369</v>
+      </c>
+      <c r="C637" t="s" s="2">
         <v>1370</v>
-      </c>
-      <c r="C637" t="s" s="2">
-        <v>1371</v>
       </c>
       <c r="D637" s="2"/>
     </row>
@@ -14923,10 +14902,10 @@
         <v>95</v>
       </c>
       <c r="B638" t="s" s="2">
+        <v>1371</v>
+      </c>
+      <c r="C638" t="s" s="2">
         <v>1372</v>
-      </c>
-      <c r="C638" t="s" s="2">
-        <v>1373</v>
       </c>
       <c r="D638" s="2"/>
     </row>
@@ -14935,10 +14914,10 @@
         <v>95</v>
       </c>
       <c r="B639" t="s" s="2">
+        <v>1373</v>
+      </c>
+      <c r="C639" t="s" s="2">
         <v>1374</v>
-      </c>
-      <c r="C639" t="s" s="2">
-        <v>1375</v>
       </c>
       <c r="D639" s="2"/>
     </row>
@@ -14947,10 +14926,10 @@
         <v>95</v>
       </c>
       <c r="B640" t="s" s="2">
+        <v>1375</v>
+      </c>
+      <c r="C640" t="s" s="2">
         <v>1376</v>
-      </c>
-      <c r="C640" t="s" s="2">
-        <v>1377</v>
       </c>
       <c r="D640" s="2"/>
     </row>
@@ -14959,10 +14938,10 @@
         <v>95</v>
       </c>
       <c r="B641" t="s" s="2">
+        <v>1377</v>
+      </c>
+      <c r="C641" t="s" s="2">
         <v>1378</v>
-      </c>
-      <c r="C641" t="s" s="2">
-        <v>1379</v>
       </c>
       <c r="D641" s="2"/>
     </row>
@@ -14971,10 +14950,10 @@
         <v>95</v>
       </c>
       <c r="B642" t="s" s="2">
+        <v>1379</v>
+      </c>
+      <c r="C642" t="s" s="2">
         <v>1380</v>
-      </c>
-      <c r="C642" t="s" s="2">
-        <v>1381</v>
       </c>
       <c r="D642" s="2"/>
     </row>
@@ -14983,10 +14962,10 @@
         <v>95</v>
       </c>
       <c r="B643" t="s" s="2">
+        <v>1381</v>
+      </c>
+      <c r="C643" t="s" s="2">
         <v>1382</v>
-      </c>
-      <c r="C643" t="s" s="2">
-        <v>1383</v>
       </c>
       <c r="D643" s="2"/>
     </row>
@@ -14995,10 +14974,10 @@
         <v>95</v>
       </c>
       <c r="B644" t="s" s="2">
+        <v>1383</v>
+      </c>
+      <c r="C644" t="s" s="2">
         <v>1384</v>
-      </c>
-      <c r="C644" t="s" s="2">
-        <v>1385</v>
       </c>
       <c r="D644" s="2"/>
     </row>
@@ -15007,10 +14986,10 @@
         <v>95</v>
       </c>
       <c r="B645" t="s" s="2">
+        <v>1385</v>
+      </c>
+      <c r="C645" t="s" s="2">
         <v>1386</v>
-      </c>
-      <c r="C645" t="s" s="2">
-        <v>1387</v>
       </c>
       <c r="D645" s="2"/>
     </row>
@@ -15019,10 +14998,10 @@
         <v>95</v>
       </c>
       <c r="B646" t="s" s="2">
+        <v>1387</v>
+      </c>
+      <c r="C646" t="s" s="2">
         <v>1388</v>
-      </c>
-      <c r="C646" t="s" s="2">
-        <v>1389</v>
       </c>
       <c r="D646" s="2"/>
     </row>
@@ -15031,10 +15010,10 @@
         <v>95</v>
       </c>
       <c r="B647" t="s" s="2">
+        <v>1389</v>
+      </c>
+      <c r="C647" t="s" s="2">
         <v>1390</v>
-      </c>
-      <c r="C647" t="s" s="2">
-        <v>1391</v>
       </c>
       <c r="D647" s="2"/>
     </row>
@@ -15043,10 +15022,10 @@
         <v>95</v>
       </c>
       <c r="B648" t="s" s="2">
+        <v>1391</v>
+      </c>
+      <c r="C648" t="s" s="2">
         <v>1392</v>
-      </c>
-      <c r="C648" t="s" s="2">
-        <v>1393</v>
       </c>
       <c r="D648" s="2"/>
     </row>
@@ -15055,10 +15034,10 @@
         <v>95</v>
       </c>
       <c r="B649" t="s" s="2">
+        <v>1393</v>
+      </c>
+      <c r="C649" t="s" s="2">
         <v>1394</v>
-      </c>
-      <c r="C649" t="s" s="2">
-        <v>1395</v>
       </c>
       <c r="D649" s="2"/>
     </row>
@@ -15067,10 +15046,10 @@
         <v>95</v>
       </c>
       <c r="B650" t="s" s="2">
+        <v>1395</v>
+      </c>
+      <c r="C650" t="s" s="2">
         <v>1396</v>
-      </c>
-      <c r="C650" t="s" s="2">
-        <v>1397</v>
       </c>
       <c r="D650" s="2"/>
     </row>
@@ -15079,10 +15058,10 @@
         <v>95</v>
       </c>
       <c r="B651" t="s" s="2">
+        <v>1397</v>
+      </c>
+      <c r="C651" t="s" s="2">
         <v>1398</v>
-      </c>
-      <c r="C651" t="s" s="2">
-        <v>1399</v>
       </c>
       <c r="D651" s="2"/>
     </row>
@@ -15091,10 +15070,10 @@
         <v>95</v>
       </c>
       <c r="B652" t="s" s="2">
+        <v>1399</v>
+      </c>
+      <c r="C652" t="s" s="2">
         <v>1400</v>
-      </c>
-      <c r="C652" t="s" s="2">
-        <v>1401</v>
       </c>
       <c r="D652" s="2"/>
     </row>
@@ -15103,10 +15082,10 @@
         <v>95</v>
       </c>
       <c r="B653" t="s" s="2">
+        <v>1401</v>
+      </c>
+      <c r="C653" t="s" s="2">
         <v>1402</v>
-      </c>
-      <c r="C653" t="s" s="2">
-        <v>1403</v>
       </c>
       <c r="D653" s="2"/>
     </row>
@@ -15115,10 +15094,10 @@
         <v>95</v>
       </c>
       <c r="B654" t="s" s="2">
+        <v>1403</v>
+      </c>
+      <c r="C654" t="s" s="2">
         <v>1404</v>
-      </c>
-      <c r="C654" t="s" s="2">
-        <v>1405</v>
       </c>
       <c r="D654" s="2"/>
     </row>
@@ -15127,10 +15106,10 @@
         <v>95</v>
       </c>
       <c r="B655" t="s" s="2">
+        <v>1405</v>
+      </c>
+      <c r="C655" t="s" s="2">
         <v>1406</v>
-      </c>
-      <c r="C655" t="s" s="2">
-        <v>1407</v>
       </c>
       <c r="D655" s="2"/>
     </row>
@@ -15139,10 +15118,10 @@
         <v>95</v>
       </c>
       <c r="B656" t="s" s="2">
+        <v>1407</v>
+      </c>
+      <c r="C656" t="s" s="2">
         <v>1408</v>
-      </c>
-      <c r="C656" t="s" s="2">
-        <v>1409</v>
       </c>
       <c r="D656" s="2"/>
     </row>
@@ -15151,10 +15130,10 @@
         <v>95</v>
       </c>
       <c r="B657" t="s" s="2">
+        <v>1409</v>
+      </c>
+      <c r="C657" t="s" s="2">
         <v>1410</v>
-      </c>
-      <c r="C657" t="s" s="2">
-        <v>1411</v>
       </c>
       <c r="D657" s="2"/>
     </row>
@@ -15163,10 +15142,10 @@
         <v>95</v>
       </c>
       <c r="B658" t="s" s="2">
+        <v>1411</v>
+      </c>
+      <c r="C658" t="s" s="2">
         <v>1412</v>
-      </c>
-      <c r="C658" t="s" s="2">
-        <v>1413</v>
       </c>
       <c r="D658" s="2"/>
     </row>
@@ -15175,10 +15154,10 @@
         <v>95</v>
       </c>
       <c r="B659" t="s" s="2">
+        <v>1413</v>
+      </c>
+      <c r="C659" t="s" s="2">
         <v>1414</v>
-      </c>
-      <c r="C659" t="s" s="2">
-        <v>1415</v>
       </c>
       <c r="D659" s="2"/>
     </row>
@@ -15187,10 +15166,10 @@
         <v>95</v>
       </c>
       <c r="B660" t="s" s="2">
+        <v>1415</v>
+      </c>
+      <c r="C660" t="s" s="2">
         <v>1416</v>
-      </c>
-      <c r="C660" t="s" s="2">
-        <v>1417</v>
       </c>
       <c r="D660" s="2"/>
     </row>
@@ -15199,10 +15178,10 @@
         <v>95</v>
       </c>
       <c r="B661" t="s" s="2">
-        <v>1418</v>
+        <v>1417</v>
       </c>
       <c r="C661" t="s" s="2">
-        <v>1419</v>
+        <v>258</v>
       </c>
       <c r="D661" s="2"/>
     </row>
@@ -15211,10 +15190,10 @@
         <v>95</v>
       </c>
       <c r="B662" t="s" s="2">
-        <v>1420</v>
+        <v>1418</v>
       </c>
       <c r="C662" t="s" s="2">
-        <v>1421</v>
+        <v>1419</v>
       </c>
       <c r="D662" s="2"/>
     </row>
@@ -15223,10 +15202,10 @@
         <v>95</v>
       </c>
       <c r="B663" t="s" s="2">
-        <v>1422</v>
+        <v>1420</v>
       </c>
       <c r="C663" t="s" s="2">
-        <v>1423</v>
+        <v>1421</v>
       </c>
       <c r="D663" s="2"/>
     </row>
@@ -15235,10 +15214,10 @@
         <v>95</v>
       </c>
       <c r="B664" t="s" s="2">
-        <v>1424</v>
+        <v>1422</v>
       </c>
       <c r="C664" t="s" s="2">
-        <v>1425</v>
+        <v>1423</v>
       </c>
       <c r="D664" s="2"/>
     </row>
@@ -15247,10 +15226,10 @@
         <v>95</v>
       </c>
       <c r="B665" t="s" s="2">
-        <v>1426</v>
+        <v>1424</v>
       </c>
       <c r="C665" t="s" s="2">
-        <v>1427</v>
+        <v>1425</v>
       </c>
       <c r="D665" s="2"/>
     </row>
@@ -15259,10 +15238,10 @@
         <v>95</v>
       </c>
       <c r="B666" t="s" s="2">
-        <v>1428</v>
+        <v>1426</v>
       </c>
       <c r="C666" t="s" s="2">
-        <v>1429</v>
+        <v>1427</v>
       </c>
       <c r="D666" s="2"/>
     </row>
@@ -15271,10 +15250,10 @@
         <v>95</v>
       </c>
       <c r="B667" t="s" s="2">
-        <v>1430</v>
+        <v>1428</v>
       </c>
       <c r="C667" t="s" s="2">
-        <v>1431</v>
+        <v>1429</v>
       </c>
       <c r="D667" s="2"/>
     </row>
@@ -15283,10 +15262,10 @@
         <v>95</v>
       </c>
       <c r="B668" t="s" s="2">
-        <v>1432</v>
+        <v>1430</v>
       </c>
       <c r="C668" t="s" s="2">
-        <v>1433</v>
+        <v>1431</v>
       </c>
       <c r="D668" s="2"/>
     </row>
@@ -15295,10 +15274,10 @@
         <v>95</v>
       </c>
       <c r="B669" t="s" s="2">
-        <v>1434</v>
+        <v>1432</v>
       </c>
       <c r="C669" t="s" s="2">
-        <v>1435</v>
+        <v>1433</v>
       </c>
       <c r="D669" s="2"/>
     </row>
@@ -15307,10 +15286,10 @@
         <v>95</v>
       </c>
       <c r="B670" t="s" s="2">
-        <v>1436</v>
+        <v>1434</v>
       </c>
       <c r="C670" t="s" s="2">
-        <v>1437</v>
+        <v>1435</v>
       </c>
       <c r="D670" s="2"/>
     </row>
@@ -15319,10 +15298,10 @@
         <v>95</v>
       </c>
       <c r="B671" t="s" s="2">
-        <v>1438</v>
+        <v>1436</v>
       </c>
       <c r="C671" t="s" s="2">
-        <v>1439</v>
+        <v>1437</v>
       </c>
       <c r="D671" s="2"/>
     </row>
@@ -15331,10 +15310,10 @@
         <v>95</v>
       </c>
       <c r="B672" t="s" s="2">
-        <v>1440</v>
+        <v>1438</v>
       </c>
       <c r="C672" t="s" s="2">
-        <v>1441</v>
+        <v>1439</v>
       </c>
       <c r="D672" s="2"/>
     </row>
@@ -15343,10 +15322,10 @@
         <v>95</v>
       </c>
       <c r="B673" t="s" s="2">
-        <v>1442</v>
+        <v>1440</v>
       </c>
       <c r="C673" t="s" s="2">
-        <v>1443</v>
+        <v>1441</v>
       </c>
       <c r="D673" s="2"/>
     </row>
@@ -15355,10 +15334,10 @@
         <v>95</v>
       </c>
       <c r="B674" t="s" s="2">
-        <v>1444</v>
+        <v>1442</v>
       </c>
       <c r="C674" t="s" s="2">
-        <v>1445</v>
+        <v>1443</v>
       </c>
       <c r="D674" s="2"/>
     </row>
@@ -15367,10 +15346,10 @@
         <v>95</v>
       </c>
       <c r="B675" t="s" s="2">
-        <v>1446</v>
+        <v>1444</v>
       </c>
       <c r="C675" t="s" s="2">
-        <v>1447</v>
+        <v>1445</v>
       </c>
       <c r="D675" s="2"/>
     </row>
@@ -15379,10 +15358,10 @@
         <v>95</v>
       </c>
       <c r="B676" t="s" s="2">
-        <v>1448</v>
+        <v>1446</v>
       </c>
       <c r="C676" t="s" s="2">
-        <v>1449</v>
+        <v>1447</v>
       </c>
       <c r="D676" s="2"/>
     </row>
@@ -15391,10 +15370,10 @@
         <v>95</v>
       </c>
       <c r="B677" t="s" s="2">
-        <v>1450</v>
+        <v>1448</v>
       </c>
       <c r="C677" t="s" s="2">
-        <v>1451</v>
+        <v>1449</v>
       </c>
       <c r="D677" s="2"/>
     </row>
@@ -15403,10 +15382,10 @@
         <v>95</v>
       </c>
       <c r="B678" t="s" s="2">
-        <v>1452</v>
+        <v>1450</v>
       </c>
       <c r="C678" t="s" s="2">
-        <v>1453</v>
+        <v>1451</v>
       </c>
       <c r="D678" s="2"/>
     </row>
@@ -15415,10 +15394,10 @@
         <v>95</v>
       </c>
       <c r="B679" t="s" s="2">
-        <v>1454</v>
+        <v>1452</v>
       </c>
       <c r="C679" t="s" s="2">
-        <v>1455</v>
+        <v>1453</v>
       </c>
       <c r="D679" s="2"/>
     </row>
@@ -15427,10 +15406,10 @@
         <v>95</v>
       </c>
       <c r="B680" t="s" s="2">
-        <v>1456</v>
+        <v>1454</v>
       </c>
       <c r="C680" t="s" s="2">
-        <v>1457</v>
+        <v>1455</v>
       </c>
       <c r="D680" s="2"/>
     </row>
@@ -15439,10 +15418,10 @@
         <v>95</v>
       </c>
       <c r="B681" t="s" s="2">
-        <v>1458</v>
+        <v>1456</v>
       </c>
       <c r="C681" t="s" s="2">
-        <v>1459</v>
+        <v>1457</v>
       </c>
       <c r="D681" s="2"/>
     </row>
@@ -15451,10 +15430,10 @@
         <v>95</v>
       </c>
       <c r="B682" t="s" s="2">
-        <v>1460</v>
+        <v>1458</v>
       </c>
       <c r="C682" t="s" s="2">
-        <v>1461</v>
+        <v>1459</v>
       </c>
       <c r="D682" s="2"/>
     </row>
@@ -15463,10 +15442,10 @@
         <v>95</v>
       </c>
       <c r="B683" t="s" s="2">
-        <v>1462</v>
+        <v>1460</v>
       </c>
       <c r="C683" t="s" s="2">
-        <v>1463</v>
+        <v>1461</v>
       </c>
       <c r="D683" s="2"/>
     </row>
@@ -15475,10 +15454,10 @@
         <v>95</v>
       </c>
       <c r="B684" t="s" s="2">
-        <v>1464</v>
+        <v>1462</v>
       </c>
       <c r="C684" t="s" s="2">
-        <v>1465</v>
+        <v>1463</v>
       </c>
       <c r="D684" s="2"/>
     </row>
@@ -15487,10 +15466,10 @@
         <v>95</v>
       </c>
       <c r="B685" t="s" s="2">
-        <v>1466</v>
+        <v>1464</v>
       </c>
       <c r="C685" t="s" s="2">
-        <v>1467</v>
+        <v>1465</v>
       </c>
       <c r="D685" s="2"/>
     </row>
@@ -15499,10 +15478,10 @@
         <v>95</v>
       </c>
       <c r="B686" t="s" s="2">
-        <v>1468</v>
+        <v>1466</v>
       </c>
       <c r="C686" t="s" s="2">
-        <v>1469</v>
+        <v>1467</v>
       </c>
       <c r="D686" s="2"/>
     </row>
@@ -15511,10 +15490,10 @@
         <v>95</v>
       </c>
       <c r="B687" t="s" s="2">
-        <v>1470</v>
+        <v>1468</v>
       </c>
       <c r="C687" t="s" s="2">
-        <v>1471</v>
+        <v>1469</v>
       </c>
       <c r="D687" s="2"/>
     </row>
@@ -15523,10 +15502,10 @@
         <v>95</v>
       </c>
       <c r="B688" t="s" s="2">
-        <v>1472</v>
+        <v>1470</v>
       </c>
       <c r="C688" t="s" s="2">
-        <v>1473</v>
+        <v>1471</v>
       </c>
       <c r="D688" s="2"/>
     </row>
@@ -15535,10 +15514,10 @@
         <v>95</v>
       </c>
       <c r="B689" t="s" s="2">
-        <v>38</v>
+        <v>1472</v>
       </c>
       <c r="C689" t="s" s="2">
-        <v>1474</v>
+        <v>1473</v>
       </c>
       <c r="D689" s="2"/>
     </row>
@@ -15547,10 +15526,10 @@
         <v>95</v>
       </c>
       <c r="B690" t="s" s="2">
+        <v>1474</v>
+      </c>
+      <c r="C690" t="s" s="2">
         <v>1475</v>
-      </c>
-      <c r="C690" t="s" s="2">
-        <v>1476</v>
       </c>
       <c r="D690" s="2"/>
     </row>
@@ -15559,10 +15538,10 @@
         <v>95</v>
       </c>
       <c r="B691" t="s" s="2">
+        <v>1476</v>
+      </c>
+      <c r="C691" t="s" s="2">
         <v>1477</v>
-      </c>
-      <c r="C691" t="s" s="2">
-        <v>1478</v>
       </c>
       <c r="D691" s="2"/>
     </row>
@@ -15571,10 +15550,10 @@
         <v>95</v>
       </c>
       <c r="B692" t="s" s="2">
+        <v>1478</v>
+      </c>
+      <c r="C692" t="s" s="2">
         <v>1479</v>
-      </c>
-      <c r="C692" t="s" s="2">
-        <v>1480</v>
       </c>
       <c r="D692" s="2"/>
     </row>
@@ -15583,10 +15562,10 @@
         <v>95</v>
       </c>
       <c r="B693" t="s" s="2">
+        <v>1480</v>
+      </c>
+      <c r="C693" t="s" s="2">
         <v>1481</v>
-      </c>
-      <c r="C693" t="s" s="2">
-        <v>1482</v>
       </c>
       <c r="D693" s="2"/>
     </row>
@@ -15595,10 +15574,10 @@
         <v>95</v>
       </c>
       <c r="B694" t="s" s="2">
+        <v>1482</v>
+      </c>
+      <c r="C694" t="s" s="2">
         <v>1483</v>
-      </c>
-      <c r="C694" t="s" s="2">
-        <v>1484</v>
       </c>
       <c r="D694" s="2"/>
     </row>
@@ -15607,10 +15586,10 @@
         <v>95</v>
       </c>
       <c r="B695" t="s" s="2">
+        <v>1484</v>
+      </c>
+      <c r="C695" t="s" s="2">
         <v>1485</v>
-      </c>
-      <c r="C695" t="s" s="2">
-        <v>1486</v>
       </c>
       <c r="D695" s="2"/>
     </row>
@@ -15619,10 +15598,10 @@
         <v>95</v>
       </c>
       <c r="B696" t="s" s="2">
+        <v>1486</v>
+      </c>
+      <c r="C696" t="s" s="2">
         <v>1487</v>
-      </c>
-      <c r="C696" t="s" s="2">
-        <v>1488</v>
       </c>
       <c r="D696" s="2"/>
     </row>
@@ -15631,10 +15610,10 @@
         <v>95</v>
       </c>
       <c r="B697" t="s" s="2">
+        <v>1488</v>
+      </c>
+      <c r="C697" t="s" s="2">
         <v>1489</v>
-      </c>
-      <c r="C697" t="s" s="2">
-        <v>1490</v>
       </c>
       <c r="D697" s="2"/>
     </row>
@@ -15643,10 +15622,10 @@
         <v>95</v>
       </c>
       <c r="B698" t="s" s="2">
+        <v>1490</v>
+      </c>
+      <c r="C698" t="s" s="2">
         <v>1491</v>
-      </c>
-      <c r="C698" t="s" s="2">
-        <v>1492</v>
       </c>
       <c r="D698" s="2"/>
     </row>
@@ -15655,10 +15634,10 @@
         <v>95</v>
       </c>
       <c r="B699" t="s" s="2">
+        <v>1492</v>
+      </c>
+      <c r="C699" t="s" s="2">
         <v>1493</v>
-      </c>
-      <c r="C699" t="s" s="2">
-        <v>1494</v>
       </c>
       <c r="D699" s="2"/>
     </row>
@@ -15667,10 +15646,10 @@
         <v>95</v>
       </c>
       <c r="B700" t="s" s="2">
+        <v>1494</v>
+      </c>
+      <c r="C700" t="s" s="2">
         <v>1495</v>
-      </c>
-      <c r="C700" t="s" s="2">
-        <v>1496</v>
       </c>
       <c r="D700" s="2"/>
     </row>
@@ -15679,10 +15658,10 @@
         <v>95</v>
       </c>
       <c r="B701" t="s" s="2">
+        <v>1496</v>
+      </c>
+      <c r="C701" t="s" s="2">
         <v>1497</v>
-      </c>
-      <c r="C701" t="s" s="2">
-        <v>1498</v>
       </c>
       <c r="D701" s="2"/>
     </row>
@@ -15691,10 +15670,10 @@
         <v>95</v>
       </c>
       <c r="B702" t="s" s="2">
+        <v>1498</v>
+      </c>
+      <c r="C702" t="s" s="2">
         <v>1499</v>
-      </c>
-      <c r="C702" t="s" s="2">
-        <v>1500</v>
       </c>
       <c r="D702" s="2"/>
     </row>
@@ -15703,10 +15682,10 @@
         <v>95</v>
       </c>
       <c r="B703" t="s" s="2">
+        <v>1500</v>
+      </c>
+      <c r="C703" t="s" s="2">
         <v>1501</v>
-      </c>
-      <c r="C703" t="s" s="2">
-        <v>1502</v>
       </c>
       <c r="D703" s="2"/>
     </row>
@@ -15715,10 +15694,10 @@
         <v>95</v>
       </c>
       <c r="B704" t="s" s="2">
+        <v>1502</v>
+      </c>
+      <c r="C704" t="s" s="2">
         <v>1503</v>
-      </c>
-      <c r="C704" t="s" s="2">
-        <v>1504</v>
       </c>
       <c r="D704" s="2"/>
     </row>
@@ -15727,10 +15706,10 @@
         <v>95</v>
       </c>
       <c r="B705" t="s" s="2">
+        <v>1504</v>
+      </c>
+      <c r="C705" t="s" s="2">
         <v>1505</v>
-      </c>
-      <c r="C705" t="s" s="2">
-        <v>1506</v>
       </c>
       <c r="D705" s="2"/>
     </row>
@@ -15739,10 +15718,10 @@
         <v>95</v>
       </c>
       <c r="B706" t="s" s="2">
+        <v>1506</v>
+      </c>
+      <c r="C706" t="s" s="2">
         <v>1507</v>
-      </c>
-      <c r="C706" t="s" s="2">
-        <v>1508</v>
       </c>
       <c r="D706" s="2"/>
     </row>
@@ -15751,10 +15730,10 @@
         <v>95</v>
       </c>
       <c r="B707" t="s" s="2">
+        <v>1508</v>
+      </c>
+      <c r="C707" t="s" s="2">
         <v>1509</v>
-      </c>
-      <c r="C707" t="s" s="2">
-        <v>1510</v>
       </c>
       <c r="D707" s="2"/>
     </row>
@@ -15763,10 +15742,10 @@
         <v>95</v>
       </c>
       <c r="B708" t="s" s="2">
+        <v>1510</v>
+      </c>
+      <c r="C708" t="s" s="2">
         <v>1511</v>
-      </c>
-      <c r="C708" t="s" s="2">
-        <v>1512</v>
       </c>
       <c r="D708" s="2"/>
     </row>
@@ -15775,10 +15754,10 @@
         <v>95</v>
       </c>
       <c r="B709" t="s" s="2">
+        <v>1512</v>
+      </c>
+      <c r="C709" t="s" s="2">
         <v>1513</v>
-      </c>
-      <c r="C709" t="s" s="2">
-        <v>1514</v>
       </c>
       <c r="D709" s="2"/>
     </row>
@@ -15787,10 +15766,10 @@
         <v>95</v>
       </c>
       <c r="B710" t="s" s="2">
+        <v>1514</v>
+      </c>
+      <c r="C710" t="s" s="2">
         <v>1515</v>
-      </c>
-      <c r="C710" t="s" s="2">
-        <v>1516</v>
       </c>
       <c r="D710" s="2"/>
     </row>
@@ -15799,10 +15778,10 @@
         <v>95</v>
       </c>
       <c r="B711" t="s" s="2">
+        <v>1516</v>
+      </c>
+      <c r="C711" t="s" s="2">
         <v>1517</v>
-      </c>
-      <c r="C711" t="s" s="2">
-        <v>1518</v>
       </c>
       <c r="D711" s="2"/>
     </row>
@@ -15811,10 +15790,10 @@
         <v>95</v>
       </c>
       <c r="B712" t="s" s="2">
+        <v>1518</v>
+      </c>
+      <c r="C712" t="s" s="2">
         <v>1519</v>
-      </c>
-      <c r="C712" t="s" s="2">
-        <v>1520</v>
       </c>
       <c r="D712" s="2"/>
     </row>
@@ -15823,10 +15802,10 @@
         <v>95</v>
       </c>
       <c r="B713" t="s" s="2">
+        <v>1520</v>
+      </c>
+      <c r="C713" t="s" s="2">
         <v>1521</v>
-      </c>
-      <c r="C713" t="s" s="2">
-        <v>1522</v>
       </c>
       <c r="D713" s="2"/>
     </row>
@@ -15835,10 +15814,10 @@
         <v>95</v>
       </c>
       <c r="B714" t="s" s="2">
+        <v>1522</v>
+      </c>
+      <c r="C714" t="s" s="2">
         <v>1523</v>
-      </c>
-      <c r="C714" t="s" s="2">
-        <v>1524</v>
       </c>
       <c r="D714" s="2"/>
     </row>
@@ -15847,10 +15826,10 @@
         <v>95</v>
       </c>
       <c r="B715" t="s" s="2">
+        <v>1524</v>
+      </c>
+      <c r="C715" t="s" s="2">
         <v>1525</v>
-      </c>
-      <c r="C715" t="s" s="2">
-        <v>1526</v>
       </c>
       <c r="D715" s="2"/>
     </row>
@@ -15859,10 +15838,10 @@
         <v>95</v>
       </c>
       <c r="B716" t="s" s="2">
+        <v>1526</v>
+      </c>
+      <c r="C716" t="s" s="2">
         <v>1527</v>
-      </c>
-      <c r="C716" t="s" s="2">
-        <v>1528</v>
       </c>
       <c r="D716" s="2"/>
     </row>
@@ -15871,10 +15850,10 @@
         <v>95</v>
       </c>
       <c r="B717" t="s" s="2">
+        <v>1528</v>
+      </c>
+      <c r="C717" t="s" s="2">
         <v>1529</v>
-      </c>
-      <c r="C717" t="s" s="2">
-        <v>1530</v>
       </c>
       <c r="D717" s="2"/>
     </row>
@@ -15883,10 +15862,10 @@
         <v>95</v>
       </c>
       <c r="B718" t="s" s="2">
+        <v>1530</v>
+      </c>
+      <c r="C718" t="s" s="2">
         <v>1531</v>
-      </c>
-      <c r="C718" t="s" s="2">
-        <v>1532</v>
       </c>
       <c r="D718" s="2"/>
     </row>
@@ -15895,10 +15874,10 @@
         <v>95</v>
       </c>
       <c r="B719" t="s" s="2">
+        <v>1532</v>
+      </c>
+      <c r="C719" t="s" s="2">
         <v>1533</v>
-      </c>
-      <c r="C719" t="s" s="2">
-        <v>1534</v>
       </c>
       <c r="D719" s="2"/>
     </row>
@@ -15907,10 +15886,10 @@
         <v>95</v>
       </c>
       <c r="B720" t="s" s="2">
+        <v>1534</v>
+      </c>
+      <c r="C720" t="s" s="2">
         <v>1535</v>
-      </c>
-      <c r="C720" t="s" s="2">
-        <v>1536</v>
       </c>
       <c r="D720" s="2"/>
     </row>
@@ -15919,10 +15898,10 @@
         <v>95</v>
       </c>
       <c r="B721" t="s" s="2">
+        <v>1536</v>
+      </c>
+      <c r="C721" t="s" s="2">
         <v>1537</v>
-      </c>
-      <c r="C721" t="s" s="2">
-        <v>1538</v>
       </c>
       <c r="D721" s="2"/>
     </row>
@@ -15931,10 +15910,10 @@
         <v>95</v>
       </c>
       <c r="B722" t="s" s="2">
+        <v>1538</v>
+      </c>
+      <c r="C722" t="s" s="2">
         <v>1539</v>
-      </c>
-      <c r="C722" t="s" s="2">
-        <v>1540</v>
       </c>
       <c r="D722" s="2"/>
     </row>
@@ -15943,10 +15922,10 @@
         <v>95</v>
       </c>
       <c r="B723" t="s" s="2">
+        <v>1540</v>
+      </c>
+      <c r="C723" t="s" s="2">
         <v>1541</v>
-      </c>
-      <c r="C723" t="s" s="2">
-        <v>1542</v>
       </c>
       <c r="D723" s="2"/>
     </row>
@@ -15955,10 +15934,10 @@
         <v>95</v>
       </c>
       <c r="B724" t="s" s="2">
+        <v>1542</v>
+      </c>
+      <c r="C724" t="s" s="2">
         <v>1543</v>
-      </c>
-      <c r="C724" t="s" s="2">
-        <v>1544</v>
       </c>
       <c r="D724" s="2"/>
     </row>
@@ -15967,10 +15946,10 @@
         <v>95</v>
       </c>
       <c r="B725" t="s" s="2">
+        <v>1544</v>
+      </c>
+      <c r="C725" t="s" s="2">
         <v>1545</v>
-      </c>
-      <c r="C725" t="s" s="2">
-        <v>1546</v>
       </c>
       <c r="D725" s="2"/>
     </row>
@@ -15979,10 +15958,10 @@
         <v>95</v>
       </c>
       <c r="B726" t="s" s="2">
+        <v>1546</v>
+      </c>
+      <c r="C726" t="s" s="2">
         <v>1547</v>
-      </c>
-      <c r="C726" t="s" s="2">
-        <v>1548</v>
       </c>
       <c r="D726" s="2"/>
     </row>
@@ -15991,10 +15970,10 @@
         <v>95</v>
       </c>
       <c r="B727" t="s" s="2">
+        <v>1548</v>
+      </c>
+      <c r="C727" t="s" s="2">
         <v>1549</v>
-      </c>
-      <c r="C727" t="s" s="2">
-        <v>1550</v>
       </c>
       <c r="D727" s="2"/>
     </row>
@@ -16003,10 +15982,10 @@
         <v>95</v>
       </c>
       <c r="B728" t="s" s="2">
+        <v>1550</v>
+      </c>
+      <c r="C728" t="s" s="2">
         <v>1551</v>
-      </c>
-      <c r="C728" t="s" s="2">
-        <v>1552</v>
       </c>
       <c r="D728" s="2"/>
     </row>
@@ -16015,10 +15994,10 @@
         <v>95</v>
       </c>
       <c r="B729" t="s" s="2">
+        <v>1552</v>
+      </c>
+      <c r="C729" t="s" s="2">
         <v>1553</v>
-      </c>
-      <c r="C729" t="s" s="2">
-        <v>1554</v>
       </c>
       <c r="D729" s="2"/>
     </row>
@@ -16027,10 +16006,10 @@
         <v>95</v>
       </c>
       <c r="B730" t="s" s="2">
+        <v>1554</v>
+      </c>
+      <c r="C730" t="s" s="2">
         <v>1555</v>
-      </c>
-      <c r="C730" t="s" s="2">
-        <v>1556</v>
       </c>
       <c r="D730" s="2"/>
     </row>
@@ -16039,10 +16018,10 @@
         <v>95</v>
       </c>
       <c r="B731" t="s" s="2">
+        <v>1556</v>
+      </c>
+      <c r="C731" t="s" s="2">
         <v>1557</v>
-      </c>
-      <c r="C731" t="s" s="2">
-        <v>1558</v>
       </c>
       <c r="D731" s="2"/>
     </row>
@@ -16051,10 +16030,10 @@
         <v>95</v>
       </c>
       <c r="B732" t="s" s="2">
+        <v>1558</v>
+      </c>
+      <c r="C732" t="s" s="2">
         <v>1559</v>
-      </c>
-      <c r="C732" t="s" s="2">
-        <v>1560</v>
       </c>
       <c r="D732" s="2"/>
     </row>
@@ -16063,10 +16042,10 @@
         <v>95</v>
       </c>
       <c r="B733" t="s" s="2">
+        <v>1560</v>
+      </c>
+      <c r="C733" t="s" s="2">
         <v>1561</v>
-      </c>
-      <c r="C733" t="s" s="2">
-        <v>1562</v>
       </c>
       <c r="D733" s="2"/>
     </row>
@@ -16075,10 +16054,10 @@
         <v>95</v>
       </c>
       <c r="B734" t="s" s="2">
+        <v>1562</v>
+      </c>
+      <c r="C734" t="s" s="2">
         <v>1563</v>
-      </c>
-      <c r="C734" t="s" s="2">
-        <v>1564</v>
       </c>
       <c r="D734" s="2"/>
     </row>
@@ -16087,10 +16066,10 @@
         <v>95</v>
       </c>
       <c r="B735" t="s" s="2">
+        <v>1564</v>
+      </c>
+      <c r="C735" t="s" s="2">
         <v>1565</v>
-      </c>
-      <c r="C735" t="s" s="2">
-        <v>1566</v>
       </c>
       <c r="D735" s="2"/>
     </row>
@@ -16099,10 +16078,10 @@
         <v>95</v>
       </c>
       <c r="B736" t="s" s="2">
+        <v>1566</v>
+      </c>
+      <c r="C736" t="s" s="2">
         <v>1567</v>
-      </c>
-      <c r="C736" t="s" s="2">
-        <v>1568</v>
       </c>
       <c r="D736" s="2"/>
     </row>
@@ -16111,10 +16090,10 @@
         <v>95</v>
       </c>
       <c r="B737" t="s" s="2">
+        <v>1568</v>
+      </c>
+      <c r="C737" t="s" s="2">
         <v>1569</v>
-      </c>
-      <c r="C737" t="s" s="2">
-        <v>1570</v>
       </c>
       <c r="D737" s="2"/>
     </row>
@@ -16123,10 +16102,10 @@
         <v>95</v>
       </c>
       <c r="B738" t="s" s="2">
+        <v>1570</v>
+      </c>
+      <c r="C738" t="s" s="2">
         <v>1571</v>
-      </c>
-      <c r="C738" t="s" s="2">
-        <v>1572</v>
       </c>
       <c r="D738" s="2"/>
     </row>
@@ -16135,10 +16114,10 @@
         <v>95</v>
       </c>
       <c r="B739" t="s" s="2">
+        <v>1572</v>
+      </c>
+      <c r="C739" t="s" s="2">
         <v>1573</v>
-      </c>
-      <c r="C739" t="s" s="2">
-        <v>1574</v>
       </c>
       <c r="D739" s="2"/>
     </row>
@@ -16147,10 +16126,10 @@
         <v>95</v>
       </c>
       <c r="B740" t="s" s="2">
+        <v>1574</v>
+      </c>
+      <c r="C740" t="s" s="2">
         <v>1575</v>
-      </c>
-      <c r="C740" t="s" s="2">
-        <v>1576</v>
       </c>
       <c r="D740" s="2"/>
     </row>
@@ -16159,10 +16138,10 @@
         <v>95</v>
       </c>
       <c r="B741" t="s" s="2">
+        <v>1576</v>
+      </c>
+      <c r="C741" t="s" s="2">
         <v>1577</v>
-      </c>
-      <c r="C741" t="s" s="2">
-        <v>1578</v>
       </c>
       <c r="D741" s="2"/>
     </row>
@@ -16171,10 +16150,10 @@
         <v>95</v>
       </c>
       <c r="B742" t="s" s="2">
+        <v>1578</v>
+      </c>
+      <c r="C742" t="s" s="2">
         <v>1579</v>
-      </c>
-      <c r="C742" t="s" s="2">
-        <v>1580</v>
       </c>
       <c r="D742" s="2"/>
     </row>
@@ -16183,10 +16162,10 @@
         <v>95</v>
       </c>
       <c r="B743" t="s" s="2">
+        <v>1580</v>
+      </c>
+      <c r="C743" t="s" s="2">
         <v>1581</v>
-      </c>
-      <c r="C743" t="s" s="2">
-        <v>1582</v>
       </c>
       <c r="D743" s="2"/>
     </row>
@@ -16195,10 +16174,10 @@
         <v>95</v>
       </c>
       <c r="B744" t="s" s="2">
+        <v>1582</v>
+      </c>
+      <c r="C744" t="s" s="2">
         <v>1583</v>
-      </c>
-      <c r="C744" t="s" s="2">
-        <v>1584</v>
       </c>
       <c r="D744" s="2"/>
     </row>
@@ -16207,10 +16186,10 @@
         <v>95</v>
       </c>
       <c r="B745" t="s" s="2">
+        <v>1584</v>
+      </c>
+      <c r="C745" t="s" s="2">
         <v>1585</v>
-      </c>
-      <c r="C745" t="s" s="2">
-        <v>1586</v>
       </c>
       <c r="D745" s="2"/>
     </row>
@@ -16219,10 +16198,10 @@
         <v>95</v>
       </c>
       <c r="B746" t="s" s="2">
+        <v>1586</v>
+      </c>
+      <c r="C746" t="s" s="2">
         <v>1587</v>
-      </c>
-      <c r="C746" t="s" s="2">
-        <v>1588</v>
       </c>
       <c r="D746" s="2"/>
     </row>
@@ -16231,10 +16210,10 @@
         <v>95</v>
       </c>
       <c r="B747" t="s" s="2">
+        <v>1588</v>
+      </c>
+      <c r="C747" t="s" s="2">
         <v>1589</v>
-      </c>
-      <c r="C747" t="s" s="2">
-        <v>1590</v>
       </c>
       <c r="D747" s="2"/>
     </row>
@@ -16243,10 +16222,10 @@
         <v>95</v>
       </c>
       <c r="B748" t="s" s="2">
+        <v>1590</v>
+      </c>
+      <c r="C748" t="s" s="2">
         <v>1591</v>
-      </c>
-      <c r="C748" t="s" s="2">
-        <v>1592</v>
       </c>
       <c r="D748" s="2"/>
     </row>
@@ -16255,10 +16234,10 @@
         <v>95</v>
       </c>
       <c r="B749" t="s" s="2">
+        <v>1592</v>
+      </c>
+      <c r="C749" t="s" s="2">
         <v>1593</v>
-      </c>
-      <c r="C749" t="s" s="2">
-        <v>1594</v>
       </c>
       <c r="D749" s="2"/>
     </row>
@@ -16267,10 +16246,10 @@
         <v>95</v>
       </c>
       <c r="B750" t="s" s="2">
+        <v>1594</v>
+      </c>
+      <c r="C750" t="s" s="2">
         <v>1595</v>
-      </c>
-      <c r="C750" t="s" s="2">
-        <v>1596</v>
       </c>
       <c r="D750" s="2"/>
     </row>
@@ -16279,10 +16258,10 @@
         <v>95</v>
       </c>
       <c r="B751" t="s" s="2">
+        <v>1596</v>
+      </c>
+      <c r="C751" t="s" s="2">
         <v>1597</v>
-      </c>
-      <c r="C751" t="s" s="2">
-        <v>1598</v>
       </c>
       <c r="D751" s="2"/>
     </row>
@@ -16291,10 +16270,10 @@
         <v>95</v>
       </c>
       <c r="B752" t="s" s="2">
+        <v>1598</v>
+      </c>
+      <c r="C752" t="s" s="2">
         <v>1599</v>
-      </c>
-      <c r="C752" t="s" s="2">
-        <v>1600</v>
       </c>
       <c r="D752" s="2"/>
     </row>
@@ -16303,10 +16282,10 @@
         <v>95</v>
       </c>
       <c r="B753" t="s" s="2">
+        <v>1600</v>
+      </c>
+      <c r="C753" t="s" s="2">
         <v>1601</v>
-      </c>
-      <c r="C753" t="s" s="2">
-        <v>1602</v>
       </c>
       <c r="D753" s="2"/>
     </row>
@@ -16315,10 +16294,10 @@
         <v>95</v>
       </c>
       <c r="B754" t="s" s="2">
+        <v>1602</v>
+      </c>
+      <c r="C754" t="s" s="2">
         <v>1603</v>
-      </c>
-      <c r="C754" t="s" s="2">
-        <v>1604</v>
       </c>
       <c r="D754" s="2"/>
     </row>
@@ -16327,10 +16306,10 @@
         <v>95</v>
       </c>
       <c r="B755" t="s" s="2">
+        <v>1604</v>
+      </c>
+      <c r="C755" t="s" s="2">
         <v>1605</v>
-      </c>
-      <c r="C755" t="s" s="2">
-        <v>1606</v>
       </c>
       <c r="D755" s="2"/>
     </row>
@@ -16339,10 +16318,10 @@
         <v>95</v>
       </c>
       <c r="B756" t="s" s="2">
+        <v>1606</v>
+      </c>
+      <c r="C756" t="s" s="2">
         <v>1607</v>
-      </c>
-      <c r="C756" t="s" s="2">
-        <v>1608</v>
       </c>
       <c r="D756" s="2"/>
     </row>
@@ -16351,10 +16330,10 @@
         <v>95</v>
       </c>
       <c r="B757" t="s" s="2">
+        <v>1608</v>
+      </c>
+      <c r="C757" t="s" s="2">
         <v>1609</v>
-      </c>
-      <c r="C757" t="s" s="2">
-        <v>1610</v>
       </c>
       <c r="D757" s="2"/>
     </row>
@@ -16363,10 +16342,10 @@
         <v>95</v>
       </c>
       <c r="B758" t="s" s="2">
+        <v>1610</v>
+      </c>
+      <c r="C758" t="s" s="2">
         <v>1611</v>
-      </c>
-      <c r="C758" t="s" s="2">
-        <v>1612</v>
       </c>
       <c r="D758" s="2"/>
     </row>
@@ -16375,10 +16354,10 @@
         <v>95</v>
       </c>
       <c r="B759" t="s" s="2">
+        <v>1612</v>
+      </c>
+      <c r="C759" t="s" s="2">
         <v>1613</v>
-      </c>
-      <c r="C759" t="s" s="2">
-        <v>1614</v>
       </c>
       <c r="D759" s="2"/>
     </row>
@@ -16387,10 +16366,10 @@
         <v>95</v>
       </c>
       <c r="B760" t="s" s="2">
+        <v>1614</v>
+      </c>
+      <c r="C760" t="s" s="2">
         <v>1615</v>
-      </c>
-      <c r="C760" t="s" s="2">
-        <v>1616</v>
       </c>
       <c r="D760" s="2"/>
     </row>
@@ -16399,10 +16378,10 @@
         <v>95</v>
       </c>
       <c r="B761" t="s" s="2">
+        <v>1616</v>
+      </c>
+      <c r="C761" t="s" s="2">
         <v>1617</v>
-      </c>
-      <c r="C761" t="s" s="2">
-        <v>1618</v>
       </c>
       <c r="D761" s="2"/>
     </row>
@@ -16411,10 +16390,10 @@
         <v>95</v>
       </c>
       <c r="B762" t="s" s="2">
+        <v>1618</v>
+      </c>
+      <c r="C762" t="s" s="2">
         <v>1619</v>
-      </c>
-      <c r="C762" t="s" s="2">
-        <v>1620</v>
       </c>
       <c r="D762" s="2"/>
     </row>
@@ -16423,10 +16402,10 @@
         <v>95</v>
       </c>
       <c r="B763" t="s" s="2">
+        <v>1620</v>
+      </c>
+      <c r="C763" t="s" s="2">
         <v>1621</v>
-      </c>
-      <c r="C763" t="s" s="2">
-        <v>1622</v>
       </c>
       <c r="D763" s="2"/>
     </row>
@@ -16435,10 +16414,10 @@
         <v>95</v>
       </c>
       <c r="B764" t="s" s="2">
+        <v>1622</v>
+      </c>
+      <c r="C764" t="s" s="2">
         <v>1623</v>
-      </c>
-      <c r="C764" t="s" s="2">
-        <v>1624</v>
       </c>
       <c r="D764" s="2"/>
     </row>
@@ -16447,10 +16426,10 @@
         <v>95</v>
       </c>
       <c r="B765" t="s" s="2">
+        <v>1624</v>
+      </c>
+      <c r="C765" t="s" s="2">
         <v>1625</v>
-      </c>
-      <c r="C765" t="s" s="2">
-        <v>1626</v>
       </c>
       <c r="D765" s="2"/>
     </row>
@@ -16459,10 +16438,10 @@
         <v>95</v>
       </c>
       <c r="B766" t="s" s="2">
+        <v>1626</v>
+      </c>
+      <c r="C766" t="s" s="2">
         <v>1627</v>
-      </c>
-      <c r="C766" t="s" s="2">
-        <v>1628</v>
       </c>
       <c r="D766" s="2"/>
     </row>
@@ -16471,10 +16450,10 @@
         <v>95</v>
       </c>
       <c r="B767" t="s" s="2">
+        <v>1628</v>
+      </c>
+      <c r="C767" t="s" s="2">
         <v>1629</v>
-      </c>
-      <c r="C767" t="s" s="2">
-        <v>1630</v>
       </c>
       <c r="D767" s="2"/>
     </row>
@@ -16483,10 +16462,10 @@
         <v>95</v>
       </c>
       <c r="B768" t="s" s="2">
+        <v>1630</v>
+      </c>
+      <c r="C768" t="s" s="2">
         <v>1631</v>
-      </c>
-      <c r="C768" t="s" s="2">
-        <v>1632</v>
       </c>
       <c r="D768" s="2"/>
     </row>
@@ -16495,10 +16474,10 @@
         <v>95</v>
       </c>
       <c r="B769" t="s" s="2">
+        <v>1632</v>
+      </c>
+      <c r="C769" t="s" s="2">
         <v>1633</v>
-      </c>
-      <c r="C769" t="s" s="2">
-        <v>1634</v>
       </c>
       <c r="D769" s="2"/>
     </row>
@@ -16507,10 +16486,10 @@
         <v>95</v>
       </c>
       <c r="B770" t="s" s="2">
+        <v>1634</v>
+      </c>
+      <c r="C770" t="s" s="2">
         <v>1635</v>
-      </c>
-      <c r="C770" t="s" s="2">
-        <v>1636</v>
       </c>
       <c r="D770" s="2"/>
     </row>
@@ -16519,10 +16498,10 @@
         <v>95</v>
       </c>
       <c r="B771" t="s" s="2">
+        <v>1636</v>
+      </c>
+      <c r="C771" t="s" s="2">
         <v>1637</v>
-      </c>
-      <c r="C771" t="s" s="2">
-        <v>1638</v>
       </c>
       <c r="D771" s="2"/>
     </row>
@@ -16531,10 +16510,10 @@
         <v>95</v>
       </c>
       <c r="B772" t="s" s="2">
+        <v>1638</v>
+      </c>
+      <c r="C772" t="s" s="2">
         <v>1639</v>
-      </c>
-      <c r="C772" t="s" s="2">
-        <v>1640</v>
       </c>
       <c r="D772" s="2"/>
     </row>
@@ -16543,10 +16522,10 @@
         <v>95</v>
       </c>
       <c r="B773" t="s" s="2">
+        <v>1640</v>
+      </c>
+      <c r="C773" t="s" s="2">
         <v>1641</v>
-      </c>
-      <c r="C773" t="s" s="2">
-        <v>1642</v>
       </c>
       <c r="D773" s="2"/>
     </row>
@@ -16555,10 +16534,10 @@
         <v>95</v>
       </c>
       <c r="B774" t="s" s="2">
+        <v>1642</v>
+      </c>
+      <c r="C774" t="s" s="2">
         <v>1643</v>
-      </c>
-      <c r="C774" t="s" s="2">
-        <v>1644</v>
       </c>
       <c r="D774" s="2"/>
     </row>
@@ -16567,10 +16546,10 @@
         <v>95</v>
       </c>
       <c r="B775" t="s" s="2">
+        <v>1644</v>
+      </c>
+      <c r="C775" t="s" s="2">
         <v>1645</v>
-      </c>
-      <c r="C775" t="s" s="2">
-        <v>1646</v>
       </c>
       <c r="D775" s="2"/>
     </row>
@@ -16579,10 +16558,10 @@
         <v>95</v>
       </c>
       <c r="B776" t="s" s="2">
+        <v>1646</v>
+      </c>
+      <c r="C776" t="s" s="2">
         <v>1647</v>
-      </c>
-      <c r="C776" t="s" s="2">
-        <v>1648</v>
       </c>
       <c r="D776" s="2"/>
     </row>
@@ -16591,10 +16570,10 @@
         <v>95</v>
       </c>
       <c r="B777" t="s" s="2">
+        <v>1648</v>
+      </c>
+      <c r="C777" t="s" s="2">
         <v>1649</v>
-      </c>
-      <c r="C777" t="s" s="2">
-        <v>1650</v>
       </c>
       <c r="D777" s="2"/>
     </row>
@@ -16603,10 +16582,10 @@
         <v>95</v>
       </c>
       <c r="B778" t="s" s="2">
+        <v>1650</v>
+      </c>
+      <c r="C778" t="s" s="2">
         <v>1651</v>
-      </c>
-      <c r="C778" t="s" s="2">
-        <v>1652</v>
       </c>
       <c r="D778" s="2"/>
     </row>
@@ -16615,10 +16594,10 @@
         <v>95</v>
       </c>
       <c r="B779" t="s" s="2">
+        <v>1652</v>
+      </c>
+      <c r="C779" t="s" s="2">
         <v>1653</v>
-      </c>
-      <c r="C779" t="s" s="2">
-        <v>1654</v>
       </c>
       <c r="D779" s="2"/>
     </row>
@@ -16627,10 +16606,10 @@
         <v>95</v>
       </c>
       <c r="B780" t="s" s="2">
+        <v>1654</v>
+      </c>
+      <c r="C780" t="s" s="2">
         <v>1655</v>
-      </c>
-      <c r="C780" t="s" s="2">
-        <v>1656</v>
       </c>
       <c r="D780" s="2"/>
     </row>
@@ -16639,10 +16618,10 @@
         <v>95</v>
       </c>
       <c r="B781" t="s" s="2">
+        <v>1656</v>
+      </c>
+      <c r="C781" t="s" s="2">
         <v>1657</v>
-      </c>
-      <c r="C781" t="s" s="2">
-        <v>1658</v>
       </c>
       <c r="D781" s="2"/>
     </row>
@@ -16651,10 +16630,10 @@
         <v>95</v>
       </c>
       <c r="B782" t="s" s="2">
+        <v>1658</v>
+      </c>
+      <c r="C782" t="s" s="2">
         <v>1659</v>
-      </c>
-      <c r="C782" t="s" s="2">
-        <v>1660</v>
       </c>
       <c r="D782" s="2"/>
     </row>
@@ -16663,10 +16642,10 @@
         <v>95</v>
       </c>
       <c r="B783" t="s" s="2">
+        <v>1660</v>
+      </c>
+      <c r="C783" t="s" s="2">
         <v>1661</v>
-      </c>
-      <c r="C783" t="s" s="2">
-        <v>1662</v>
       </c>
       <c r="D783" s="2"/>
     </row>
@@ -16675,10 +16654,10 @@
         <v>95</v>
       </c>
       <c r="B784" t="s" s="2">
+        <v>1662</v>
+      </c>
+      <c r="C784" t="s" s="2">
         <v>1663</v>
-      </c>
-      <c r="C784" t="s" s="2">
-        <v>1664</v>
       </c>
       <c r="D784" s="2"/>
     </row>
@@ -16687,10 +16666,10 @@
         <v>95</v>
       </c>
       <c r="B785" t="s" s="2">
+        <v>1664</v>
+      </c>
+      <c r="C785" t="s" s="2">
         <v>1665</v>
-      </c>
-      <c r="C785" t="s" s="2">
-        <v>1666</v>
       </c>
       <c r="D785" s="2"/>
     </row>
@@ -16699,10 +16678,10 @@
         <v>95</v>
       </c>
       <c r="B786" t="s" s="2">
+        <v>1666</v>
+      </c>
+      <c r="C786" t="s" s="2">
         <v>1667</v>
-      </c>
-      <c r="C786" t="s" s="2">
-        <v>1668</v>
       </c>
       <c r="D786" s="2"/>
     </row>
@@ -16711,10 +16690,10 @@
         <v>95</v>
       </c>
       <c r="B787" t="s" s="2">
+        <v>1668</v>
+      </c>
+      <c r="C787" t="s" s="2">
         <v>1669</v>
-      </c>
-      <c r="C787" t="s" s="2">
-        <v>1670</v>
       </c>
       <c r="D787" s="2"/>
     </row>
@@ -16723,10 +16702,10 @@
         <v>95</v>
       </c>
       <c r="B788" t="s" s="2">
+        <v>1670</v>
+      </c>
+      <c r="C788" t="s" s="2">
         <v>1671</v>
-      </c>
-      <c r="C788" t="s" s="2">
-        <v>1672</v>
       </c>
       <c r="D788" s="2"/>
     </row>
@@ -16735,10 +16714,10 @@
         <v>95</v>
       </c>
       <c r="B789" t="s" s="2">
+        <v>1672</v>
+      </c>
+      <c r="C789" t="s" s="2">
         <v>1673</v>
-      </c>
-      <c r="C789" t="s" s="2">
-        <v>1674</v>
       </c>
       <c r="D789" s="2"/>
     </row>
@@ -16747,10 +16726,10 @@
         <v>95</v>
       </c>
       <c r="B790" t="s" s="2">
+        <v>1674</v>
+      </c>
+      <c r="C790" t="s" s="2">
         <v>1675</v>
-      </c>
-      <c r="C790" t="s" s="2">
-        <v>1676</v>
       </c>
       <c r="D790" s="2"/>
     </row>
@@ -16759,10 +16738,10 @@
         <v>95</v>
       </c>
       <c r="B791" t="s" s="2">
+        <v>1676</v>
+      </c>
+      <c r="C791" t="s" s="2">
         <v>1677</v>
-      </c>
-      <c r="C791" t="s" s="2">
-        <v>1678</v>
       </c>
       <c r="D791" s="2"/>
     </row>
@@ -16771,10 +16750,10 @@
         <v>95</v>
       </c>
       <c r="B792" t="s" s="2">
+        <v>1678</v>
+      </c>
+      <c r="C792" t="s" s="2">
         <v>1679</v>
-      </c>
-      <c r="C792" t="s" s="2">
-        <v>1680</v>
       </c>
       <c r="D792" s="2"/>
     </row>
@@ -16783,10 +16762,10 @@
         <v>95</v>
       </c>
       <c r="B793" t="s" s="2">
+        <v>1680</v>
+      </c>
+      <c r="C793" t="s" s="2">
         <v>1681</v>
-      </c>
-      <c r="C793" t="s" s="2">
-        <v>1682</v>
       </c>
       <c r="D793" s="2"/>
     </row>
@@ -16795,10 +16774,10 @@
         <v>95</v>
       </c>
       <c r="B794" t="s" s="2">
+        <v>1682</v>
+      </c>
+      <c r="C794" t="s" s="2">
         <v>1683</v>
-      </c>
-      <c r="C794" t="s" s="2">
-        <v>1684</v>
       </c>
       <c r="D794" s="2"/>
     </row>
@@ -16807,10 +16786,10 @@
         <v>95</v>
       </c>
       <c r="B795" t="s" s="2">
+        <v>1684</v>
+      </c>
+      <c r="C795" t="s" s="2">
         <v>1685</v>
-      </c>
-      <c r="C795" t="s" s="2">
-        <v>1686</v>
       </c>
       <c r="D795" s="2"/>
     </row>
@@ -16819,10 +16798,10 @@
         <v>95</v>
       </c>
       <c r="B796" t="s" s="2">
+        <v>1686</v>
+      </c>
+      <c r="C796" t="s" s="2">
         <v>1687</v>
-      </c>
-      <c r="C796" t="s" s="2">
-        <v>1688</v>
       </c>
       <c r="D796" s="2"/>
     </row>
@@ -16831,10 +16810,10 @@
         <v>95</v>
       </c>
       <c r="B797" t="s" s="2">
+        <v>1688</v>
+      </c>
+      <c r="C797" t="s" s="2">
         <v>1689</v>
-      </c>
-      <c r="C797" t="s" s="2">
-        <v>1690</v>
       </c>
       <c r="D797" s="2"/>
     </row>
@@ -16843,10 +16822,10 @@
         <v>95</v>
       </c>
       <c r="B798" t="s" s="2">
+        <v>1690</v>
+      </c>
+      <c r="C798" t="s" s="2">
         <v>1691</v>
-      </c>
-      <c r="C798" t="s" s="2">
-        <v>1692</v>
       </c>
       <c r="D798" s="2"/>
     </row>
@@ -16855,10 +16834,10 @@
         <v>95</v>
       </c>
       <c r="B799" t="s" s="2">
+        <v>1692</v>
+      </c>
+      <c r="C799" t="s" s="2">
         <v>1693</v>
-      </c>
-      <c r="C799" t="s" s="2">
-        <v>1694</v>
       </c>
       <c r="D799" s="2"/>
     </row>
@@ -16867,10 +16846,10 @@
         <v>95</v>
       </c>
       <c r="B800" t="s" s="2">
+        <v>1694</v>
+      </c>
+      <c r="C800" t="s" s="2">
         <v>1695</v>
-      </c>
-      <c r="C800" t="s" s="2">
-        <v>1696</v>
       </c>
       <c r="D800" s="2"/>
     </row>
@@ -16879,10 +16858,10 @@
         <v>95</v>
       </c>
       <c r="B801" t="s" s="2">
+        <v>1696</v>
+      </c>
+      <c r="C801" t="s" s="2">
         <v>1697</v>
-      </c>
-      <c r="C801" t="s" s="2">
-        <v>1698</v>
       </c>
       <c r="D801" s="2"/>
     </row>
@@ -16891,10 +16870,10 @@
         <v>95</v>
       </c>
       <c r="B802" t="s" s="2">
+        <v>1698</v>
+      </c>
+      <c r="C802" t="s" s="2">
         <v>1699</v>
-      </c>
-      <c r="C802" t="s" s="2">
-        <v>1700</v>
       </c>
       <c r="D802" s="2"/>
     </row>
@@ -16903,10 +16882,10 @@
         <v>95</v>
       </c>
       <c r="B803" t="s" s="2">
+        <v>1700</v>
+      </c>
+      <c r="C803" t="s" s="2">
         <v>1701</v>
-      </c>
-      <c r="C803" t="s" s="2">
-        <v>1702</v>
       </c>
       <c r="D803" s="2"/>
     </row>
@@ -16915,10 +16894,10 @@
         <v>95</v>
       </c>
       <c r="B804" t="s" s="2">
+        <v>1702</v>
+      </c>
+      <c r="C804" t="s" s="2">
         <v>1703</v>
-      </c>
-      <c r="C804" t="s" s="2">
-        <v>1704</v>
       </c>
       <c r="D804" s="2"/>
     </row>
@@ -16927,10 +16906,10 @@
         <v>95</v>
       </c>
       <c r="B805" t="s" s="2">
+        <v>1704</v>
+      </c>
+      <c r="C805" t="s" s="2">
         <v>1705</v>
-      </c>
-      <c r="C805" t="s" s="2">
-        <v>1706</v>
       </c>
       <c r="D805" s="2"/>
     </row>
@@ -16939,10 +16918,10 @@
         <v>95</v>
       </c>
       <c r="B806" t="s" s="2">
+        <v>1706</v>
+      </c>
+      <c r="C806" t="s" s="2">
         <v>1707</v>
-      </c>
-      <c r="C806" t="s" s="2">
-        <v>1708</v>
       </c>
       <c r="D806" s="2"/>
     </row>
@@ -16951,10 +16930,10 @@
         <v>95</v>
       </c>
       <c r="B807" t="s" s="2">
+        <v>1708</v>
+      </c>
+      <c r="C807" t="s" s="2">
         <v>1709</v>
-      </c>
-      <c r="C807" t="s" s="2">
-        <v>1710</v>
       </c>
       <c r="D807" s="2"/>
     </row>
@@ -16963,10 +16942,10 @@
         <v>95</v>
       </c>
       <c r="B808" t="s" s="2">
+        <v>1710</v>
+      </c>
+      <c r="C808" t="s" s="2">
         <v>1711</v>
-      </c>
-      <c r="C808" t="s" s="2">
-        <v>1712</v>
       </c>
       <c r="D808" s="2"/>
     </row>
@@ -16975,10 +16954,10 @@
         <v>95</v>
       </c>
       <c r="B809" t="s" s="2">
+        <v>1712</v>
+      </c>
+      <c r="C809" t="s" s="2">
         <v>1713</v>
-      </c>
-      <c r="C809" t="s" s="2">
-        <v>1714</v>
       </c>
       <c r="D809" s="2"/>
     </row>
@@ -16987,10 +16966,10 @@
         <v>95</v>
       </c>
       <c r="B810" t="s" s="2">
+        <v>1714</v>
+      </c>
+      <c r="C810" t="s" s="2">
         <v>1715</v>
-      </c>
-      <c r="C810" t="s" s="2">
-        <v>1716</v>
       </c>
       <c r="D810" s="2"/>
     </row>
@@ -16999,10 +16978,10 @@
         <v>95</v>
       </c>
       <c r="B811" t="s" s="2">
+        <v>1716</v>
+      </c>
+      <c r="C811" t="s" s="2">
         <v>1717</v>
-      </c>
-      <c r="C811" t="s" s="2">
-        <v>1718</v>
       </c>
       <c r="D811" s="2"/>
     </row>
@@ -17011,10 +16990,10 @@
         <v>95</v>
       </c>
       <c r="B812" t="s" s="2">
+        <v>1718</v>
+      </c>
+      <c r="C812" t="s" s="2">
         <v>1719</v>
-      </c>
-      <c r="C812" t="s" s="2">
-        <v>1720</v>
       </c>
       <c r="D812" s="2"/>
     </row>
@@ -17023,10 +17002,10 @@
         <v>95</v>
       </c>
       <c r="B813" t="s" s="2">
+        <v>1720</v>
+      </c>
+      <c r="C813" t="s" s="2">
         <v>1721</v>
-      </c>
-      <c r="C813" t="s" s="2">
-        <v>1722</v>
       </c>
       <c r="D813" s="2"/>
     </row>
@@ -17035,10 +17014,10 @@
         <v>95</v>
       </c>
       <c r="B814" t="s" s="2">
+        <v>1722</v>
+      </c>
+      <c r="C814" t="s" s="2">
         <v>1723</v>
-      </c>
-      <c r="C814" t="s" s="2">
-        <v>1724</v>
       </c>
       <c r="D814" s="2"/>
     </row>
@@ -17047,10 +17026,10 @@
         <v>95</v>
       </c>
       <c r="B815" t="s" s="2">
+        <v>1724</v>
+      </c>
+      <c r="C815" t="s" s="2">
         <v>1725</v>
-      </c>
-      <c r="C815" t="s" s="2">
-        <v>1726</v>
       </c>
       <c r="D815" s="2"/>
     </row>
@@ -17059,10 +17038,10 @@
         <v>95</v>
       </c>
       <c r="B816" t="s" s="2">
+        <v>1726</v>
+      </c>
+      <c r="C816" t="s" s="2">
         <v>1727</v>
-      </c>
-      <c r="C816" t="s" s="2">
-        <v>1728</v>
       </c>
       <c r="D816" s="2"/>
     </row>
@@ -17071,10 +17050,10 @@
         <v>95</v>
       </c>
       <c r="B817" t="s" s="2">
+        <v>1728</v>
+      </c>
+      <c r="C817" t="s" s="2">
         <v>1729</v>
-      </c>
-      <c r="C817" t="s" s="2">
-        <v>1730</v>
       </c>
       <c r="D817" s="2"/>
     </row>
@@ -17083,10 +17062,10 @@
         <v>95</v>
       </c>
       <c r="B818" t="s" s="2">
+        <v>1730</v>
+      </c>
+      <c r="C818" t="s" s="2">
         <v>1731</v>
-      </c>
-      <c r="C818" t="s" s="2">
-        <v>1732</v>
       </c>
       <c r="D818" s="2"/>
     </row>
@@ -17095,10 +17074,10 @@
         <v>95</v>
       </c>
       <c r="B819" t="s" s="2">
+        <v>1732</v>
+      </c>
+      <c r="C819" t="s" s="2">
         <v>1733</v>
-      </c>
-      <c r="C819" t="s" s="2">
-        <v>1734</v>
       </c>
       <c r="D819" s="2"/>
     </row>
@@ -17107,10 +17086,10 @@
         <v>95</v>
       </c>
       <c r="B820" t="s" s="2">
+        <v>1734</v>
+      </c>
+      <c r="C820" t="s" s="2">
         <v>1735</v>
-      </c>
-      <c r="C820" t="s" s="2">
-        <v>1736</v>
       </c>
       <c r="D820" s="2"/>
     </row>
@@ -17119,10 +17098,10 @@
         <v>95</v>
       </c>
       <c r="B821" t="s" s="2">
+        <v>1736</v>
+      </c>
+      <c r="C821" t="s" s="2">
         <v>1737</v>
-      </c>
-      <c r="C821" t="s" s="2">
-        <v>1738</v>
       </c>
       <c r="D821" s="2"/>
     </row>
@@ -17131,10 +17110,10 @@
         <v>95</v>
       </c>
       <c r="B822" t="s" s="2">
+        <v>1738</v>
+      </c>
+      <c r="C822" t="s" s="2">
         <v>1739</v>
-      </c>
-      <c r="C822" t="s" s="2">
-        <v>1740</v>
       </c>
       <c r="D822" s="2"/>
     </row>
@@ -17143,10 +17122,10 @@
         <v>95</v>
       </c>
       <c r="B823" t="s" s="2">
+        <v>1740</v>
+      </c>
+      <c r="C823" t="s" s="2">
         <v>1741</v>
-      </c>
-      <c r="C823" t="s" s="2">
-        <v>1742</v>
       </c>
       <c r="D823" s="2"/>
     </row>
@@ -17155,10 +17134,10 @@
         <v>95</v>
       </c>
       <c r="B824" t="s" s="2">
+        <v>1742</v>
+      </c>
+      <c r="C824" t="s" s="2">
         <v>1743</v>
-      </c>
-      <c r="C824" t="s" s="2">
-        <v>1744</v>
       </c>
       <c r="D824" s="2"/>
     </row>
@@ -17167,10 +17146,10 @@
         <v>95</v>
       </c>
       <c r="B825" t="s" s="2">
+        <v>1744</v>
+      </c>
+      <c r="C825" t="s" s="2">
         <v>1745</v>
-      </c>
-      <c r="C825" t="s" s="2">
-        <v>1746</v>
       </c>
       <c r="D825" s="2"/>
     </row>
@@ -17179,10 +17158,10 @@
         <v>95</v>
       </c>
       <c r="B826" t="s" s="2">
+        <v>1746</v>
+      </c>
+      <c r="C826" t="s" s="2">
         <v>1747</v>
-      </c>
-      <c r="C826" t="s" s="2">
-        <v>1748</v>
       </c>
       <c r="D826" s="2"/>
     </row>
@@ -17191,10 +17170,10 @@
         <v>95</v>
       </c>
       <c r="B827" t="s" s="2">
+        <v>1748</v>
+      </c>
+      <c r="C827" t="s" s="2">
         <v>1749</v>
-      </c>
-      <c r="C827" t="s" s="2">
-        <v>1750</v>
       </c>
       <c r="D827" s="2"/>
     </row>
@@ -17203,10 +17182,10 @@
         <v>95</v>
       </c>
       <c r="B828" t="s" s="2">
+        <v>1750</v>
+      </c>
+      <c r="C828" t="s" s="2">
         <v>1751</v>
-      </c>
-      <c r="C828" t="s" s="2">
-        <v>1752</v>
       </c>
       <c r="D828" s="2"/>
     </row>
@@ -17215,10 +17194,10 @@
         <v>95</v>
       </c>
       <c r="B829" t="s" s="2">
+        <v>1752</v>
+      </c>
+      <c r="C829" t="s" s="2">
         <v>1753</v>
-      </c>
-      <c r="C829" t="s" s="2">
-        <v>1754</v>
       </c>
       <c r="D829" s="2"/>
     </row>
@@ -17227,10 +17206,10 @@
         <v>95</v>
       </c>
       <c r="B830" t="s" s="2">
+        <v>1754</v>
+      </c>
+      <c r="C830" t="s" s="2">
         <v>1755</v>
-      </c>
-      <c r="C830" t="s" s="2">
-        <v>1756</v>
       </c>
       <c r="D830" s="2"/>
     </row>
@@ -17239,10 +17218,10 @@
         <v>95</v>
       </c>
       <c r="B831" t="s" s="2">
+        <v>1756</v>
+      </c>
+      <c r="C831" t="s" s="2">
         <v>1757</v>
-      </c>
-      <c r="C831" t="s" s="2">
-        <v>1758</v>
       </c>
       <c r="D831" s="2"/>
     </row>
@@ -17251,10 +17230,10 @@
         <v>95</v>
       </c>
       <c r="B832" t="s" s="2">
+        <v>1758</v>
+      </c>
+      <c r="C832" t="s" s="2">
         <v>1759</v>
-      </c>
-      <c r="C832" t="s" s="2">
-        <v>1760</v>
       </c>
       <c r="D832" s="2"/>
     </row>
@@ -17263,10 +17242,10 @@
         <v>95</v>
       </c>
       <c r="B833" t="s" s="2">
+        <v>1760</v>
+      </c>
+      <c r="C833" t="s" s="2">
         <v>1761</v>
-      </c>
-      <c r="C833" t="s" s="2">
-        <v>1762</v>
       </c>
       <c r="D833" s="2"/>
     </row>
@@ -17275,10 +17254,10 @@
         <v>95</v>
       </c>
       <c r="B834" t="s" s="2">
+        <v>1762</v>
+      </c>
+      <c r="C834" t="s" s="2">
         <v>1763</v>
-      </c>
-      <c r="C834" t="s" s="2">
-        <v>1764</v>
       </c>
       <c r="D834" s="2"/>
     </row>
@@ -17287,10 +17266,10 @@
         <v>95</v>
       </c>
       <c r="B835" t="s" s="2">
+        <v>1764</v>
+      </c>
+      <c r="C835" t="s" s="2">
         <v>1765</v>
-      </c>
-      <c r="C835" t="s" s="2">
-        <v>1766</v>
       </c>
       <c r="D835" s="2"/>
     </row>
@@ -17299,10 +17278,10 @@
         <v>95</v>
       </c>
       <c r="B836" t="s" s="2">
+        <v>1766</v>
+      </c>
+      <c r="C836" t="s" s="2">
         <v>1767</v>
-      </c>
-      <c r="C836" t="s" s="2">
-        <v>1768</v>
       </c>
       <c r="D836" s="2"/>
     </row>
@@ -17311,10 +17290,10 @@
         <v>95</v>
       </c>
       <c r="B837" t="s" s="2">
+        <v>1768</v>
+      </c>
+      <c r="C837" t="s" s="2">
         <v>1769</v>
-      </c>
-      <c r="C837" t="s" s="2">
-        <v>1770</v>
       </c>
       <c r="D837" s="2"/>
     </row>
@@ -17323,10 +17302,10 @@
         <v>95</v>
       </c>
       <c r="B838" t="s" s="2">
+        <v>1770</v>
+      </c>
+      <c r="C838" t="s" s="2">
         <v>1771</v>
-      </c>
-      <c r="C838" t="s" s="2">
-        <v>1772</v>
       </c>
       <c r="D838" s="2"/>
     </row>
@@ -17335,10 +17314,10 @@
         <v>95</v>
       </c>
       <c r="B839" t="s" s="2">
+        <v>1772</v>
+      </c>
+      <c r="C839" t="s" s="2">
         <v>1773</v>
-      </c>
-      <c r="C839" t="s" s="2">
-        <v>1774</v>
       </c>
       <c r="D839" s="2"/>
     </row>
@@ -17347,10 +17326,10 @@
         <v>95</v>
       </c>
       <c r="B840" t="s" s="2">
+        <v>1774</v>
+      </c>
+      <c r="C840" t="s" s="2">
         <v>1775</v>
-      </c>
-      <c r="C840" t="s" s="2">
-        <v>1776</v>
       </c>
       <c r="D840" s="2"/>
     </row>
@@ -17359,10 +17338,10 @@
         <v>95</v>
       </c>
       <c r="B841" t="s" s="2">
+        <v>1776</v>
+      </c>
+      <c r="C841" t="s" s="2">
         <v>1777</v>
-      </c>
-      <c r="C841" t="s" s="2">
-        <v>1778</v>
       </c>
       <c r="D841" s="2"/>
     </row>
@@ -17371,10 +17350,10 @@
         <v>95</v>
       </c>
       <c r="B842" t="s" s="2">
+        <v>1778</v>
+      </c>
+      <c r="C842" t="s" s="2">
         <v>1779</v>
-      </c>
-      <c r="C842" t="s" s="2">
-        <v>1780</v>
       </c>
       <c r="D842" s="2"/>
     </row>
@@ -17383,10 +17362,10 @@
         <v>95</v>
       </c>
       <c r="B843" t="s" s="2">
+        <v>1780</v>
+      </c>
+      <c r="C843" t="s" s="2">
         <v>1781</v>
-      </c>
-      <c r="C843" t="s" s="2">
-        <v>1782</v>
       </c>
       <c r="D843" s="2"/>
     </row>
@@ -17395,10 +17374,10 @@
         <v>95</v>
       </c>
       <c r="B844" t="s" s="2">
+        <v>1782</v>
+      </c>
+      <c r="C844" t="s" s="2">
         <v>1783</v>
-      </c>
-      <c r="C844" t="s" s="2">
-        <v>1784</v>
       </c>
       <c r="D844" s="2"/>
     </row>
@@ -17407,10 +17386,10 @@
         <v>95</v>
       </c>
       <c r="B845" t="s" s="2">
+        <v>1784</v>
+      </c>
+      <c r="C845" t="s" s="2">
         <v>1785</v>
-      </c>
-      <c r="C845" t="s" s="2">
-        <v>1786</v>
       </c>
       <c r="D845" s="2"/>
     </row>
@@ -17419,10 +17398,10 @@
         <v>95</v>
       </c>
       <c r="B846" t="s" s="2">
+        <v>1786</v>
+      </c>
+      <c r="C846" t="s" s="2">
         <v>1787</v>
-      </c>
-      <c r="C846" t="s" s="2">
-        <v>1788</v>
       </c>
       <c r="D846" s="2"/>
     </row>
@@ -17431,10 +17410,10 @@
         <v>95</v>
       </c>
       <c r="B847" t="s" s="2">
+        <v>1788</v>
+      </c>
+      <c r="C847" t="s" s="2">
         <v>1789</v>
-      </c>
-      <c r="C847" t="s" s="2">
-        <v>1790</v>
       </c>
       <c r="D847" s="2"/>
     </row>
@@ -17443,10 +17422,10 @@
         <v>95</v>
       </c>
       <c r="B848" t="s" s="2">
+        <v>1790</v>
+      </c>
+      <c r="C848" t="s" s="2">
         <v>1791</v>
-      </c>
-      <c r="C848" t="s" s="2">
-        <v>1792</v>
       </c>
       <c r="D848" s="2"/>
     </row>
@@ -17455,10 +17434,10 @@
         <v>95</v>
       </c>
       <c r="B849" t="s" s="2">
+        <v>1792</v>
+      </c>
+      <c r="C849" t="s" s="2">
         <v>1793</v>
-      </c>
-      <c r="C849" t="s" s="2">
-        <v>1794</v>
       </c>
       <c r="D849" s="2"/>
     </row>
@@ -17467,10 +17446,10 @@
         <v>95</v>
       </c>
       <c r="B850" t="s" s="2">
+        <v>1794</v>
+      </c>
+      <c r="C850" t="s" s="2">
         <v>1795</v>
-      </c>
-      <c r="C850" t="s" s="2">
-        <v>1796</v>
       </c>
       <c r="D850" s="2"/>
     </row>
@@ -17479,10 +17458,10 @@
         <v>95</v>
       </c>
       <c r="B851" t="s" s="2">
+        <v>1796</v>
+      </c>
+      <c r="C851" t="s" s="2">
         <v>1797</v>
-      </c>
-      <c r="C851" t="s" s="2">
-        <v>1798</v>
       </c>
       <c r="D851" s="2"/>
     </row>
@@ -17491,10 +17470,10 @@
         <v>95</v>
       </c>
       <c r="B852" t="s" s="2">
+        <v>1798</v>
+      </c>
+      <c r="C852" t="s" s="2">
         <v>1799</v>
-      </c>
-      <c r="C852" t="s" s="2">
-        <v>1800</v>
       </c>
       <c r="D852" s="2"/>
     </row>
@@ -17503,10 +17482,10 @@
         <v>95</v>
       </c>
       <c r="B853" t="s" s="2">
+        <v>1800</v>
+      </c>
+      <c r="C853" t="s" s="2">
         <v>1801</v>
-      </c>
-      <c r="C853" t="s" s="2">
-        <v>1802</v>
       </c>
       <c r="D853" s="2"/>
     </row>
@@ -17515,10 +17494,10 @@
         <v>95</v>
       </c>
       <c r="B854" t="s" s="2">
+        <v>1802</v>
+      </c>
+      <c r="C854" t="s" s="2">
         <v>1803</v>
-      </c>
-      <c r="C854" t="s" s="2">
-        <v>1804</v>
       </c>
       <c r="D854" s="2"/>
     </row>
@@ -17527,10 +17506,10 @@
         <v>95</v>
       </c>
       <c r="B855" t="s" s="2">
+        <v>1804</v>
+      </c>
+      <c r="C855" t="s" s="2">
         <v>1805</v>
-      </c>
-      <c r="C855" t="s" s="2">
-        <v>1806</v>
       </c>
       <c r="D855" s="2"/>
     </row>
@@ -17539,10 +17518,10 @@
         <v>95</v>
       </c>
       <c r="B856" t="s" s="2">
+        <v>1806</v>
+      </c>
+      <c r="C856" t="s" s="2">
         <v>1807</v>
-      </c>
-      <c r="C856" t="s" s="2">
-        <v>1808</v>
       </c>
       <c r="D856" s="2"/>
     </row>
@@ -17551,10 +17530,10 @@
         <v>95</v>
       </c>
       <c r="B857" t="s" s="2">
+        <v>1808</v>
+      </c>
+      <c r="C857" t="s" s="2">
         <v>1809</v>
-      </c>
-      <c r="C857" t="s" s="2">
-        <v>1810</v>
       </c>
       <c r="D857" s="2"/>
     </row>
@@ -17563,10 +17542,10 @@
         <v>95</v>
       </c>
       <c r="B858" t="s" s="2">
+        <v>1810</v>
+      </c>
+      <c r="C858" t="s" s="2">
         <v>1811</v>
-      </c>
-      <c r="C858" t="s" s="2">
-        <v>1812</v>
       </c>
       <c r="D858" s="2"/>
     </row>
@@ -17575,10 +17554,10 @@
         <v>95</v>
       </c>
       <c r="B859" t="s" s="2">
+        <v>1812</v>
+      </c>
+      <c r="C859" t="s" s="2">
         <v>1813</v>
-      </c>
-      <c r="C859" t="s" s="2">
-        <v>1814</v>
       </c>
       <c r="D859" s="2"/>
     </row>
@@ -17587,10 +17566,10 @@
         <v>95</v>
       </c>
       <c r="B860" t="s" s="2">
+        <v>1814</v>
+      </c>
+      <c r="C860" t="s" s="2">
         <v>1815</v>
-      </c>
-      <c r="C860" t="s" s="2">
-        <v>1816</v>
       </c>
       <c r="D860" s="2"/>
     </row>
@@ -17599,10 +17578,10 @@
         <v>95</v>
       </c>
       <c r="B861" t="s" s="2">
+        <v>1816</v>
+      </c>
+      <c r="C861" t="s" s="2">
         <v>1817</v>
-      </c>
-      <c r="C861" t="s" s="2">
-        <v>1818</v>
       </c>
       <c r="D861" s="2"/>
     </row>
@@ -17611,10 +17590,10 @@
         <v>95</v>
       </c>
       <c r="B862" t="s" s="2">
+        <v>1818</v>
+      </c>
+      <c r="C862" t="s" s="2">
         <v>1819</v>
-      </c>
-      <c r="C862" t="s" s="2">
-        <v>1820</v>
       </c>
       <c r="D862" s="2"/>
     </row>
@@ -17623,10 +17602,10 @@
         <v>95</v>
       </c>
       <c r="B863" t="s" s="2">
+        <v>1820</v>
+      </c>
+      <c r="C863" t="s" s="2">
         <v>1821</v>
-      </c>
-      <c r="C863" t="s" s="2">
-        <v>1822</v>
       </c>
       <c r="D863" s="2"/>
     </row>
@@ -17635,10 +17614,10 @@
         <v>95</v>
       </c>
       <c r="B864" t="s" s="2">
+        <v>1822</v>
+      </c>
+      <c r="C864" t="s" s="2">
         <v>1823</v>
-      </c>
-      <c r="C864" t="s" s="2">
-        <v>1824</v>
       </c>
       <c r="D864" s="2"/>
     </row>
@@ -17647,10 +17626,10 @@
         <v>95</v>
       </c>
       <c r="B865" t="s" s="2">
+        <v>1824</v>
+      </c>
+      <c r="C865" t="s" s="2">
         <v>1825</v>
-      </c>
-      <c r="C865" t="s" s="2">
-        <v>1826</v>
       </c>
       <c r="D865" s="2"/>
     </row>
@@ -17659,10 +17638,10 @@
         <v>95</v>
       </c>
       <c r="B866" t="s" s="2">
+        <v>1826</v>
+      </c>
+      <c r="C866" t="s" s="2">
         <v>1827</v>
-      </c>
-      <c r="C866" t="s" s="2">
-        <v>1828</v>
       </c>
       <c r="D866" s="2"/>
     </row>
@@ -17671,10 +17650,10 @@
         <v>95</v>
       </c>
       <c r="B867" t="s" s="2">
+        <v>1828</v>
+      </c>
+      <c r="C867" t="s" s="2">
         <v>1829</v>
-      </c>
-      <c r="C867" t="s" s="2">
-        <v>1830</v>
       </c>
       <c r="D867" s="2"/>
     </row>
@@ -17683,10 +17662,10 @@
         <v>95</v>
       </c>
       <c r="B868" t="s" s="2">
+        <v>1830</v>
+      </c>
+      <c r="C868" t="s" s="2">
         <v>1831</v>
-      </c>
-      <c r="C868" t="s" s="2">
-        <v>1832</v>
       </c>
       <c r="D868" s="2"/>
     </row>
@@ -17695,10 +17674,10 @@
         <v>95</v>
       </c>
       <c r="B869" t="s" s="2">
+        <v>1832</v>
+      </c>
+      <c r="C869" t="s" s="2">
         <v>1833</v>
-      </c>
-      <c r="C869" t="s" s="2">
-        <v>1834</v>
       </c>
       <c r="D869" s="2"/>
     </row>
@@ -17707,10 +17686,10 @@
         <v>95</v>
       </c>
       <c r="B870" t="s" s="2">
+        <v>1834</v>
+      </c>
+      <c r="C870" t="s" s="2">
         <v>1835</v>
-      </c>
-      <c r="C870" t="s" s="2">
-        <v>1836</v>
       </c>
       <c r="D870" s="2"/>
     </row>
@@ -17719,10 +17698,10 @@
         <v>95</v>
       </c>
       <c r="B871" t="s" s="2">
+        <v>1836</v>
+      </c>
+      <c r="C871" t="s" s="2">
         <v>1837</v>
-      </c>
-      <c r="C871" t="s" s="2">
-        <v>1838</v>
       </c>
       <c r="D871" s="2"/>
     </row>
@@ -17731,10 +17710,10 @@
         <v>95</v>
       </c>
       <c r="B872" t="s" s="2">
+        <v>1838</v>
+      </c>
+      <c r="C872" t="s" s="2">
         <v>1839</v>
-      </c>
-      <c r="C872" t="s" s="2">
-        <v>1840</v>
       </c>
       <c r="D872" s="2"/>
     </row>
@@ -17743,10 +17722,10 @@
         <v>95</v>
       </c>
       <c r="B873" t="s" s="2">
+        <v>1840</v>
+      </c>
+      <c r="C873" t="s" s="2">
         <v>1841</v>
-      </c>
-      <c r="C873" t="s" s="2">
-        <v>1842</v>
       </c>
       <c r="D873" s="2"/>
     </row>
@@ -17755,10 +17734,10 @@
         <v>95</v>
       </c>
       <c r="B874" t="s" s="2">
+        <v>1842</v>
+      </c>
+      <c r="C874" t="s" s="2">
         <v>1843</v>
-      </c>
-      <c r="C874" t="s" s="2">
-        <v>1844</v>
       </c>
       <c r="D874" s="2"/>
     </row>
@@ -17767,10 +17746,10 @@
         <v>95</v>
       </c>
       <c r="B875" t="s" s="2">
+        <v>1844</v>
+      </c>
+      <c r="C875" t="s" s="2">
         <v>1845</v>
-      </c>
-      <c r="C875" t="s" s="2">
-        <v>1846</v>
       </c>
       <c r="D875" s="2"/>
     </row>
@@ -17779,10 +17758,10 @@
         <v>95</v>
       </c>
       <c r="B876" t="s" s="2">
+        <v>1846</v>
+      </c>
+      <c r="C876" t="s" s="2">
         <v>1847</v>
-      </c>
-      <c r="C876" t="s" s="2">
-        <v>1848</v>
       </c>
       <c r="D876" s="2"/>
     </row>
@@ -17791,10 +17770,10 @@
         <v>95</v>
       </c>
       <c r="B877" t="s" s="2">
+        <v>1848</v>
+      </c>
+      <c r="C877" t="s" s="2">
         <v>1849</v>
-      </c>
-      <c r="C877" t="s" s="2">
-        <v>1850</v>
       </c>
       <c r="D877" s="2"/>
     </row>
@@ -17803,10 +17782,10 @@
         <v>95</v>
       </c>
       <c r="B878" t="s" s="2">
+        <v>1850</v>
+      </c>
+      <c r="C878" t="s" s="2">
         <v>1851</v>
-      </c>
-      <c r="C878" t="s" s="2">
-        <v>1852</v>
       </c>
       <c r="D878" s="2"/>
     </row>
@@ -17815,10 +17794,10 @@
         <v>95</v>
       </c>
       <c r="B879" t="s" s="2">
+        <v>1852</v>
+      </c>
+      <c r="C879" t="s" s="2">
         <v>1853</v>
-      </c>
-      <c r="C879" t="s" s="2">
-        <v>1854</v>
       </c>
       <c r="D879" s="2"/>
     </row>
@@ -17827,10 +17806,10 @@
         <v>95</v>
       </c>
       <c r="B880" t="s" s="2">
+        <v>1854</v>
+      </c>
+      <c r="C880" t="s" s="2">
         <v>1855</v>
-      </c>
-      <c r="C880" t="s" s="2">
-        <v>1856</v>
       </c>
       <c r="D880" s="2"/>
     </row>
@@ -17839,10 +17818,10 @@
         <v>95</v>
       </c>
       <c r="B881" t="s" s="2">
+        <v>1856</v>
+      </c>
+      <c r="C881" t="s" s="2">
         <v>1857</v>
-      </c>
-      <c r="C881" t="s" s="2">
-        <v>1858</v>
       </c>
       <c r="D881" s="2"/>
     </row>
@@ -17851,10 +17830,10 @@
         <v>95</v>
       </c>
       <c r="B882" t="s" s="2">
+        <v>1858</v>
+      </c>
+      <c r="C882" t="s" s="2">
         <v>1859</v>
-      </c>
-      <c r="C882" t="s" s="2">
-        <v>1860</v>
       </c>
       <c r="D882" s="2"/>
     </row>
@@ -17863,10 +17842,10 @@
         <v>95</v>
       </c>
       <c r="B883" t="s" s="2">
+        <v>1860</v>
+      </c>
+      <c r="C883" t="s" s="2">
         <v>1861</v>
-      </c>
-      <c r="C883" t="s" s="2">
-        <v>1862</v>
       </c>
       <c r="D883" s="2"/>
     </row>
@@ -17875,10 +17854,10 @@
         <v>95</v>
       </c>
       <c r="B884" t="s" s="2">
+        <v>1862</v>
+      </c>
+      <c r="C884" t="s" s="2">
         <v>1863</v>
-      </c>
-      <c r="C884" t="s" s="2">
-        <v>1864</v>
       </c>
       <c r="D884" s="2"/>
     </row>
@@ -17887,10 +17866,10 @@
         <v>95</v>
       </c>
       <c r="B885" t="s" s="2">
+        <v>1864</v>
+      </c>
+      <c r="C885" t="s" s="2">
         <v>1865</v>
-      </c>
-      <c r="C885" t="s" s="2">
-        <v>1866</v>
       </c>
       <c r="D885" s="2"/>
     </row>
@@ -17899,10 +17878,10 @@
         <v>95</v>
       </c>
       <c r="B886" t="s" s="2">
+        <v>1866</v>
+      </c>
+      <c r="C886" t="s" s="2">
         <v>1867</v>
-      </c>
-      <c r="C886" t="s" s="2">
-        <v>1868</v>
       </c>
       <c r="D886" s="2"/>
     </row>
@@ -17911,10 +17890,10 @@
         <v>95</v>
       </c>
       <c r="B887" t="s" s="2">
+        <v>1868</v>
+      </c>
+      <c r="C887" t="s" s="2">
         <v>1869</v>
-      </c>
-      <c r="C887" t="s" s="2">
-        <v>1870</v>
       </c>
       <c r="D887" s="2"/>
     </row>
@@ -17923,10 +17902,10 @@
         <v>95</v>
       </c>
       <c r="B888" t="s" s="2">
+        <v>1870</v>
+      </c>
+      <c r="C888" t="s" s="2">
         <v>1871</v>
-      </c>
-      <c r="C888" t="s" s="2">
-        <v>1872</v>
       </c>
       <c r="D888" s="2"/>
     </row>
@@ -17935,10 +17914,10 @@
         <v>95</v>
       </c>
       <c r="B889" t="s" s="2">
+        <v>1872</v>
+      </c>
+      <c r="C889" t="s" s="2">
         <v>1873</v>
-      </c>
-      <c r="C889" t="s" s="2">
-        <v>1874</v>
       </c>
       <c r="D889" s="2"/>
     </row>
@@ -17947,10 +17926,10 @@
         <v>95</v>
       </c>
       <c r="B890" t="s" s="2">
+        <v>1874</v>
+      </c>
+      <c r="C890" t="s" s="2">
         <v>1875</v>
-      </c>
-      <c r="C890" t="s" s="2">
-        <v>1876</v>
       </c>
       <c r="D890" s="2"/>
     </row>
@@ -17959,10 +17938,10 @@
         <v>95</v>
       </c>
       <c r="B891" t="s" s="2">
+        <v>1876</v>
+      </c>
+      <c r="C891" t="s" s="2">
         <v>1877</v>
-      </c>
-      <c r="C891" t="s" s="2">
-        <v>1878</v>
       </c>
       <c r="D891" s="2"/>
     </row>
@@ -17971,10 +17950,10 @@
         <v>95</v>
       </c>
       <c r="B892" t="s" s="2">
+        <v>1878</v>
+      </c>
+      <c r="C892" t="s" s="2">
         <v>1879</v>
-      </c>
-      <c r="C892" t="s" s="2">
-        <v>1880</v>
       </c>
       <c r="D892" s="2"/>
     </row>
@@ -17983,10 +17962,10 @@
         <v>95</v>
       </c>
       <c r="B893" t="s" s="2">
+        <v>1880</v>
+      </c>
+      <c r="C893" t="s" s="2">
         <v>1881</v>
-      </c>
-      <c r="C893" t="s" s="2">
-        <v>1882</v>
       </c>
       <c r="D893" s="2"/>
     </row>
@@ -17995,10 +17974,10 @@
         <v>95</v>
       </c>
       <c r="B894" t="s" s="2">
+        <v>1882</v>
+      </c>
+      <c r="C894" t="s" s="2">
         <v>1883</v>
-      </c>
-      <c r="C894" t="s" s="2">
-        <v>1884</v>
       </c>
       <c r="D894" s="2"/>
     </row>
@@ -18007,10 +17986,10 @@
         <v>95</v>
       </c>
       <c r="B895" t="s" s="2">
+        <v>1884</v>
+      </c>
+      <c r="C895" t="s" s="2">
         <v>1885</v>
-      </c>
-      <c r="C895" t="s" s="2">
-        <v>1886</v>
       </c>
       <c r="D895" s="2"/>
     </row>
@@ -18019,10 +17998,10 @@
         <v>95</v>
       </c>
       <c r="B896" t="s" s="2">
+        <v>1886</v>
+      </c>
+      <c r="C896" t="s" s="2">
         <v>1887</v>
-      </c>
-      <c r="C896" t="s" s="2">
-        <v>1888</v>
       </c>
       <c r="D896" s="2"/>
     </row>
@@ -18031,10 +18010,10 @@
         <v>95</v>
       </c>
       <c r="B897" t="s" s="2">
+        <v>1888</v>
+      </c>
+      <c r="C897" t="s" s="2">
         <v>1889</v>
-      </c>
-      <c r="C897" t="s" s="2">
-        <v>1890</v>
       </c>
       <c r="D897" s="2"/>
     </row>
@@ -18043,10 +18022,10 @@
         <v>95</v>
       </c>
       <c r="B898" t="s" s="2">
+        <v>1890</v>
+      </c>
+      <c r="C898" t="s" s="2">
         <v>1891</v>
-      </c>
-      <c r="C898" t="s" s="2">
-        <v>1892</v>
       </c>
       <c r="D898" s="2"/>
     </row>
@@ -18055,10 +18034,10 @@
         <v>95</v>
       </c>
       <c r="B899" t="s" s="2">
+        <v>1892</v>
+      </c>
+      <c r="C899" t="s" s="2">
         <v>1893</v>
-      </c>
-      <c r="C899" t="s" s="2">
-        <v>1894</v>
       </c>
       <c r="D899" s="2"/>
     </row>
@@ -18067,10 +18046,10 @@
         <v>95</v>
       </c>
       <c r="B900" t="s" s="2">
+        <v>1894</v>
+      </c>
+      <c r="C900" t="s" s="2">
         <v>1895</v>
-      </c>
-      <c r="C900" t="s" s="2">
-        <v>1896</v>
       </c>
       <c r="D900" s="2"/>
     </row>
@@ -18079,10 +18058,10 @@
         <v>95</v>
       </c>
       <c r="B901" t="s" s="2">
+        <v>1896</v>
+      </c>
+      <c r="C901" t="s" s="2">
         <v>1897</v>
-      </c>
-      <c r="C901" t="s" s="2">
-        <v>1898</v>
       </c>
       <c r="D901" s="2"/>
     </row>
@@ -18091,10 +18070,10 @@
         <v>95</v>
       </c>
       <c r="B902" t="s" s="2">
+        <v>1898</v>
+      </c>
+      <c r="C902" t="s" s="2">
         <v>1899</v>
-      </c>
-      <c r="C902" t="s" s="2">
-        <v>1900</v>
       </c>
       <c r="D902" s="2"/>
     </row>
@@ -18103,10 +18082,10 @@
         <v>95</v>
       </c>
       <c r="B903" t="s" s="2">
+        <v>1900</v>
+      </c>
+      <c r="C903" t="s" s="2">
         <v>1901</v>
-      </c>
-      <c r="C903" t="s" s="2">
-        <v>1902</v>
       </c>
       <c r="D903" s="2"/>
     </row>
@@ -18115,10 +18094,10 @@
         <v>95</v>
       </c>
       <c r="B904" t="s" s="2">
+        <v>1902</v>
+      </c>
+      <c r="C904" t="s" s="2">
         <v>1903</v>
-      </c>
-      <c r="C904" t="s" s="2">
-        <v>1904</v>
       </c>
       <c r="D904" s="2"/>
     </row>
@@ -18127,10 +18106,10 @@
         <v>95</v>
       </c>
       <c r="B905" t="s" s="2">
+        <v>1904</v>
+      </c>
+      <c r="C905" t="s" s="2">
         <v>1905</v>
-      </c>
-      <c r="C905" t="s" s="2">
-        <v>1906</v>
       </c>
       <c r="D905" s="2"/>
     </row>
@@ -18139,10 +18118,10 @@
         <v>95</v>
       </c>
       <c r="B906" t="s" s="2">
+        <v>1906</v>
+      </c>
+      <c r="C906" t="s" s="2">
         <v>1907</v>
-      </c>
-      <c r="C906" t="s" s="2">
-        <v>1908</v>
       </c>
       <c r="D906" s="2"/>
     </row>
@@ -18151,10 +18130,10 @@
         <v>95</v>
       </c>
       <c r="B907" t="s" s="2">
+        <v>1908</v>
+      </c>
+      <c r="C907" t="s" s="2">
         <v>1909</v>
-      </c>
-      <c r="C907" t="s" s="2">
-        <v>1910</v>
       </c>
       <c r="D907" s="2"/>
     </row>
@@ -18163,10 +18142,10 @@
         <v>95</v>
       </c>
       <c r="B908" t="s" s="2">
+        <v>1910</v>
+      </c>
+      <c r="C908" t="s" s="2">
         <v>1911</v>
-      </c>
-      <c r="C908" t="s" s="2">
-        <v>1912</v>
       </c>
       <c r="D908" s="2"/>
     </row>
@@ -18175,10 +18154,10 @@
         <v>95</v>
       </c>
       <c r="B909" t="s" s="2">
+        <v>1912</v>
+      </c>
+      <c r="C909" t="s" s="2">
         <v>1913</v>
-      </c>
-      <c r="C909" t="s" s="2">
-        <v>1914</v>
       </c>
       <c r="D909" s="2"/>
     </row>
@@ -18187,10 +18166,10 @@
         <v>95</v>
       </c>
       <c r="B910" t="s" s="2">
+        <v>1914</v>
+      </c>
+      <c r="C910" t="s" s="2">
         <v>1915</v>
-      </c>
-      <c r="C910" t="s" s="2">
-        <v>1916</v>
       </c>
       <c r="D910" s="2"/>
     </row>
@@ -18199,10 +18178,10 @@
         <v>95</v>
       </c>
       <c r="B911" t="s" s="2">
+        <v>1916</v>
+      </c>
+      <c r="C911" t="s" s="2">
         <v>1917</v>
-      </c>
-      <c r="C911" t="s" s="2">
-        <v>1918</v>
       </c>
       <c r="D911" s="2"/>
     </row>
@@ -18211,10 +18190,10 @@
         <v>95</v>
       </c>
       <c r="B912" t="s" s="2">
+        <v>1918</v>
+      </c>
+      <c r="C912" t="s" s="2">
         <v>1919</v>
-      </c>
-      <c r="C912" t="s" s="2">
-        <v>1920</v>
       </c>
       <c r="D912" s="2"/>
     </row>
@@ -18223,10 +18202,10 @@
         <v>95</v>
       </c>
       <c r="B913" t="s" s="2">
+        <v>1920</v>
+      </c>
+      <c r="C913" t="s" s="2">
         <v>1921</v>
-      </c>
-      <c r="C913" t="s" s="2">
-        <v>1922</v>
       </c>
       <c r="D913" s="2"/>
     </row>
@@ -18235,10 +18214,10 @@
         <v>95</v>
       </c>
       <c r="B914" t="s" s="2">
+        <v>1922</v>
+      </c>
+      <c r="C914" t="s" s="2">
         <v>1923</v>
-      </c>
-      <c r="C914" t="s" s="2">
-        <v>1924</v>
       </c>
       <c r="D914" s="2"/>
     </row>
@@ -18247,10 +18226,10 @@
         <v>95</v>
       </c>
       <c r="B915" t="s" s="2">
+        <v>1924</v>
+      </c>
+      <c r="C915" t="s" s="2">
         <v>1925</v>
-      </c>
-      <c r="C915" t="s" s="2">
-        <v>1926</v>
       </c>
       <c r="D915" s="2"/>
     </row>
@@ -18259,10 +18238,10 @@
         <v>95</v>
       </c>
       <c r="B916" t="s" s="2">
+        <v>1926</v>
+      </c>
+      <c r="C916" t="s" s="2">
         <v>1927</v>
-      </c>
-      <c r="C916" t="s" s="2">
-        <v>1928</v>
       </c>
       <c r="D916" s="2"/>
     </row>
@@ -18271,10 +18250,10 @@
         <v>95</v>
       </c>
       <c r="B917" t="s" s="2">
+        <v>1928</v>
+      </c>
+      <c r="C917" t="s" s="2">
         <v>1929</v>
-      </c>
-      <c r="C917" t="s" s="2">
-        <v>1930</v>
       </c>
       <c r="D917" s="2"/>
     </row>
@@ -18283,10 +18262,10 @@
         <v>95</v>
       </c>
       <c r="B918" t="s" s="2">
+        <v>1930</v>
+      </c>
+      <c r="C918" t="s" s="2">
         <v>1931</v>
-      </c>
-      <c r="C918" t="s" s="2">
-        <v>1932</v>
       </c>
       <c r="D918" s="2"/>
     </row>
@@ -18295,10 +18274,10 @@
         <v>95</v>
       </c>
       <c r="B919" t="s" s="2">
+        <v>1932</v>
+      </c>
+      <c r="C919" t="s" s="2">
         <v>1933</v>
-      </c>
-      <c r="C919" t="s" s="2">
-        <v>1934</v>
       </c>
       <c r="D919" s="2"/>
     </row>
@@ -18307,10 +18286,10 @@
         <v>95</v>
       </c>
       <c r="B920" t="s" s="2">
+        <v>1934</v>
+      </c>
+      <c r="C920" t="s" s="2">
         <v>1935</v>
-      </c>
-      <c r="C920" t="s" s="2">
-        <v>1936</v>
       </c>
       <c r="D920" s="2"/>
     </row>
@@ -18319,10 +18298,10 @@
         <v>95</v>
       </c>
       <c r="B921" t="s" s="2">
+        <v>1936</v>
+      </c>
+      <c r="C921" t="s" s="2">
         <v>1937</v>
-      </c>
-      <c r="C921" t="s" s="2">
-        <v>1938</v>
       </c>
       <c r="D921" s="2"/>
     </row>
@@ -18331,10 +18310,10 @@
         <v>95</v>
       </c>
       <c r="B922" t="s" s="2">
+        <v>1938</v>
+      </c>
+      <c r="C922" t="s" s="2">
         <v>1939</v>
-      </c>
-      <c r="C922" t="s" s="2">
-        <v>1940</v>
       </c>
       <c r="D922" s="2"/>
     </row>
@@ -18343,10 +18322,10 @@
         <v>95</v>
       </c>
       <c r="B923" t="s" s="2">
+        <v>1940</v>
+      </c>
+      <c r="C923" t="s" s="2">
         <v>1941</v>
-      </c>
-      <c r="C923" t="s" s="2">
-        <v>1942</v>
       </c>
       <c r="D923" s="2"/>
     </row>
@@ -18355,10 +18334,10 @@
         <v>95</v>
       </c>
       <c r="B924" t="s" s="2">
+        <v>1942</v>
+      </c>
+      <c r="C924" t="s" s="2">
         <v>1943</v>
-      </c>
-      <c r="C924" t="s" s="2">
-        <v>1944</v>
       </c>
       <c r="D924" s="2"/>
     </row>
@@ -18367,10 +18346,10 @@
         <v>95</v>
       </c>
       <c r="B925" t="s" s="2">
+        <v>1944</v>
+      </c>
+      <c r="C925" t="s" s="2">
         <v>1945</v>
-      </c>
-      <c r="C925" t="s" s="2">
-        <v>1946</v>
       </c>
       <c r="D925" s="2"/>
     </row>
@@ -18379,10 +18358,10 @@
         <v>95</v>
       </c>
       <c r="B926" t="s" s="2">
+        <v>1946</v>
+      </c>
+      <c r="C926" t="s" s="2">
         <v>1947</v>
-      </c>
-      <c r="C926" t="s" s="2">
-        <v>1948</v>
       </c>
       <c r="D926" s="2"/>
     </row>
@@ -18391,10 +18370,10 @@
         <v>95</v>
       </c>
       <c r="B927" t="s" s="2">
+        <v>1948</v>
+      </c>
+      <c r="C927" t="s" s="2">
         <v>1949</v>
-      </c>
-      <c r="C927" t="s" s="2">
-        <v>1950</v>
       </c>
       <c r="D927" s="2"/>
     </row>
@@ -18403,10 +18382,10 @@
         <v>95</v>
       </c>
       <c r="B928" t="s" s="2">
+        <v>1950</v>
+      </c>
+      <c r="C928" t="s" s="2">
         <v>1951</v>
-      </c>
-      <c r="C928" t="s" s="2">
-        <v>1952</v>
       </c>
       <c r="D928" s="2"/>
     </row>
@@ -18415,10 +18394,10 @@
         <v>95</v>
       </c>
       <c r="B929" t="s" s="2">
+        <v>1952</v>
+      </c>
+      <c r="C929" t="s" s="2">
         <v>1953</v>
-      </c>
-      <c r="C929" t="s" s="2">
-        <v>1954</v>
       </c>
       <c r="D929" s="2"/>
     </row>
@@ -18427,10 +18406,10 @@
         <v>95</v>
       </c>
       <c r="B930" t="s" s="2">
+        <v>1954</v>
+      </c>
+      <c r="C930" t="s" s="2">
         <v>1955</v>
-      </c>
-      <c r="C930" t="s" s="2">
-        <v>1956</v>
       </c>
       <c r="D930" s="2"/>
     </row>
@@ -18439,10 +18418,10 @@
         <v>95</v>
       </c>
       <c r="B931" t="s" s="2">
+        <v>1956</v>
+      </c>
+      <c r="C931" t="s" s="2">
         <v>1957</v>
-      </c>
-      <c r="C931" t="s" s="2">
-        <v>1958</v>
       </c>
       <c r="D931" s="2"/>
     </row>
@@ -18451,10 +18430,10 @@
         <v>95</v>
       </c>
       <c r="B932" t="s" s="2">
+        <v>1958</v>
+      </c>
+      <c r="C932" t="s" s="2">
         <v>1959</v>
-      </c>
-      <c r="C932" t="s" s="2">
-        <v>1960</v>
       </c>
       <c r="D932" s="2"/>
     </row>
@@ -18463,10 +18442,10 @@
         <v>95</v>
       </c>
       <c r="B933" t="s" s="2">
+        <v>1960</v>
+      </c>
+      <c r="C933" t="s" s="2">
         <v>1961</v>
-      </c>
-      <c r="C933" t="s" s="2">
-        <v>1962</v>
       </c>
       <c r="D933" s="2"/>
     </row>
@@ -18475,10 +18454,10 @@
         <v>95</v>
       </c>
       <c r="B934" t="s" s="2">
+        <v>1962</v>
+      </c>
+      <c r="C934" t="s" s="2">
         <v>1963</v>
-      </c>
-      <c r="C934" t="s" s="2">
-        <v>1964</v>
       </c>
       <c r="D934" s="2"/>
     </row>
@@ -18487,10 +18466,10 @@
         <v>95</v>
       </c>
       <c r="B935" t="s" s="2">
+        <v>1964</v>
+      </c>
+      <c r="C935" t="s" s="2">
         <v>1965</v>
-      </c>
-      <c r="C935" t="s" s="2">
-        <v>1966</v>
       </c>
       <c r="D935" s="2"/>
     </row>
@@ -18499,10 +18478,10 @@
         <v>95</v>
       </c>
       <c r="B936" t="s" s="2">
+        <v>1966</v>
+      </c>
+      <c r="C936" t="s" s="2">
         <v>1967</v>
-      </c>
-      <c r="C936" t="s" s="2">
-        <v>1968</v>
       </c>
       <c r="D936" s="2"/>
     </row>
@@ -18511,10 +18490,10 @@
         <v>95</v>
       </c>
       <c r="B937" t="s" s="2">
+        <v>1968</v>
+      </c>
+      <c r="C937" t="s" s="2">
         <v>1969</v>
-      </c>
-      <c r="C937" t="s" s="2">
-        <v>1970</v>
       </c>
       <c r="D937" s="2"/>
     </row>
@@ -18523,10 +18502,10 @@
         <v>95</v>
       </c>
       <c r="B938" t="s" s="2">
+        <v>1970</v>
+      </c>
+      <c r="C938" t="s" s="2">
         <v>1971</v>
-      </c>
-      <c r="C938" t="s" s="2">
-        <v>1972</v>
       </c>
       <c r="D938" s="2"/>
     </row>
@@ -18535,10 +18514,10 @@
         <v>95</v>
       </c>
       <c r="B939" t="s" s="2">
+        <v>1972</v>
+      </c>
+      <c r="C939" t="s" s="2">
         <v>1973</v>
-      </c>
-      <c r="C939" t="s" s="2">
-        <v>1974</v>
       </c>
       <c r="D939" s="2"/>
     </row>
@@ -18547,10 +18526,10 @@
         <v>95</v>
       </c>
       <c r="B940" t="s" s="2">
+        <v>1974</v>
+      </c>
+      <c r="C940" t="s" s="2">
         <v>1975</v>
-      </c>
-      <c r="C940" t="s" s="2">
-        <v>1976</v>
       </c>
       <c r="D940" s="2"/>
     </row>
@@ -18559,10 +18538,10 @@
         <v>95</v>
       </c>
       <c r="B941" t="s" s="2">
+        <v>1976</v>
+      </c>
+      <c r="C941" t="s" s="2">
         <v>1977</v>
-      </c>
-      <c r="C941" t="s" s="2">
-        <v>1978</v>
       </c>
       <c r="D941" s="2"/>
     </row>
@@ -18571,10 +18550,10 @@
         <v>95</v>
       </c>
       <c r="B942" t="s" s="2">
+        <v>1978</v>
+      </c>
+      <c r="C942" t="s" s="2">
         <v>1979</v>
-      </c>
-      <c r="C942" t="s" s="2">
-        <v>1980</v>
       </c>
       <c r="D942" s="2"/>
     </row>
@@ -18583,10 +18562,10 @@
         <v>95</v>
       </c>
       <c r="B943" t="s" s="2">
+        <v>1980</v>
+      </c>
+      <c r="C943" t="s" s="2">
         <v>1981</v>
-      </c>
-      <c r="C943" t="s" s="2">
-        <v>1982</v>
       </c>
       <c r="D943" s="2"/>
     </row>
@@ -18595,10 +18574,10 @@
         <v>95</v>
       </c>
       <c r="B944" t="s" s="2">
+        <v>1982</v>
+      </c>
+      <c r="C944" t="s" s="2">
         <v>1983</v>
-      </c>
-      <c r="C944" t="s" s="2">
-        <v>1984</v>
       </c>
       <c r="D944" s="2"/>
     </row>
@@ -18607,10 +18586,10 @@
         <v>95</v>
       </c>
       <c r="B945" t="s" s="2">
+        <v>1984</v>
+      </c>
+      <c r="C945" t="s" s="2">
         <v>1985</v>
-      </c>
-      <c r="C945" t="s" s="2">
-        <v>1986</v>
       </c>
       <c r="D945" s="2"/>
     </row>
@@ -18619,10 +18598,10 @@
         <v>95</v>
       </c>
       <c r="B946" t="s" s="2">
+        <v>1986</v>
+      </c>
+      <c r="C946" t="s" s="2">
         <v>1987</v>
-      </c>
-      <c r="C946" t="s" s="2">
-        <v>1988</v>
       </c>
       <c r="D946" s="2"/>
     </row>
@@ -18631,10 +18610,10 @@
         <v>95</v>
       </c>
       <c r="B947" t="s" s="2">
+        <v>1988</v>
+      </c>
+      <c r="C947" t="s" s="2">
         <v>1989</v>
-      </c>
-      <c r="C947" t="s" s="2">
-        <v>1990</v>
       </c>
       <c r="D947" s="2"/>
     </row>
@@ -18643,10 +18622,10 @@
         <v>95</v>
       </c>
       <c r="B948" t="s" s="2">
+        <v>1990</v>
+      </c>
+      <c r="C948" t="s" s="2">
         <v>1991</v>
-      </c>
-      <c r="C948" t="s" s="2">
-        <v>1992</v>
       </c>
       <c r="D948" s="2"/>
     </row>
@@ -18655,10 +18634,10 @@
         <v>95</v>
       </c>
       <c r="B949" t="s" s="2">
+        <v>1992</v>
+      </c>
+      <c r="C949" t="s" s="2">
         <v>1993</v>
-      </c>
-      <c r="C949" t="s" s="2">
-        <v>1994</v>
       </c>
       <c r="D949" s="2"/>
     </row>
@@ -18667,10 +18646,10 @@
         <v>95</v>
       </c>
       <c r="B950" t="s" s="2">
+        <v>1994</v>
+      </c>
+      <c r="C950" t="s" s="2">
         <v>1995</v>
-      </c>
-      <c r="C950" t="s" s="2">
-        <v>1996</v>
       </c>
       <c r="D950" s="2"/>
     </row>
@@ -18679,10 +18658,10 @@
         <v>95</v>
       </c>
       <c r="B951" t="s" s="2">
+        <v>1996</v>
+      </c>
+      <c r="C951" t="s" s="2">
         <v>1997</v>
-      </c>
-      <c r="C951" t="s" s="2">
-        <v>1998</v>
       </c>
       <c r="D951" s="2"/>
     </row>
@@ -18691,10 +18670,10 @@
         <v>95</v>
       </c>
       <c r="B952" t="s" s="2">
+        <v>1998</v>
+      </c>
+      <c r="C952" t="s" s="2">
         <v>1999</v>
-      </c>
-      <c r="C952" t="s" s="2">
-        <v>2000</v>
       </c>
       <c r="D952" s="2"/>
     </row>
@@ -18703,10 +18682,10 @@
         <v>95</v>
       </c>
       <c r="B953" t="s" s="2">
+        <v>2000</v>
+      </c>
+      <c r="C953" t="s" s="2">
         <v>2001</v>
-      </c>
-      <c r="C953" t="s" s="2">
-        <v>2002</v>
       </c>
       <c r="D953" s="2"/>
     </row>
@@ -18715,10 +18694,10 @@
         <v>95</v>
       </c>
       <c r="B954" t="s" s="2">
+        <v>2002</v>
+      </c>
+      <c r="C954" t="s" s="2">
         <v>2003</v>
-      </c>
-      <c r="C954" t="s" s="2">
-        <v>2004</v>
       </c>
       <c r="D954" s="2"/>
     </row>
@@ -18727,10 +18706,10 @@
         <v>95</v>
       </c>
       <c r="B955" t="s" s="2">
+        <v>2004</v>
+      </c>
+      <c r="C955" t="s" s="2">
         <v>2005</v>
-      </c>
-      <c r="C955" t="s" s="2">
-        <v>2006</v>
       </c>
       <c r="D955" s="2"/>
     </row>
@@ -18739,10 +18718,10 @@
         <v>95</v>
       </c>
       <c r="B956" t="s" s="2">
+        <v>2006</v>
+      </c>
+      <c r="C956" t="s" s="2">
         <v>2007</v>
-      </c>
-      <c r="C956" t="s" s="2">
-        <v>2008</v>
       </c>
       <c r="D956" s="2"/>
     </row>
@@ -18751,10 +18730,10 @@
         <v>95</v>
       </c>
       <c r="B957" t="s" s="2">
+        <v>2008</v>
+      </c>
+      <c r="C957" t="s" s="2">
         <v>2009</v>
-      </c>
-      <c r="C957" t="s" s="2">
-        <v>2010</v>
       </c>
       <c r="D957" s="2"/>
     </row>
@@ -18763,10 +18742,10 @@
         <v>95</v>
       </c>
       <c r="B958" t="s" s="2">
+        <v>2010</v>
+      </c>
+      <c r="C958" t="s" s="2">
         <v>2011</v>
-      </c>
-      <c r="C958" t="s" s="2">
-        <v>2012</v>
       </c>
       <c r="D958" s="2"/>
     </row>
@@ -18775,10 +18754,10 @@
         <v>95</v>
       </c>
       <c r="B959" t="s" s="2">
+        <v>2012</v>
+      </c>
+      <c r="C959" t="s" s="2">
         <v>2013</v>
-      </c>
-      <c r="C959" t="s" s="2">
-        <v>2014</v>
       </c>
       <c r="D959" s="2"/>
     </row>
@@ -18787,10 +18766,10 @@
         <v>95</v>
       </c>
       <c r="B960" t="s" s="2">
+        <v>2014</v>
+      </c>
+      <c r="C960" t="s" s="2">
         <v>2015</v>
-      </c>
-      <c r="C960" t="s" s="2">
-        <v>2016</v>
       </c>
       <c r="D960" s="2"/>
     </row>
@@ -18799,10 +18778,10 @@
         <v>95</v>
       </c>
       <c r="B961" t="s" s="2">
+        <v>2016</v>
+      </c>
+      <c r="C961" t="s" s="2">
         <v>2017</v>
-      </c>
-      <c r="C961" t="s" s="2">
-        <v>2018</v>
       </c>
       <c r="D961" s="2"/>
     </row>
@@ -18811,10 +18790,10 @@
         <v>95</v>
       </c>
       <c r="B962" t="s" s="2">
+        <v>2018</v>
+      </c>
+      <c r="C962" t="s" s="2">
         <v>2019</v>
-      </c>
-      <c r="C962" t="s" s="2">
-        <v>2020</v>
       </c>
       <c r="D962" s="2"/>
     </row>
@@ -18823,10 +18802,10 @@
         <v>95</v>
       </c>
       <c r="B963" t="s" s="2">
+        <v>2020</v>
+      </c>
+      <c r="C963" t="s" s="2">
         <v>2021</v>
-      </c>
-      <c r="C963" t="s" s="2">
-        <v>2022</v>
       </c>
       <c r="D963" s="2"/>
     </row>
@@ -18835,10 +18814,10 @@
         <v>95</v>
       </c>
       <c r="B964" t="s" s="2">
+        <v>2022</v>
+      </c>
+      <c r="C964" t="s" s="2">
         <v>2023</v>
-      </c>
-      <c r="C964" t="s" s="2">
-        <v>2024</v>
       </c>
       <c r="D964" s="2"/>
     </row>
@@ -18847,10 +18826,10 @@
         <v>95</v>
       </c>
       <c r="B965" t="s" s="2">
+        <v>2024</v>
+      </c>
+      <c r="C965" t="s" s="2">
         <v>2025</v>
-      </c>
-      <c r="C965" t="s" s="2">
-        <v>2026</v>
       </c>
       <c r="D965" s="2"/>
     </row>
@@ -18859,10 +18838,10 @@
         <v>95</v>
       </c>
       <c r="B966" t="s" s="2">
+        <v>2026</v>
+      </c>
+      <c r="C966" t="s" s="2">
         <v>2027</v>
-      </c>
-      <c r="C966" t="s" s="2">
-        <v>2028</v>
       </c>
       <c r="D966" s="2"/>
     </row>
@@ -18871,10 +18850,10 @@
         <v>95</v>
       </c>
       <c r="B967" t="s" s="2">
+        <v>2028</v>
+      </c>
+      <c r="C967" t="s" s="2">
         <v>2029</v>
-      </c>
-      <c r="C967" t="s" s="2">
-        <v>2030</v>
       </c>
       <c r="D967" s="2"/>
     </row>
@@ -18883,10 +18862,10 @@
         <v>95</v>
       </c>
       <c r="B968" t="s" s="2">
+        <v>2030</v>
+      </c>
+      <c r="C968" t="s" s="2">
         <v>2031</v>
-      </c>
-      <c r="C968" t="s" s="2">
-        <v>2032</v>
       </c>
       <c r="D968" s="2"/>
     </row>
@@ -18895,10 +18874,10 @@
         <v>95</v>
       </c>
       <c r="B969" t="s" s="2">
+        <v>2032</v>
+      </c>
+      <c r="C969" t="s" s="2">
         <v>2033</v>
-      </c>
-      <c r="C969" t="s" s="2">
-        <v>2034</v>
       </c>
       <c r="D969" s="2"/>
     </row>
@@ -18907,10 +18886,10 @@
         <v>95</v>
       </c>
       <c r="B970" t="s" s="2">
+        <v>2034</v>
+      </c>
+      <c r="C970" t="s" s="2">
         <v>2035</v>
-      </c>
-      <c r="C970" t="s" s="2">
-        <v>2036</v>
       </c>
       <c r="D970" s="2"/>
     </row>
@@ -18919,10 +18898,10 @@
         <v>95</v>
       </c>
       <c r="B971" t="s" s="2">
+        <v>2036</v>
+      </c>
+      <c r="C971" t="s" s="2">
         <v>2037</v>
-      </c>
-      <c r="C971" t="s" s="2">
-        <v>2038</v>
       </c>
       <c r="D971" s="2"/>
     </row>
@@ -18931,10 +18910,10 @@
         <v>95</v>
       </c>
       <c r="B972" t="s" s="2">
+        <v>2038</v>
+      </c>
+      <c r="C972" t="s" s="2">
         <v>2039</v>
-      </c>
-      <c r="C972" t="s" s="2">
-        <v>2040</v>
       </c>
       <c r="D972" s="2"/>
     </row>
@@ -18943,10 +18922,10 @@
         <v>95</v>
       </c>
       <c r="B973" t="s" s="2">
+        <v>2040</v>
+      </c>
+      <c r="C973" t="s" s="2">
         <v>2041</v>
-      </c>
-      <c r="C973" t="s" s="2">
-        <v>2042</v>
       </c>
       <c r="D973" s="2"/>
     </row>
@@ -18955,10 +18934,10 @@
         <v>95</v>
       </c>
       <c r="B974" t="s" s="2">
+        <v>2042</v>
+      </c>
+      <c r="C974" t="s" s="2">
         <v>2043</v>
-      </c>
-      <c r="C974" t="s" s="2">
-        <v>2044</v>
       </c>
       <c r="D974" s="2"/>
     </row>
@@ -18967,10 +18946,10 @@
         <v>95</v>
       </c>
       <c r="B975" t="s" s="2">
+        <v>2044</v>
+      </c>
+      <c r="C975" t="s" s="2">
         <v>2045</v>
-      </c>
-      <c r="C975" t="s" s="2">
-        <v>2046</v>
       </c>
       <c r="D975" s="2"/>
     </row>
@@ -18979,10 +18958,10 @@
         <v>95</v>
       </c>
       <c r="B976" t="s" s="2">
+        <v>2046</v>
+      </c>
+      <c r="C976" t="s" s="2">
         <v>2047</v>
-      </c>
-      <c r="C976" t="s" s="2">
-        <v>2048</v>
       </c>
       <c r="D976" s="2"/>
     </row>
@@ -18991,10 +18970,10 @@
         <v>95</v>
       </c>
       <c r="B977" t="s" s="2">
+        <v>2048</v>
+      </c>
+      <c r="C977" t="s" s="2">
         <v>2049</v>
-      </c>
-      <c r="C977" t="s" s="2">
-        <v>2050</v>
       </c>
       <c r="D977" s="2"/>
     </row>
@@ -19003,10 +18982,10 @@
         <v>95</v>
       </c>
       <c r="B978" t="s" s="2">
+        <v>2050</v>
+      </c>
+      <c r="C978" t="s" s="2">
         <v>2051</v>
-      </c>
-      <c r="C978" t="s" s="2">
-        <v>2052</v>
       </c>
       <c r="D978" s="2"/>
     </row>
@@ -19015,10 +18994,10 @@
         <v>95</v>
       </c>
       <c r="B979" t="s" s="2">
+        <v>2052</v>
+      </c>
+      <c r="C979" t="s" s="2">
         <v>2053</v>
-      </c>
-      <c r="C979" t="s" s="2">
-        <v>2054</v>
       </c>
       <c r="D979" s="2"/>
     </row>
@@ -19027,10 +19006,10 @@
         <v>95</v>
       </c>
       <c r="B980" t="s" s="2">
+        <v>2054</v>
+      </c>
+      <c r="C980" t="s" s="2">
         <v>2055</v>
-      </c>
-      <c r="C980" t="s" s="2">
-        <v>2056</v>
       </c>
       <c r="D980" s="2"/>
     </row>
@@ -19039,10 +19018,10 @@
         <v>95</v>
       </c>
       <c r="B981" t="s" s="2">
+        <v>2056</v>
+      </c>
+      <c r="C981" t="s" s="2">
         <v>2057</v>
-      </c>
-      <c r="C981" t="s" s="2">
-        <v>2058</v>
       </c>
       <c r="D981" s="2"/>
     </row>
@@ -19051,10 +19030,10 @@
         <v>95</v>
       </c>
       <c r="B982" t="s" s="2">
+        <v>2058</v>
+      </c>
+      <c r="C982" t="s" s="2">
         <v>2059</v>
-      </c>
-      <c r="C982" t="s" s="2">
-        <v>2060</v>
       </c>
       <c r="D982" s="2"/>
     </row>
@@ -19063,10 +19042,10 @@
         <v>95</v>
       </c>
       <c r="B983" t="s" s="2">
+        <v>2060</v>
+      </c>
+      <c r="C983" t="s" s="2">
         <v>2061</v>
-      </c>
-      <c r="C983" t="s" s="2">
-        <v>2062</v>
       </c>
       <c r="D983" s="2"/>
     </row>
@@ -19075,10 +19054,10 @@
         <v>95</v>
       </c>
       <c r="B984" t="s" s="2">
+        <v>2062</v>
+      </c>
+      <c r="C984" t="s" s="2">
         <v>2063</v>
-      </c>
-      <c r="C984" t="s" s="2">
-        <v>2064</v>
       </c>
       <c r="D984" s="2"/>
     </row>
@@ -19087,10 +19066,10 @@
         <v>95</v>
       </c>
       <c r="B985" t="s" s="2">
+        <v>2064</v>
+      </c>
+      <c r="C985" t="s" s="2">
         <v>2065</v>
-      </c>
-      <c r="C985" t="s" s="2">
-        <v>2066</v>
       </c>
       <c r="D985" s="2"/>
     </row>
@@ -19099,10 +19078,10 @@
         <v>95</v>
       </c>
       <c r="B986" t="s" s="2">
+        <v>2066</v>
+      </c>
+      <c r="C986" t="s" s="2">
         <v>2067</v>
-      </c>
-      <c r="C986" t="s" s="2">
-        <v>2068</v>
       </c>
       <c r="D986" s="2"/>
     </row>
@@ -19111,10 +19090,10 @@
         <v>95</v>
       </c>
       <c r="B987" t="s" s="2">
+        <v>2068</v>
+      </c>
+      <c r="C987" t="s" s="2">
         <v>2069</v>
-      </c>
-      <c r="C987" t="s" s="2">
-        <v>2070</v>
       </c>
       <c r="D987" s="2"/>
     </row>
@@ -19123,10 +19102,10 @@
         <v>95</v>
       </c>
       <c r="B988" t="s" s="2">
+        <v>2070</v>
+      </c>
+      <c r="C988" t="s" s="2">
         <v>2071</v>
-      </c>
-      <c r="C988" t="s" s="2">
-        <v>2072</v>
       </c>
       <c r="D988" s="2"/>
     </row>
@@ -19135,10 +19114,10 @@
         <v>95</v>
       </c>
       <c r="B989" t="s" s="2">
+        <v>2072</v>
+      </c>
+      <c r="C989" t="s" s="2">
         <v>2073</v>
-      </c>
-      <c r="C989" t="s" s="2">
-        <v>2074</v>
       </c>
       <c r="D989" s="2"/>
     </row>
@@ -19147,10 +19126,10 @@
         <v>95</v>
       </c>
       <c r="B990" t="s" s="2">
+        <v>2074</v>
+      </c>
+      <c r="C990" t="s" s="2">
         <v>2075</v>
-      </c>
-      <c r="C990" t="s" s="2">
-        <v>2076</v>
       </c>
       <c r="D990" s="2"/>
     </row>
@@ -19159,10 +19138,10 @@
         <v>95</v>
       </c>
       <c r="B991" t="s" s="2">
+        <v>2076</v>
+      </c>
+      <c r="C991" t="s" s="2">
         <v>2077</v>
-      </c>
-      <c r="C991" t="s" s="2">
-        <v>2078</v>
       </c>
       <c r="D991" s="2"/>
     </row>
@@ -19171,10 +19150,10 @@
         <v>95</v>
       </c>
       <c r="B992" t="s" s="2">
+        <v>2078</v>
+      </c>
+      <c r="C992" t="s" s="2">
         <v>2079</v>
-      </c>
-      <c r="C992" t="s" s="2">
-        <v>2080</v>
       </c>
       <c r="D992" s="2"/>
     </row>
@@ -19183,12 +19162,14 @@
         <v>95</v>
       </c>
       <c r="B993" t="s" s="2">
+        <v>2080</v>
+      </c>
+      <c r="C993" t="s" s="2">
         <v>2081</v>
       </c>
-      <c r="C993" t="s" s="2">
+      <c r="D993" t="s" s="2">
         <v>2082</v>
       </c>
-      <c r="D993" s="2"/>
     </row>
     <row r="994">
       <c r="A994" t="s" s="2">
@@ -19224,19 +19205,17 @@
       <c r="C996" t="s" s="2">
         <v>2088</v>
       </c>
-      <c r="D996" t="s" s="2">
-        <v>2089</v>
-      </c>
+      <c r="D996" s="2"/>
     </row>
     <row r="997">
       <c r="A997" t="s" s="2">
         <v>95</v>
       </c>
       <c r="B997" t="s" s="2">
+        <v>2089</v>
+      </c>
+      <c r="C997" t="s" s="2">
         <v>2090</v>
-      </c>
-      <c r="C997" t="s" s="2">
-        <v>2091</v>
       </c>
       <c r="D997" s="2"/>
     </row>
@@ -19245,10 +19224,10 @@
         <v>95</v>
       </c>
       <c r="B998" t="s" s="2">
+        <v>2091</v>
+      </c>
+      <c r="C998" t="s" s="2">
         <v>2092</v>
-      </c>
-      <c r="C998" t="s" s="2">
-        <v>2093</v>
       </c>
       <c r="D998" s="2"/>
     </row>
@@ -19257,10 +19236,10 @@
         <v>95</v>
       </c>
       <c r="B999" t="s" s="2">
+        <v>2093</v>
+      </c>
+      <c r="C999" t="s" s="2">
         <v>2094</v>
-      </c>
-      <c r="C999" t="s" s="2">
-        <v>2095</v>
       </c>
       <c r="D999" s="2"/>
     </row>
@@ -19269,10 +19248,10 @@
         <v>95</v>
       </c>
       <c r="B1000" t="s" s="2">
+        <v>2095</v>
+      </c>
+      <c r="C1000" t="s" s="2">
         <v>2096</v>
-      </c>
-      <c r="C1000" t="s" s="2">
-        <v>2097</v>
       </c>
       <c r="D1000" s="2"/>
     </row>
@@ -19281,10 +19260,10 @@
         <v>95</v>
       </c>
       <c r="B1001" t="s" s="2">
+        <v>2097</v>
+      </c>
+      <c r="C1001" t="s" s="2">
         <v>2098</v>
-      </c>
-      <c r="C1001" t="s" s="2">
-        <v>2099</v>
       </c>
       <c r="D1001" s="2"/>
     </row>
@@ -19293,10 +19272,10 @@
         <v>95</v>
       </c>
       <c r="B1002" t="s" s="2">
-        <v>2100</v>
+        <v>2099</v>
       </c>
       <c r="C1002" t="s" s="2">
-        <v>2101</v>
+        <v>2099</v>
       </c>
       <c r="D1002" s="2"/>
     </row>
@@ -19305,10 +19284,10 @@
         <v>95</v>
       </c>
       <c r="B1003" t="s" s="2">
-        <v>2102</v>
+        <v>2100</v>
       </c>
       <c r="C1003" t="s" s="2">
-        <v>2103</v>
+        <v>2101</v>
       </c>
       <c r="D1003" s="2"/>
     </row>
@@ -19317,10 +19296,10 @@
         <v>95</v>
       </c>
       <c r="B1004" t="s" s="2">
-        <v>2104</v>
+        <v>2102</v>
       </c>
       <c r="C1004" t="s" s="2">
-        <v>2105</v>
+        <v>2103</v>
       </c>
       <c r="D1004" s="2"/>
     </row>
@@ -19329,10 +19308,10 @@
         <v>95</v>
       </c>
       <c r="B1005" t="s" s="2">
-        <v>2106</v>
+        <v>2104</v>
       </c>
       <c r="C1005" t="s" s="2">
-        <v>2106</v>
+        <v>2105</v>
       </c>
       <c r="D1005" s="2"/>
     </row>
@@ -19341,12 +19320,14 @@
         <v>95</v>
       </c>
       <c r="B1006" t="s" s="2">
+        <v>2106</v>
+      </c>
+      <c r="C1006" t="s" s="2">
         <v>2107</v>
       </c>
-      <c r="C1006" t="s" s="2">
+      <c r="D1006" t="s" s="2">
         <v>2108</v>
       </c>
-      <c r="D1006" s="2"/>
     </row>
     <row r="1007">
       <c r="A1007" t="s" s="2">
@@ -19382,19 +19363,17 @@
       <c r="C1009" t="s" s="2">
         <v>2114</v>
       </c>
-      <c r="D1009" t="s" s="2">
-        <v>2115</v>
-      </c>
+      <c r="D1009" s="2"/>
     </row>
     <row r="1010">
       <c r="A1010" t="s" s="2">
         <v>95</v>
       </c>
       <c r="B1010" t="s" s="2">
+        <v>2115</v>
+      </c>
+      <c r="C1010" t="s" s="2">
         <v>2116</v>
-      </c>
-      <c r="C1010" t="s" s="2">
-        <v>2117</v>
       </c>
       <c r="D1010" s="2"/>
     </row>
@@ -19403,10 +19382,10 @@
         <v>95</v>
       </c>
       <c r="B1011" t="s" s="2">
+        <v>2117</v>
+      </c>
+      <c r="C1011" t="s" s="2">
         <v>2118</v>
-      </c>
-      <c r="C1011" t="s" s="2">
-        <v>2119</v>
       </c>
       <c r="D1011" s="2"/>
     </row>
@@ -19415,10 +19394,10 @@
         <v>95</v>
       </c>
       <c r="B1012" t="s" s="2">
+        <v>2119</v>
+      </c>
+      <c r="C1012" t="s" s="2">
         <v>2120</v>
-      </c>
-      <c r="C1012" t="s" s="2">
-        <v>2121</v>
       </c>
       <c r="D1012" s="2"/>
     </row>
@@ -19427,10 +19406,10 @@
         <v>95</v>
       </c>
       <c r="B1013" t="s" s="2">
+        <v>2121</v>
+      </c>
+      <c r="C1013" t="s" s="2">
         <v>2122</v>
-      </c>
-      <c r="C1013" t="s" s="2">
-        <v>2123</v>
       </c>
       <c r="D1013" s="2"/>
     </row>
@@ -19439,10 +19418,10 @@
         <v>95</v>
       </c>
       <c r="B1014" t="s" s="2">
+        <v>2123</v>
+      </c>
+      <c r="C1014" t="s" s="2">
         <v>2124</v>
-      </c>
-      <c r="C1014" t="s" s="2">
-        <v>2125</v>
       </c>
       <c r="D1014" s="2"/>
     </row>
@@ -19451,10 +19430,10 @@
         <v>95</v>
       </c>
       <c r="B1015" t="s" s="2">
+        <v>2125</v>
+      </c>
+      <c r="C1015" t="s" s="2">
         <v>2126</v>
-      </c>
-      <c r="C1015" t="s" s="2">
-        <v>2127</v>
       </c>
       <c r="D1015" s="2"/>
     </row>
@@ -19463,10 +19442,10 @@
         <v>95</v>
       </c>
       <c r="B1016" t="s" s="2">
+        <v>2127</v>
+      </c>
+      <c r="C1016" t="s" s="2">
         <v>2128</v>
-      </c>
-      <c r="C1016" t="s" s="2">
-        <v>2129</v>
       </c>
       <c r="D1016" s="2"/>
     </row>
@@ -19475,10 +19454,10 @@
         <v>95</v>
       </c>
       <c r="B1017" t="s" s="2">
+        <v>2129</v>
+      </c>
+      <c r="C1017" t="s" s="2">
         <v>2130</v>
-      </c>
-      <c r="C1017" t="s" s="2">
-        <v>2131</v>
       </c>
       <c r="D1017" s="2"/>
     </row>
@@ -19487,10 +19466,10 @@
         <v>95</v>
       </c>
       <c r="B1018" t="s" s="2">
+        <v>2131</v>
+      </c>
+      <c r="C1018" t="s" s="2">
         <v>2132</v>
-      </c>
-      <c r="C1018" t="s" s="2">
-        <v>2133</v>
       </c>
       <c r="D1018" s="2"/>
     </row>
@@ -19499,10 +19478,10 @@
         <v>95</v>
       </c>
       <c r="B1019" t="s" s="2">
+        <v>2133</v>
+      </c>
+      <c r="C1019" t="s" s="2">
         <v>2134</v>
-      </c>
-      <c r="C1019" t="s" s="2">
-        <v>2135</v>
       </c>
       <c r="D1019" s="2"/>
     </row>
@@ -19511,10 +19490,10 @@
         <v>95</v>
       </c>
       <c r="B1020" t="s" s="2">
+        <v>2135</v>
+      </c>
+      <c r="C1020" t="s" s="2">
         <v>2136</v>
-      </c>
-      <c r="C1020" t="s" s="2">
-        <v>2137</v>
       </c>
       <c r="D1020" s="2"/>
     </row>
@@ -19523,10 +19502,10 @@
         <v>95</v>
       </c>
       <c r="B1021" t="s" s="2">
+        <v>2137</v>
+      </c>
+      <c r="C1021" t="s" s="2">
         <v>2138</v>
-      </c>
-      <c r="C1021" t="s" s="2">
-        <v>2139</v>
       </c>
       <c r="D1021" s="2"/>
     </row>
@@ -19535,10 +19514,10 @@
         <v>95</v>
       </c>
       <c r="B1022" t="s" s="2">
+        <v>2139</v>
+      </c>
+      <c r="C1022" t="s" s="2">
         <v>2140</v>
-      </c>
-      <c r="C1022" t="s" s="2">
-        <v>2141</v>
       </c>
       <c r="D1022" s="2"/>
     </row>
@@ -19547,10 +19526,10 @@
         <v>95</v>
       </c>
       <c r="B1023" t="s" s="2">
+        <v>2141</v>
+      </c>
+      <c r="C1023" t="s" s="2">
         <v>2142</v>
-      </c>
-      <c r="C1023" t="s" s="2">
-        <v>2143</v>
       </c>
       <c r="D1023" s="2"/>
     </row>
@@ -19559,10 +19538,10 @@
         <v>95</v>
       </c>
       <c r="B1024" t="s" s="2">
+        <v>2143</v>
+      </c>
+      <c r="C1024" t="s" s="2">
         <v>2144</v>
-      </c>
-      <c r="C1024" t="s" s="2">
-        <v>2145</v>
       </c>
       <c r="D1024" s="2"/>
     </row>
@@ -19571,10 +19550,10 @@
         <v>95</v>
       </c>
       <c r="B1025" t="s" s="2">
+        <v>2145</v>
+      </c>
+      <c r="C1025" t="s" s="2">
         <v>2146</v>
-      </c>
-      <c r="C1025" t="s" s="2">
-        <v>2147</v>
       </c>
       <c r="D1025" s="2"/>
     </row>
@@ -19583,10 +19562,10 @@
         <v>95</v>
       </c>
       <c r="B1026" t="s" s="2">
+        <v>2147</v>
+      </c>
+      <c r="C1026" t="s" s="2">
         <v>2148</v>
-      </c>
-      <c r="C1026" t="s" s="2">
-        <v>2149</v>
       </c>
       <c r="D1026" s="2"/>
     </row>
@@ -19595,10 +19574,10 @@
         <v>95</v>
       </c>
       <c r="B1027" t="s" s="2">
+        <v>2149</v>
+      </c>
+      <c r="C1027" t="s" s="2">
         <v>2150</v>
-      </c>
-      <c r="C1027" t="s" s="2">
-        <v>2151</v>
       </c>
       <c r="D1027" s="2"/>
     </row>
@@ -19607,10 +19586,10 @@
         <v>95</v>
       </c>
       <c r="B1028" t="s" s="2">
+        <v>2151</v>
+      </c>
+      <c r="C1028" t="s" s="2">
         <v>2152</v>
-      </c>
-      <c r="C1028" t="s" s="2">
-        <v>2153</v>
       </c>
       <c r="D1028" s="2"/>
     </row>
@@ -19619,10 +19598,10 @@
         <v>95</v>
       </c>
       <c r="B1029" t="s" s="2">
+        <v>2153</v>
+      </c>
+      <c r="C1029" t="s" s="2">
         <v>2154</v>
-      </c>
-      <c r="C1029" t="s" s="2">
-        <v>2155</v>
       </c>
       <c r="D1029" s="2"/>
     </row>
@@ -19631,10 +19610,10 @@
         <v>95</v>
       </c>
       <c r="B1030" t="s" s="2">
+        <v>2155</v>
+      </c>
+      <c r="C1030" t="s" s="2">
         <v>2156</v>
-      </c>
-      <c r="C1030" t="s" s="2">
-        <v>2157</v>
       </c>
       <c r="D1030" s="2"/>
     </row>
@@ -19643,10 +19622,10 @@
         <v>95</v>
       </c>
       <c r="B1031" t="s" s="2">
+        <v>2157</v>
+      </c>
+      <c r="C1031" t="s" s="2">
         <v>2158</v>
-      </c>
-      <c r="C1031" t="s" s="2">
-        <v>2159</v>
       </c>
       <c r="D1031" s="2"/>
     </row>
@@ -19655,10 +19634,10 @@
         <v>95</v>
       </c>
       <c r="B1032" t="s" s="2">
+        <v>2159</v>
+      </c>
+      <c r="C1032" t="s" s="2">
         <v>2160</v>
-      </c>
-      <c r="C1032" t="s" s="2">
-        <v>2161</v>
       </c>
       <c r="D1032" s="2"/>
     </row>
@@ -19667,10 +19646,10 @@
         <v>95</v>
       </c>
       <c r="B1033" t="s" s="2">
+        <v>2161</v>
+      </c>
+      <c r="C1033" t="s" s="2">
         <v>2162</v>
-      </c>
-      <c r="C1033" t="s" s="2">
-        <v>2163</v>
       </c>
       <c r="D1033" s="2"/>
     </row>
@@ -19679,10 +19658,10 @@
         <v>95</v>
       </c>
       <c r="B1034" t="s" s="2">
+        <v>2163</v>
+      </c>
+      <c r="C1034" t="s" s="2">
         <v>2164</v>
-      </c>
-      <c r="C1034" t="s" s="2">
-        <v>2165</v>
       </c>
       <c r="D1034" s="2"/>
     </row>
@@ -19691,10 +19670,10 @@
         <v>95</v>
       </c>
       <c r="B1035" t="s" s="2">
+        <v>2165</v>
+      </c>
+      <c r="C1035" t="s" s="2">
         <v>2166</v>
-      </c>
-      <c r="C1035" t="s" s="2">
-        <v>2167</v>
       </c>
       <c r="D1035" s="2"/>
     </row>
@@ -19703,10 +19682,10 @@
         <v>95</v>
       </c>
       <c r="B1036" t="s" s="2">
+        <v>2167</v>
+      </c>
+      <c r="C1036" t="s" s="2">
         <v>2168</v>
-      </c>
-      <c r="C1036" t="s" s="2">
-        <v>2169</v>
       </c>
       <c r="D1036" s="2"/>
     </row>
@@ -19715,10 +19694,10 @@
         <v>95</v>
       </c>
       <c r="B1037" t="s" s="2">
+        <v>2169</v>
+      </c>
+      <c r="C1037" t="s" s="2">
         <v>2170</v>
-      </c>
-      <c r="C1037" t="s" s="2">
-        <v>2171</v>
       </c>
       <c r="D1037" s="2"/>
     </row>
@@ -19727,10 +19706,10 @@
         <v>95</v>
       </c>
       <c r="B1038" t="s" s="2">
+        <v>2171</v>
+      </c>
+      <c r="C1038" t="s" s="2">
         <v>2172</v>
-      </c>
-      <c r="C1038" t="s" s="2">
-        <v>2173</v>
       </c>
       <c r="D1038" s="2"/>
     </row>
@@ -19739,10 +19718,10 @@
         <v>95</v>
       </c>
       <c r="B1039" t="s" s="2">
+        <v>2173</v>
+      </c>
+      <c r="C1039" t="s" s="2">
         <v>2174</v>
-      </c>
-      <c r="C1039" t="s" s="2">
-        <v>2175</v>
       </c>
       <c r="D1039" s="2"/>
     </row>
@@ -19751,10 +19730,10 @@
         <v>95</v>
       </c>
       <c r="B1040" t="s" s="2">
+        <v>2175</v>
+      </c>
+      <c r="C1040" t="s" s="2">
         <v>2176</v>
-      </c>
-      <c r="C1040" t="s" s="2">
-        <v>2177</v>
       </c>
       <c r="D1040" s="2"/>
     </row>
@@ -19763,10 +19742,10 @@
         <v>95</v>
       </c>
       <c r="B1041" t="s" s="2">
+        <v>2177</v>
+      </c>
+      <c r="C1041" t="s" s="2">
         <v>2178</v>
-      </c>
-      <c r="C1041" t="s" s="2">
-        <v>2179</v>
       </c>
       <c r="D1041" s="2"/>
     </row>
@@ -19775,10 +19754,10 @@
         <v>95</v>
       </c>
       <c r="B1042" t="s" s="2">
+        <v>2179</v>
+      </c>
+      <c r="C1042" t="s" s="2">
         <v>2180</v>
-      </c>
-      <c r="C1042" t="s" s="2">
-        <v>2181</v>
       </c>
       <c r="D1042" s="2"/>
     </row>
@@ -19787,10 +19766,10 @@
         <v>95</v>
       </c>
       <c r="B1043" t="s" s="2">
+        <v>2181</v>
+      </c>
+      <c r="C1043" t="s" s="2">
         <v>2182</v>
-      </c>
-      <c r="C1043" t="s" s="2">
-        <v>2183</v>
       </c>
       <c r="D1043" s="2"/>
     </row>
@@ -19799,10 +19778,10 @@
         <v>95</v>
       </c>
       <c r="B1044" t="s" s="2">
+        <v>2183</v>
+      </c>
+      <c r="C1044" t="s" s="2">
         <v>2184</v>
-      </c>
-      <c r="C1044" t="s" s="2">
-        <v>2185</v>
       </c>
       <c r="D1044" s="2"/>
     </row>
@@ -19811,10 +19790,10 @@
         <v>95</v>
       </c>
       <c r="B1045" t="s" s="2">
+        <v>2185</v>
+      </c>
+      <c r="C1045" t="s" s="2">
         <v>2186</v>
-      </c>
-      <c r="C1045" t="s" s="2">
-        <v>2187</v>
       </c>
       <c r="D1045" s="2"/>
     </row>
@@ -19823,10 +19802,10 @@
         <v>95</v>
       </c>
       <c r="B1046" t="s" s="2">
+        <v>2187</v>
+      </c>
+      <c r="C1046" t="s" s="2">
         <v>2188</v>
-      </c>
-      <c r="C1046" t="s" s="2">
-        <v>2189</v>
       </c>
       <c r="D1046" s="2"/>
     </row>
@@ -19835,10 +19814,10 @@
         <v>95</v>
       </c>
       <c r="B1047" t="s" s="2">
+        <v>2189</v>
+      </c>
+      <c r="C1047" t="s" s="2">
         <v>2190</v>
-      </c>
-      <c r="C1047" t="s" s="2">
-        <v>2191</v>
       </c>
       <c r="D1047" s="2"/>
     </row>
@@ -19847,48 +19826,12 @@
         <v>95</v>
       </c>
       <c r="B1048" t="s" s="2">
+        <v>2191</v>
+      </c>
+      <c r="C1048" t="s" s="2">
         <v>2192</v>
       </c>
-      <c r="C1048" t="s" s="2">
-        <v>2193</v>
-      </c>
       <c r="D1048" s="2"/>
-    </row>
-    <row r="1049">
-      <c r="A1049" t="s" s="2">
-        <v>95</v>
-      </c>
-      <c r="B1049" t="s" s="2">
-        <v>2194</v>
-      </c>
-      <c r="C1049" t="s" s="2">
-        <v>2195</v>
-      </c>
-      <c r="D1049" s="2"/>
-    </row>
-    <row r="1050">
-      <c r="A1050" t="s" s="2">
-        <v>95</v>
-      </c>
-      <c r="B1050" t="s" s="2">
-        <v>2196</v>
-      </c>
-      <c r="C1050" t="s" s="2">
-        <v>2197</v>
-      </c>
-      <c r="D1050" s="2"/>
-    </row>
-    <row r="1051">
-      <c r="A1051" t="s" s="2">
-        <v>95</v>
-      </c>
-      <c r="B1051" t="s" s="2">
-        <v>2198</v>
-      </c>
-      <c r="C1051" t="s" s="2">
-        <v>2199</v>
-      </c>
-      <c r="D1051" s="2"/>
     </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>

--- a/ig/main/CodeSystem-terminologie-nabm.xlsx
+++ b/ig/main/CodeSystem-terminologie-nabm.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3271" uniqueCount="2193">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3277" uniqueCount="2197">
   <si>
     <t>Property</t>
   </si>
@@ -41,7 +41,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>V100</t>
+    <t>V101</t>
   </si>
   <si>
     <t>Name</t>
@@ -71,7 +71,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-12-18T00:00:00+00:00</t>
+    <t>2026-01-13T00:00:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -131,7 +131,7 @@
     <t>Count</t>
   </si>
   <si>
-    <t>1047</t>
+    <t>1049</t>
   </si>
   <si>
     <t>Code</t>
@@ -720,6 +720,12 @@
   </si>
   <si>
     <t>ELECTROPHORESE DE L'HEMOGLOBINE (GEL POLYACRYLAMIDE)</t>
+  </si>
+  <si>
+    <t>1004</t>
+  </si>
+  <si>
+    <t>HYBRIDATION SUR PUCE A ADN EN CONTEXTE POST NATAL</t>
   </si>
   <si>
     <t>1246</t>
@@ -6180,6 +6186,12 @@
   </si>
   <si>
     <t>OSTEOCALCINE (SANG)</t>
+  </si>
+  <si>
+    <t>1005</t>
+  </si>
+  <si>
+    <t>REINTERPRETATION - HYBRIDATION SUR PUCE A ADN EN CONTEXTE POST NATAL</t>
   </si>
   <si>
     <t>1114</t>
@@ -7234,7 +7246,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:D1048"/>
+  <dimension ref="A1:D1050"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -10717,21 +10729,21 @@
       <c r="C290" t="s" s="2">
         <v>672</v>
       </c>
-      <c r="D290" t="s" s="2">
-        <v>673</v>
-      </c>
+      <c r="D290" s="2"/>
     </row>
     <row r="291">
       <c r="A291" t="s" s="2">
         <v>95</v>
       </c>
       <c r="B291" t="s" s="2">
+        <v>673</v>
+      </c>
+      <c r="C291" t="s" s="2">
         <v>674</v>
       </c>
-      <c r="C291" t="s" s="2">
+      <c r="D291" t="s" s="2">
         <v>675</v>
       </c>
-      <c r="D291" s="2"/>
     </row>
     <row r="292">
       <c r="A292" t="s" s="2">
@@ -10911,21 +10923,21 @@
       <c r="C306" t="s" s="2">
         <v>705</v>
       </c>
-      <c r="D306" t="s" s="2">
-        <v>706</v>
-      </c>
+      <c r="D306" s="2"/>
     </row>
     <row r="307">
       <c r="A307" t="s" s="2">
         <v>95</v>
       </c>
       <c r="B307" t="s" s="2">
+        <v>706</v>
+      </c>
+      <c r="C307" t="s" s="2">
         <v>707</v>
       </c>
-      <c r="C307" t="s" s="2">
+      <c r="D307" t="s" s="2">
         <v>708</v>
       </c>
-      <c r="D307" s="2"/>
     </row>
     <row r="308">
       <c r="A308" t="s" s="2">
@@ -11081,21 +11093,21 @@
       <c r="C320" t="s" s="2">
         <v>734</v>
       </c>
-      <c r="D320" t="s" s="2">
-        <v>735</v>
-      </c>
+      <c r="D320" s="2"/>
     </row>
     <row r="321">
       <c r="A321" t="s" s="2">
         <v>95</v>
       </c>
       <c r="B321" t="s" s="2">
+        <v>735</v>
+      </c>
+      <c r="C321" t="s" s="2">
         <v>736</v>
       </c>
-      <c r="C321" t="s" s="2">
+      <c r="D321" t="s" s="2">
         <v>737</v>
       </c>
-      <c r="D321" s="2"/>
     </row>
     <row r="322">
       <c r="A322" t="s" s="2">
@@ -11203,21 +11215,21 @@
       <c r="C330" t="s" s="2">
         <v>755</v>
       </c>
-      <c r="D330" t="s" s="2">
-        <v>756</v>
-      </c>
+      <c r="D330" s="2"/>
     </row>
     <row r="331">
       <c r="A331" t="s" s="2">
         <v>95</v>
       </c>
       <c r="B331" t="s" s="2">
+        <v>756</v>
+      </c>
+      <c r="C331" t="s" s="2">
         <v>757</v>
       </c>
-      <c r="C331" t="s" s="2">
+      <c r="D331" t="s" s="2">
         <v>758</v>
       </c>
-      <c r="D331" s="2"/>
     </row>
     <row r="332">
       <c r="A332" t="s" s="2">
@@ -11325,21 +11337,21 @@
       <c r="C340" t="s" s="2">
         <v>776</v>
       </c>
-      <c r="D340" t="s" s="2">
-        <v>777</v>
-      </c>
+      <c r="D340" s="2"/>
     </row>
     <row r="341">
       <c r="A341" t="s" s="2">
         <v>95</v>
       </c>
       <c r="B341" t="s" s="2">
+        <v>777</v>
+      </c>
+      <c r="C341" t="s" s="2">
         <v>778</v>
       </c>
-      <c r="C341" t="s" s="2">
+      <c r="D341" t="s" s="2">
         <v>779</v>
       </c>
-      <c r="D341" s="2"/>
     </row>
     <row r="342">
       <c r="A342" t="s" s="2">
@@ -11579,21 +11591,21 @@
       <c r="C361" t="s" s="2">
         <v>819</v>
       </c>
-      <c r="D361" t="s" s="2">
-        <v>820</v>
-      </c>
+      <c r="D361" s="2"/>
     </row>
     <row r="362">
       <c r="A362" t="s" s="2">
         <v>95</v>
       </c>
       <c r="B362" t="s" s="2">
+        <v>820</v>
+      </c>
+      <c r="C362" t="s" s="2">
         <v>821</v>
       </c>
-      <c r="C362" t="s" s="2">
+      <c r="D362" t="s" s="2">
         <v>822</v>
       </c>
-      <c r="D362" s="2"/>
     </row>
     <row r="363">
       <c r="A363" t="s" s="2">
@@ -11821,21 +11833,21 @@
       <c r="C381" t="s" s="2">
         <v>860</v>
       </c>
-      <c r="D381" t="s" s="2">
-        <v>861</v>
-      </c>
+      <c r="D381" s="2"/>
     </row>
     <row r="382">
       <c r="A382" t="s" s="2">
         <v>95</v>
       </c>
       <c r="B382" t="s" s="2">
+        <v>861</v>
+      </c>
+      <c r="C382" t="s" s="2">
         <v>862</v>
       </c>
-      <c r="C382" t="s" s="2">
+      <c r="D382" t="s" s="2">
         <v>863</v>
       </c>
-      <c r="D382" s="2"/>
     </row>
     <row r="383">
       <c r="A383" t="s" s="2">
@@ -12646,10 +12658,10 @@
         <v>95</v>
       </c>
       <c r="B450" t="s" s="2">
-        <v>10</v>
+        <v>998</v>
       </c>
       <c r="C450" t="s" s="2">
-        <v>10</v>
+        <v>999</v>
       </c>
       <c r="D450" s="2"/>
     </row>
@@ -12658,10 +12670,10 @@
         <v>95</v>
       </c>
       <c r="B451" t="s" s="2">
-        <v>998</v>
+        <v>10</v>
       </c>
       <c r="C451" t="s" s="2">
-        <v>999</v>
+        <v>10</v>
       </c>
       <c r="D451" s="2"/>
     </row>
@@ -13561,7 +13573,7 @@
         <v>1148</v>
       </c>
       <c r="C526" t="s" s="2">
-        <v>997</v>
+        <v>1149</v>
       </c>
       <c r="D526" s="2"/>
     </row>
@@ -13570,10 +13582,10 @@
         <v>95</v>
       </c>
       <c r="B527" t="s" s="2">
-        <v>1149</v>
+        <v>1150</v>
       </c>
       <c r="C527" t="s" s="2">
-        <v>1150</v>
+        <v>999</v>
       </c>
       <c r="D527" s="2"/>
     </row>
@@ -15181,7 +15193,7 @@
         <v>1417</v>
       </c>
       <c r="C661" t="s" s="2">
-        <v>258</v>
+        <v>1418</v>
       </c>
       <c r="D661" s="2"/>
     </row>
@@ -15190,10 +15202,10 @@
         <v>95</v>
       </c>
       <c r="B662" t="s" s="2">
-        <v>1418</v>
+        <v>1419</v>
       </c>
       <c r="C662" t="s" s="2">
-        <v>1419</v>
+        <v>260</v>
       </c>
       <c r="D662" s="2"/>
     </row>
@@ -19167,19 +19179,17 @@
       <c r="C993" t="s" s="2">
         <v>2081</v>
       </c>
-      <c r="D993" t="s" s="2">
-        <v>2082</v>
-      </c>
+      <c r="D993" s="2"/>
     </row>
     <row r="994">
       <c r="A994" t="s" s="2">
         <v>95</v>
       </c>
       <c r="B994" t="s" s="2">
+        <v>2082</v>
+      </c>
+      <c r="C994" t="s" s="2">
         <v>2083</v>
-      </c>
-      <c r="C994" t="s" s="2">
-        <v>2084</v>
       </c>
       <c r="D994" s="2"/>
     </row>
@@ -19188,12 +19198,14 @@
         <v>95</v>
       </c>
       <c r="B995" t="s" s="2">
+        <v>2084</v>
+      </c>
+      <c r="C995" t="s" s="2">
         <v>2085</v>
       </c>
-      <c r="C995" t="s" s="2">
+      <c r="D995" t="s" s="2">
         <v>2086</v>
       </c>
-      <c r="D995" s="2"/>
     </row>
     <row r="996">
       <c r="A996" t="s" s="2">
@@ -19275,7 +19287,7 @@
         <v>2099</v>
       </c>
       <c r="C1002" t="s" s="2">
-        <v>2099</v>
+        <v>2100</v>
       </c>
       <c r="D1002" s="2"/>
     </row>
@@ -19284,10 +19296,10 @@
         <v>95</v>
       </c>
       <c r="B1003" t="s" s="2">
-        <v>2100</v>
+        <v>2101</v>
       </c>
       <c r="C1003" t="s" s="2">
-        <v>2101</v>
+        <v>2102</v>
       </c>
       <c r="D1003" s="2"/>
     </row>
@@ -19296,7 +19308,7 @@
         <v>95</v>
       </c>
       <c r="B1004" t="s" s="2">
-        <v>2102</v>
+        <v>2103</v>
       </c>
       <c r="C1004" t="s" s="2">
         <v>2103</v>
@@ -19325,19 +19337,17 @@
       <c r="C1006" t="s" s="2">
         <v>2107</v>
       </c>
-      <c r="D1006" t="s" s="2">
-        <v>2108</v>
-      </c>
+      <c r="D1006" s="2"/>
     </row>
     <row r="1007">
       <c r="A1007" t="s" s="2">
         <v>95</v>
       </c>
       <c r="B1007" t="s" s="2">
+        <v>2108</v>
+      </c>
+      <c r="C1007" t="s" s="2">
         <v>2109</v>
-      </c>
-      <c r="C1007" t="s" s="2">
-        <v>2110</v>
       </c>
       <c r="D1007" s="2"/>
     </row>
@@ -19346,12 +19356,14 @@
         <v>95</v>
       </c>
       <c r="B1008" t="s" s="2">
+        <v>2110</v>
+      </c>
+      <c r="C1008" t="s" s="2">
         <v>2111</v>
       </c>
-      <c r="C1008" t="s" s="2">
+      <c r="D1008" t="s" s="2">
         <v>2112</v>
       </c>
-      <c r="D1008" s="2"/>
     </row>
     <row r="1009">
       <c r="A1009" t="s" s="2">
@@ -19832,6 +19844,30 @@
         <v>2192</v>
       </c>
       <c r="D1048" s="2"/>
+    </row>
+    <row r="1049">
+      <c r="A1049" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="B1049" t="s" s="2">
+        <v>2193</v>
+      </c>
+      <c r="C1049" t="s" s="2">
+        <v>2194</v>
+      </c>
+      <c r="D1049" s="2"/>
+    </row>
+    <row r="1050">
+      <c r="A1050" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="B1050" t="s" s="2">
+        <v>2195</v>
+      </c>
+      <c r="C1050" t="s" s="2">
+        <v>2196</v>
+      </c>
+      <c r="D1050" s="2"/>
     </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>

--- a/ig/main/CodeSystem-terminologie-nabm.xlsx
+++ b/ig/main/CodeSystem-terminologie-nabm.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3277" uniqueCount="2197">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3271" uniqueCount="2193">
   <si>
     <t>Property</t>
   </si>
@@ -41,7 +41,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>V101</t>
+    <t>V102</t>
   </si>
   <si>
     <t>Name</t>
@@ -71,7 +71,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-13T00:00:00+00:00</t>
+    <t>2026-02-23T00:00:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -131,7 +131,7 @@
     <t>Count</t>
   </si>
   <si>
-    <t>1049</t>
+    <t>1047</t>
   </si>
   <si>
     <t>Code</t>
@@ -1556,12 +1556,6 @@
     <t>HCG OU BETA HCG (URINES)</t>
   </si>
   <si>
-    <t>4353</t>
-  </si>
-  <si>
-    <t>PALUDISME : SD PAR ELS</t>
-  </si>
-  <si>
     <t>4220</t>
   </si>
   <si>
@@ -1637,7 +1631,7 @@
     <t>4354</t>
   </si>
   <si>
-    <t>PALUDISME : SD PAR IFI</t>
+    <t>PALUDISME</t>
   </si>
   <si>
     <t>0085</t>
@@ -4610,6 +4604,12 @@
     <t>MESURE DE LA CHARGE VIRALE PLASMATIQUE VIH</t>
   </si>
   <si>
+    <t>4364</t>
+  </si>
+  <si>
+    <t>RECHERCHE DE PROTEINES PLASMODIALES DANS LE SANG PAR ICG</t>
+  </si>
+  <si>
     <t>0075</t>
   </si>
   <si>
@@ -5480,12 +5480,6 @@
     <t>OREILLONS (V. OURLIEN) : IMMUNITE ANCIENNE : SD : IGG PAR EIA</t>
   </si>
   <si>
-    <t>1649</t>
-  </si>
-  <si>
-    <t>THEOPHYLLINE DANS UN AUTRE LIQUIDE BIOLOGIQUE QUE LE SANG</t>
-  </si>
-  <si>
     <t>1734</t>
   </si>
   <si>
@@ -6321,12 +6315,6 @@
   </si>
   <si>
     <t>IGE SPEC. : IDENTIF. ALLERGENE UNIQUE (TROPHALLERGENES)</t>
-  </si>
-  <si>
-    <t>0335</t>
-  </si>
-  <si>
-    <t>THEOPHYLLINE (SANG)</t>
   </si>
   <si>
     <t>REGLE_SPECIFIQUE</t>
@@ -7246,7 +7234,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:D1050"/>
+  <dimension ref="A1:D1048"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -10729,21 +10717,21 @@
       <c r="C290" t="s" s="2">
         <v>672</v>
       </c>
-      <c r="D290" s="2"/>
+      <c r="D290" t="s" s="2">
+        <v>673</v>
+      </c>
     </row>
     <row r="291">
       <c r="A291" t="s" s="2">
         <v>95</v>
       </c>
       <c r="B291" t="s" s="2">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="C291" t="s" s="2">
-        <v>674</v>
-      </c>
-      <c r="D291" t="s" s="2">
         <v>675</v>
       </c>
+      <c r="D291" s="2"/>
     </row>
     <row r="292">
       <c r="A292" t="s" s="2">
@@ -10923,21 +10911,21 @@
       <c r="C306" t="s" s="2">
         <v>705</v>
       </c>
-      <c r="D306" s="2"/>
+      <c r="D306" t="s" s="2">
+        <v>706</v>
+      </c>
     </row>
     <row r="307">
       <c r="A307" t="s" s="2">
         <v>95</v>
       </c>
       <c r="B307" t="s" s="2">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="C307" t="s" s="2">
-        <v>707</v>
-      </c>
-      <c r="D307" t="s" s="2">
         <v>708</v>
       </c>
+      <c r="D307" s="2"/>
     </row>
     <row r="308">
       <c r="A308" t="s" s="2">
@@ -11093,21 +11081,21 @@
       <c r="C320" t="s" s="2">
         <v>734</v>
       </c>
-      <c r="D320" s="2"/>
+      <c r="D320" t="s" s="2">
+        <v>735</v>
+      </c>
     </row>
     <row r="321">
       <c r="A321" t="s" s="2">
         <v>95</v>
       </c>
       <c r="B321" t="s" s="2">
-        <v>735</v>
+        <v>736</v>
       </c>
       <c r="C321" t="s" s="2">
-        <v>736</v>
-      </c>
-      <c r="D321" t="s" s="2">
         <v>737</v>
       </c>
+      <c r="D321" s="2"/>
     </row>
     <row r="322">
       <c r="A322" t="s" s="2">
@@ -11215,21 +11203,21 @@
       <c r="C330" t="s" s="2">
         <v>755</v>
       </c>
-      <c r="D330" s="2"/>
+      <c r="D330" t="s" s="2">
+        <v>756</v>
+      </c>
     </row>
     <row r="331">
       <c r="A331" t="s" s="2">
         <v>95</v>
       </c>
       <c r="B331" t="s" s="2">
-        <v>756</v>
+        <v>757</v>
       </c>
       <c r="C331" t="s" s="2">
-        <v>757</v>
-      </c>
-      <c r="D331" t="s" s="2">
         <v>758</v>
       </c>
+      <c r="D331" s="2"/>
     </row>
     <row r="332">
       <c r="A332" t="s" s="2">
@@ -11337,21 +11325,21 @@
       <c r="C340" t="s" s="2">
         <v>776</v>
       </c>
-      <c r="D340" s="2"/>
+      <c r="D340" t="s" s="2">
+        <v>777</v>
+      </c>
     </row>
     <row r="341">
       <c r="A341" t="s" s="2">
         <v>95</v>
       </c>
       <c r="B341" t="s" s="2">
-        <v>777</v>
+        <v>778</v>
       </c>
       <c r="C341" t="s" s="2">
-        <v>778</v>
-      </c>
-      <c r="D341" t="s" s="2">
         <v>779</v>
       </c>
+      <c r="D341" s="2"/>
     </row>
     <row r="342">
       <c r="A342" t="s" s="2">
@@ -11591,21 +11579,21 @@
       <c r="C361" t="s" s="2">
         <v>819</v>
       </c>
-      <c r="D361" s="2"/>
+      <c r="D361" t="s" s="2">
+        <v>820</v>
+      </c>
     </row>
     <row r="362">
       <c r="A362" t="s" s="2">
         <v>95</v>
       </c>
       <c r="B362" t="s" s="2">
-        <v>820</v>
+        <v>821</v>
       </c>
       <c r="C362" t="s" s="2">
-        <v>821</v>
-      </c>
-      <c r="D362" t="s" s="2">
         <v>822</v>
       </c>
+      <c r="D362" s="2"/>
     </row>
     <row r="363">
       <c r="A363" t="s" s="2">
@@ -11833,21 +11821,21 @@
       <c r="C381" t="s" s="2">
         <v>860</v>
       </c>
-      <c r="D381" s="2"/>
+      <c r="D381" t="s" s="2">
+        <v>861</v>
+      </c>
     </row>
     <row r="382">
       <c r="A382" t="s" s="2">
         <v>95</v>
       </c>
       <c r="B382" t="s" s="2">
-        <v>861</v>
+        <v>862</v>
       </c>
       <c r="C382" t="s" s="2">
-        <v>862</v>
-      </c>
-      <c r="D382" t="s" s="2">
         <v>863</v>
       </c>
+      <c r="D382" s="2"/>
     </row>
     <row r="383">
       <c r="A383" t="s" s="2">
@@ -12658,10 +12646,10 @@
         <v>95</v>
       </c>
       <c r="B450" t="s" s="2">
-        <v>998</v>
+        <v>10</v>
       </c>
       <c r="C450" t="s" s="2">
-        <v>999</v>
+        <v>10</v>
       </c>
       <c r="D450" s="2"/>
     </row>
@@ -12670,10 +12658,10 @@
         <v>95</v>
       </c>
       <c r="B451" t="s" s="2">
-        <v>10</v>
+        <v>998</v>
       </c>
       <c r="C451" t="s" s="2">
-        <v>10</v>
+        <v>999</v>
       </c>
       <c r="D451" s="2"/>
     </row>
@@ -13573,7 +13561,7 @@
         <v>1148</v>
       </c>
       <c r="C526" t="s" s="2">
-        <v>1149</v>
+        <v>997</v>
       </c>
       <c r="D526" s="2"/>
     </row>
@@ -13582,10 +13570,10 @@
         <v>95</v>
       </c>
       <c r="B527" t="s" s="2">
+        <v>1149</v>
+      </c>
+      <c r="C527" t="s" s="2">
         <v>1150</v>
-      </c>
-      <c r="C527" t="s" s="2">
-        <v>999</v>
       </c>
       <c r="D527" s="2"/>
     </row>
@@ -15193,7 +15181,7 @@
         <v>1417</v>
       </c>
       <c r="C661" t="s" s="2">
-        <v>1418</v>
+        <v>260</v>
       </c>
       <c r="D661" s="2"/>
     </row>
@@ -15202,10 +15190,10 @@
         <v>95</v>
       </c>
       <c r="B662" t="s" s="2">
+        <v>1418</v>
+      </c>
+      <c r="C662" t="s" s="2">
         <v>1419</v>
-      </c>
-      <c r="C662" t="s" s="2">
-        <v>260</v>
       </c>
       <c r="D662" s="2"/>
     </row>
@@ -19191,21 +19179,21 @@
       <c r="C994" t="s" s="2">
         <v>2083</v>
       </c>
-      <c r="D994" s="2"/>
+      <c r="D994" t="s" s="2">
+        <v>2084</v>
+      </c>
     </row>
     <row r="995">
       <c r="A995" t="s" s="2">
         <v>95</v>
       </c>
       <c r="B995" t="s" s="2">
-        <v>2084</v>
+        <v>2085</v>
       </c>
       <c r="C995" t="s" s="2">
-        <v>2085</v>
-      </c>
-      <c r="D995" t="s" s="2">
         <v>2086</v>
       </c>
+      <c r="D995" s="2"/>
     </row>
     <row r="996">
       <c r="A996" t="s" s="2">
@@ -19287,7 +19275,7 @@
         <v>2099</v>
       </c>
       <c r="C1002" t="s" s="2">
-        <v>2100</v>
+        <v>2099</v>
       </c>
       <c r="D1002" s="2"/>
     </row>
@@ -19296,10 +19284,10 @@
         <v>95</v>
       </c>
       <c r="B1003" t="s" s="2">
+        <v>2100</v>
+      </c>
+      <c r="C1003" t="s" s="2">
         <v>2101</v>
-      </c>
-      <c r="C1003" t="s" s="2">
-        <v>2102</v>
       </c>
       <c r="D1003" s="2"/>
     </row>
@@ -19308,7 +19296,7 @@
         <v>95</v>
       </c>
       <c r="B1004" t="s" s="2">
-        <v>2103</v>
+        <v>2102</v>
       </c>
       <c r="C1004" t="s" s="2">
         <v>2103</v>
@@ -19337,17 +19325,19 @@
       <c r="C1006" t="s" s="2">
         <v>2107</v>
       </c>
-      <c r="D1006" s="2"/>
+      <c r="D1006" t="s" s="2">
+        <v>2108</v>
+      </c>
     </row>
     <row r="1007">
       <c r="A1007" t="s" s="2">
         <v>95</v>
       </c>
       <c r="B1007" t="s" s="2">
-        <v>2108</v>
+        <v>2109</v>
       </c>
       <c r="C1007" t="s" s="2">
-        <v>2109</v>
+        <v>2110</v>
       </c>
       <c r="D1007" s="2"/>
     </row>
@@ -19356,14 +19346,12 @@
         <v>95</v>
       </c>
       <c r="B1008" t="s" s="2">
-        <v>2110</v>
+        <v>2111</v>
       </c>
       <c r="C1008" t="s" s="2">
-        <v>2111</v>
-      </c>
-      <c r="D1008" t="s" s="2">
         <v>2112</v>
       </c>
+      <c r="D1008" s="2"/>
     </row>
     <row r="1009">
       <c r="A1009" t="s" s="2">
@@ -19844,30 +19832,6 @@
         <v>2192</v>
       </c>
       <c r="D1048" s="2"/>
-    </row>
-    <row r="1049">
-      <c r="A1049" t="s" s="2">
-        <v>95</v>
-      </c>
-      <c r="B1049" t="s" s="2">
-        <v>2193</v>
-      </c>
-      <c r="C1049" t="s" s="2">
-        <v>2194</v>
-      </c>
-      <c r="D1049" s="2"/>
-    </row>
-    <row r="1050">
-      <c r="A1050" t="s" s="2">
-        <v>95</v>
-      </c>
-      <c r="B1050" t="s" s="2">
-        <v>2195</v>
-      </c>
-      <c r="C1050" t="s" s="2">
-        <v>2196</v>
-      </c>
-      <c r="D1050" s="2"/>
     </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>

--- a/ig/main/CodeSystem-terminologie-nabm.xlsx
+++ b/ig/main/CodeSystem-terminologie-nabm.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3271" uniqueCount="2193">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3268" uniqueCount="2191">
   <si>
     <t>Property</t>
   </si>
@@ -41,7 +41,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>V102</t>
+    <t>V103</t>
   </si>
   <si>
     <t>Name</t>
@@ -71,7 +71,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-23T00:00:00+00:00</t>
+    <t>2026-04-13T00:00:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -131,7 +131,7 @@
     <t>Count</t>
   </si>
   <si>
-    <t>1047</t>
+    <t>1046</t>
   </si>
   <si>
     <t>Code</t>
@@ -1769,7 +1769,7 @@
     <t>4004</t>
   </si>
   <si>
-    <t>DPN : TRISOMIE 21 FOETALE : DEPISTAGE 2E TRIMESTRE, MARQUEURS SERIQUES MATERNELS</t>
+    <t>DPN:TRISOMIE 21 FOETALE : DEPISTAGE 2E TRIMESTRE,MARQUEURS SERIQUES MATERNELS</t>
   </si>
   <si>
     <t>1704</t>
@@ -1937,7 +1937,7 @@
     <t>4046</t>
   </si>
   <si>
-    <t>DPN PROPREMENT DIT  : MUCOVISCIDOSE : POLYMORPHISME DE L'ADN</t>
+    <t>DPN PROPREMENT DIT : MUCOVISCIDOSE : POLYMORPHISME DE L'ADN</t>
   </si>
   <si>
     <t>1415</t>
@@ -4013,12 +4013,6 @@
     <t>FACTEUR V (PROACCELERINE)- DOSAGE ACTIVITE COAGULANTE</t>
   </si>
   <si>
-    <t>1124</t>
-  </si>
-  <si>
-    <t>VITESSE DE SEDIMENTATION (VS)</t>
-  </si>
-  <si>
     <t>1257</t>
   </si>
   <si>
@@ -5081,7 +5075,7 @@
     <t>4058</t>
   </si>
   <si>
-    <t>DPN : ALPHA-THALASSEMIE AVEC ANTECEDENTS FAMILIAUX CONNUS</t>
+    <t>DPN:ALPHA-THALASSEMIE AVEC ANTECEDENTS FAMILIAUX CONNUS</t>
   </si>
   <si>
     <t>1318</t>
@@ -6398,7 +6392,7 @@
     <t>4095</t>
   </si>
   <si>
-    <t>DPN : DEFICIT CONGENITAL EN FACTEUR DE L'HEMOSTASE (VIII , IX , W, PROT C, S..)</t>
+    <t>DPN:DEFICIT CONGENITAL EN FACTEUR DE L'HEMOSTASE(VIII , IX , W, PROT C, S..)</t>
   </si>
   <si>
     <t>0332</t>
@@ -7234,7 +7228,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:D1048"/>
+  <dimension ref="A1:D1047"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -15169,7 +15163,7 @@
         <v>1415</v>
       </c>
       <c r="C660" t="s" s="2">
-        <v>1416</v>
+        <v>260</v>
       </c>
       <c r="D660" s="2"/>
     </row>
@@ -15178,10 +15172,10 @@
         <v>95</v>
       </c>
       <c r="B661" t="s" s="2">
+        <v>1416</v>
+      </c>
+      <c r="C661" t="s" s="2">
         <v>1417</v>
-      </c>
-      <c r="C661" t="s" s="2">
-        <v>260</v>
       </c>
       <c r="D661" s="2"/>
     </row>
@@ -19167,21 +19161,21 @@
       <c r="C993" t="s" s="2">
         <v>2081</v>
       </c>
-      <c r="D993" s="2"/>
+      <c r="D993" t="s" s="2">
+        <v>2082</v>
+      </c>
     </row>
     <row r="994">
       <c r="A994" t="s" s="2">
         <v>95</v>
       </c>
       <c r="B994" t="s" s="2">
-        <v>2082</v>
+        <v>2083</v>
       </c>
       <c r="C994" t="s" s="2">
-        <v>2083</v>
-      </c>
-      <c r="D994" t="s" s="2">
         <v>2084</v>
       </c>
+      <c r="D994" s="2"/>
     </row>
     <row r="995">
       <c r="A995" t="s" s="2">
@@ -19263,7 +19257,7 @@
         <v>2097</v>
       </c>
       <c r="C1001" t="s" s="2">
-        <v>2098</v>
+        <v>2097</v>
       </c>
       <c r="D1001" s="2"/>
     </row>
@@ -19272,7 +19266,7 @@
         <v>95</v>
       </c>
       <c r="B1002" t="s" s="2">
-        <v>2099</v>
+        <v>2098</v>
       </c>
       <c r="C1002" t="s" s="2">
         <v>2099</v>
@@ -19313,21 +19307,21 @@
       <c r="C1005" t="s" s="2">
         <v>2105</v>
       </c>
-      <c r="D1005" s="2"/>
+      <c r="D1005" t="s" s="2">
+        <v>2106</v>
+      </c>
     </row>
     <row r="1006">
       <c r="A1006" t="s" s="2">
         <v>95</v>
       </c>
       <c r="B1006" t="s" s="2">
-        <v>2106</v>
+        <v>2107</v>
       </c>
       <c r="C1006" t="s" s="2">
-        <v>2107</v>
-      </c>
-      <c r="D1006" t="s" s="2">
         <v>2108</v>
       </c>
+      <c r="D1006" s="2"/>
     </row>
     <row r="1007">
       <c r="A1007" t="s" s="2">
@@ -19820,18 +19814,6 @@
         <v>2190</v>
       </c>
       <c r="D1047" s="2"/>
-    </row>
-    <row r="1048">
-      <c r="A1048" t="s" s="2">
-        <v>95</v>
-      </c>
-      <c r="B1048" t="s" s="2">
-        <v>2191</v>
-      </c>
-      <c r="C1048" t="s" s="2">
-        <v>2192</v>
-      </c>
-      <c r="D1048" s="2"/>
     </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>

--- a/ig/main/CodeSystem-terminologie-nabm.xlsx
+++ b/ig/main/CodeSystem-terminologie-nabm.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3268" uniqueCount="2192">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3280" uniqueCount="2199">
   <si>
     <t>Property</t>
   </si>
@@ -41,7 +41,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>V104</t>
+    <t>V105</t>
   </si>
   <si>
     <t>Name</t>
@@ -71,7 +71,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-26T00:00:00+00:00</t>
+    <t>2026-06-04T00:00:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -131,7 +131,7 @@
     <t>Count</t>
   </si>
   <si>
-    <t>1046</t>
+    <t>1050</t>
   </si>
   <si>
     <t>Code</t>
@@ -2690,6 +2690,12 @@
     <t>EXAMEN ANATOMOPATHOLOGIQUE PAR HYBRIDATION IN SITU</t>
   </si>
   <si>
+    <t>4515</t>
+  </si>
+  <si>
+    <t>SHD DANS LE DIAGNOSTIC DES FORMES DIVERSES DE CARDIOMYOPATHIES</t>
+  </si>
+  <si>
     <t>0024</t>
   </si>
   <si>
@@ -3276,6 +3282,12 @@
   </si>
   <si>
     <t>UR. : CUIVRE</t>
+  </si>
+  <si>
+    <t>4514</t>
+  </si>
+  <si>
+    <t>SHD DANS LE DIAGNOSTIC DES CARDIOMYOPATHIES HYPERTROPHIQUES</t>
   </si>
   <si>
     <t>0463</t>
@@ -4330,9 +4342,6 @@
     <t>HEPATITE C (VHC) : DETECTION QUANTITATIVE GENOME (ARN):</t>
   </si>
   <si>
-    <t>1050</t>
-  </si>
-  <si>
     <t>MESURE DE L'ACTIVITE D'ADAMTS 13</t>
   </si>
   <si>
@@ -6308,6 +6317,12 @@
     <t>PROTOPORPHYRINES ZINC (PPZ)</t>
   </si>
   <si>
+    <t>1692</t>
+  </si>
+  <si>
+    <t>DOSAGE URINAIRE DU CADMIUM (CADMIURIE)</t>
+  </si>
+  <si>
     <t>1014</t>
   </si>
   <si>
@@ -6396,6 +6411,12 @@
   </si>
   <si>
     <t>PARAINFLUENZA (PARAMYXOVIRUS) : SD PAR RFC + ITERATIF</t>
+  </si>
+  <si>
+    <t>1693</t>
+  </si>
+  <si>
+    <t>DOSAGE DANS LE SANG TOTAL DU CADMIUM (CADMIEMIE)</t>
   </si>
   <si>
     <t>8000</t>
@@ -7231,7 +7252,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:D1047"/>
+  <dimension ref="A1:D1051"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -15303,10 +15324,10 @@
         <v>96</v>
       </c>
       <c r="B672" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="C672" t="s" s="2">
         <v>1441</v>
-      </c>
-      <c r="C672" t="s" s="2">
-        <v>1442</v>
       </c>
       <c r="D672" s="2"/>
     </row>
@@ -15315,10 +15336,10 @@
         <v>96</v>
       </c>
       <c r="B673" t="s" s="2">
+        <v>1442</v>
+      </c>
+      <c r="C673" t="s" s="2">
         <v>1443</v>
-      </c>
-      <c r="C673" t="s" s="2">
-        <v>1444</v>
       </c>
       <c r="D673" s="2"/>
     </row>
@@ -15327,10 +15348,10 @@
         <v>96</v>
       </c>
       <c r="B674" t="s" s="2">
+        <v>1444</v>
+      </c>
+      <c r="C674" t="s" s="2">
         <v>1445</v>
-      </c>
-      <c r="C674" t="s" s="2">
-        <v>1446</v>
       </c>
       <c r="D674" s="2"/>
     </row>
@@ -15339,10 +15360,10 @@
         <v>96</v>
       </c>
       <c r="B675" t="s" s="2">
+        <v>1446</v>
+      </c>
+      <c r="C675" t="s" s="2">
         <v>1447</v>
-      </c>
-      <c r="C675" t="s" s="2">
-        <v>1448</v>
       </c>
       <c r="D675" s="2"/>
     </row>
@@ -15351,10 +15372,10 @@
         <v>96</v>
       </c>
       <c r="B676" t="s" s="2">
+        <v>1448</v>
+      </c>
+      <c r="C676" t="s" s="2">
         <v>1449</v>
-      </c>
-      <c r="C676" t="s" s="2">
-        <v>1450</v>
       </c>
       <c r="D676" s="2"/>
     </row>
@@ -15363,10 +15384,10 @@
         <v>96</v>
       </c>
       <c r="B677" t="s" s="2">
+        <v>1450</v>
+      </c>
+      <c r="C677" t="s" s="2">
         <v>1451</v>
-      </c>
-      <c r="C677" t="s" s="2">
-        <v>1452</v>
       </c>
       <c r="D677" s="2"/>
     </row>
@@ -15375,10 +15396,10 @@
         <v>96</v>
       </c>
       <c r="B678" t="s" s="2">
+        <v>1452</v>
+      </c>
+      <c r="C678" t="s" s="2">
         <v>1453</v>
-      </c>
-      <c r="C678" t="s" s="2">
-        <v>1454</v>
       </c>
       <c r="D678" s="2"/>
     </row>
@@ -15387,10 +15408,10 @@
         <v>96</v>
       </c>
       <c r="B679" t="s" s="2">
+        <v>1454</v>
+      </c>
+      <c r="C679" t="s" s="2">
         <v>1455</v>
-      </c>
-      <c r="C679" t="s" s="2">
-        <v>1456</v>
       </c>
       <c r="D679" s="2"/>
     </row>
@@ -15399,10 +15420,10 @@
         <v>96</v>
       </c>
       <c r="B680" t="s" s="2">
+        <v>1456</v>
+      </c>
+      <c r="C680" t="s" s="2">
         <v>1457</v>
-      </c>
-      <c r="C680" t="s" s="2">
-        <v>1458</v>
       </c>
       <c r="D680" s="2"/>
     </row>
@@ -15411,10 +15432,10 @@
         <v>96</v>
       </c>
       <c r="B681" t="s" s="2">
+        <v>1458</v>
+      </c>
+      <c r="C681" t="s" s="2">
         <v>1459</v>
-      </c>
-      <c r="C681" t="s" s="2">
-        <v>1460</v>
       </c>
       <c r="D681" s="2"/>
     </row>
@@ -15423,10 +15444,10 @@
         <v>96</v>
       </c>
       <c r="B682" t="s" s="2">
+        <v>1460</v>
+      </c>
+      <c r="C682" t="s" s="2">
         <v>1461</v>
-      </c>
-      <c r="C682" t="s" s="2">
-        <v>1462</v>
       </c>
       <c r="D682" s="2"/>
     </row>
@@ -15435,10 +15456,10 @@
         <v>96</v>
       </c>
       <c r="B683" t="s" s="2">
+        <v>1462</v>
+      </c>
+      <c r="C683" t="s" s="2">
         <v>1463</v>
-      </c>
-      <c r="C683" t="s" s="2">
-        <v>1464</v>
       </c>
       <c r="D683" s="2"/>
     </row>
@@ -15447,10 +15468,10 @@
         <v>96</v>
       </c>
       <c r="B684" t="s" s="2">
+        <v>1464</v>
+      </c>
+      <c r="C684" t="s" s="2">
         <v>1465</v>
-      </c>
-      <c r="C684" t="s" s="2">
-        <v>1466</v>
       </c>
       <c r="D684" s="2"/>
     </row>
@@ -15459,10 +15480,10 @@
         <v>96</v>
       </c>
       <c r="B685" t="s" s="2">
+        <v>1466</v>
+      </c>
+      <c r="C685" t="s" s="2">
         <v>1467</v>
-      </c>
-      <c r="C685" t="s" s="2">
-        <v>1468</v>
       </c>
       <c r="D685" s="2"/>
     </row>
@@ -15471,10 +15492,10 @@
         <v>96</v>
       </c>
       <c r="B686" t="s" s="2">
+        <v>1468</v>
+      </c>
+      <c r="C686" t="s" s="2">
         <v>1469</v>
-      </c>
-      <c r="C686" t="s" s="2">
-        <v>1470</v>
       </c>
       <c r="D686" s="2"/>
     </row>
@@ -15483,10 +15504,10 @@
         <v>96</v>
       </c>
       <c r="B687" t="s" s="2">
+        <v>1470</v>
+      </c>
+      <c r="C687" t="s" s="2">
         <v>1471</v>
-      </c>
-      <c r="C687" t="s" s="2">
-        <v>1472</v>
       </c>
       <c r="D687" s="2"/>
     </row>
@@ -15495,10 +15516,10 @@
         <v>96</v>
       </c>
       <c r="B688" t="s" s="2">
+        <v>1472</v>
+      </c>
+      <c r="C688" t="s" s="2">
         <v>1473</v>
-      </c>
-      <c r="C688" t="s" s="2">
-        <v>1474</v>
       </c>
       <c r="D688" s="2"/>
     </row>
@@ -15507,10 +15528,10 @@
         <v>96</v>
       </c>
       <c r="B689" t="s" s="2">
+        <v>1474</v>
+      </c>
+      <c r="C689" t="s" s="2">
         <v>1475</v>
-      </c>
-      <c r="C689" t="s" s="2">
-        <v>1476</v>
       </c>
       <c r="D689" s="2"/>
     </row>
@@ -15519,10 +15540,10 @@
         <v>96</v>
       </c>
       <c r="B690" t="s" s="2">
+        <v>1476</v>
+      </c>
+      <c r="C690" t="s" s="2">
         <v>1477</v>
-      </c>
-      <c r="C690" t="s" s="2">
-        <v>1478</v>
       </c>
       <c r="D690" s="2"/>
     </row>
@@ -15531,10 +15552,10 @@
         <v>96</v>
       </c>
       <c r="B691" t="s" s="2">
+        <v>1478</v>
+      </c>
+      <c r="C691" t="s" s="2">
         <v>1479</v>
-      </c>
-      <c r="C691" t="s" s="2">
-        <v>1480</v>
       </c>
       <c r="D691" s="2"/>
     </row>
@@ -15543,10 +15564,10 @@
         <v>96</v>
       </c>
       <c r="B692" t="s" s="2">
+        <v>1480</v>
+      </c>
+      <c r="C692" t="s" s="2">
         <v>1481</v>
-      </c>
-      <c r="C692" t="s" s="2">
-        <v>1482</v>
       </c>
       <c r="D692" s="2"/>
     </row>
@@ -15555,10 +15576,10 @@
         <v>96</v>
       </c>
       <c r="B693" t="s" s="2">
+        <v>1482</v>
+      </c>
+      <c r="C693" t="s" s="2">
         <v>1483</v>
-      </c>
-      <c r="C693" t="s" s="2">
-        <v>1484</v>
       </c>
       <c r="D693" s="2"/>
     </row>
@@ -15567,10 +15588,10 @@
         <v>96</v>
       </c>
       <c r="B694" t="s" s="2">
+        <v>1484</v>
+      </c>
+      <c r="C694" t="s" s="2">
         <v>1485</v>
-      </c>
-      <c r="C694" t="s" s="2">
-        <v>1486</v>
       </c>
       <c r="D694" s="2"/>
     </row>
@@ -15579,10 +15600,10 @@
         <v>96</v>
       </c>
       <c r="B695" t="s" s="2">
+        <v>1486</v>
+      </c>
+      <c r="C695" t="s" s="2">
         <v>1487</v>
-      </c>
-      <c r="C695" t="s" s="2">
-        <v>1488</v>
       </c>
       <c r="D695" s="2"/>
     </row>
@@ -15591,10 +15612,10 @@
         <v>96</v>
       </c>
       <c r="B696" t="s" s="2">
+        <v>1488</v>
+      </c>
+      <c r="C696" t="s" s="2">
         <v>1489</v>
-      </c>
-      <c r="C696" t="s" s="2">
-        <v>1490</v>
       </c>
       <c r="D696" s="2"/>
     </row>
@@ -15603,10 +15624,10 @@
         <v>96</v>
       </c>
       <c r="B697" t="s" s="2">
+        <v>1490</v>
+      </c>
+      <c r="C697" t="s" s="2">
         <v>1491</v>
-      </c>
-      <c r="C697" t="s" s="2">
-        <v>1492</v>
       </c>
       <c r="D697" s="2"/>
     </row>
@@ -15615,10 +15636,10 @@
         <v>96</v>
       </c>
       <c r="B698" t="s" s="2">
+        <v>1492</v>
+      </c>
+      <c r="C698" t="s" s="2">
         <v>1493</v>
-      </c>
-      <c r="C698" t="s" s="2">
-        <v>1494</v>
       </c>
       <c r="D698" s="2"/>
     </row>
@@ -15627,10 +15648,10 @@
         <v>96</v>
       </c>
       <c r="B699" t="s" s="2">
+        <v>1494</v>
+      </c>
+      <c r="C699" t="s" s="2">
         <v>1495</v>
-      </c>
-      <c r="C699" t="s" s="2">
-        <v>1496</v>
       </c>
       <c r="D699" s="2"/>
     </row>
@@ -15639,10 +15660,10 @@
         <v>96</v>
       </c>
       <c r="B700" t="s" s="2">
+        <v>1496</v>
+      </c>
+      <c r="C700" t="s" s="2">
         <v>1497</v>
-      </c>
-      <c r="C700" t="s" s="2">
-        <v>1498</v>
       </c>
       <c r="D700" s="2"/>
     </row>
@@ -15651,10 +15672,10 @@
         <v>96</v>
       </c>
       <c r="B701" t="s" s="2">
+        <v>1498</v>
+      </c>
+      <c r="C701" t="s" s="2">
         <v>1499</v>
-      </c>
-      <c r="C701" t="s" s="2">
-        <v>1500</v>
       </c>
       <c r="D701" s="2"/>
     </row>
@@ -15663,10 +15684,10 @@
         <v>96</v>
       </c>
       <c r="B702" t="s" s="2">
+        <v>1500</v>
+      </c>
+      <c r="C702" t="s" s="2">
         <v>1501</v>
-      </c>
-      <c r="C702" t="s" s="2">
-        <v>1502</v>
       </c>
       <c r="D702" s="2"/>
     </row>
@@ -15675,10 +15696,10 @@
         <v>96</v>
       </c>
       <c r="B703" t="s" s="2">
+        <v>1502</v>
+      </c>
+      <c r="C703" t="s" s="2">
         <v>1503</v>
-      </c>
-      <c r="C703" t="s" s="2">
-        <v>1504</v>
       </c>
       <c r="D703" s="2"/>
     </row>
@@ -15687,10 +15708,10 @@
         <v>96</v>
       </c>
       <c r="B704" t="s" s="2">
+        <v>1504</v>
+      </c>
+      <c r="C704" t="s" s="2">
         <v>1505</v>
-      </c>
-      <c r="C704" t="s" s="2">
-        <v>1506</v>
       </c>
       <c r="D704" s="2"/>
     </row>
@@ -15699,10 +15720,10 @@
         <v>96</v>
       </c>
       <c r="B705" t="s" s="2">
+        <v>1506</v>
+      </c>
+      <c r="C705" t="s" s="2">
         <v>1507</v>
-      </c>
-      <c r="C705" t="s" s="2">
-        <v>1508</v>
       </c>
       <c r="D705" s="2"/>
     </row>
@@ -15711,10 +15732,10 @@
         <v>96</v>
       </c>
       <c r="B706" t="s" s="2">
+        <v>1508</v>
+      </c>
+      <c r="C706" t="s" s="2">
         <v>1509</v>
-      </c>
-      <c r="C706" t="s" s="2">
-        <v>1510</v>
       </c>
       <c r="D706" s="2"/>
     </row>
@@ -15723,10 +15744,10 @@
         <v>96</v>
       </c>
       <c r="B707" t="s" s="2">
+        <v>1510</v>
+      </c>
+      <c r="C707" t="s" s="2">
         <v>1511</v>
-      </c>
-      <c r="C707" t="s" s="2">
-        <v>1512</v>
       </c>
       <c r="D707" s="2"/>
     </row>
@@ -15735,10 +15756,10 @@
         <v>96</v>
       </c>
       <c r="B708" t="s" s="2">
+        <v>1512</v>
+      </c>
+      <c r="C708" t="s" s="2">
         <v>1513</v>
-      </c>
-      <c r="C708" t="s" s="2">
-        <v>1514</v>
       </c>
       <c r="D708" s="2"/>
     </row>
@@ -15747,10 +15768,10 @@
         <v>96</v>
       </c>
       <c r="B709" t="s" s="2">
+        <v>1514</v>
+      </c>
+      <c r="C709" t="s" s="2">
         <v>1515</v>
-      </c>
-      <c r="C709" t="s" s="2">
-        <v>1516</v>
       </c>
       <c r="D709" s="2"/>
     </row>
@@ -15759,10 +15780,10 @@
         <v>96</v>
       </c>
       <c r="B710" t="s" s="2">
+        <v>1516</v>
+      </c>
+      <c r="C710" t="s" s="2">
         <v>1517</v>
-      </c>
-      <c r="C710" t="s" s="2">
-        <v>1518</v>
       </c>
       <c r="D710" s="2"/>
     </row>
@@ -15771,10 +15792,10 @@
         <v>96</v>
       </c>
       <c r="B711" t="s" s="2">
+        <v>1518</v>
+      </c>
+      <c r="C711" t="s" s="2">
         <v>1519</v>
-      </c>
-      <c r="C711" t="s" s="2">
-        <v>1520</v>
       </c>
       <c r="D711" s="2"/>
     </row>
@@ -15783,10 +15804,10 @@
         <v>96</v>
       </c>
       <c r="B712" t="s" s="2">
+        <v>1520</v>
+      </c>
+      <c r="C712" t="s" s="2">
         <v>1521</v>
-      </c>
-      <c r="C712" t="s" s="2">
-        <v>1522</v>
       </c>
       <c r="D712" s="2"/>
     </row>
@@ -15795,10 +15816,10 @@
         <v>96</v>
       </c>
       <c r="B713" t="s" s="2">
+        <v>1522</v>
+      </c>
+      <c r="C713" t="s" s="2">
         <v>1523</v>
-      </c>
-      <c r="C713" t="s" s="2">
-        <v>1524</v>
       </c>
       <c r="D713" s="2"/>
     </row>
@@ -15807,10 +15828,10 @@
         <v>96</v>
       </c>
       <c r="B714" t="s" s="2">
+        <v>1524</v>
+      </c>
+      <c r="C714" t="s" s="2">
         <v>1525</v>
-      </c>
-      <c r="C714" t="s" s="2">
-        <v>1526</v>
       </c>
       <c r="D714" s="2"/>
     </row>
@@ -15819,10 +15840,10 @@
         <v>96</v>
       </c>
       <c r="B715" t="s" s="2">
+        <v>1526</v>
+      </c>
+      <c r="C715" t="s" s="2">
         <v>1527</v>
-      </c>
-      <c r="C715" t="s" s="2">
-        <v>1528</v>
       </c>
       <c r="D715" s="2"/>
     </row>
@@ -15831,10 +15852,10 @@
         <v>96</v>
       </c>
       <c r="B716" t="s" s="2">
+        <v>1528</v>
+      </c>
+      <c r="C716" t="s" s="2">
         <v>1529</v>
-      </c>
-      <c r="C716" t="s" s="2">
-        <v>1530</v>
       </c>
       <c r="D716" s="2"/>
     </row>
@@ -15843,10 +15864,10 @@
         <v>96</v>
       </c>
       <c r="B717" t="s" s="2">
+        <v>1530</v>
+      </c>
+      <c r="C717" t="s" s="2">
         <v>1531</v>
-      </c>
-      <c r="C717" t="s" s="2">
-        <v>1532</v>
       </c>
       <c r="D717" s="2"/>
     </row>
@@ -15855,10 +15876,10 @@
         <v>96</v>
       </c>
       <c r="B718" t="s" s="2">
+        <v>1532</v>
+      </c>
+      <c r="C718" t="s" s="2">
         <v>1533</v>
-      </c>
-      <c r="C718" t="s" s="2">
-        <v>1534</v>
       </c>
       <c r="D718" s="2"/>
     </row>
@@ -15867,10 +15888,10 @@
         <v>96</v>
       </c>
       <c r="B719" t="s" s="2">
+        <v>1534</v>
+      </c>
+      <c r="C719" t="s" s="2">
         <v>1535</v>
-      </c>
-      <c r="C719" t="s" s="2">
-        <v>1536</v>
       </c>
       <c r="D719" s="2"/>
     </row>
@@ -15879,10 +15900,10 @@
         <v>96</v>
       </c>
       <c r="B720" t="s" s="2">
+        <v>1536</v>
+      </c>
+      <c r="C720" t="s" s="2">
         <v>1537</v>
-      </c>
-      <c r="C720" t="s" s="2">
-        <v>1538</v>
       </c>
       <c r="D720" s="2"/>
     </row>
@@ -15891,10 +15912,10 @@
         <v>96</v>
       </c>
       <c r="B721" t="s" s="2">
+        <v>1538</v>
+      </c>
+      <c r="C721" t="s" s="2">
         <v>1539</v>
-      </c>
-      <c r="C721" t="s" s="2">
-        <v>1540</v>
       </c>
       <c r="D721" s="2"/>
     </row>
@@ -15903,10 +15924,10 @@
         <v>96</v>
       </c>
       <c r="B722" t="s" s="2">
+        <v>1540</v>
+      </c>
+      <c r="C722" t="s" s="2">
         <v>1541</v>
-      </c>
-      <c r="C722" t="s" s="2">
-        <v>1542</v>
       </c>
       <c r="D722" s="2"/>
     </row>
@@ -15915,10 +15936,10 @@
         <v>96</v>
       </c>
       <c r="B723" t="s" s="2">
+        <v>1542</v>
+      </c>
+      <c r="C723" t="s" s="2">
         <v>1543</v>
-      </c>
-      <c r="C723" t="s" s="2">
-        <v>1544</v>
       </c>
       <c r="D723" s="2"/>
     </row>
@@ -15927,10 +15948,10 @@
         <v>96</v>
       </c>
       <c r="B724" t="s" s="2">
+        <v>1544</v>
+      </c>
+      <c r="C724" t="s" s="2">
         <v>1545</v>
-      </c>
-      <c r="C724" t="s" s="2">
-        <v>1546</v>
       </c>
       <c r="D724" s="2"/>
     </row>
@@ -15939,10 +15960,10 @@
         <v>96</v>
       </c>
       <c r="B725" t="s" s="2">
+        <v>1546</v>
+      </c>
+      <c r="C725" t="s" s="2">
         <v>1547</v>
-      </c>
-      <c r="C725" t="s" s="2">
-        <v>1548</v>
       </c>
       <c r="D725" s="2"/>
     </row>
@@ -15951,10 +15972,10 @@
         <v>96</v>
       </c>
       <c r="B726" t="s" s="2">
+        <v>1548</v>
+      </c>
+      <c r="C726" t="s" s="2">
         <v>1549</v>
-      </c>
-      <c r="C726" t="s" s="2">
-        <v>1550</v>
       </c>
       <c r="D726" s="2"/>
     </row>
@@ -15963,10 +15984,10 @@
         <v>96</v>
       </c>
       <c r="B727" t="s" s="2">
+        <v>1550</v>
+      </c>
+      <c r="C727" t="s" s="2">
         <v>1551</v>
-      </c>
-      <c r="C727" t="s" s="2">
-        <v>1552</v>
       </c>
       <c r="D727" s="2"/>
     </row>
@@ -15975,10 +15996,10 @@
         <v>96</v>
       </c>
       <c r="B728" t="s" s="2">
+        <v>1552</v>
+      </c>
+      <c r="C728" t="s" s="2">
         <v>1553</v>
-      </c>
-      <c r="C728" t="s" s="2">
-        <v>1554</v>
       </c>
       <c r="D728" s="2"/>
     </row>
@@ -15987,10 +16008,10 @@
         <v>96</v>
       </c>
       <c r="B729" t="s" s="2">
+        <v>1554</v>
+      </c>
+      <c r="C729" t="s" s="2">
         <v>1555</v>
-      </c>
-      <c r="C729" t="s" s="2">
-        <v>1556</v>
       </c>
       <c r="D729" s="2"/>
     </row>
@@ -15999,10 +16020,10 @@
         <v>96</v>
       </c>
       <c r="B730" t="s" s="2">
+        <v>1556</v>
+      </c>
+      <c r="C730" t="s" s="2">
         <v>1557</v>
-      </c>
-      <c r="C730" t="s" s="2">
-        <v>1558</v>
       </c>
       <c r="D730" s="2"/>
     </row>
@@ -16011,10 +16032,10 @@
         <v>96</v>
       </c>
       <c r="B731" t="s" s="2">
+        <v>1558</v>
+      </c>
+      <c r="C731" t="s" s="2">
         <v>1559</v>
-      </c>
-      <c r="C731" t="s" s="2">
-        <v>1560</v>
       </c>
       <c r="D731" s="2"/>
     </row>
@@ -16023,10 +16044,10 @@
         <v>96</v>
       </c>
       <c r="B732" t="s" s="2">
+        <v>1560</v>
+      </c>
+      <c r="C732" t="s" s="2">
         <v>1561</v>
-      </c>
-      <c r="C732" t="s" s="2">
-        <v>1562</v>
       </c>
       <c r="D732" s="2"/>
     </row>
@@ -16035,10 +16056,10 @@
         <v>96</v>
       </c>
       <c r="B733" t="s" s="2">
+        <v>1562</v>
+      </c>
+      <c r="C733" t="s" s="2">
         <v>1563</v>
-      </c>
-      <c r="C733" t="s" s="2">
-        <v>1564</v>
       </c>
       <c r="D733" s="2"/>
     </row>
@@ -16047,10 +16068,10 @@
         <v>96</v>
       </c>
       <c r="B734" t="s" s="2">
+        <v>1564</v>
+      </c>
+      <c r="C734" t="s" s="2">
         <v>1565</v>
-      </c>
-      <c r="C734" t="s" s="2">
-        <v>1566</v>
       </c>
       <c r="D734" s="2"/>
     </row>
@@ -16059,10 +16080,10 @@
         <v>96</v>
       </c>
       <c r="B735" t="s" s="2">
+        <v>1566</v>
+      </c>
+      <c r="C735" t="s" s="2">
         <v>1567</v>
-      </c>
-      <c r="C735" t="s" s="2">
-        <v>1568</v>
       </c>
       <c r="D735" s="2"/>
     </row>
@@ -16071,10 +16092,10 @@
         <v>96</v>
       </c>
       <c r="B736" t="s" s="2">
+        <v>1568</v>
+      </c>
+      <c r="C736" t="s" s="2">
         <v>1569</v>
-      </c>
-      <c r="C736" t="s" s="2">
-        <v>1570</v>
       </c>
       <c r="D736" s="2"/>
     </row>
@@ -16083,10 +16104,10 @@
         <v>96</v>
       </c>
       <c r="B737" t="s" s="2">
+        <v>1570</v>
+      </c>
+      <c r="C737" t="s" s="2">
         <v>1571</v>
-      </c>
-      <c r="C737" t="s" s="2">
-        <v>1572</v>
       </c>
       <c r="D737" s="2"/>
     </row>
@@ -16095,10 +16116,10 @@
         <v>96</v>
       </c>
       <c r="B738" t="s" s="2">
+        <v>1572</v>
+      </c>
+      <c r="C738" t="s" s="2">
         <v>1573</v>
-      </c>
-      <c r="C738" t="s" s="2">
-        <v>1574</v>
       </c>
       <c r="D738" s="2"/>
     </row>
@@ -16107,10 +16128,10 @@
         <v>96</v>
       </c>
       <c r="B739" t="s" s="2">
+        <v>1574</v>
+      </c>
+      <c r="C739" t="s" s="2">
         <v>1575</v>
-      </c>
-      <c r="C739" t="s" s="2">
-        <v>1576</v>
       </c>
       <c r="D739" s="2"/>
     </row>
@@ -16119,10 +16140,10 @@
         <v>96</v>
       </c>
       <c r="B740" t="s" s="2">
+        <v>1576</v>
+      </c>
+      <c r="C740" t="s" s="2">
         <v>1577</v>
-      </c>
-      <c r="C740" t="s" s="2">
-        <v>1578</v>
       </c>
       <c r="D740" s="2"/>
     </row>
@@ -16131,10 +16152,10 @@
         <v>96</v>
       </c>
       <c r="B741" t="s" s="2">
+        <v>1578</v>
+      </c>
+      <c r="C741" t="s" s="2">
         <v>1579</v>
-      </c>
-      <c r="C741" t="s" s="2">
-        <v>1580</v>
       </c>
       <c r="D741" s="2"/>
     </row>
@@ -16143,10 +16164,10 @@
         <v>96</v>
       </c>
       <c r="B742" t="s" s="2">
+        <v>1580</v>
+      </c>
+      <c r="C742" t="s" s="2">
         <v>1581</v>
-      </c>
-      <c r="C742" t="s" s="2">
-        <v>1582</v>
       </c>
       <c r="D742" s="2"/>
     </row>
@@ -16155,10 +16176,10 @@
         <v>96</v>
       </c>
       <c r="B743" t="s" s="2">
+        <v>1582</v>
+      </c>
+      <c r="C743" t="s" s="2">
         <v>1583</v>
-      </c>
-      <c r="C743" t="s" s="2">
-        <v>1584</v>
       </c>
       <c r="D743" s="2"/>
     </row>
@@ -16167,10 +16188,10 @@
         <v>96</v>
       </c>
       <c r="B744" t="s" s="2">
+        <v>1584</v>
+      </c>
+      <c r="C744" t="s" s="2">
         <v>1585</v>
-      </c>
-      <c r="C744" t="s" s="2">
-        <v>1586</v>
       </c>
       <c r="D744" s="2"/>
     </row>
@@ -16179,10 +16200,10 @@
         <v>96</v>
       </c>
       <c r="B745" t="s" s="2">
+        <v>1586</v>
+      </c>
+      <c r="C745" t="s" s="2">
         <v>1587</v>
-      </c>
-      <c r="C745" t="s" s="2">
-        <v>1588</v>
       </c>
       <c r="D745" s="2"/>
     </row>
@@ -16191,10 +16212,10 @@
         <v>96</v>
       </c>
       <c r="B746" t="s" s="2">
+        <v>1588</v>
+      </c>
+      <c r="C746" t="s" s="2">
         <v>1589</v>
-      </c>
-      <c r="C746" t="s" s="2">
-        <v>1590</v>
       </c>
       <c r="D746" s="2"/>
     </row>
@@ -16203,10 +16224,10 @@
         <v>96</v>
       </c>
       <c r="B747" t="s" s="2">
+        <v>1590</v>
+      </c>
+      <c r="C747" t="s" s="2">
         <v>1591</v>
-      </c>
-      <c r="C747" t="s" s="2">
-        <v>1592</v>
       </c>
       <c r="D747" s="2"/>
     </row>
@@ -16215,10 +16236,10 @@
         <v>96</v>
       </c>
       <c r="B748" t="s" s="2">
+        <v>1592</v>
+      </c>
+      <c r="C748" t="s" s="2">
         <v>1593</v>
-      </c>
-      <c r="C748" t="s" s="2">
-        <v>1594</v>
       </c>
       <c r="D748" s="2"/>
     </row>
@@ -16227,10 +16248,10 @@
         <v>96</v>
       </c>
       <c r="B749" t="s" s="2">
+        <v>1594</v>
+      </c>
+      <c r="C749" t="s" s="2">
         <v>1595</v>
-      </c>
-      <c r="C749" t="s" s="2">
-        <v>1596</v>
       </c>
       <c r="D749" s="2"/>
     </row>
@@ -16239,10 +16260,10 @@
         <v>96</v>
       </c>
       <c r="B750" t="s" s="2">
+        <v>1596</v>
+      </c>
+      <c r="C750" t="s" s="2">
         <v>1597</v>
-      </c>
-      <c r="C750" t="s" s="2">
-        <v>1598</v>
       </c>
       <c r="D750" s="2"/>
     </row>
@@ -16251,10 +16272,10 @@
         <v>96</v>
       </c>
       <c r="B751" t="s" s="2">
+        <v>1598</v>
+      </c>
+      <c r="C751" t="s" s="2">
         <v>1599</v>
-      </c>
-      <c r="C751" t="s" s="2">
-        <v>1600</v>
       </c>
       <c r="D751" s="2"/>
     </row>
@@ -16263,10 +16284,10 @@
         <v>96</v>
       </c>
       <c r="B752" t="s" s="2">
+        <v>1600</v>
+      </c>
+      <c r="C752" t="s" s="2">
         <v>1601</v>
-      </c>
-      <c r="C752" t="s" s="2">
-        <v>1602</v>
       </c>
       <c r="D752" s="2"/>
     </row>
@@ -16275,10 +16296,10 @@
         <v>96</v>
       </c>
       <c r="B753" t="s" s="2">
+        <v>1602</v>
+      </c>
+      <c r="C753" t="s" s="2">
         <v>1603</v>
-      </c>
-      <c r="C753" t="s" s="2">
-        <v>1604</v>
       </c>
       <c r="D753" s="2"/>
     </row>
@@ -16287,10 +16308,10 @@
         <v>96</v>
       </c>
       <c r="B754" t="s" s="2">
+        <v>1604</v>
+      </c>
+      <c r="C754" t="s" s="2">
         <v>1605</v>
-      </c>
-      <c r="C754" t="s" s="2">
-        <v>1606</v>
       </c>
       <c r="D754" s="2"/>
     </row>
@@ -16299,10 +16320,10 @@
         <v>96</v>
       </c>
       <c r="B755" t="s" s="2">
+        <v>1606</v>
+      </c>
+      <c r="C755" t="s" s="2">
         <v>1607</v>
-      </c>
-      <c r="C755" t="s" s="2">
-        <v>1608</v>
       </c>
       <c r="D755" s="2"/>
     </row>
@@ -16311,10 +16332,10 @@
         <v>96</v>
       </c>
       <c r="B756" t="s" s="2">
+        <v>1608</v>
+      </c>
+      <c r="C756" t="s" s="2">
         <v>1609</v>
-      </c>
-      <c r="C756" t="s" s="2">
-        <v>1610</v>
       </c>
       <c r="D756" s="2"/>
     </row>
@@ -16323,10 +16344,10 @@
         <v>96</v>
       </c>
       <c r="B757" t="s" s="2">
+        <v>1610</v>
+      </c>
+      <c r="C757" t="s" s="2">
         <v>1611</v>
-      </c>
-      <c r="C757" t="s" s="2">
-        <v>1612</v>
       </c>
       <c r="D757" s="2"/>
     </row>
@@ -16335,10 +16356,10 @@
         <v>96</v>
       </c>
       <c r="B758" t="s" s="2">
+        <v>1612</v>
+      </c>
+      <c r="C758" t="s" s="2">
         <v>1613</v>
-      </c>
-      <c r="C758" t="s" s="2">
-        <v>1614</v>
       </c>
       <c r="D758" s="2"/>
     </row>
@@ -16347,10 +16368,10 @@
         <v>96</v>
       </c>
       <c r="B759" t="s" s="2">
+        <v>1614</v>
+      </c>
+      <c r="C759" t="s" s="2">
         <v>1615</v>
-      </c>
-      <c r="C759" t="s" s="2">
-        <v>1616</v>
       </c>
       <c r="D759" s="2"/>
     </row>
@@ -16359,10 +16380,10 @@
         <v>96</v>
       </c>
       <c r="B760" t="s" s="2">
+        <v>1616</v>
+      </c>
+      <c r="C760" t="s" s="2">
         <v>1617</v>
-      </c>
-      <c r="C760" t="s" s="2">
-        <v>1618</v>
       </c>
       <c r="D760" s="2"/>
     </row>
@@ -16371,10 +16392,10 @@
         <v>96</v>
       </c>
       <c r="B761" t="s" s="2">
+        <v>1618</v>
+      </c>
+      <c r="C761" t="s" s="2">
         <v>1619</v>
-      </c>
-      <c r="C761" t="s" s="2">
-        <v>1620</v>
       </c>
       <c r="D761" s="2"/>
     </row>
@@ -16383,10 +16404,10 @@
         <v>96</v>
       </c>
       <c r="B762" t="s" s="2">
+        <v>1620</v>
+      </c>
+      <c r="C762" t="s" s="2">
         <v>1621</v>
-      </c>
-      <c r="C762" t="s" s="2">
-        <v>1622</v>
       </c>
       <c r="D762" s="2"/>
     </row>
@@ -16395,10 +16416,10 @@
         <v>96</v>
       </c>
       <c r="B763" t="s" s="2">
+        <v>1622</v>
+      </c>
+      <c r="C763" t="s" s="2">
         <v>1623</v>
-      </c>
-      <c r="C763" t="s" s="2">
-        <v>1624</v>
       </c>
       <c r="D763" s="2"/>
     </row>
@@ -16407,10 +16428,10 @@
         <v>96</v>
       </c>
       <c r="B764" t="s" s="2">
+        <v>1624</v>
+      </c>
+      <c r="C764" t="s" s="2">
         <v>1625</v>
-      </c>
-      <c r="C764" t="s" s="2">
-        <v>1626</v>
       </c>
       <c r="D764" s="2"/>
     </row>
@@ -16419,10 +16440,10 @@
         <v>96</v>
       </c>
       <c r="B765" t="s" s="2">
+        <v>1626</v>
+      </c>
+      <c r="C765" t="s" s="2">
         <v>1627</v>
-      </c>
-      <c r="C765" t="s" s="2">
-        <v>1628</v>
       </c>
       <c r="D765" s="2"/>
     </row>
@@ -16431,10 +16452,10 @@
         <v>96</v>
       </c>
       <c r="B766" t="s" s="2">
+        <v>1628</v>
+      </c>
+      <c r="C766" t="s" s="2">
         <v>1629</v>
-      </c>
-      <c r="C766" t="s" s="2">
-        <v>1630</v>
       </c>
       <c r="D766" s="2"/>
     </row>
@@ -16443,10 +16464,10 @@
         <v>96</v>
       </c>
       <c r="B767" t="s" s="2">
+        <v>1630</v>
+      </c>
+      <c r="C767" t="s" s="2">
         <v>1631</v>
-      </c>
-      <c r="C767" t="s" s="2">
-        <v>1632</v>
       </c>
       <c r="D767" s="2"/>
     </row>
@@ -16455,10 +16476,10 @@
         <v>96</v>
       </c>
       <c r="B768" t="s" s="2">
+        <v>1632</v>
+      </c>
+      <c r="C768" t="s" s="2">
         <v>1633</v>
-      </c>
-      <c r="C768" t="s" s="2">
-        <v>1634</v>
       </c>
       <c r="D768" s="2"/>
     </row>
@@ -16467,10 +16488,10 @@
         <v>96</v>
       </c>
       <c r="B769" t="s" s="2">
+        <v>1634</v>
+      </c>
+      <c r="C769" t="s" s="2">
         <v>1635</v>
-      </c>
-      <c r="C769" t="s" s="2">
-        <v>1636</v>
       </c>
       <c r="D769" s="2"/>
     </row>
@@ -16479,10 +16500,10 @@
         <v>96</v>
       </c>
       <c r="B770" t="s" s="2">
+        <v>1636</v>
+      </c>
+      <c r="C770" t="s" s="2">
         <v>1637</v>
-      </c>
-      <c r="C770" t="s" s="2">
-        <v>1638</v>
       </c>
       <c r="D770" s="2"/>
     </row>
@@ -16491,10 +16512,10 @@
         <v>96</v>
       </c>
       <c r="B771" t="s" s="2">
+        <v>1638</v>
+      </c>
+      <c r="C771" t="s" s="2">
         <v>1639</v>
-      </c>
-      <c r="C771" t="s" s="2">
-        <v>1640</v>
       </c>
       <c r="D771" s="2"/>
     </row>
@@ -16503,10 +16524,10 @@
         <v>96</v>
       </c>
       <c r="B772" t="s" s="2">
+        <v>1640</v>
+      </c>
+      <c r="C772" t="s" s="2">
         <v>1641</v>
-      </c>
-      <c r="C772" t="s" s="2">
-        <v>1642</v>
       </c>
       <c r="D772" s="2"/>
     </row>
@@ -16515,10 +16536,10 @@
         <v>96</v>
       </c>
       <c r="B773" t="s" s="2">
+        <v>1642</v>
+      </c>
+      <c r="C773" t="s" s="2">
         <v>1643</v>
-      </c>
-      <c r="C773" t="s" s="2">
-        <v>1644</v>
       </c>
       <c r="D773" s="2"/>
     </row>
@@ -16527,10 +16548,10 @@
         <v>96</v>
       </c>
       <c r="B774" t="s" s="2">
+        <v>1644</v>
+      </c>
+      <c r="C774" t="s" s="2">
         <v>1645</v>
-      </c>
-      <c r="C774" t="s" s="2">
-        <v>1646</v>
       </c>
       <c r="D774" s="2"/>
     </row>
@@ -16539,10 +16560,10 @@
         <v>96</v>
       </c>
       <c r="B775" t="s" s="2">
+        <v>1646</v>
+      </c>
+      <c r="C775" t="s" s="2">
         <v>1647</v>
-      </c>
-      <c r="C775" t="s" s="2">
-        <v>1648</v>
       </c>
       <c r="D775" s="2"/>
     </row>
@@ -16551,10 +16572,10 @@
         <v>96</v>
       </c>
       <c r="B776" t="s" s="2">
+        <v>1648</v>
+      </c>
+      <c r="C776" t="s" s="2">
         <v>1649</v>
-      </c>
-      <c r="C776" t="s" s="2">
-        <v>1650</v>
       </c>
       <c r="D776" s="2"/>
     </row>
@@ -16563,10 +16584,10 @@
         <v>96</v>
       </c>
       <c r="B777" t="s" s="2">
+        <v>1650</v>
+      </c>
+      <c r="C777" t="s" s="2">
         <v>1651</v>
-      </c>
-      <c r="C777" t="s" s="2">
-        <v>1652</v>
       </c>
       <c r="D777" s="2"/>
     </row>
@@ -16575,10 +16596,10 @@
         <v>96</v>
       </c>
       <c r="B778" t="s" s="2">
+        <v>1652</v>
+      </c>
+      <c r="C778" t="s" s="2">
         <v>1653</v>
-      </c>
-      <c r="C778" t="s" s="2">
-        <v>1654</v>
       </c>
       <c r="D778" s="2"/>
     </row>
@@ -16587,10 +16608,10 @@
         <v>96</v>
       </c>
       <c r="B779" t="s" s="2">
+        <v>1654</v>
+      </c>
+      <c r="C779" t="s" s="2">
         <v>1655</v>
-      </c>
-      <c r="C779" t="s" s="2">
-        <v>1656</v>
       </c>
       <c r="D779" s="2"/>
     </row>
@@ -16599,10 +16620,10 @@
         <v>96</v>
       </c>
       <c r="B780" t="s" s="2">
+        <v>1656</v>
+      </c>
+      <c r="C780" t="s" s="2">
         <v>1657</v>
-      </c>
-      <c r="C780" t="s" s="2">
-        <v>1658</v>
       </c>
       <c r="D780" s="2"/>
     </row>
@@ -16611,10 +16632,10 @@
         <v>96</v>
       </c>
       <c r="B781" t="s" s="2">
+        <v>1658</v>
+      </c>
+      <c r="C781" t="s" s="2">
         <v>1659</v>
-      </c>
-      <c r="C781" t="s" s="2">
-        <v>1660</v>
       </c>
       <c r="D781" s="2"/>
     </row>
@@ -16623,10 +16644,10 @@
         <v>96</v>
       </c>
       <c r="B782" t="s" s="2">
+        <v>1660</v>
+      </c>
+      <c r="C782" t="s" s="2">
         <v>1661</v>
-      </c>
-      <c r="C782" t="s" s="2">
-        <v>1662</v>
       </c>
       <c r="D782" s="2"/>
     </row>
@@ -16635,10 +16656,10 @@
         <v>96</v>
       </c>
       <c r="B783" t="s" s="2">
+        <v>1662</v>
+      </c>
+      <c r="C783" t="s" s="2">
         <v>1663</v>
-      </c>
-      <c r="C783" t="s" s="2">
-        <v>1664</v>
       </c>
       <c r="D783" s="2"/>
     </row>
@@ -16647,10 +16668,10 @@
         <v>96</v>
       </c>
       <c r="B784" t="s" s="2">
+        <v>1664</v>
+      </c>
+      <c r="C784" t="s" s="2">
         <v>1665</v>
-      </c>
-      <c r="C784" t="s" s="2">
-        <v>1666</v>
       </c>
       <c r="D784" s="2"/>
     </row>
@@ -16659,10 +16680,10 @@
         <v>96</v>
       </c>
       <c r="B785" t="s" s="2">
+        <v>1666</v>
+      </c>
+      <c r="C785" t="s" s="2">
         <v>1667</v>
-      </c>
-      <c r="C785" t="s" s="2">
-        <v>1668</v>
       </c>
       <c r="D785" s="2"/>
     </row>
@@ -16671,10 +16692,10 @@
         <v>96</v>
       </c>
       <c r="B786" t="s" s="2">
+        <v>1668</v>
+      </c>
+      <c r="C786" t="s" s="2">
         <v>1669</v>
-      </c>
-      <c r="C786" t="s" s="2">
-        <v>1670</v>
       </c>
       <c r="D786" s="2"/>
     </row>
@@ -16683,10 +16704,10 @@
         <v>96</v>
       </c>
       <c r="B787" t="s" s="2">
+        <v>1670</v>
+      </c>
+      <c r="C787" t="s" s="2">
         <v>1671</v>
-      </c>
-      <c r="C787" t="s" s="2">
-        <v>1672</v>
       </c>
       <c r="D787" s="2"/>
     </row>
@@ -16695,10 +16716,10 @@
         <v>96</v>
       </c>
       <c r="B788" t="s" s="2">
+        <v>1672</v>
+      </c>
+      <c r="C788" t="s" s="2">
         <v>1673</v>
-      </c>
-      <c r="C788" t="s" s="2">
-        <v>1674</v>
       </c>
       <c r="D788" s="2"/>
     </row>
@@ -16707,10 +16728,10 @@
         <v>96</v>
       </c>
       <c r="B789" t="s" s="2">
+        <v>1674</v>
+      </c>
+      <c r="C789" t="s" s="2">
         <v>1675</v>
-      </c>
-      <c r="C789" t="s" s="2">
-        <v>1676</v>
       </c>
       <c r="D789" s="2"/>
     </row>
@@ -16719,10 +16740,10 @@
         <v>96</v>
       </c>
       <c r="B790" t="s" s="2">
+        <v>1676</v>
+      </c>
+      <c r="C790" t="s" s="2">
         <v>1677</v>
-      </c>
-      <c r="C790" t="s" s="2">
-        <v>1678</v>
       </c>
       <c r="D790" s="2"/>
     </row>
@@ -16731,10 +16752,10 @@
         <v>96</v>
       </c>
       <c r="B791" t="s" s="2">
+        <v>1678</v>
+      </c>
+      <c r="C791" t="s" s="2">
         <v>1679</v>
-      </c>
-      <c r="C791" t="s" s="2">
-        <v>1680</v>
       </c>
       <c r="D791" s="2"/>
     </row>
@@ -16743,10 +16764,10 @@
         <v>96</v>
       </c>
       <c r="B792" t="s" s="2">
+        <v>1680</v>
+      </c>
+      <c r="C792" t="s" s="2">
         <v>1681</v>
-      </c>
-      <c r="C792" t="s" s="2">
-        <v>1682</v>
       </c>
       <c r="D792" s="2"/>
     </row>
@@ -16755,10 +16776,10 @@
         <v>96</v>
       </c>
       <c r="B793" t="s" s="2">
+        <v>1682</v>
+      </c>
+      <c r="C793" t="s" s="2">
         <v>1683</v>
-      </c>
-      <c r="C793" t="s" s="2">
-        <v>1684</v>
       </c>
       <c r="D793" s="2"/>
     </row>
@@ -16767,10 +16788,10 @@
         <v>96</v>
       </c>
       <c r="B794" t="s" s="2">
+        <v>1684</v>
+      </c>
+      <c r="C794" t="s" s="2">
         <v>1685</v>
-      </c>
-      <c r="C794" t="s" s="2">
-        <v>1686</v>
       </c>
       <c r="D794" s="2"/>
     </row>
@@ -16779,10 +16800,10 @@
         <v>96</v>
       </c>
       <c r="B795" t="s" s="2">
+        <v>1686</v>
+      </c>
+      <c r="C795" t="s" s="2">
         <v>1687</v>
-      </c>
-      <c r="C795" t="s" s="2">
-        <v>1688</v>
       </c>
       <c r="D795" s="2"/>
     </row>
@@ -16791,10 +16812,10 @@
         <v>96</v>
       </c>
       <c r="B796" t="s" s="2">
+        <v>1688</v>
+      </c>
+      <c r="C796" t="s" s="2">
         <v>1689</v>
-      </c>
-      <c r="C796" t="s" s="2">
-        <v>1690</v>
       </c>
       <c r="D796" s="2"/>
     </row>
@@ -16803,10 +16824,10 @@
         <v>96</v>
       </c>
       <c r="B797" t="s" s="2">
+        <v>1690</v>
+      </c>
+      <c r="C797" t="s" s="2">
         <v>1691</v>
-      </c>
-      <c r="C797" t="s" s="2">
-        <v>1692</v>
       </c>
       <c r="D797" s="2"/>
     </row>
@@ -16815,24 +16836,22 @@
         <v>96</v>
       </c>
       <c r="B798" t="s" s="2">
+        <v>1692</v>
+      </c>
+      <c r="C798" t="s" s="2">
         <v>1693</v>
       </c>
-      <c r="C798" t="s" s="2">
-        <v>1694</v>
-      </c>
-      <c r="D798" t="s" s="2">
-        <v>1695</v>
-      </c>
+      <c r="D798" s="2"/>
     </row>
     <row r="799">
       <c r="A799" t="s" s="2">
         <v>96</v>
       </c>
       <c r="B799" t="s" s="2">
-        <v>1696</v>
+        <v>1694</v>
       </c>
       <c r="C799" t="s" s="2">
-        <v>1697</v>
+        <v>1695</v>
       </c>
       <c r="D799" s="2"/>
     </row>
@@ -16841,22 +16860,24 @@
         <v>96</v>
       </c>
       <c r="B800" t="s" s="2">
+        <v>1696</v>
+      </c>
+      <c r="C800" t="s" s="2">
+        <v>1697</v>
+      </c>
+      <c r="D800" t="s" s="2">
         <v>1698</v>
       </c>
-      <c r="C800" t="s" s="2">
-        <v>1699</v>
-      </c>
-      <c r="D800" s="2"/>
     </row>
     <row r="801">
       <c r="A801" t="s" s="2">
         <v>96</v>
       </c>
       <c r="B801" t="s" s="2">
+        <v>1699</v>
+      </c>
+      <c r="C801" t="s" s="2">
         <v>1700</v>
-      </c>
-      <c r="C801" t="s" s="2">
-        <v>1701</v>
       </c>
       <c r="D801" s="2"/>
     </row>
@@ -16865,10 +16886,10 @@
         <v>96</v>
       </c>
       <c r="B802" t="s" s="2">
+        <v>1701</v>
+      </c>
+      <c r="C802" t="s" s="2">
         <v>1702</v>
-      </c>
-      <c r="C802" t="s" s="2">
-        <v>1703</v>
       </c>
       <c r="D802" s="2"/>
     </row>
@@ -16877,10 +16898,10 @@
         <v>96</v>
       </c>
       <c r="B803" t="s" s="2">
+        <v>1703</v>
+      </c>
+      <c r="C803" t="s" s="2">
         <v>1704</v>
-      </c>
-      <c r="C803" t="s" s="2">
-        <v>1705</v>
       </c>
       <c r="D803" s="2"/>
     </row>
@@ -16889,10 +16910,10 @@
         <v>96</v>
       </c>
       <c r="B804" t="s" s="2">
+        <v>1705</v>
+      </c>
+      <c r="C804" t="s" s="2">
         <v>1706</v>
-      </c>
-      <c r="C804" t="s" s="2">
-        <v>1707</v>
       </c>
       <c r="D804" s="2"/>
     </row>
@@ -16901,10 +16922,10 @@
         <v>96</v>
       </c>
       <c r="B805" t="s" s="2">
+        <v>1707</v>
+      </c>
+      <c r="C805" t="s" s="2">
         <v>1708</v>
-      </c>
-      <c r="C805" t="s" s="2">
-        <v>1709</v>
       </c>
       <c r="D805" s="2"/>
     </row>
@@ -16913,10 +16934,10 @@
         <v>96</v>
       </c>
       <c r="B806" t="s" s="2">
+        <v>1709</v>
+      </c>
+      <c r="C806" t="s" s="2">
         <v>1710</v>
-      </c>
-      <c r="C806" t="s" s="2">
-        <v>1711</v>
       </c>
       <c r="D806" s="2"/>
     </row>
@@ -16925,10 +16946,10 @@
         <v>96</v>
       </c>
       <c r="B807" t="s" s="2">
+        <v>1711</v>
+      </c>
+      <c r="C807" t="s" s="2">
         <v>1712</v>
-      </c>
-      <c r="C807" t="s" s="2">
-        <v>1713</v>
       </c>
       <c r="D807" s="2"/>
     </row>
@@ -16937,10 +16958,10 @@
         <v>96</v>
       </c>
       <c r="B808" t="s" s="2">
+        <v>1713</v>
+      </c>
+      <c r="C808" t="s" s="2">
         <v>1714</v>
-      </c>
-      <c r="C808" t="s" s="2">
-        <v>1715</v>
       </c>
       <c r="D808" s="2"/>
     </row>
@@ -16949,10 +16970,10 @@
         <v>96</v>
       </c>
       <c r="B809" t="s" s="2">
+        <v>1715</v>
+      </c>
+      <c r="C809" t="s" s="2">
         <v>1716</v>
-      </c>
-      <c r="C809" t="s" s="2">
-        <v>1717</v>
       </c>
       <c r="D809" s="2"/>
     </row>
@@ -16961,10 +16982,10 @@
         <v>96</v>
       </c>
       <c r="B810" t="s" s="2">
+        <v>1717</v>
+      </c>
+      <c r="C810" t="s" s="2">
         <v>1718</v>
-      </c>
-      <c r="C810" t="s" s="2">
-        <v>1719</v>
       </c>
       <c r="D810" s="2"/>
     </row>
@@ -16973,10 +16994,10 @@
         <v>96</v>
       </c>
       <c r="B811" t="s" s="2">
+        <v>1719</v>
+      </c>
+      <c r="C811" t="s" s="2">
         <v>1720</v>
-      </c>
-      <c r="C811" t="s" s="2">
-        <v>1721</v>
       </c>
       <c r="D811" s="2"/>
     </row>
@@ -16985,10 +17006,10 @@
         <v>96</v>
       </c>
       <c r="B812" t="s" s="2">
+        <v>1721</v>
+      </c>
+      <c r="C812" t="s" s="2">
         <v>1722</v>
-      </c>
-      <c r="C812" t="s" s="2">
-        <v>1723</v>
       </c>
       <c r="D812" s="2"/>
     </row>
@@ -16997,10 +17018,10 @@
         <v>96</v>
       </c>
       <c r="B813" t="s" s="2">
+        <v>1723</v>
+      </c>
+      <c r="C813" t="s" s="2">
         <v>1724</v>
-      </c>
-      <c r="C813" t="s" s="2">
-        <v>1725</v>
       </c>
       <c r="D813" s="2"/>
     </row>
@@ -17009,24 +17030,22 @@
         <v>96</v>
       </c>
       <c r="B814" t="s" s="2">
+        <v>1725</v>
+      </c>
+      <c r="C814" t="s" s="2">
         <v>1726</v>
       </c>
-      <c r="C814" t="s" s="2">
-        <v>1727</v>
-      </c>
-      <c r="D814" t="s" s="2">
-        <v>1728</v>
-      </c>
+      <c r="D814" s="2"/>
     </row>
     <row r="815">
       <c r="A815" t="s" s="2">
         <v>96</v>
       </c>
       <c r="B815" t="s" s="2">
-        <v>1729</v>
+        <v>1727</v>
       </c>
       <c r="C815" t="s" s="2">
-        <v>1730</v>
+        <v>1728</v>
       </c>
       <c r="D815" s="2"/>
     </row>
@@ -17035,22 +17054,24 @@
         <v>96</v>
       </c>
       <c r="B816" t="s" s="2">
+        <v>1729</v>
+      </c>
+      <c r="C816" t="s" s="2">
+        <v>1730</v>
+      </c>
+      <c r="D816" t="s" s="2">
         <v>1731</v>
       </c>
-      <c r="C816" t="s" s="2">
-        <v>1732</v>
-      </c>
-      <c r="D816" s="2"/>
     </row>
     <row r="817">
       <c r="A817" t="s" s="2">
         <v>96</v>
       </c>
       <c r="B817" t="s" s="2">
+        <v>1732</v>
+      </c>
+      <c r="C817" t="s" s="2">
         <v>1733</v>
-      </c>
-      <c r="C817" t="s" s="2">
-        <v>1734</v>
       </c>
       <c r="D817" s="2"/>
     </row>
@@ -17059,10 +17080,10 @@
         <v>96</v>
       </c>
       <c r="B818" t="s" s="2">
+        <v>1734</v>
+      </c>
+      <c r="C818" t="s" s="2">
         <v>1735</v>
-      </c>
-      <c r="C818" t="s" s="2">
-        <v>1736</v>
       </c>
       <c r="D818" s="2"/>
     </row>
@@ -17071,10 +17092,10 @@
         <v>96</v>
       </c>
       <c r="B819" t="s" s="2">
+        <v>1736</v>
+      </c>
+      <c r="C819" t="s" s="2">
         <v>1737</v>
-      </c>
-      <c r="C819" t="s" s="2">
-        <v>1738</v>
       </c>
       <c r="D819" s="2"/>
     </row>
@@ -17083,7 +17104,7 @@
         <v>96</v>
       </c>
       <c r="B820" t="s" s="2">
-        <v>1739</v>
+        <v>1738</v>
       </c>
       <c r="C820" t="s" s="2">
         <v>1739</v>
@@ -17110,7 +17131,7 @@
         <v>1742</v>
       </c>
       <c r="C822" t="s" s="2">
-        <v>1743</v>
+        <v>1742</v>
       </c>
       <c r="D822" s="2"/>
     </row>
@@ -17119,10 +17140,10 @@
         <v>96</v>
       </c>
       <c r="B823" t="s" s="2">
+        <v>1743</v>
+      </c>
+      <c r="C823" t="s" s="2">
         <v>1744</v>
-      </c>
-      <c r="C823" t="s" s="2">
-        <v>1745</v>
       </c>
       <c r="D823" s="2"/>
     </row>
@@ -17131,10 +17152,10 @@
         <v>96</v>
       </c>
       <c r="B824" t="s" s="2">
+        <v>1745</v>
+      </c>
+      <c r="C824" t="s" s="2">
         <v>1746</v>
-      </c>
-      <c r="C824" t="s" s="2">
-        <v>1747</v>
       </c>
       <c r="D824" s="2"/>
     </row>
@@ -17143,10 +17164,10 @@
         <v>96</v>
       </c>
       <c r="B825" t="s" s="2">
+        <v>1747</v>
+      </c>
+      <c r="C825" t="s" s="2">
         <v>1748</v>
-      </c>
-      <c r="C825" t="s" s="2">
-        <v>1749</v>
       </c>
       <c r="D825" s="2"/>
     </row>
@@ -17155,10 +17176,10 @@
         <v>96</v>
       </c>
       <c r="B826" t="s" s="2">
+        <v>1749</v>
+      </c>
+      <c r="C826" t="s" s="2">
         <v>1750</v>
-      </c>
-      <c r="C826" t="s" s="2">
-        <v>1751</v>
       </c>
       <c r="D826" s="2"/>
     </row>
@@ -17167,10 +17188,10 @@
         <v>96</v>
       </c>
       <c r="B827" t="s" s="2">
+        <v>1751</v>
+      </c>
+      <c r="C827" t="s" s="2">
         <v>1752</v>
-      </c>
-      <c r="C827" t="s" s="2">
-        <v>1753</v>
       </c>
       <c r="D827" s="2"/>
     </row>
@@ -17179,10 +17200,10 @@
         <v>96</v>
       </c>
       <c r="B828" t="s" s="2">
+        <v>1753</v>
+      </c>
+      <c r="C828" t="s" s="2">
         <v>1754</v>
-      </c>
-      <c r="C828" t="s" s="2">
-        <v>1755</v>
       </c>
       <c r="D828" s="2"/>
     </row>
@@ -17191,10 +17212,10 @@
         <v>96</v>
       </c>
       <c r="B829" t="s" s="2">
+        <v>1755</v>
+      </c>
+      <c r="C829" t="s" s="2">
         <v>1756</v>
-      </c>
-      <c r="C829" t="s" s="2">
-        <v>1757</v>
       </c>
       <c r="D829" s="2"/>
     </row>
@@ -17203,10 +17224,10 @@
         <v>96</v>
       </c>
       <c r="B830" t="s" s="2">
+        <v>1757</v>
+      </c>
+      <c r="C830" t="s" s="2">
         <v>1758</v>
-      </c>
-      <c r="C830" t="s" s="2">
-        <v>1759</v>
       </c>
       <c r="D830" s="2"/>
     </row>
@@ -17215,10 +17236,10 @@
         <v>96</v>
       </c>
       <c r="B831" t="s" s="2">
+        <v>1759</v>
+      </c>
+      <c r="C831" t="s" s="2">
         <v>1760</v>
-      </c>
-      <c r="C831" t="s" s="2">
-        <v>1761</v>
       </c>
       <c r="D831" s="2"/>
     </row>
@@ -17227,10 +17248,10 @@
         <v>96</v>
       </c>
       <c r="B832" t="s" s="2">
+        <v>1761</v>
+      </c>
+      <c r="C832" t="s" s="2">
         <v>1762</v>
-      </c>
-      <c r="C832" t="s" s="2">
-        <v>1763</v>
       </c>
       <c r="D832" s="2"/>
     </row>
@@ -17239,10 +17260,10 @@
         <v>96</v>
       </c>
       <c r="B833" t="s" s="2">
+        <v>1763</v>
+      </c>
+      <c r="C833" t="s" s="2">
         <v>1764</v>
-      </c>
-      <c r="C833" t="s" s="2">
-        <v>1765</v>
       </c>
       <c r="D833" s="2"/>
     </row>
@@ -17251,10 +17272,10 @@
         <v>96</v>
       </c>
       <c r="B834" t="s" s="2">
+        <v>1765</v>
+      </c>
+      <c r="C834" t="s" s="2">
         <v>1766</v>
-      </c>
-      <c r="C834" t="s" s="2">
-        <v>1767</v>
       </c>
       <c r="D834" s="2"/>
     </row>
@@ -17263,10 +17284,10 @@
         <v>96</v>
       </c>
       <c r="B835" t="s" s="2">
+        <v>1767</v>
+      </c>
+      <c r="C835" t="s" s="2">
         <v>1768</v>
-      </c>
-      <c r="C835" t="s" s="2">
-        <v>1769</v>
       </c>
       <c r="D835" s="2"/>
     </row>
@@ -17275,10 +17296,10 @@
         <v>96</v>
       </c>
       <c r="B836" t="s" s="2">
+        <v>1769</v>
+      </c>
+      <c r="C836" t="s" s="2">
         <v>1770</v>
-      </c>
-      <c r="C836" t="s" s="2">
-        <v>1771</v>
       </c>
       <c r="D836" s="2"/>
     </row>
@@ -17287,10 +17308,10 @@
         <v>96</v>
       </c>
       <c r="B837" t="s" s="2">
+        <v>1771</v>
+      </c>
+      <c r="C837" t="s" s="2">
         <v>1772</v>
-      </c>
-      <c r="C837" t="s" s="2">
-        <v>1773</v>
       </c>
       <c r="D837" s="2"/>
     </row>
@@ -17299,10 +17320,10 @@
         <v>96</v>
       </c>
       <c r="B838" t="s" s="2">
+        <v>1773</v>
+      </c>
+      <c r="C838" t="s" s="2">
         <v>1774</v>
-      </c>
-      <c r="C838" t="s" s="2">
-        <v>1775</v>
       </c>
       <c r="D838" s="2"/>
     </row>
@@ -17311,10 +17332,10 @@
         <v>96</v>
       </c>
       <c r="B839" t="s" s="2">
+        <v>1775</v>
+      </c>
+      <c r="C839" t="s" s="2">
         <v>1776</v>
-      </c>
-      <c r="C839" t="s" s="2">
-        <v>1777</v>
       </c>
       <c r="D839" s="2"/>
     </row>
@@ -17323,10 +17344,10 @@
         <v>96</v>
       </c>
       <c r="B840" t="s" s="2">
+        <v>1777</v>
+      </c>
+      <c r="C840" t="s" s="2">
         <v>1778</v>
-      </c>
-      <c r="C840" t="s" s="2">
-        <v>1779</v>
       </c>
       <c r="D840" s="2"/>
     </row>
@@ -17335,10 +17356,10 @@
         <v>96</v>
       </c>
       <c r="B841" t="s" s="2">
+        <v>1779</v>
+      </c>
+      <c r="C841" t="s" s="2">
         <v>1780</v>
-      </c>
-      <c r="C841" t="s" s="2">
-        <v>1781</v>
       </c>
       <c r="D841" s="2"/>
     </row>
@@ -17347,10 +17368,10 @@
         <v>96</v>
       </c>
       <c r="B842" t="s" s="2">
+        <v>1781</v>
+      </c>
+      <c r="C842" t="s" s="2">
         <v>1782</v>
-      </c>
-      <c r="C842" t="s" s="2">
-        <v>1783</v>
       </c>
       <c r="D842" s="2"/>
     </row>
@@ -17359,10 +17380,10 @@
         <v>96</v>
       </c>
       <c r="B843" t="s" s="2">
+        <v>1783</v>
+      </c>
+      <c r="C843" t="s" s="2">
         <v>1784</v>
-      </c>
-      <c r="C843" t="s" s="2">
-        <v>1785</v>
       </c>
       <c r="D843" s="2"/>
     </row>
@@ -17371,10 +17392,10 @@
         <v>96</v>
       </c>
       <c r="B844" t="s" s="2">
+        <v>1785</v>
+      </c>
+      <c r="C844" t="s" s="2">
         <v>1786</v>
-      </c>
-      <c r="C844" t="s" s="2">
-        <v>1787</v>
       </c>
       <c r="D844" s="2"/>
     </row>
@@ -17383,10 +17404,10 @@
         <v>96</v>
       </c>
       <c r="B845" t="s" s="2">
+        <v>1787</v>
+      </c>
+      <c r="C845" t="s" s="2">
         <v>1788</v>
-      </c>
-      <c r="C845" t="s" s="2">
-        <v>1789</v>
       </c>
       <c r="D845" s="2"/>
     </row>
@@ -17395,10 +17416,10 @@
         <v>96</v>
       </c>
       <c r="B846" t="s" s="2">
+        <v>1789</v>
+      </c>
+      <c r="C846" t="s" s="2">
         <v>1790</v>
-      </c>
-      <c r="C846" t="s" s="2">
-        <v>1791</v>
       </c>
       <c r="D846" s="2"/>
     </row>
@@ -17407,10 +17428,10 @@
         <v>96</v>
       </c>
       <c r="B847" t="s" s="2">
+        <v>1791</v>
+      </c>
+      <c r="C847" t="s" s="2">
         <v>1792</v>
-      </c>
-      <c r="C847" t="s" s="2">
-        <v>1793</v>
       </c>
       <c r="D847" s="2"/>
     </row>
@@ -17419,10 +17440,10 @@
         <v>96</v>
       </c>
       <c r="B848" t="s" s="2">
+        <v>1793</v>
+      </c>
+      <c r="C848" t="s" s="2">
         <v>1794</v>
-      </c>
-      <c r="C848" t="s" s="2">
-        <v>1795</v>
       </c>
       <c r="D848" s="2"/>
     </row>
@@ -17431,10 +17452,10 @@
         <v>96</v>
       </c>
       <c r="B849" t="s" s="2">
+        <v>1795</v>
+      </c>
+      <c r="C849" t="s" s="2">
         <v>1796</v>
-      </c>
-      <c r="C849" t="s" s="2">
-        <v>1797</v>
       </c>
       <c r="D849" s="2"/>
     </row>
@@ -17443,10 +17464,10 @@
         <v>96</v>
       </c>
       <c r="B850" t="s" s="2">
+        <v>1797</v>
+      </c>
+      <c r="C850" t="s" s="2">
         <v>1798</v>
-      </c>
-      <c r="C850" t="s" s="2">
-        <v>1799</v>
       </c>
       <c r="D850" s="2"/>
     </row>
@@ -17455,10 +17476,10 @@
         <v>96</v>
       </c>
       <c r="B851" t="s" s="2">
+        <v>1799</v>
+      </c>
+      <c r="C851" t="s" s="2">
         <v>1800</v>
-      </c>
-      <c r="C851" t="s" s="2">
-        <v>1801</v>
       </c>
       <c r="D851" s="2"/>
     </row>
@@ -17467,10 +17488,10 @@
         <v>96</v>
       </c>
       <c r="B852" t="s" s="2">
+        <v>1801</v>
+      </c>
+      <c r="C852" t="s" s="2">
         <v>1802</v>
-      </c>
-      <c r="C852" t="s" s="2">
-        <v>1803</v>
       </c>
       <c r="D852" s="2"/>
     </row>
@@ -17479,10 +17500,10 @@
         <v>96</v>
       </c>
       <c r="B853" t="s" s="2">
+        <v>1803</v>
+      </c>
+      <c r="C853" t="s" s="2">
         <v>1804</v>
-      </c>
-      <c r="C853" t="s" s="2">
-        <v>1805</v>
       </c>
       <c r="D853" s="2"/>
     </row>
@@ -17491,10 +17512,10 @@
         <v>96</v>
       </c>
       <c r="B854" t="s" s="2">
+        <v>1805</v>
+      </c>
+      <c r="C854" t="s" s="2">
         <v>1806</v>
-      </c>
-      <c r="C854" t="s" s="2">
-        <v>1807</v>
       </c>
       <c r="D854" s="2"/>
     </row>
@@ -17503,10 +17524,10 @@
         <v>96</v>
       </c>
       <c r="B855" t="s" s="2">
+        <v>1807</v>
+      </c>
+      <c r="C855" t="s" s="2">
         <v>1808</v>
-      </c>
-      <c r="C855" t="s" s="2">
-        <v>1809</v>
       </c>
       <c r="D855" s="2"/>
     </row>
@@ -17515,10 +17536,10 @@
         <v>96</v>
       </c>
       <c r="B856" t="s" s="2">
+        <v>1809</v>
+      </c>
+      <c r="C856" t="s" s="2">
         <v>1810</v>
-      </c>
-      <c r="C856" t="s" s="2">
-        <v>1811</v>
       </c>
       <c r="D856" s="2"/>
     </row>
@@ -17527,10 +17548,10 @@
         <v>96</v>
       </c>
       <c r="B857" t="s" s="2">
+        <v>1811</v>
+      </c>
+      <c r="C857" t="s" s="2">
         <v>1812</v>
-      </c>
-      <c r="C857" t="s" s="2">
-        <v>1813</v>
       </c>
       <c r="D857" s="2"/>
     </row>
@@ -17539,10 +17560,10 @@
         <v>96</v>
       </c>
       <c r="B858" t="s" s="2">
+        <v>1813</v>
+      </c>
+      <c r="C858" t="s" s="2">
         <v>1814</v>
-      </c>
-      <c r="C858" t="s" s="2">
-        <v>1815</v>
       </c>
       <c r="D858" s="2"/>
     </row>
@@ -17551,10 +17572,10 @@
         <v>96</v>
       </c>
       <c r="B859" t="s" s="2">
+        <v>1815</v>
+      </c>
+      <c r="C859" t="s" s="2">
         <v>1816</v>
-      </c>
-      <c r="C859" t="s" s="2">
-        <v>1817</v>
       </c>
       <c r="D859" s="2"/>
     </row>
@@ -17563,10 +17584,10 @@
         <v>96</v>
       </c>
       <c r="B860" t="s" s="2">
+        <v>1817</v>
+      </c>
+      <c r="C860" t="s" s="2">
         <v>1818</v>
-      </c>
-      <c r="C860" t="s" s="2">
-        <v>1819</v>
       </c>
       <c r="D860" s="2"/>
     </row>
@@ -17575,10 +17596,10 @@
         <v>96</v>
       </c>
       <c r="B861" t="s" s="2">
+        <v>1819</v>
+      </c>
+      <c r="C861" t="s" s="2">
         <v>1820</v>
-      </c>
-      <c r="C861" t="s" s="2">
-        <v>1821</v>
       </c>
       <c r="D861" s="2"/>
     </row>
@@ -17587,10 +17608,10 @@
         <v>96</v>
       </c>
       <c r="B862" t="s" s="2">
+        <v>1821</v>
+      </c>
+      <c r="C862" t="s" s="2">
         <v>1822</v>
-      </c>
-      <c r="C862" t="s" s="2">
-        <v>1823</v>
       </c>
       <c r="D862" s="2"/>
     </row>
@@ -17599,24 +17620,22 @@
         <v>96</v>
       </c>
       <c r="B863" t="s" s="2">
+        <v>1823</v>
+      </c>
+      <c r="C863" t="s" s="2">
         <v>1824</v>
       </c>
-      <c r="C863" t="s" s="2">
-        <v>1825</v>
-      </c>
-      <c r="D863" t="s" s="2">
-        <v>1826</v>
-      </c>
+      <c r="D863" s="2"/>
     </row>
     <row r="864">
       <c r="A864" t="s" s="2">
         <v>96</v>
       </c>
       <c r="B864" t="s" s="2">
-        <v>1827</v>
+        <v>1825</v>
       </c>
       <c r="C864" t="s" s="2">
-        <v>1828</v>
+        <v>1826</v>
       </c>
       <c r="D864" s="2"/>
     </row>
@@ -17625,22 +17644,24 @@
         <v>96</v>
       </c>
       <c r="B865" t="s" s="2">
+        <v>1827</v>
+      </c>
+      <c r="C865" t="s" s="2">
+        <v>1828</v>
+      </c>
+      <c r="D865" t="s" s="2">
         <v>1829</v>
       </c>
-      <c r="C865" t="s" s="2">
-        <v>1830</v>
-      </c>
-      <c r="D865" s="2"/>
     </row>
     <row r="866">
       <c r="A866" t="s" s="2">
         <v>96</v>
       </c>
       <c r="B866" t="s" s="2">
+        <v>1830</v>
+      </c>
+      <c r="C866" t="s" s="2">
         <v>1831</v>
-      </c>
-      <c r="C866" t="s" s="2">
-        <v>1832</v>
       </c>
       <c r="D866" s="2"/>
     </row>
@@ -17649,10 +17670,10 @@
         <v>96</v>
       </c>
       <c r="B867" t="s" s="2">
+        <v>1832</v>
+      </c>
+      <c r="C867" t="s" s="2">
         <v>1833</v>
-      </c>
-      <c r="C867" t="s" s="2">
-        <v>1834</v>
       </c>
       <c r="D867" s="2"/>
     </row>
@@ -17661,10 +17682,10 @@
         <v>96</v>
       </c>
       <c r="B868" t="s" s="2">
+        <v>1834</v>
+      </c>
+      <c r="C868" t="s" s="2">
         <v>1835</v>
-      </c>
-      <c r="C868" t="s" s="2">
-        <v>1836</v>
       </c>
       <c r="D868" s="2"/>
     </row>
@@ -17673,10 +17694,10 @@
         <v>96</v>
       </c>
       <c r="B869" t="s" s="2">
+        <v>1836</v>
+      </c>
+      <c r="C869" t="s" s="2">
         <v>1837</v>
-      </c>
-      <c r="C869" t="s" s="2">
-        <v>1838</v>
       </c>
       <c r="D869" s="2"/>
     </row>
@@ -17685,10 +17706,10 @@
         <v>96</v>
       </c>
       <c r="B870" t="s" s="2">
+        <v>1838</v>
+      </c>
+      <c r="C870" t="s" s="2">
         <v>1839</v>
-      </c>
-      <c r="C870" t="s" s="2">
-        <v>1840</v>
       </c>
       <c r="D870" s="2"/>
     </row>
@@ -17697,10 +17718,10 @@
         <v>96</v>
       </c>
       <c r="B871" t="s" s="2">
+        <v>1840</v>
+      </c>
+      <c r="C871" t="s" s="2">
         <v>1841</v>
-      </c>
-      <c r="C871" t="s" s="2">
-        <v>1842</v>
       </c>
       <c r="D871" s="2"/>
     </row>
@@ -17709,10 +17730,10 @@
         <v>96</v>
       </c>
       <c r="B872" t="s" s="2">
+        <v>1842</v>
+      </c>
+      <c r="C872" t="s" s="2">
         <v>1843</v>
-      </c>
-      <c r="C872" t="s" s="2">
-        <v>1844</v>
       </c>
       <c r="D872" s="2"/>
     </row>
@@ -17721,10 +17742,10 @@
         <v>96</v>
       </c>
       <c r="B873" t="s" s="2">
+        <v>1844</v>
+      </c>
+      <c r="C873" t="s" s="2">
         <v>1845</v>
-      </c>
-      <c r="C873" t="s" s="2">
-        <v>1846</v>
       </c>
       <c r="D873" s="2"/>
     </row>
@@ -17733,10 +17754,10 @@
         <v>96</v>
       </c>
       <c r="B874" t="s" s="2">
+        <v>1846</v>
+      </c>
+      <c r="C874" t="s" s="2">
         <v>1847</v>
-      </c>
-      <c r="C874" t="s" s="2">
-        <v>1848</v>
       </c>
       <c r="D874" s="2"/>
     </row>
@@ -17745,10 +17766,10 @@
         <v>96</v>
       </c>
       <c r="B875" t="s" s="2">
+        <v>1848</v>
+      </c>
+      <c r="C875" t="s" s="2">
         <v>1849</v>
-      </c>
-      <c r="C875" t="s" s="2">
-        <v>1850</v>
       </c>
       <c r="D875" s="2"/>
     </row>
@@ -17757,10 +17778,10 @@
         <v>96</v>
       </c>
       <c r="B876" t="s" s="2">
+        <v>1850</v>
+      </c>
+      <c r="C876" t="s" s="2">
         <v>1851</v>
-      </c>
-      <c r="C876" t="s" s="2">
-        <v>1852</v>
       </c>
       <c r="D876" s="2"/>
     </row>
@@ -17769,10 +17790,10 @@
         <v>96</v>
       </c>
       <c r="B877" t="s" s="2">
+        <v>1852</v>
+      </c>
+      <c r="C877" t="s" s="2">
         <v>1853</v>
-      </c>
-      <c r="C877" t="s" s="2">
-        <v>1854</v>
       </c>
       <c r="D877" s="2"/>
     </row>
@@ -17781,10 +17802,10 @@
         <v>96</v>
       </c>
       <c r="B878" t="s" s="2">
+        <v>1854</v>
+      </c>
+      <c r="C878" t="s" s="2">
         <v>1855</v>
-      </c>
-      <c r="C878" t="s" s="2">
-        <v>1856</v>
       </c>
       <c r="D878" s="2"/>
     </row>
@@ -17793,24 +17814,22 @@
         <v>96</v>
       </c>
       <c r="B879" t="s" s="2">
+        <v>1856</v>
+      </c>
+      <c r="C879" t="s" s="2">
         <v>1857</v>
       </c>
-      <c r="C879" t="s" s="2">
-        <v>1858</v>
-      </c>
-      <c r="D879" t="s" s="2">
-        <v>1859</v>
-      </c>
+      <c r="D879" s="2"/>
     </row>
     <row r="880">
       <c r="A880" t="s" s="2">
         <v>96</v>
       </c>
       <c r="B880" t="s" s="2">
-        <v>1860</v>
+        <v>1858</v>
       </c>
       <c r="C880" t="s" s="2">
-        <v>1861</v>
+        <v>1859</v>
       </c>
       <c r="D880" s="2"/>
     </row>
@@ -17819,22 +17838,24 @@
         <v>96</v>
       </c>
       <c r="B881" t="s" s="2">
+        <v>1860</v>
+      </c>
+      <c r="C881" t="s" s="2">
+        <v>1861</v>
+      </c>
+      <c r="D881" t="s" s="2">
         <v>1862</v>
       </c>
-      <c r="C881" t="s" s="2">
-        <v>1863</v>
-      </c>
-      <c r="D881" s="2"/>
     </row>
     <row r="882">
       <c r="A882" t="s" s="2">
         <v>96</v>
       </c>
       <c r="B882" t="s" s="2">
+        <v>1863</v>
+      </c>
+      <c r="C882" t="s" s="2">
         <v>1864</v>
-      </c>
-      <c r="C882" t="s" s="2">
-        <v>1865</v>
       </c>
       <c r="D882" s="2"/>
     </row>
@@ -17843,10 +17864,10 @@
         <v>96</v>
       </c>
       <c r="B883" t="s" s="2">
+        <v>1865</v>
+      </c>
+      <c r="C883" t="s" s="2">
         <v>1866</v>
-      </c>
-      <c r="C883" t="s" s="2">
-        <v>1867</v>
       </c>
       <c r="D883" s="2"/>
     </row>
@@ -17855,10 +17876,10 @@
         <v>96</v>
       </c>
       <c r="B884" t="s" s="2">
+        <v>1867</v>
+      </c>
+      <c r="C884" t="s" s="2">
         <v>1868</v>
-      </c>
-      <c r="C884" t="s" s="2">
-        <v>1869</v>
       </c>
       <c r="D884" s="2"/>
     </row>
@@ -17867,10 +17888,10 @@
         <v>96</v>
       </c>
       <c r="B885" t="s" s="2">
+        <v>1869</v>
+      </c>
+      <c r="C885" t="s" s="2">
         <v>1870</v>
-      </c>
-      <c r="C885" t="s" s="2">
-        <v>1871</v>
       </c>
       <c r="D885" s="2"/>
     </row>
@@ -17879,10 +17900,10 @@
         <v>96</v>
       </c>
       <c r="B886" t="s" s="2">
+        <v>1871</v>
+      </c>
+      <c r="C886" t="s" s="2">
         <v>1872</v>
-      </c>
-      <c r="C886" t="s" s="2">
-        <v>1873</v>
       </c>
       <c r="D886" s="2"/>
     </row>
@@ -17891,10 +17912,10 @@
         <v>96</v>
       </c>
       <c r="B887" t="s" s="2">
+        <v>1873</v>
+      </c>
+      <c r="C887" t="s" s="2">
         <v>1874</v>
-      </c>
-      <c r="C887" t="s" s="2">
-        <v>1875</v>
       </c>
       <c r="D887" s="2"/>
     </row>
@@ -17903,10 +17924,10 @@
         <v>96</v>
       </c>
       <c r="B888" t="s" s="2">
+        <v>1875</v>
+      </c>
+      <c r="C888" t="s" s="2">
         <v>1876</v>
-      </c>
-      <c r="C888" t="s" s="2">
-        <v>1877</v>
       </c>
       <c r="D888" s="2"/>
     </row>
@@ -17915,10 +17936,10 @@
         <v>96</v>
       </c>
       <c r="B889" t="s" s="2">
+        <v>1877</v>
+      </c>
+      <c r="C889" t="s" s="2">
         <v>1878</v>
-      </c>
-      <c r="C889" t="s" s="2">
-        <v>1879</v>
       </c>
       <c r="D889" s="2"/>
     </row>
@@ -17927,10 +17948,10 @@
         <v>96</v>
       </c>
       <c r="B890" t="s" s="2">
+        <v>1879</v>
+      </c>
+      <c r="C890" t="s" s="2">
         <v>1880</v>
-      </c>
-      <c r="C890" t="s" s="2">
-        <v>1881</v>
       </c>
       <c r="D890" s="2"/>
     </row>
@@ -17939,10 +17960,10 @@
         <v>96</v>
       </c>
       <c r="B891" t="s" s="2">
+        <v>1881</v>
+      </c>
+      <c r="C891" t="s" s="2">
         <v>1882</v>
-      </c>
-      <c r="C891" t="s" s="2">
-        <v>1883</v>
       </c>
       <c r="D891" s="2"/>
     </row>
@@ -17951,10 +17972,10 @@
         <v>96</v>
       </c>
       <c r="B892" t="s" s="2">
+        <v>1883</v>
+      </c>
+      <c r="C892" t="s" s="2">
         <v>1884</v>
-      </c>
-      <c r="C892" t="s" s="2">
-        <v>892</v>
       </c>
       <c r="D892" s="2"/>
     </row>
@@ -17978,7 +17999,7 @@
         <v>1887</v>
       </c>
       <c r="C894" t="s" s="2">
-        <v>1888</v>
+        <v>894</v>
       </c>
       <c r="D894" s="2"/>
     </row>
@@ -17987,10 +18008,10 @@
         <v>96</v>
       </c>
       <c r="B895" t="s" s="2">
+        <v>1888</v>
+      </c>
+      <c r="C895" t="s" s="2">
         <v>1889</v>
-      </c>
-      <c r="C895" t="s" s="2">
-        <v>1890</v>
       </c>
       <c r="D895" s="2"/>
     </row>
@@ -17999,10 +18020,10 @@
         <v>96</v>
       </c>
       <c r="B896" t="s" s="2">
+        <v>1890</v>
+      </c>
+      <c r="C896" t="s" s="2">
         <v>1891</v>
-      </c>
-      <c r="C896" t="s" s="2">
-        <v>1892</v>
       </c>
       <c r="D896" s="2"/>
     </row>
@@ -18011,10 +18032,10 @@
         <v>96</v>
       </c>
       <c r="B897" t="s" s="2">
+        <v>1892</v>
+      </c>
+      <c r="C897" t="s" s="2">
         <v>1893</v>
-      </c>
-      <c r="C897" t="s" s="2">
-        <v>1894</v>
       </c>
       <c r="D897" s="2"/>
     </row>
@@ -18023,10 +18044,10 @@
         <v>96</v>
       </c>
       <c r="B898" t="s" s="2">
+        <v>1894</v>
+      </c>
+      <c r="C898" t="s" s="2">
         <v>1895</v>
-      </c>
-      <c r="C898" t="s" s="2">
-        <v>1896</v>
       </c>
       <c r="D898" s="2"/>
     </row>
@@ -18035,10 +18056,10 @@
         <v>96</v>
       </c>
       <c r="B899" t="s" s="2">
+        <v>1896</v>
+      </c>
+      <c r="C899" t="s" s="2">
         <v>1897</v>
-      </c>
-      <c r="C899" t="s" s="2">
-        <v>1898</v>
       </c>
       <c r="D899" s="2"/>
     </row>
@@ -18047,10 +18068,10 @@
         <v>96</v>
       </c>
       <c r="B900" t="s" s="2">
+        <v>1898</v>
+      </c>
+      <c r="C900" t="s" s="2">
         <v>1899</v>
-      </c>
-      <c r="C900" t="s" s="2">
-        <v>1900</v>
       </c>
       <c r="D900" s="2"/>
     </row>
@@ -18059,10 +18080,10 @@
         <v>96</v>
       </c>
       <c r="B901" t="s" s="2">
+        <v>1900</v>
+      </c>
+      <c r="C901" t="s" s="2">
         <v>1901</v>
-      </c>
-      <c r="C901" t="s" s="2">
-        <v>1902</v>
       </c>
       <c r="D901" s="2"/>
     </row>
@@ -18071,10 +18092,10 @@
         <v>96</v>
       </c>
       <c r="B902" t="s" s="2">
+        <v>1902</v>
+      </c>
+      <c r="C902" t="s" s="2">
         <v>1903</v>
-      </c>
-      <c r="C902" t="s" s="2">
-        <v>322</v>
       </c>
       <c r="D902" s="2"/>
     </row>
@@ -18098,7 +18119,7 @@
         <v>1906</v>
       </c>
       <c r="C904" t="s" s="2">
-        <v>1907</v>
+        <v>322</v>
       </c>
       <c r="D904" s="2"/>
     </row>
@@ -18107,10 +18128,10 @@
         <v>96</v>
       </c>
       <c r="B905" t="s" s="2">
+        <v>1907</v>
+      </c>
+      <c r="C905" t="s" s="2">
         <v>1908</v>
-      </c>
-      <c r="C905" t="s" s="2">
-        <v>1909</v>
       </c>
       <c r="D905" s="2"/>
     </row>
@@ -18119,10 +18140,10 @@
         <v>96</v>
       </c>
       <c r="B906" t="s" s="2">
+        <v>1909</v>
+      </c>
+      <c r="C906" t="s" s="2">
         <v>1910</v>
-      </c>
-      <c r="C906" t="s" s="2">
-        <v>1911</v>
       </c>
       <c r="D906" s="2"/>
     </row>
@@ -18131,10 +18152,10 @@
         <v>96</v>
       </c>
       <c r="B907" t="s" s="2">
+        <v>1911</v>
+      </c>
+      <c r="C907" t="s" s="2">
         <v>1912</v>
-      </c>
-      <c r="C907" t="s" s="2">
-        <v>1913</v>
       </c>
       <c r="D907" s="2"/>
     </row>
@@ -18143,10 +18164,10 @@
         <v>96</v>
       </c>
       <c r="B908" t="s" s="2">
+        <v>1913</v>
+      </c>
+      <c r="C908" t="s" s="2">
         <v>1914</v>
-      </c>
-      <c r="C908" t="s" s="2">
-        <v>1915</v>
       </c>
       <c r="D908" s="2"/>
     </row>
@@ -18155,10 +18176,10 @@
         <v>96</v>
       </c>
       <c r="B909" t="s" s="2">
+        <v>1915</v>
+      </c>
+      <c r="C909" t="s" s="2">
         <v>1916</v>
-      </c>
-      <c r="C909" t="s" s="2">
-        <v>1917</v>
       </c>
       <c r="D909" s="2"/>
     </row>
@@ -18167,10 +18188,10 @@
         <v>96</v>
       </c>
       <c r="B910" t="s" s="2">
+        <v>1917</v>
+      </c>
+      <c r="C910" t="s" s="2">
         <v>1918</v>
-      </c>
-      <c r="C910" t="s" s="2">
-        <v>1919</v>
       </c>
       <c r="D910" s="2"/>
     </row>
@@ -18179,10 +18200,10 @@
         <v>96</v>
       </c>
       <c r="B911" t="s" s="2">
+        <v>1919</v>
+      </c>
+      <c r="C911" t="s" s="2">
         <v>1920</v>
-      </c>
-      <c r="C911" t="s" s="2">
-        <v>1921</v>
       </c>
       <c r="D911" s="2"/>
     </row>
@@ -18191,10 +18212,10 @@
         <v>96</v>
       </c>
       <c r="B912" t="s" s="2">
+        <v>1921</v>
+      </c>
+      <c r="C912" t="s" s="2">
         <v>1922</v>
-      </c>
-      <c r="C912" t="s" s="2">
-        <v>1923</v>
       </c>
       <c r="D912" s="2"/>
     </row>
@@ -18203,10 +18224,10 @@
         <v>96</v>
       </c>
       <c r="B913" t="s" s="2">
+        <v>1923</v>
+      </c>
+      <c r="C913" t="s" s="2">
         <v>1924</v>
-      </c>
-      <c r="C913" t="s" s="2">
-        <v>1925</v>
       </c>
       <c r="D913" s="2"/>
     </row>
@@ -18215,10 +18236,10 @@
         <v>96</v>
       </c>
       <c r="B914" t="s" s="2">
+        <v>1925</v>
+      </c>
+      <c r="C914" t="s" s="2">
         <v>1926</v>
-      </c>
-      <c r="C914" t="s" s="2">
-        <v>1927</v>
       </c>
       <c r="D914" s="2"/>
     </row>
@@ -18227,10 +18248,10 @@
         <v>96</v>
       </c>
       <c r="B915" t="s" s="2">
+        <v>1927</v>
+      </c>
+      <c r="C915" t="s" s="2">
         <v>1928</v>
-      </c>
-      <c r="C915" t="s" s="2">
-        <v>1929</v>
       </c>
       <c r="D915" s="2"/>
     </row>
@@ -18239,10 +18260,10 @@
         <v>96</v>
       </c>
       <c r="B916" t="s" s="2">
+        <v>1929</v>
+      </c>
+      <c r="C916" t="s" s="2">
         <v>1930</v>
-      </c>
-      <c r="C916" t="s" s="2">
-        <v>1931</v>
       </c>
       <c r="D916" s="2"/>
     </row>
@@ -18251,10 +18272,10 @@
         <v>96</v>
       </c>
       <c r="B917" t="s" s="2">
+        <v>1931</v>
+      </c>
+      <c r="C917" t="s" s="2">
         <v>1932</v>
-      </c>
-      <c r="C917" t="s" s="2">
-        <v>1933</v>
       </c>
       <c r="D917" s="2"/>
     </row>
@@ -18263,10 +18284,10 @@
         <v>96</v>
       </c>
       <c r="B918" t="s" s="2">
+        <v>1933</v>
+      </c>
+      <c r="C918" t="s" s="2">
         <v>1934</v>
-      </c>
-      <c r="C918" t="s" s="2">
-        <v>1935</v>
       </c>
       <c r="D918" s="2"/>
     </row>
@@ -18275,10 +18296,10 @@
         <v>96</v>
       </c>
       <c r="B919" t="s" s="2">
+        <v>1935</v>
+      </c>
+      <c r="C919" t="s" s="2">
         <v>1936</v>
-      </c>
-      <c r="C919" t="s" s="2">
-        <v>1937</v>
       </c>
       <c r="D919" s="2"/>
     </row>
@@ -18287,10 +18308,10 @@
         <v>96</v>
       </c>
       <c r="B920" t="s" s="2">
+        <v>1937</v>
+      </c>
+      <c r="C920" t="s" s="2">
         <v>1938</v>
-      </c>
-      <c r="C920" t="s" s="2">
-        <v>1939</v>
       </c>
       <c r="D920" s="2"/>
     </row>
@@ -18299,10 +18320,10 @@
         <v>96</v>
       </c>
       <c r="B921" t="s" s="2">
+        <v>1939</v>
+      </c>
+      <c r="C921" t="s" s="2">
         <v>1940</v>
-      </c>
-      <c r="C921" t="s" s="2">
-        <v>1941</v>
       </c>
       <c r="D921" s="2"/>
     </row>
@@ -18311,10 +18332,10 @@
         <v>96</v>
       </c>
       <c r="B922" t="s" s="2">
+        <v>1941</v>
+      </c>
+      <c r="C922" t="s" s="2">
         <v>1942</v>
-      </c>
-      <c r="C922" t="s" s="2">
-        <v>1943</v>
       </c>
       <c r="D922" s="2"/>
     </row>
@@ -18323,10 +18344,10 @@
         <v>96</v>
       </c>
       <c r="B923" t="s" s="2">
+        <v>1943</v>
+      </c>
+      <c r="C923" t="s" s="2">
         <v>1944</v>
-      </c>
-      <c r="C923" t="s" s="2">
-        <v>1945</v>
       </c>
       <c r="D923" s="2"/>
     </row>
@@ -18335,10 +18356,10 @@
         <v>96</v>
       </c>
       <c r="B924" t="s" s="2">
+        <v>1945</v>
+      </c>
+      <c r="C924" t="s" s="2">
         <v>1946</v>
-      </c>
-      <c r="C924" t="s" s="2">
-        <v>1947</v>
       </c>
       <c r="D924" s="2"/>
     </row>
@@ -18347,10 +18368,10 @@
         <v>96</v>
       </c>
       <c r="B925" t="s" s="2">
+        <v>1947</v>
+      </c>
+      <c r="C925" t="s" s="2">
         <v>1948</v>
-      </c>
-      <c r="C925" t="s" s="2">
-        <v>1949</v>
       </c>
       <c r="D925" s="2"/>
     </row>
@@ -18359,10 +18380,10 @@
         <v>96</v>
       </c>
       <c r="B926" t="s" s="2">
+        <v>1949</v>
+      </c>
+      <c r="C926" t="s" s="2">
         <v>1950</v>
-      </c>
-      <c r="C926" t="s" s="2">
-        <v>1951</v>
       </c>
       <c r="D926" s="2"/>
     </row>
@@ -18371,10 +18392,10 @@
         <v>96</v>
       </c>
       <c r="B927" t="s" s="2">
+        <v>1951</v>
+      </c>
+      <c r="C927" t="s" s="2">
         <v>1952</v>
-      </c>
-      <c r="C927" t="s" s="2">
-        <v>1953</v>
       </c>
       <c r="D927" s="2"/>
     </row>
@@ -18383,10 +18404,10 @@
         <v>96</v>
       </c>
       <c r="B928" t="s" s="2">
+        <v>1953</v>
+      </c>
+      <c r="C928" t="s" s="2">
         <v>1954</v>
-      </c>
-      <c r="C928" t="s" s="2">
-        <v>1955</v>
       </c>
       <c r="D928" s="2"/>
     </row>
@@ -18395,10 +18416,10 @@
         <v>96</v>
       </c>
       <c r="B929" t="s" s="2">
+        <v>1955</v>
+      </c>
+      <c r="C929" t="s" s="2">
         <v>1956</v>
-      </c>
-      <c r="C929" t="s" s="2">
-        <v>1957</v>
       </c>
       <c r="D929" s="2"/>
     </row>
@@ -18407,10 +18428,10 @@
         <v>96</v>
       </c>
       <c r="B930" t="s" s="2">
+        <v>1957</v>
+      </c>
+      <c r="C930" t="s" s="2">
         <v>1958</v>
-      </c>
-      <c r="C930" t="s" s="2">
-        <v>1959</v>
       </c>
       <c r="D930" s="2"/>
     </row>
@@ -18419,10 +18440,10 @@
         <v>96</v>
       </c>
       <c r="B931" t="s" s="2">
+        <v>1959</v>
+      </c>
+      <c r="C931" t="s" s="2">
         <v>1960</v>
-      </c>
-      <c r="C931" t="s" s="2">
-        <v>1961</v>
       </c>
       <c r="D931" s="2"/>
     </row>
@@ -18431,10 +18452,10 @@
         <v>96</v>
       </c>
       <c r="B932" t="s" s="2">
+        <v>1961</v>
+      </c>
+      <c r="C932" t="s" s="2">
         <v>1962</v>
-      </c>
-      <c r="C932" t="s" s="2">
-        <v>1963</v>
       </c>
       <c r="D932" s="2"/>
     </row>
@@ -18443,10 +18464,10 @@
         <v>96</v>
       </c>
       <c r="B933" t="s" s="2">
+        <v>1963</v>
+      </c>
+      <c r="C933" t="s" s="2">
         <v>1964</v>
-      </c>
-      <c r="C933" t="s" s="2">
-        <v>1965</v>
       </c>
       <c r="D933" s="2"/>
     </row>
@@ -18455,10 +18476,10 @@
         <v>96</v>
       </c>
       <c r="B934" t="s" s="2">
+        <v>1965</v>
+      </c>
+      <c r="C934" t="s" s="2">
         <v>1966</v>
-      </c>
-      <c r="C934" t="s" s="2">
-        <v>1967</v>
       </c>
       <c r="D934" s="2"/>
     </row>
@@ -18467,10 +18488,10 @@
         <v>96</v>
       </c>
       <c r="B935" t="s" s="2">
+        <v>1967</v>
+      </c>
+      <c r="C935" t="s" s="2">
         <v>1968</v>
-      </c>
-      <c r="C935" t="s" s="2">
-        <v>1969</v>
       </c>
       <c r="D935" s="2"/>
     </row>
@@ -18479,10 +18500,10 @@
         <v>96</v>
       </c>
       <c r="B936" t="s" s="2">
+        <v>1969</v>
+      </c>
+      <c r="C936" t="s" s="2">
         <v>1970</v>
-      </c>
-      <c r="C936" t="s" s="2">
-        <v>1971</v>
       </c>
       <c r="D936" s="2"/>
     </row>
@@ -18491,10 +18512,10 @@
         <v>96</v>
       </c>
       <c r="B937" t="s" s="2">
+        <v>1971</v>
+      </c>
+      <c r="C937" t="s" s="2">
         <v>1972</v>
-      </c>
-      <c r="C937" t="s" s="2">
-        <v>1973</v>
       </c>
       <c r="D937" s="2"/>
     </row>
@@ -18503,10 +18524,10 @@
         <v>96</v>
       </c>
       <c r="B938" t="s" s="2">
+        <v>1973</v>
+      </c>
+      <c r="C938" t="s" s="2">
         <v>1974</v>
-      </c>
-      <c r="C938" t="s" s="2">
-        <v>1975</v>
       </c>
       <c r="D938" s="2"/>
     </row>
@@ -18515,10 +18536,10 @@
         <v>96</v>
       </c>
       <c r="B939" t="s" s="2">
+        <v>1975</v>
+      </c>
+      <c r="C939" t="s" s="2">
         <v>1976</v>
-      </c>
-      <c r="C939" t="s" s="2">
-        <v>1977</v>
       </c>
       <c r="D939" s="2"/>
     </row>
@@ -18527,10 +18548,10 @@
         <v>96</v>
       </c>
       <c r="B940" t="s" s="2">
+        <v>1977</v>
+      </c>
+      <c r="C940" t="s" s="2">
         <v>1978</v>
-      </c>
-      <c r="C940" t="s" s="2">
-        <v>1979</v>
       </c>
       <c r="D940" s="2"/>
     </row>
@@ -18539,10 +18560,10 @@
         <v>96</v>
       </c>
       <c r="B941" t="s" s="2">
+        <v>1979</v>
+      </c>
+      <c r="C941" t="s" s="2">
         <v>1980</v>
-      </c>
-      <c r="C941" t="s" s="2">
-        <v>1981</v>
       </c>
       <c r="D941" s="2"/>
     </row>
@@ -18551,10 +18572,10 @@
         <v>96</v>
       </c>
       <c r="B942" t="s" s="2">
+        <v>1981</v>
+      </c>
+      <c r="C942" t="s" s="2">
         <v>1982</v>
-      </c>
-      <c r="C942" t="s" s="2">
-        <v>1983</v>
       </c>
       <c r="D942" s="2"/>
     </row>
@@ -18563,10 +18584,10 @@
         <v>96</v>
       </c>
       <c r="B943" t="s" s="2">
+        <v>1983</v>
+      </c>
+      <c r="C943" t="s" s="2">
         <v>1984</v>
-      </c>
-      <c r="C943" t="s" s="2">
-        <v>1985</v>
       </c>
       <c r="D943" s="2"/>
     </row>
@@ -18575,10 +18596,10 @@
         <v>96</v>
       </c>
       <c r="B944" t="s" s="2">
+        <v>1985</v>
+      </c>
+      <c r="C944" t="s" s="2">
         <v>1986</v>
-      </c>
-      <c r="C944" t="s" s="2">
-        <v>1987</v>
       </c>
       <c r="D944" s="2"/>
     </row>
@@ -18587,10 +18608,10 @@
         <v>96</v>
       </c>
       <c r="B945" t="s" s="2">
+        <v>1987</v>
+      </c>
+      <c r="C945" t="s" s="2">
         <v>1988</v>
-      </c>
-      <c r="C945" t="s" s="2">
-        <v>1989</v>
       </c>
       <c r="D945" s="2"/>
     </row>
@@ -18599,10 +18620,10 @@
         <v>96</v>
       </c>
       <c r="B946" t="s" s="2">
+        <v>1989</v>
+      </c>
+      <c r="C946" t="s" s="2">
         <v>1990</v>
-      </c>
-      <c r="C946" t="s" s="2">
-        <v>1991</v>
       </c>
       <c r="D946" s="2"/>
     </row>
@@ -18611,10 +18632,10 @@
         <v>96</v>
       </c>
       <c r="B947" t="s" s="2">
+        <v>1991</v>
+      </c>
+      <c r="C947" t="s" s="2">
         <v>1992</v>
-      </c>
-      <c r="C947" t="s" s="2">
-        <v>1993</v>
       </c>
       <c r="D947" s="2"/>
     </row>
@@ -18623,10 +18644,10 @@
         <v>96</v>
       </c>
       <c r="B948" t="s" s="2">
+        <v>1993</v>
+      </c>
+      <c r="C948" t="s" s="2">
         <v>1994</v>
-      </c>
-      <c r="C948" t="s" s="2">
-        <v>1995</v>
       </c>
       <c r="D948" s="2"/>
     </row>
@@ -18635,10 +18656,10 @@
         <v>96</v>
       </c>
       <c r="B949" t="s" s="2">
+        <v>1995</v>
+      </c>
+      <c r="C949" t="s" s="2">
         <v>1996</v>
-      </c>
-      <c r="C949" t="s" s="2">
-        <v>1997</v>
       </c>
       <c r="D949" s="2"/>
     </row>
@@ -18647,10 +18668,10 @@
         <v>96</v>
       </c>
       <c r="B950" t="s" s="2">
+        <v>1997</v>
+      </c>
+      <c r="C950" t="s" s="2">
         <v>1998</v>
-      </c>
-      <c r="C950" t="s" s="2">
-        <v>1999</v>
       </c>
       <c r="D950" s="2"/>
     </row>
@@ -18659,10 +18680,10 @@
         <v>96</v>
       </c>
       <c r="B951" t="s" s="2">
+        <v>1999</v>
+      </c>
+      <c r="C951" t="s" s="2">
         <v>2000</v>
-      </c>
-      <c r="C951" t="s" s="2">
-        <v>2001</v>
       </c>
       <c r="D951" s="2"/>
     </row>
@@ -18671,10 +18692,10 @@
         <v>96</v>
       </c>
       <c r="B952" t="s" s="2">
+        <v>2001</v>
+      </c>
+      <c r="C952" t="s" s="2">
         <v>2002</v>
-      </c>
-      <c r="C952" t="s" s="2">
-        <v>2003</v>
       </c>
       <c r="D952" s="2"/>
     </row>
@@ -18683,10 +18704,10 @@
         <v>96</v>
       </c>
       <c r="B953" t="s" s="2">
+        <v>2003</v>
+      </c>
+      <c r="C953" t="s" s="2">
         <v>2004</v>
-      </c>
-      <c r="C953" t="s" s="2">
-        <v>2005</v>
       </c>
       <c r="D953" s="2"/>
     </row>
@@ -18695,10 +18716,10 @@
         <v>96</v>
       </c>
       <c r="B954" t="s" s="2">
+        <v>2005</v>
+      </c>
+      <c r="C954" t="s" s="2">
         <v>2006</v>
-      </c>
-      <c r="C954" t="s" s="2">
-        <v>2007</v>
       </c>
       <c r="D954" s="2"/>
     </row>
@@ -18707,10 +18728,10 @@
         <v>96</v>
       </c>
       <c r="B955" t="s" s="2">
+        <v>2007</v>
+      </c>
+      <c r="C955" t="s" s="2">
         <v>2008</v>
-      </c>
-      <c r="C955" t="s" s="2">
-        <v>2009</v>
       </c>
       <c r="D955" s="2"/>
     </row>
@@ -18719,10 +18740,10 @@
         <v>96</v>
       </c>
       <c r="B956" t="s" s="2">
+        <v>2009</v>
+      </c>
+      <c r="C956" t="s" s="2">
         <v>2010</v>
-      </c>
-      <c r="C956" t="s" s="2">
-        <v>2011</v>
       </c>
       <c r="D956" s="2"/>
     </row>
@@ -18731,10 +18752,10 @@
         <v>96</v>
       </c>
       <c r="B957" t="s" s="2">
+        <v>2011</v>
+      </c>
+      <c r="C957" t="s" s="2">
         <v>2012</v>
-      </c>
-      <c r="C957" t="s" s="2">
-        <v>2013</v>
       </c>
       <c r="D957" s="2"/>
     </row>
@@ -18743,10 +18764,10 @@
         <v>96</v>
       </c>
       <c r="B958" t="s" s="2">
+        <v>2013</v>
+      </c>
+      <c r="C958" t="s" s="2">
         <v>2014</v>
-      </c>
-      <c r="C958" t="s" s="2">
-        <v>2015</v>
       </c>
       <c r="D958" s="2"/>
     </row>
@@ -18755,10 +18776,10 @@
         <v>96</v>
       </c>
       <c r="B959" t="s" s="2">
+        <v>2015</v>
+      </c>
+      <c r="C959" t="s" s="2">
         <v>2016</v>
-      </c>
-      <c r="C959" t="s" s="2">
-        <v>2017</v>
       </c>
       <c r="D959" s="2"/>
     </row>
@@ -18767,10 +18788,10 @@
         <v>96</v>
       </c>
       <c r="B960" t="s" s="2">
+        <v>2017</v>
+      </c>
+      <c r="C960" t="s" s="2">
         <v>2018</v>
-      </c>
-      <c r="C960" t="s" s="2">
-        <v>2019</v>
       </c>
       <c r="D960" s="2"/>
     </row>
@@ -18779,10 +18800,10 @@
         <v>96</v>
       </c>
       <c r="B961" t="s" s="2">
+        <v>2019</v>
+      </c>
+      <c r="C961" t="s" s="2">
         <v>2020</v>
-      </c>
-      <c r="C961" t="s" s="2">
-        <v>2021</v>
       </c>
       <c r="D961" s="2"/>
     </row>
@@ -18791,10 +18812,10 @@
         <v>96</v>
       </c>
       <c r="B962" t="s" s="2">
+        <v>2021</v>
+      </c>
+      <c r="C962" t="s" s="2">
         <v>2022</v>
-      </c>
-      <c r="C962" t="s" s="2">
-        <v>2023</v>
       </c>
       <c r="D962" s="2"/>
     </row>
@@ -18803,10 +18824,10 @@
         <v>96</v>
       </c>
       <c r="B963" t="s" s="2">
+        <v>2023</v>
+      </c>
+      <c r="C963" t="s" s="2">
         <v>2024</v>
-      </c>
-      <c r="C963" t="s" s="2">
-        <v>2025</v>
       </c>
       <c r="D963" s="2"/>
     </row>
@@ -18815,10 +18836,10 @@
         <v>96</v>
       </c>
       <c r="B964" t="s" s="2">
+        <v>2025</v>
+      </c>
+      <c r="C964" t="s" s="2">
         <v>2026</v>
-      </c>
-      <c r="C964" t="s" s="2">
-        <v>2027</v>
       </c>
       <c r="D964" s="2"/>
     </row>
@@ -18827,10 +18848,10 @@
         <v>96</v>
       </c>
       <c r="B965" t="s" s="2">
+        <v>2027</v>
+      </c>
+      <c r="C965" t="s" s="2">
         <v>2028</v>
-      </c>
-      <c r="C965" t="s" s="2">
-        <v>2029</v>
       </c>
       <c r="D965" s="2"/>
     </row>
@@ -18839,10 +18860,10 @@
         <v>96</v>
       </c>
       <c r="B966" t="s" s="2">
+        <v>2029</v>
+      </c>
+      <c r="C966" t="s" s="2">
         <v>2030</v>
-      </c>
-      <c r="C966" t="s" s="2">
-        <v>2031</v>
       </c>
       <c r="D966" s="2"/>
     </row>
@@ -18851,10 +18872,10 @@
         <v>96</v>
       </c>
       <c r="B967" t="s" s="2">
+        <v>2031</v>
+      </c>
+      <c r="C967" t="s" s="2">
         <v>2032</v>
-      </c>
-      <c r="C967" t="s" s="2">
-        <v>2033</v>
       </c>
       <c r="D967" s="2"/>
     </row>
@@ -18863,10 +18884,10 @@
         <v>96</v>
       </c>
       <c r="B968" t="s" s="2">
+        <v>2033</v>
+      </c>
+      <c r="C968" t="s" s="2">
         <v>2034</v>
-      </c>
-      <c r="C968" t="s" s="2">
-        <v>2035</v>
       </c>
       <c r="D968" s="2"/>
     </row>
@@ -18875,10 +18896,10 @@
         <v>96</v>
       </c>
       <c r="B969" t="s" s="2">
+        <v>2035</v>
+      </c>
+      <c r="C969" t="s" s="2">
         <v>2036</v>
-      </c>
-      <c r="C969" t="s" s="2">
-        <v>2037</v>
       </c>
       <c r="D969" s="2"/>
     </row>
@@ -18887,10 +18908,10 @@
         <v>96</v>
       </c>
       <c r="B970" t="s" s="2">
+        <v>2037</v>
+      </c>
+      <c r="C970" t="s" s="2">
         <v>2038</v>
-      </c>
-      <c r="C970" t="s" s="2">
-        <v>2039</v>
       </c>
       <c r="D970" s="2"/>
     </row>
@@ -18899,10 +18920,10 @@
         <v>96</v>
       </c>
       <c r="B971" t="s" s="2">
+        <v>2039</v>
+      </c>
+      <c r="C971" t="s" s="2">
         <v>2040</v>
-      </c>
-      <c r="C971" t="s" s="2">
-        <v>2041</v>
       </c>
       <c r="D971" s="2"/>
     </row>
@@ -18911,10 +18932,10 @@
         <v>96</v>
       </c>
       <c r="B972" t="s" s="2">
+        <v>2041</v>
+      </c>
+      <c r="C972" t="s" s="2">
         <v>2042</v>
-      </c>
-      <c r="C972" t="s" s="2">
-        <v>2043</v>
       </c>
       <c r="D972" s="2"/>
     </row>
@@ -18923,10 +18944,10 @@
         <v>96</v>
       </c>
       <c r="B973" t="s" s="2">
+        <v>2043</v>
+      </c>
+      <c r="C973" t="s" s="2">
         <v>2044</v>
-      </c>
-      <c r="C973" t="s" s="2">
-        <v>2045</v>
       </c>
       <c r="D973" s="2"/>
     </row>
@@ -18935,10 +18956,10 @@
         <v>96</v>
       </c>
       <c r="B974" t="s" s="2">
+        <v>2045</v>
+      </c>
+      <c r="C974" t="s" s="2">
         <v>2046</v>
-      </c>
-      <c r="C974" t="s" s="2">
-        <v>2047</v>
       </c>
       <c r="D974" s="2"/>
     </row>
@@ -18947,10 +18968,10 @@
         <v>96</v>
       </c>
       <c r="B975" t="s" s="2">
+        <v>2047</v>
+      </c>
+      <c r="C975" t="s" s="2">
         <v>2048</v>
-      </c>
-      <c r="C975" t="s" s="2">
-        <v>2049</v>
       </c>
       <c r="D975" s="2"/>
     </row>
@@ -18959,10 +18980,10 @@
         <v>96</v>
       </c>
       <c r="B976" t="s" s="2">
+        <v>2049</v>
+      </c>
+      <c r="C976" t="s" s="2">
         <v>2050</v>
-      </c>
-      <c r="C976" t="s" s="2">
-        <v>2051</v>
       </c>
       <c r="D976" s="2"/>
     </row>
@@ -18971,10 +18992,10 @@
         <v>96</v>
       </c>
       <c r="B977" t="s" s="2">
+        <v>2051</v>
+      </c>
+      <c r="C977" t="s" s="2">
         <v>2052</v>
-      </c>
-      <c r="C977" t="s" s="2">
-        <v>2053</v>
       </c>
       <c r="D977" s="2"/>
     </row>
@@ -18983,10 +19004,10 @@
         <v>96</v>
       </c>
       <c r="B978" t="s" s="2">
+        <v>2053</v>
+      </c>
+      <c r="C978" t="s" s="2">
         <v>2054</v>
-      </c>
-      <c r="C978" t="s" s="2">
-        <v>2055</v>
       </c>
       <c r="D978" s="2"/>
     </row>
@@ -18995,10 +19016,10 @@
         <v>96</v>
       </c>
       <c r="B979" t="s" s="2">
+        <v>2055</v>
+      </c>
+      <c r="C979" t="s" s="2">
         <v>2056</v>
-      </c>
-      <c r="C979" t="s" s="2">
-        <v>2057</v>
       </c>
       <c r="D979" s="2"/>
     </row>
@@ -19007,10 +19028,10 @@
         <v>96</v>
       </c>
       <c r="B980" t="s" s="2">
+        <v>2057</v>
+      </c>
+      <c r="C980" t="s" s="2">
         <v>2058</v>
-      </c>
-      <c r="C980" t="s" s="2">
-        <v>2059</v>
       </c>
       <c r="D980" s="2"/>
     </row>
@@ -19019,10 +19040,10 @@
         <v>96</v>
       </c>
       <c r="B981" t="s" s="2">
+        <v>2059</v>
+      </c>
+      <c r="C981" t="s" s="2">
         <v>2060</v>
-      </c>
-      <c r="C981" t="s" s="2">
-        <v>2061</v>
       </c>
       <c r="D981" s="2"/>
     </row>
@@ -19031,10 +19052,10 @@
         <v>96</v>
       </c>
       <c r="B982" t="s" s="2">
+        <v>2061</v>
+      </c>
+      <c r="C982" t="s" s="2">
         <v>2062</v>
-      </c>
-      <c r="C982" t="s" s="2">
-        <v>2063</v>
       </c>
       <c r="D982" s="2"/>
     </row>
@@ -19043,10 +19064,10 @@
         <v>96</v>
       </c>
       <c r="B983" t="s" s="2">
+        <v>2063</v>
+      </c>
+      <c r="C983" t="s" s="2">
         <v>2064</v>
-      </c>
-      <c r="C983" t="s" s="2">
-        <v>2065</v>
       </c>
       <c r="D983" s="2"/>
     </row>
@@ -19055,10 +19076,10 @@
         <v>96</v>
       </c>
       <c r="B984" t="s" s="2">
+        <v>2065</v>
+      </c>
+      <c r="C984" t="s" s="2">
         <v>2066</v>
-      </c>
-      <c r="C984" t="s" s="2">
-        <v>2067</v>
       </c>
       <c r="D984" s="2"/>
     </row>
@@ -19067,10 +19088,10 @@
         <v>96</v>
       </c>
       <c r="B985" t="s" s="2">
+        <v>2067</v>
+      </c>
+      <c r="C985" t="s" s="2">
         <v>2068</v>
-      </c>
-      <c r="C985" t="s" s="2">
-        <v>2069</v>
       </c>
       <c r="D985" s="2"/>
     </row>
@@ -19079,10 +19100,10 @@
         <v>96</v>
       </c>
       <c r="B986" t="s" s="2">
+        <v>2069</v>
+      </c>
+      <c r="C986" t="s" s="2">
         <v>2070</v>
-      </c>
-      <c r="C986" t="s" s="2">
-        <v>2071</v>
       </c>
       <c r="D986" s="2"/>
     </row>
@@ -19091,10 +19112,10 @@
         <v>96</v>
       </c>
       <c r="B987" t="s" s="2">
+        <v>2071</v>
+      </c>
+      <c r="C987" t="s" s="2">
         <v>2072</v>
-      </c>
-      <c r="C987" t="s" s="2">
-        <v>2073</v>
       </c>
       <c r="D987" s="2"/>
     </row>
@@ -19103,10 +19124,10 @@
         <v>96</v>
       </c>
       <c r="B988" t="s" s="2">
+        <v>2073</v>
+      </c>
+      <c r="C988" t="s" s="2">
         <v>2074</v>
-      </c>
-      <c r="C988" t="s" s="2">
-        <v>2075</v>
       </c>
       <c r="D988" s="2"/>
     </row>
@@ -19115,10 +19136,10 @@
         <v>96</v>
       </c>
       <c r="B989" t="s" s="2">
+        <v>2075</v>
+      </c>
+      <c r="C989" t="s" s="2">
         <v>2076</v>
-      </c>
-      <c r="C989" t="s" s="2">
-        <v>2077</v>
       </c>
       <c r="D989" s="2"/>
     </row>
@@ -19127,10 +19148,10 @@
         <v>96</v>
       </c>
       <c r="B990" t="s" s="2">
+        <v>2077</v>
+      </c>
+      <c r="C990" t="s" s="2">
         <v>2078</v>
-      </c>
-      <c r="C990" t="s" s="2">
-        <v>2079</v>
       </c>
       <c r="D990" s="2"/>
     </row>
@@ -19139,10 +19160,10 @@
         <v>96</v>
       </c>
       <c r="B991" t="s" s="2">
+        <v>2079</v>
+      </c>
+      <c r="C991" t="s" s="2">
         <v>2080</v>
-      </c>
-      <c r="C991" t="s" s="2">
-        <v>2081</v>
       </c>
       <c r="D991" s="2"/>
     </row>
@@ -19151,10 +19172,10 @@
         <v>96</v>
       </c>
       <c r="B992" t="s" s="2">
+        <v>2081</v>
+      </c>
+      <c r="C992" t="s" s="2">
         <v>2082</v>
-      </c>
-      <c r="C992" t="s" s="2">
-        <v>2083</v>
       </c>
       <c r="D992" s="2"/>
     </row>
@@ -19163,10 +19184,10 @@
         <v>96</v>
       </c>
       <c r="B993" t="s" s="2">
+        <v>2083</v>
+      </c>
+      <c r="C993" t="s" s="2">
         <v>2084</v>
-      </c>
-      <c r="C993" t="s" s="2">
-        <v>2085</v>
       </c>
       <c r="D993" s="2"/>
     </row>
@@ -19175,10 +19196,10 @@
         <v>96</v>
       </c>
       <c r="B994" t="s" s="2">
+        <v>2085</v>
+      </c>
+      <c r="C994" t="s" s="2">
         <v>2086</v>
-      </c>
-      <c r="C994" t="s" s="2">
-        <v>2087</v>
       </c>
       <c r="D994" s="2"/>
     </row>
@@ -19187,10 +19208,10 @@
         <v>96</v>
       </c>
       <c r="B995" t="s" s="2">
+        <v>2087</v>
+      </c>
+      <c r="C995" t="s" s="2">
         <v>2088</v>
-      </c>
-      <c r="C995" t="s" s="2">
-        <v>2089</v>
       </c>
       <c r="D995" s="2"/>
     </row>
@@ -19199,10 +19220,10 @@
         <v>96</v>
       </c>
       <c r="B996" t="s" s="2">
+        <v>2089</v>
+      </c>
+      <c r="C996" t="s" s="2">
         <v>2090</v>
-      </c>
-      <c r="C996" t="s" s="2">
-        <v>2091</v>
       </c>
       <c r="D996" s="2"/>
     </row>
@@ -19211,10 +19232,10 @@
         <v>96</v>
       </c>
       <c r="B997" t="s" s="2">
+        <v>2091</v>
+      </c>
+      <c r="C997" t="s" s="2">
         <v>2092</v>
-      </c>
-      <c r="C997" t="s" s="2">
-        <v>2093</v>
       </c>
       <c r="D997" s="2"/>
     </row>
@@ -19223,10 +19244,10 @@
         <v>96</v>
       </c>
       <c r="B998" t="s" s="2">
+        <v>2093</v>
+      </c>
+      <c r="C998" t="s" s="2">
         <v>2094</v>
-      </c>
-      <c r="C998" t="s" s="2">
-        <v>2095</v>
       </c>
       <c r="D998" s="2"/>
     </row>
@@ -19235,10 +19256,10 @@
         <v>96</v>
       </c>
       <c r="B999" t="s" s="2">
+        <v>2095</v>
+      </c>
+      <c r="C999" t="s" s="2">
         <v>2096</v>
-      </c>
-      <c r="C999" t="s" s="2">
-        <v>2097</v>
       </c>
       <c r="D999" s="2"/>
     </row>
@@ -19247,10 +19268,10 @@
         <v>96</v>
       </c>
       <c r="B1000" t="s" s="2">
+        <v>2097</v>
+      </c>
+      <c r="C1000" t="s" s="2">
         <v>2098</v>
-      </c>
-      <c r="C1000" t="s" s="2">
-        <v>2099</v>
       </c>
       <c r="D1000" s="2"/>
     </row>
@@ -19259,10 +19280,10 @@
         <v>96</v>
       </c>
       <c r="B1001" t="s" s="2">
+        <v>2099</v>
+      </c>
+      <c r="C1001" t="s" s="2">
         <v>2100</v>
-      </c>
-      <c r="C1001" t="s" s="2">
-        <v>2101</v>
       </c>
       <c r="D1001" s="2"/>
     </row>
@@ -19271,10 +19292,10 @@
         <v>96</v>
       </c>
       <c r="B1002" t="s" s="2">
+        <v>2101</v>
+      </c>
+      <c r="C1002" t="s" s="2">
         <v>2102</v>
-      </c>
-      <c r="C1002" t="s" s="2">
-        <v>2103</v>
       </c>
       <c r="D1002" s="2"/>
     </row>
@@ -19283,10 +19304,10 @@
         <v>96</v>
       </c>
       <c r="B1003" t="s" s="2">
+        <v>2103</v>
+      </c>
+      <c r="C1003" t="s" s="2">
         <v>2104</v>
-      </c>
-      <c r="C1003" t="s" s="2">
-        <v>2105</v>
       </c>
       <c r="D1003" s="2"/>
     </row>
@@ -19295,10 +19316,10 @@
         <v>96</v>
       </c>
       <c r="B1004" t="s" s="2">
+        <v>2105</v>
+      </c>
+      <c r="C1004" t="s" s="2">
         <v>2106</v>
-      </c>
-      <c r="C1004" t="s" s="2">
-        <v>2107</v>
       </c>
       <c r="D1004" s="2"/>
     </row>
@@ -19307,10 +19328,10 @@
         <v>96</v>
       </c>
       <c r="B1005" t="s" s="2">
+        <v>2107</v>
+      </c>
+      <c r="C1005" t="s" s="2">
         <v>2108</v>
-      </c>
-      <c r="C1005" t="s" s="2">
-        <v>2109</v>
       </c>
       <c r="D1005" s="2"/>
     </row>
@@ -19319,10 +19340,10 @@
         <v>96</v>
       </c>
       <c r="B1006" t="s" s="2">
+        <v>2109</v>
+      </c>
+      <c r="C1006" t="s" s="2">
         <v>2110</v>
-      </c>
-      <c r="C1006" t="s" s="2">
-        <v>2111</v>
       </c>
       <c r="D1006" s="2"/>
     </row>
@@ -19331,10 +19352,10 @@
         <v>96</v>
       </c>
       <c r="B1007" t="s" s="2">
+        <v>2111</v>
+      </c>
+      <c r="C1007" t="s" s="2">
         <v>2112</v>
-      </c>
-      <c r="C1007" t="s" s="2">
-        <v>2113</v>
       </c>
       <c r="D1007" s="2"/>
     </row>
@@ -19343,10 +19364,10 @@
         <v>96</v>
       </c>
       <c r="B1008" t="s" s="2">
+        <v>2113</v>
+      </c>
+      <c r="C1008" t="s" s="2">
         <v>2114</v>
-      </c>
-      <c r="C1008" t="s" s="2">
-        <v>2115</v>
       </c>
       <c r="D1008" s="2"/>
     </row>
@@ -19355,10 +19376,10 @@
         <v>96</v>
       </c>
       <c r="B1009" t="s" s="2">
+        <v>2115</v>
+      </c>
+      <c r="C1009" t="s" s="2">
         <v>2116</v>
-      </c>
-      <c r="C1009" t="s" s="2">
-        <v>2117</v>
       </c>
       <c r="D1009" s="2"/>
     </row>
@@ -19367,10 +19388,10 @@
         <v>96</v>
       </c>
       <c r="B1010" t="s" s="2">
+        <v>2117</v>
+      </c>
+      <c r="C1010" t="s" s="2">
         <v>2118</v>
-      </c>
-      <c r="C1010" t="s" s="2">
-        <v>2119</v>
       </c>
       <c r="D1010" s="2"/>
     </row>
@@ -19379,10 +19400,10 @@
         <v>96</v>
       </c>
       <c r="B1011" t="s" s="2">
+        <v>2119</v>
+      </c>
+      <c r="C1011" t="s" s="2">
         <v>2120</v>
-      </c>
-      <c r="C1011" t="s" s="2">
-        <v>2121</v>
       </c>
       <c r="D1011" s="2"/>
     </row>
@@ -19391,10 +19412,10 @@
         <v>96</v>
       </c>
       <c r="B1012" t="s" s="2">
+        <v>2121</v>
+      </c>
+      <c r="C1012" t="s" s="2">
         <v>2122</v>
-      </c>
-      <c r="C1012" t="s" s="2">
-        <v>2123</v>
       </c>
       <c r="D1012" s="2"/>
     </row>
@@ -19403,10 +19424,10 @@
         <v>96</v>
       </c>
       <c r="B1013" t="s" s="2">
+        <v>2123</v>
+      </c>
+      <c r="C1013" t="s" s="2">
         <v>2124</v>
-      </c>
-      <c r="C1013" t="s" s="2">
-        <v>2125</v>
       </c>
       <c r="D1013" s="2"/>
     </row>
@@ -19415,10 +19436,10 @@
         <v>96</v>
       </c>
       <c r="B1014" t="s" s="2">
+        <v>2125</v>
+      </c>
+      <c r="C1014" t="s" s="2">
         <v>2126</v>
-      </c>
-      <c r="C1014" t="s" s="2">
-        <v>2127</v>
       </c>
       <c r="D1014" s="2"/>
     </row>
@@ -19427,10 +19448,10 @@
         <v>96</v>
       </c>
       <c r="B1015" t="s" s="2">
+        <v>2127</v>
+      </c>
+      <c r="C1015" t="s" s="2">
         <v>2128</v>
-      </c>
-      <c r="C1015" t="s" s="2">
-        <v>2129</v>
       </c>
       <c r="D1015" s="2"/>
     </row>
@@ -19439,10 +19460,10 @@
         <v>96</v>
       </c>
       <c r="B1016" t="s" s="2">
+        <v>2129</v>
+      </c>
+      <c r="C1016" t="s" s="2">
         <v>2130</v>
-      </c>
-      <c r="C1016" t="s" s="2">
-        <v>2131</v>
       </c>
       <c r="D1016" s="2"/>
     </row>
@@ -19451,10 +19472,10 @@
         <v>96</v>
       </c>
       <c r="B1017" t="s" s="2">
+        <v>2131</v>
+      </c>
+      <c r="C1017" t="s" s="2">
         <v>2132</v>
-      </c>
-      <c r="C1017" t="s" s="2">
-        <v>2133</v>
       </c>
       <c r="D1017" s="2"/>
     </row>
@@ -19463,10 +19484,10 @@
         <v>96</v>
       </c>
       <c r="B1018" t="s" s="2">
+        <v>2133</v>
+      </c>
+      <c r="C1018" t="s" s="2">
         <v>2134</v>
-      </c>
-      <c r="C1018" t="s" s="2">
-        <v>2135</v>
       </c>
       <c r="D1018" s="2"/>
     </row>
@@ -19475,10 +19496,10 @@
         <v>96</v>
       </c>
       <c r="B1019" t="s" s="2">
+        <v>2135</v>
+      </c>
+      <c r="C1019" t="s" s="2">
         <v>2136</v>
-      </c>
-      <c r="C1019" t="s" s="2">
-        <v>2137</v>
       </c>
       <c r="D1019" s="2"/>
     </row>
@@ -19487,10 +19508,10 @@
         <v>96</v>
       </c>
       <c r="B1020" t="s" s="2">
+        <v>2137</v>
+      </c>
+      <c r="C1020" t="s" s="2">
         <v>2138</v>
-      </c>
-      <c r="C1020" t="s" s="2">
-        <v>2139</v>
       </c>
       <c r="D1020" s="2"/>
     </row>
@@ -19499,10 +19520,10 @@
         <v>96</v>
       </c>
       <c r="B1021" t="s" s="2">
+        <v>2139</v>
+      </c>
+      <c r="C1021" t="s" s="2">
         <v>2140</v>
-      </c>
-      <c r="C1021" t="s" s="2">
-        <v>2141</v>
       </c>
       <c r="D1021" s="2"/>
     </row>
@@ -19511,10 +19532,10 @@
         <v>96</v>
       </c>
       <c r="B1022" t="s" s="2">
+        <v>2141</v>
+      </c>
+      <c r="C1022" t="s" s="2">
         <v>2142</v>
-      </c>
-      <c r="C1022" t="s" s="2">
-        <v>2143</v>
       </c>
       <c r="D1022" s="2"/>
     </row>
@@ -19523,10 +19544,10 @@
         <v>96</v>
       </c>
       <c r="B1023" t="s" s="2">
+        <v>2143</v>
+      </c>
+      <c r="C1023" t="s" s="2">
         <v>2144</v>
-      </c>
-      <c r="C1023" t="s" s="2">
-        <v>2145</v>
       </c>
       <c r="D1023" s="2"/>
     </row>
@@ -19535,10 +19556,10 @@
         <v>96</v>
       </c>
       <c r="B1024" t="s" s="2">
+        <v>2145</v>
+      </c>
+      <c r="C1024" t="s" s="2">
         <v>2146</v>
-      </c>
-      <c r="C1024" t="s" s="2">
-        <v>2147</v>
       </c>
       <c r="D1024" s="2"/>
     </row>
@@ -19547,10 +19568,10 @@
         <v>96</v>
       </c>
       <c r="B1025" t="s" s="2">
+        <v>2147</v>
+      </c>
+      <c r="C1025" t="s" s="2">
         <v>2148</v>
-      </c>
-      <c r="C1025" t="s" s="2">
-        <v>2149</v>
       </c>
       <c r="D1025" s="2"/>
     </row>
@@ -19559,10 +19580,10 @@
         <v>96</v>
       </c>
       <c r="B1026" t="s" s="2">
+        <v>2149</v>
+      </c>
+      <c r="C1026" t="s" s="2">
         <v>2150</v>
-      </c>
-      <c r="C1026" t="s" s="2">
-        <v>2151</v>
       </c>
       <c r="D1026" s="2"/>
     </row>
@@ -19571,10 +19592,10 @@
         <v>96</v>
       </c>
       <c r="B1027" t="s" s="2">
+        <v>2151</v>
+      </c>
+      <c r="C1027" t="s" s="2">
         <v>2152</v>
-      </c>
-      <c r="C1027" t="s" s="2">
-        <v>2153</v>
       </c>
       <c r="D1027" s="2"/>
     </row>
@@ -19583,10 +19604,10 @@
         <v>96</v>
       </c>
       <c r="B1028" t="s" s="2">
+        <v>2153</v>
+      </c>
+      <c r="C1028" t="s" s="2">
         <v>2154</v>
-      </c>
-      <c r="C1028" t="s" s="2">
-        <v>2155</v>
       </c>
       <c r="D1028" s="2"/>
     </row>
@@ -19595,10 +19616,10 @@
         <v>96</v>
       </c>
       <c r="B1029" t="s" s="2">
+        <v>2155</v>
+      </c>
+      <c r="C1029" t="s" s="2">
         <v>2156</v>
-      </c>
-      <c r="C1029" t="s" s="2">
-        <v>2157</v>
       </c>
       <c r="D1029" s="2"/>
     </row>
@@ -19607,10 +19628,10 @@
         <v>96</v>
       </c>
       <c r="B1030" t="s" s="2">
+        <v>2157</v>
+      </c>
+      <c r="C1030" t="s" s="2">
         <v>2158</v>
-      </c>
-      <c r="C1030" t="s" s="2">
-        <v>2159</v>
       </c>
       <c r="D1030" s="2"/>
     </row>
@@ -19619,10 +19640,10 @@
         <v>96</v>
       </c>
       <c r="B1031" t="s" s="2">
+        <v>2159</v>
+      </c>
+      <c r="C1031" t="s" s="2">
         <v>2160</v>
-      </c>
-      <c r="C1031" t="s" s="2">
-        <v>2161</v>
       </c>
       <c r="D1031" s="2"/>
     </row>
@@ -19631,10 +19652,10 @@
         <v>96</v>
       </c>
       <c r="B1032" t="s" s="2">
+        <v>2161</v>
+      </c>
+      <c r="C1032" t="s" s="2">
         <v>2162</v>
-      </c>
-      <c r="C1032" t="s" s="2">
-        <v>2163</v>
       </c>
       <c r="D1032" s="2"/>
     </row>
@@ -19643,10 +19664,10 @@
         <v>96</v>
       </c>
       <c r="B1033" t="s" s="2">
+        <v>2163</v>
+      </c>
+      <c r="C1033" t="s" s="2">
         <v>2164</v>
-      </c>
-      <c r="C1033" t="s" s="2">
-        <v>2165</v>
       </c>
       <c r="D1033" s="2"/>
     </row>
@@ -19655,10 +19676,10 @@
         <v>96</v>
       </c>
       <c r="B1034" t="s" s="2">
+        <v>2165</v>
+      </c>
+      <c r="C1034" t="s" s="2">
         <v>2166</v>
-      </c>
-      <c r="C1034" t="s" s="2">
-        <v>2167</v>
       </c>
       <c r="D1034" s="2"/>
     </row>
@@ -19667,10 +19688,10 @@
         <v>96</v>
       </c>
       <c r="B1035" t="s" s="2">
+        <v>2167</v>
+      </c>
+      <c r="C1035" t="s" s="2">
         <v>2168</v>
-      </c>
-      <c r="C1035" t="s" s="2">
-        <v>2169</v>
       </c>
       <c r="D1035" s="2"/>
     </row>
@@ -19679,10 +19700,10 @@
         <v>96</v>
       </c>
       <c r="B1036" t="s" s="2">
+        <v>2169</v>
+      </c>
+      <c r="C1036" t="s" s="2">
         <v>2170</v>
-      </c>
-      <c r="C1036" t="s" s="2">
-        <v>2171</v>
       </c>
       <c r="D1036" s="2"/>
     </row>
@@ -19691,10 +19712,10 @@
         <v>96</v>
       </c>
       <c r="B1037" t="s" s="2">
+        <v>2171</v>
+      </c>
+      <c r="C1037" t="s" s="2">
         <v>2172</v>
-      </c>
-      <c r="C1037" t="s" s="2">
-        <v>2173</v>
       </c>
       <c r="D1037" s="2"/>
     </row>
@@ -19703,10 +19724,10 @@
         <v>96</v>
       </c>
       <c r="B1038" t="s" s="2">
+        <v>2173</v>
+      </c>
+      <c r="C1038" t="s" s="2">
         <v>2174</v>
-      </c>
-      <c r="C1038" t="s" s="2">
-        <v>2175</v>
       </c>
       <c r="D1038" s="2"/>
     </row>
@@ -19715,10 +19736,10 @@
         <v>96</v>
       </c>
       <c r="B1039" t="s" s="2">
+        <v>2175</v>
+      </c>
+      <c r="C1039" t="s" s="2">
         <v>2176</v>
-      </c>
-      <c r="C1039" t="s" s="2">
-        <v>2177</v>
       </c>
       <c r="D1039" s="2"/>
     </row>
@@ -19727,10 +19748,10 @@
         <v>96</v>
       </c>
       <c r="B1040" t="s" s="2">
+        <v>2177</v>
+      </c>
+      <c r="C1040" t="s" s="2">
         <v>2178</v>
-      </c>
-      <c r="C1040" t="s" s="2">
-        <v>2179</v>
       </c>
       <c r="D1040" s="2"/>
     </row>
@@ -19739,10 +19760,10 @@
         <v>96</v>
       </c>
       <c r="B1041" t="s" s="2">
-        <v>10</v>
+        <v>2179</v>
       </c>
       <c r="C1041" t="s" s="2">
-        <v>10</v>
+        <v>2180</v>
       </c>
       <c r="D1041" s="2"/>
     </row>
@@ -19751,10 +19772,10 @@
         <v>96</v>
       </c>
       <c r="B1042" t="s" s="2">
-        <v>2180</v>
+        <v>2181</v>
       </c>
       <c r="C1042" t="s" s="2">
-        <v>2181</v>
+        <v>2182</v>
       </c>
       <c r="D1042" s="2"/>
     </row>
@@ -19763,10 +19784,10 @@
         <v>96</v>
       </c>
       <c r="B1043" t="s" s="2">
-        <v>2182</v>
+        <v>2183</v>
       </c>
       <c r="C1043" t="s" s="2">
-        <v>2183</v>
+        <v>2184</v>
       </c>
       <c r="D1043" s="2"/>
     </row>
@@ -19775,10 +19796,10 @@
         <v>96</v>
       </c>
       <c r="B1044" t="s" s="2">
-        <v>2184</v>
+        <v>2185</v>
       </c>
       <c r="C1044" t="s" s="2">
-        <v>2185</v>
+        <v>2186</v>
       </c>
       <c r="D1044" s="2"/>
     </row>
@@ -19787,10 +19808,10 @@
         <v>96</v>
       </c>
       <c r="B1045" t="s" s="2">
-        <v>2186</v>
+        <v>10</v>
       </c>
       <c r="C1045" t="s" s="2">
-        <v>2187</v>
+        <v>10</v>
       </c>
       <c r="D1045" s="2"/>
     </row>
@@ -19799,10 +19820,10 @@
         <v>96</v>
       </c>
       <c r="B1046" t="s" s="2">
+        <v>2187</v>
+      </c>
+      <c r="C1046" t="s" s="2">
         <v>2188</v>
-      </c>
-      <c r="C1046" t="s" s="2">
-        <v>2189</v>
       </c>
       <c r="D1046" s="2"/>
     </row>
@@ -19811,12 +19832,60 @@
         <v>96</v>
       </c>
       <c r="B1047" t="s" s="2">
+        <v>2189</v>
+      </c>
+      <c r="C1047" t="s" s="2">
         <v>2190</v>
       </c>
-      <c r="C1047" t="s" s="2">
+      <c r="D1047" s="2"/>
+    </row>
+    <row r="1048">
+      <c r="A1048" t="s" s="2">
+        <v>96</v>
+      </c>
+      <c r="B1048" t="s" s="2">
         <v>2191</v>
       </c>
-      <c r="D1047" s="2"/>
+      <c r="C1048" t="s" s="2">
+        <v>2192</v>
+      </c>
+      <c r="D1048" s="2"/>
+    </row>
+    <row r="1049">
+      <c r="A1049" t="s" s="2">
+        <v>96</v>
+      </c>
+      <c r="B1049" t="s" s="2">
+        <v>2193</v>
+      </c>
+      <c r="C1049" t="s" s="2">
+        <v>2194</v>
+      </c>
+      <c r="D1049" s="2"/>
+    </row>
+    <row r="1050">
+      <c r="A1050" t="s" s="2">
+        <v>96</v>
+      </c>
+      <c r="B1050" t="s" s="2">
+        <v>2195</v>
+      </c>
+      <c r="C1050" t="s" s="2">
+        <v>2196</v>
+      </c>
+      <c r="D1050" s="2"/>
+    </row>
+    <row r="1051">
+      <c r="A1051" t="s" s="2">
+        <v>96</v>
+      </c>
+      <c r="B1051" t="s" s="2">
+        <v>2197</v>
+      </c>
+      <c r="C1051" t="s" s="2">
+        <v>2198</v>
+      </c>
+      <c r="D1051" s="2"/>
     </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
